--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,36 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>2026-10-05 01:46:57</t>
   </si>
 </sst>
 </file>
@@ -585,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +860,490 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2">
+        <v>2.82</v>
+      </c>
+      <c r="G2">
+        <v>2.96</v>
+      </c>
+      <c r="H2">
+        <v>2.38</v>
+      </c>
+      <c r="I2">
+        <v>2.48</v>
+      </c>
+      <c r="J2">
+        <v>3.95</v>
+      </c>
+      <c r="K2">
+        <v>4.3</v>
+      </c>
+      <c r="L2">
+        <v>1.26</v>
+      </c>
+      <c r="M2">
+        <v>1.03</v>
+      </c>
+      <c r="N2">
+        <v>6.8</v>
+      </c>
+      <c r="O2">
+        <v>1.16</v>
+      </c>
+      <c r="P2">
+        <v>2.92</v>
+      </c>
+      <c r="Q2">
+        <v>1.49</v>
+      </c>
+      <c r="R2">
+        <v>1.79</v>
+      </c>
+      <c r="S2">
+        <v>2.18</v>
+      </c>
+      <c r="T2">
+        <v>1.48</v>
+      </c>
+      <c r="U2">
+        <v>2.82</v>
+      </c>
+      <c r="V2">
+        <v>1.67</v>
+      </c>
+      <c r="W2">
+        <v>1.51</v>
+      </c>
+      <c r="X2">
+        <v>30</v>
+      </c>
+      <c r="Y2">
+        <v>19</v>
+      </c>
+      <c r="Z2">
+        <v>23</v>
+      </c>
+      <c r="AA2">
+        <v>40</v>
+      </c>
+      <c r="AB2">
+        <v>21</v>
+      </c>
+      <c r="AC2">
+        <v>11</v>
+      </c>
+      <c r="AD2">
+        <v>14</v>
+      </c>
+      <c r="AE2">
+        <v>24</v>
+      </c>
+      <c r="AF2">
+        <v>28</v>
+      </c>
+      <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
+        <v>15</v>
+      </c>
+      <c r="AI2">
+        <v>30</v>
+      </c>
+      <c r="AJ2">
+        <v>55</v>
+      </c>
+      <c r="AK2">
+        <v>29</v>
+      </c>
+      <c r="AL2">
+        <v>34</v>
+      </c>
+      <c r="AM2">
+        <v>55</v>
+      </c>
+      <c r="AN2">
+        <v>13.5</v>
+      </c>
+      <c r="AO2">
+        <v>11</v>
+      </c>
+      <c r="AP2">
+        <v>7.4</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>7.8</v>
+      </c>
+      <c r="AT2">
+        <v>17</v>
+      </c>
+      <c r="AU2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>11.5</v>
+      </c>
+      <c r="AW2">
+        <v>18.5</v>
+      </c>
+      <c r="AX2">
+        <v>21</v>
+      </c>
+      <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
+        <v>12.5</v>
+      </c>
+      <c r="BA2">
+        <v>21</v>
+      </c>
+      <c r="BB2">
+        <v>8</v>
+      </c>
+      <c r="BC2">
+        <v>7.2</v>
+      </c>
+      <c r="BD2">
+        <v>7.4</v>
+      </c>
+      <c r="BE2">
+        <v>36</v>
+      </c>
+      <c r="BF2">
+        <v>11.5</v>
+      </c>
+      <c r="BG2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>2.5</v>
+      </c>
+      <c r="BJ2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK2">
+        <v>6.2</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>4.3</v>
+      </c>
+      <c r="BN2">
+        <v>8</v>
+      </c>
+      <c r="BO2">
+        <v>5.1</v>
+      </c>
+      <c r="BP2">
+        <v>25</v>
+      </c>
+      <c r="BQ2">
+        <v>13.5</v>
+      </c>
+      <c r="BR2">
+        <v>30</v>
+      </c>
+      <c r="BS2">
+        <v>4</v>
+      </c>
+      <c r="BT2">
+        <v>7.2</v>
+      </c>
+      <c r="BU2">
+        <v>4.7</v>
+      </c>
+      <c r="BV2">
+        <v>21</v>
+      </c>
+      <c r="BW2">
+        <v>11.5</v>
+      </c>
+      <c r="BX2">
+        <v>29</v>
+      </c>
+      <c r="BY2">
+        <v>14.5</v>
+      </c>
+      <c r="BZ2">
+        <v>17</v>
+      </c>
+      <c r="CA2">
+        <v>8.6</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3">
+        <v>10.5</v>
+      </c>
+      <c r="G3">
+        <v>13.5</v>
+      </c>
+      <c r="H3">
+        <v>1.34</v>
+      </c>
+      <c r="I3">
+        <v>1.39</v>
+      </c>
+      <c r="J3">
+        <v>4.9</v>
+      </c>
+      <c r="K3">
+        <v>6.2</v>
+      </c>
+      <c r="L3">
+        <v>1.36</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
+        <v>3.75</v>
+      </c>
+      <c r="O3">
+        <v>1.3</v>
+      </c>
+      <c r="P3">
+        <v>1.98</v>
+      </c>
+      <c r="Q3">
+        <v>1.83</v>
+      </c>
+      <c r="R3">
+        <v>1.35</v>
+      </c>
+      <c r="S3">
+        <v>3.2</v>
+      </c>
+      <c r="T3">
+        <v>2.28</v>
+      </c>
+      <c r="U3">
+        <v>1.56</v>
+      </c>
+      <c r="V3">
+        <v>3.55</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>17.5</v>
+      </c>
+      <c r="Y3">
+        <v>970</v>
+      </c>
+      <c r="Z3">
+        <v>7.6</v>
+      </c>
+      <c r="AA3">
+        <v>970</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>13</v>
+      </c>
+      <c r="AD3">
+        <v>12</v>
+      </c>
+      <c r="AE3">
+        <v>18</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>7.2</v>
+      </c>
+      <c r="AP3">
+        <v>2.88</v>
+      </c>
+      <c r="AQ3">
+        <v>5.4</v>
+      </c>
+      <c r="AR3">
+        <v>5.4</v>
+      </c>
+      <c r="AS3">
+        <v>7.2</v>
+      </c>
+      <c r="AT3">
+        <v>3.45</v>
+      </c>
+      <c r="AU3">
+        <v>2.72</v>
+      </c>
+      <c r="AV3">
+        <v>7.6</v>
+      </c>
+      <c r="AW3">
+        <v>2.9</v>
+      </c>
+      <c r="AX3">
+        <v>3.45</v>
+      </c>
+      <c r="AY3">
+        <v>3.45</v>
+      </c>
+      <c r="AZ3">
+        <v>3.45</v>
+      </c>
+      <c r="BA3">
+        <v>3.45</v>
+      </c>
+      <c r="BB3">
+        <v>3.45</v>
+      </c>
+      <c r="BC3">
+        <v>3.45</v>
+      </c>
+      <c r="BD3">
+        <v>3.45</v>
+      </c>
+      <c r="BE3">
+        <v>3.45</v>
+      </c>
+      <c r="BF3">
+        <v>3.45</v>
+      </c>
+      <c r="BG3">
+        <v>5.2</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>2.8</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.36</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -283,7 +283,7 @@
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-10-05 01:46:57</t>
+    <t>2026-10-05 03:56:16</t>
   </si>
 </sst>
 </file>
@@ -877,19 +877,19 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I2">
         <v>2.48</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -901,34 +901,34 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O2">
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
         <v>1.49</v>
       </c>
       <c r="R2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T2">
         <v>1.48</v>
       </c>
       <c r="U2">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2">
         <v>30</v>
@@ -937,7 +937,7 @@
         <v>19</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2">
         <v>40</v>
@@ -952,7 +952,7 @@
         <v>14</v>
       </c>
       <c r="AE2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF2">
         <v>28</v>
@@ -964,7 +964,7 @@
         <v>15</v>
       </c>
       <c r="AI2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ2">
         <v>55</v>
@@ -973,7 +973,7 @@
         <v>29</v>
       </c>
       <c r="AL2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2">
         <v>55</v>
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -994,10 +994,10 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU2">
         <v>9.199999999999999</v>
@@ -1021,13 +1021,13 @@
         <v>21</v>
       </c>
       <c r="BB2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
         <v>36</v>
@@ -1119,22 +1119,22 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="H3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I3">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="J3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K3">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1143,28 +1143,28 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
         <v>3.55</v>
@@ -1173,118 +1173,118 @@
         <v>1.08</v>
       </c>
       <c r="X3">
+        <v>16.5</v>
+      </c>
+      <c r="Y3">
+        <v>7.2</v>
+      </c>
+      <c r="Z3">
+        <v>7.4</v>
+      </c>
+      <c r="AA3">
+        <v>10.5</v>
+      </c>
+      <c r="AB3">
+        <v>32</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
         <v>17.5</v>
       </c>
-      <c r="Y3">
-        <v>970</v>
-      </c>
-      <c r="Z3">
-        <v>7.6</v>
-      </c>
-      <c r="AA3">
-        <v>970</v>
-      </c>
-      <c r="AB3">
-        <v>1000</v>
-      </c>
-      <c r="AC3">
-        <v>13</v>
-      </c>
-      <c r="AD3">
-        <v>12</v>
-      </c>
-      <c r="AE3">
-        <v>18</v>
-      </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AO3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP3">
-        <v>2.88</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AT3">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>2.72</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>2.9</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AY3">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>3.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA3">
-        <v>3.45</v>
+        <v>9.4</v>
       </c>
       <c r="BB3">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BC3">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BF3">
-        <v>3.45</v>
+        <v>11</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.8</v>
+        <v>1.34</v>
       </c>
       <c r="BJ3">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -283,7 +283,7 @@
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-10-05 03:56:16</t>
+    <t>2026-10-05 06:05:49</t>
   </si>
 </sst>
 </file>
@@ -877,7 +877,7 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G2">
         <v>3</v>
@@ -886,7 +886,7 @@
         <v>2.36</v>
       </c>
       <c r="I2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -910,7 +910,7 @@
         <v>2.88</v>
       </c>
       <c r="Q2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
         <v>1.78</v>
@@ -919,19 +919,19 @@
         <v>2.2</v>
       </c>
       <c r="T2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U2">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="V2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W2">
         <v>1.5</v>
       </c>
       <c r="X2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y2">
         <v>19</v>
@@ -940,34 +940,34 @@
         <v>22</v>
       </c>
       <c r="AA2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB2">
         <v>21</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2">
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -976,16 +976,16 @@
         <v>32</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AN2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO2">
         <v>11</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -994,7 +994,7 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AT2">
         <v>17.5</v>
@@ -1021,82 +1021,82 @@
         <v>21</v>
       </c>
       <c r="BB2">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BE2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
         <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BN2">
+        <v>6.8</v>
+      </c>
+      <c r="BO2">
+        <v>5.9</v>
+      </c>
+      <c r="BP2">
+        <v>19.5</v>
+      </c>
+      <c r="BQ2">
+        <v>7.2</v>
+      </c>
+      <c r="BR2">
+        <v>25</v>
+      </c>
+      <c r="BS2">
         <v>8</v>
       </c>
-      <c r="BO2">
-        <v>5.1</v>
-      </c>
-      <c r="BP2">
-        <v>25</v>
-      </c>
-      <c r="BQ2">
+      <c r="BT2">
+        <v>6.2</v>
+      </c>
+      <c r="BU2">
+        <v>5.4</v>
+      </c>
+      <c r="BV2">
+        <v>16</v>
+      </c>
+      <c r="BW2">
+        <v>6.8</v>
+      </c>
+      <c r="BX2">
+        <v>22</v>
+      </c>
+      <c r="BY2">
+        <v>7.6</v>
+      </c>
+      <c r="BZ2">
         <v>13.5</v>
       </c>
-      <c r="BR2">
-        <v>30</v>
-      </c>
-      <c r="BS2">
-        <v>4</v>
-      </c>
-      <c r="BT2">
-        <v>7.2</v>
-      </c>
-      <c r="BU2">
-        <v>4.7</v>
-      </c>
-      <c r="BV2">
-        <v>21</v>
-      </c>
-      <c r="BW2">
-        <v>11.5</v>
-      </c>
-      <c r="BX2">
-        <v>29</v>
-      </c>
-      <c r="BY2">
-        <v>14.5</v>
-      </c>
-      <c r="BZ2">
-        <v>17</v>
-      </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1122,19 +1122,19 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1161,13 +1161,13 @@
         <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -1179,7 +1179,7 @@
         <v>7.2</v>
       </c>
       <c r="Z3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AA3">
         <v>10.5</v>
@@ -1221,7 +1221,7 @@
         <v>300</v>
       </c>
       <c r="AN3">
-        <v>530</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>7</v>
@@ -1233,16 +1233,16 @@
         <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS3">
         <v>9</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV3">
         <v>9.6</v>
@@ -1251,34 +1251,34 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3">
         <v>9</v>
       </c>
-      <c r="AZ3">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BA3">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB3">
+        <v>11.5</v>
+      </c>
+      <c r="BC3">
         <v>11</v>
       </c>
-      <c r="BC3">
-        <v>10.5</v>
-      </c>
       <c r="BD3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,15 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>CONCACAF Nations League B</t>
+  </si>
+  <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
+    <t>Chinese League 1</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -271,19 +280,73 @@
     <t>00:35:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
     <t>Ponte Preta</t>
   </si>
   <si>
+    <t>French Guyana</t>
+  </si>
+  <si>
+    <t>Taian Tiankuang</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors FC</t>
+  </si>
+  <si>
+    <t>Foshan Nanshi FC</t>
+  </si>
+  <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Jiangxi Lushan</t>
+  </si>
+  <si>
+    <t>Haimen Codion</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>2026-10-05 06:05:49</t>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Ganzhou Ruishi FC</t>
+  </si>
+  <si>
+    <t>Guangdong GZ-Power FC</t>
+  </si>
+  <si>
+    <t>Guangxi Hengchen</t>
+  </si>
+  <si>
+    <t>Shaanxi Union FC</t>
+  </si>
+  <si>
+    <t>Dalian Kewei</t>
+  </si>
+  <si>
+    <t>Xiamen Feilu</t>
+  </si>
+  <si>
+    <t>2026-10-05 08:16:12</t>
   </si>
 </sst>
 </file>
@@ -615,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -865,31 +928,31 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F2">
         <v>2.86</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -904,13 +967,13 @@
         <v>6.6</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
         <v>2.88</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R2">
         <v>1.78</v>
@@ -919,7 +982,7 @@
         <v>2.2</v>
       </c>
       <c r="T2">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="U2">
         <v>2.92</v>
@@ -928,34 +991,34 @@
         <v>1.69</v>
       </c>
       <c r="W2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
         <v>22</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG2">
         <v>14.5</v>
@@ -976,52 +1039,52 @@
         <v>32</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO2">
         <v>11</v>
       </c>
       <c r="AP2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AS2">
         <v>22</v>
       </c>
       <c r="AT2">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU2">
         <v>9.199999999999999</v>
       </c>
       <c r="AV2">
+        <v>10</v>
+      </c>
+      <c r="AW2">
+        <v>15</v>
+      </c>
+      <c r="AX2">
+        <v>17.5</v>
+      </c>
+      <c r="AY2">
         <v>11.5</v>
       </c>
-      <c r="AW2">
-        <v>18.5</v>
-      </c>
-      <c r="AX2">
-        <v>21</v>
-      </c>
-      <c r="AY2">
-        <v>12.5</v>
-      </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA2">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BC2">
         <v>17.5</v>
@@ -1039,10 +1102,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2">
         <v>8.4</v>
@@ -1054,25 +1117,25 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BP2">
         <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1084,22 +1147,22 @@
         <v>16</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
         <v>22</v>
       </c>
       <c r="BY2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2">
         <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1107,19 +1170,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>13.5</v>
@@ -1128,13 +1191,13 @@
         <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1143,148 +1206,148 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
         <v>1.62</v>
       </c>
       <c r="V3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="W3">
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="Z3">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AA3">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AB3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AE3">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
+        <v>970</v>
+      </c>
+      <c r="AP3">
+        <v>1.88</v>
+      </c>
+      <c r="AQ3">
+        <v>5.4</v>
+      </c>
+      <c r="AR3">
+        <v>5.4</v>
+      </c>
+      <c r="AS3">
         <v>7</v>
       </c>
-      <c r="AP3">
-        <v>14</v>
-      </c>
-      <c r="AQ3">
-        <v>6.2</v>
-      </c>
-      <c r="AR3">
-        <v>6.4</v>
-      </c>
-      <c r="AS3">
-        <v>9</v>
-      </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>1.88</v>
       </c>
       <c r="AU3">
-        <v>11</v>
+        <v>1.76</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>1.88</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>1.89</v>
       </c>
       <c r="AY3">
-        <v>9.4</v>
+        <v>1.88</v>
       </c>
       <c r="AZ3">
-        <v>9</v>
+        <v>1.88</v>
       </c>
       <c r="BA3">
-        <v>9.6</v>
+        <v>1.89</v>
       </c>
       <c r="BB3">
-        <v>11.5</v>
+        <v>1.89</v>
       </c>
       <c r="BC3">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="BD3">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="BE3">
-        <v>11</v>
+        <v>1.89</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>1.89</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1320,7 +1383,7 @@
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1341,7 +1404,1701 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4">
+        <v>1.1</v>
+      </c>
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4">
+        <v>1.1</v>
+      </c>
+      <c r="I4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1.1</v>
+      </c>
+      <c r="K4">
+        <v>110</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>1.12</v>
+      </c>
+      <c r="O4">
+        <v>1.36</v>
+      </c>
+      <c r="P4">
+        <v>1.12</v>
+      </c>
+      <c r="Q4">
+        <v>1.36</v>
+      </c>
+      <c r="R4">
+        <v>1.08</v>
+      </c>
+      <c r="S4">
+        <v>1.36</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.01</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5">
+        <v>1.1</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.1</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.1</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.07</v>
+      </c>
+      <c r="O5">
+        <v>1.01</v>
+      </c>
+      <c r="P5">
+        <v>1.07</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>1.07</v>
+      </c>
+      <c r="S5">
+        <v>1.01</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.01</v>
+      </c>
+      <c r="W5">
+        <v>1.02</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6">
+        <v>1.1</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.1</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.1</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.1</v>
+      </c>
+      <c r="O6">
+        <v>1.23</v>
+      </c>
+      <c r="P6">
+        <v>1.1</v>
+      </c>
+      <c r="Q6">
+        <v>1.23</v>
+      </c>
+      <c r="R6">
+        <v>1.07</v>
+      </c>
+      <c r="S6">
+        <v>1.23</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7">
+        <v>1.1</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.1</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.1</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.12</v>
+      </c>
+      <c r="O7">
+        <v>1.2</v>
+      </c>
+      <c r="P7">
+        <v>1.12</v>
+      </c>
+      <c r="Q7">
+        <v>1.19</v>
+      </c>
+      <c r="R7">
+        <v>1.08</v>
+      </c>
+      <c r="S7">
+        <v>1.2</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>1.1</v>
+      </c>
+      <c r="G8">
+        <v>1000</v>
+      </c>
+      <c r="H8">
+        <v>1.1</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>1.1</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>1.1</v>
+      </c>
+      <c r="O8">
+        <v>1.01</v>
+      </c>
+      <c r="P8">
+        <v>1.1</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>1.07</v>
+      </c>
+      <c r="S8">
+        <v>1.01</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.01</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.01</v>
+      </c>
+      <c r="AQ8">
+        <v>1.01</v>
+      </c>
+      <c r="AR8">
+        <v>1.01</v>
+      </c>
+      <c r="AS8">
+        <v>1.01</v>
+      </c>
+      <c r="AT8">
+        <v>1.01</v>
+      </c>
+      <c r="AU8">
+        <v>1.01</v>
+      </c>
+      <c r="AV8">
+        <v>1.01</v>
+      </c>
+      <c r="AW8">
+        <v>1.01</v>
+      </c>
+      <c r="AX8">
+        <v>1.01</v>
+      </c>
+      <c r="AY8">
+        <v>1.01</v>
+      </c>
+      <c r="AZ8">
+        <v>1.01</v>
+      </c>
+      <c r="BA8">
+        <v>1.01</v>
+      </c>
+      <c r="BB8">
+        <v>1.01</v>
+      </c>
+      <c r="BC8">
+        <v>1.01</v>
+      </c>
+      <c r="BD8">
+        <v>1.01</v>
+      </c>
+      <c r="BE8">
+        <v>1.01</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>1.1</v>
+      </c>
+      <c r="G9">
+        <v>1000</v>
+      </c>
+      <c r="H9">
+        <v>1.1</v>
+      </c>
+      <c r="I9">
+        <v>1000</v>
+      </c>
+      <c r="J9">
+        <v>1.1</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.07</v>
+      </c>
+      <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
+        <v>1.07</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.07</v>
+      </c>
+      <c r="S9">
+        <v>1.01</v>
+      </c>
+      <c r="T9">
+        <v>1.01</v>
+      </c>
+      <c r="U9">
+        <v>1.01</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10">
+        <v>1.1</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <v>1.1</v>
+      </c>
+      <c r="I10">
+        <v>1000</v>
+      </c>
+      <c r="J10">
+        <v>1.1</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.07</v>
+      </c>
+      <c r="O10">
+        <v>1.01</v>
+      </c>
+      <c r="P10">
+        <v>1.07</v>
+      </c>
+      <c r="Q10">
+        <v>1.01</v>
+      </c>
+      <c r="R10">
+        <v>1.07</v>
+      </c>
+      <c r="S10">
+        <v>1.01</v>
+      </c>
+      <c r="T10">
+        <v>1.01</v>
+      </c>
+      <c r="U10">
+        <v>1.01</v>
+      </c>
+      <c r="V10">
+        <v>1.01</v>
+      </c>
+      <c r="W10">
+        <v>1.01</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10">
+        <v>1.01</v>
+      </c>
+      <c r="AR10">
+        <v>1.01</v>
+      </c>
+      <c r="AS10">
+        <v>1.01</v>
+      </c>
+      <c r="AT10">
+        <v>1.01</v>
+      </c>
+      <c r="AU10">
+        <v>1.01</v>
+      </c>
+      <c r="AV10">
+        <v>1.01</v>
+      </c>
+      <c r="AW10">
+        <v>1.01</v>
+      </c>
+      <c r="AX10">
+        <v>1.01</v>
+      </c>
+      <c r="AY10">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10">
+        <v>1.01</v>
+      </c>
+      <c r="BA10">
+        <v>1.01</v>
+      </c>
+      <c r="BB10">
+        <v>1.01</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.01</v>
+      </c>
+      <c r="BE10">
+        <v>1.01</v>
+      </c>
+      <c r="BF10">
+        <v>1.01</v>
+      </c>
+      <c r="BG10">
+        <v>1.01</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.01</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.01</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.01</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.01</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.01</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.01</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.01</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -346,7 +346,7 @@
     <t>Xiamen Feilu</t>
   </si>
   <si>
-    <t>2026-10-05 08:16:12</t>
+    <t>2026-10-05 10:27:43</t>
   </si>
 </sst>
 </file>
@@ -940,10 +940,10 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>2.34</v>
@@ -952,7 +952,7 @@
         <v>2.44</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>4.3</v>
@@ -967,10 +967,10 @@
         <v>6.6</v>
       </c>
       <c r="O2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q2">
         <v>1.49</v>
@@ -982,16 +982,16 @@
         <v>2.2</v>
       </c>
       <c r="T2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U2">
         <v>2.92</v>
       </c>
       <c r="V2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X2">
         <v>44</v>
@@ -1003,19 +1003,19 @@
         <v>22</v>
       </c>
       <c r="AA2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF2">
         <v>30</v>
@@ -1027,73 +1027,73 @@
         <v>14.5</v>
       </c>
       <c r="AI2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
         <v>25</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BB2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BF2">
         <v>12.5</v>
@@ -1102,7 +1102,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI2">
         <v>4.4</v>
@@ -1114,28 +1114,28 @@
         <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP2">
         <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>25</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1147,19 +1147,19 @@
         <v>16</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
         <v>22</v>
       </c>
       <c r="BY2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ2">
         <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="CB2" t="s">
         <v>110</v>
@@ -1182,22 +1182,22 @@
         <v>102</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="H3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K3">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1206,202 +1206,202 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="W3">
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="Z3">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AA3">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD3">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AO3">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AP3">
-        <v>1.88</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT3">
-        <v>1.88</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>1.76</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>1.88</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
-        <v>1.88</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
-        <v>1.88</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA3">
-        <v>1.89</v>
+        <v>20</v>
       </c>
       <c r="BB3">
-        <v>1.89</v>
+        <v>11.5</v>
       </c>
       <c r="BC3">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="BD3">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="BE3">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="BG3">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="CB3" t="s">
         <v>110</v>
@@ -1424,46 +1424,46 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>1.1</v>
+        <v>1.72</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>5.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.36</v>
       </c>
       <c r="P4">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="Q4">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1472,10 +1472,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1532,52 +1532,52 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4">
         <v>1.01</v>
@@ -1681,7 +1681,7 @@
         <v>1.1</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1714,7 +1714,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
         <v>1.02</v>
@@ -1774,52 +1774,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1908,22 +1908,22 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H6">
-        <v>1.1</v>
+        <v>2.66</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1932,22 +1932,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q6">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>1.23</v>
+        <v>2.52</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -1956,10 +1956,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2016,52 +2016,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2150,22 +2150,22 @@
         <v>106</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2174,22 +2174,22 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.12</v>
+        <v>2.42</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
-        <v>1.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q7">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2198,10 +2198,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2258,52 +2258,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2392,22 +2392,22 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="H8">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>2.82</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2416,22 +2416,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="O8">
         <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R8">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2440,10 +2440,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2500,52 +2500,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2649,7 +2649,7 @@
         <v>1.1</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2682,10 +2682,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2891,7 +2891,7 @@
         <v>1.1</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2927,7 +2927,7 @@
         <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Chinese League 1</t>
   </si>
   <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>11:30:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Haimen Codion</t>
   </si>
   <si>
+    <t>Inter Toronto FC</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
@@ -346,7 +355,10 @@
     <t>Xiamen Feilu</t>
   </si>
   <si>
-    <t>2026-10-05 10:27:43</t>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
+    <t>2026-10-05 12:39:35</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -928,16 +940,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2">
         <v>2.88</v>
@@ -949,7 +961,7 @@
         <v>2.34</v>
       </c>
       <c r="I2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -970,55 +982,55 @@
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T2">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U2">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="V2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
         <v>1.5</v>
       </c>
       <c r="X2">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="Y2">
         <v>19.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG2">
         <v>14.5</v>
@@ -1027,142 +1039,142 @@
         <v>14.5</v>
       </c>
       <c r="AI2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ2">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AN2">
+        <v>15.5</v>
+      </c>
+      <c r="AO2">
+        <v>11</v>
+      </c>
+      <c r="AP2">
+        <v>21</v>
+      </c>
+      <c r="AQ2">
         <v>14.5</v>
       </c>
-      <c r="AO2">
-        <v>10.5</v>
-      </c>
-      <c r="AP2">
-        <v>25</v>
-      </c>
-      <c r="AQ2">
-        <v>15.5</v>
-      </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT2">
         <v>16.5</v>
       </c>
       <c r="AU2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AY2">
+        <v>12.5</v>
+      </c>
+      <c r="AZ2">
         <v>12</v>
       </c>
-      <c r="AZ2">
-        <v>12.5</v>
-      </c>
       <c r="BA2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BB2">
         <v>36</v>
       </c>
       <c r="BC2">
+        <v>17.5</v>
+      </c>
+      <c r="BD2">
         <v>19</v>
       </c>
-      <c r="BD2">
-        <v>21</v>
-      </c>
       <c r="BE2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>1.74</v>
       </c>
       <c r="BL2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>5.9</v>
+        <v>1.65</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>2.02</v>
       </c>
       <c r="BR2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>2.02</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="BV2">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>2.02</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>7.6</v>
+        <v>2.02</v>
       </c>
       <c r="BZ2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>6.2</v>
+        <v>2.02</v>
       </c>
       <c r="CB2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1170,16 +1182,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>11</v>
@@ -1215,7 +1227,7 @@
         <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R3">
         <v>1.37</v>
@@ -1224,7 +1236,7 @@
         <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
         <v>1.64</v>
@@ -1245,7 +1257,7 @@
         <v>7.2</v>
       </c>
       <c r="AA3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AB3">
         <v>32</v>
@@ -1263,7 +1275,7 @@
         <v>130</v>
       </c>
       <c r="AG3">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AH3">
         <v>38</v>
@@ -1287,7 +1299,7 @@
         <v>530</v>
       </c>
       <c r="AO3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AP3">
         <v>14</v>
@@ -1302,7 +1314,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
@@ -1314,13 +1326,13 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BA3">
         <v>20</v>
@@ -1329,16 +1341,16 @@
         <v>11.5</v>
       </c>
       <c r="BC3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG3">
         <v>6.2</v>
@@ -1347,43 +1359,43 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1395,16 +1407,16 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CB3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1412,142 +1424,142 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G4">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>3.3</v>
+      </c>
+      <c r="K4">
+        <v>3.9</v>
+      </c>
+      <c r="L4">
+        <v>1.35</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>2.86</v>
+      </c>
+      <c r="O4">
+        <v>1.39</v>
+      </c>
+      <c r="P4">
+        <v>1.71</v>
+      </c>
+      <c r="Q4">
+        <v>2.12</v>
+      </c>
+      <c r="R4">
+        <v>1.26</v>
+      </c>
+      <c r="S4">
+        <v>3.1</v>
+      </c>
+      <c r="T4">
+        <v>1.83</v>
+      </c>
+      <c r="U4">
+        <v>1.7</v>
+      </c>
+      <c r="V4">
+        <v>1.22</v>
+      </c>
+      <c r="W4">
+        <v>2.06</v>
+      </c>
+      <c r="X4">
+        <v>14.5</v>
+      </c>
+      <c r="Y4">
+        <v>19.5</v>
+      </c>
+      <c r="Z4">
+        <v>55</v>
+      </c>
+      <c r="AA4">
+        <v>190</v>
+      </c>
+      <c r="AB4">
         <v>7.6</v>
       </c>
-      <c r="J4">
-        <v>3.35</v>
-      </c>
-      <c r="K4">
-        <v>5.5</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.05</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>1.36</v>
-      </c>
-      <c r="P4">
-        <v>1.67</v>
-      </c>
-      <c r="Q4">
+      <c r="AC4">
+        <v>8.6</v>
+      </c>
+      <c r="AD4">
+        <v>27</v>
+      </c>
+      <c r="AE4">
+        <v>110</v>
+      </c>
+      <c r="AF4">
+        <v>11</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>28</v>
+      </c>
+      <c r="AI4">
+        <v>120</v>
+      </c>
+      <c r="AJ4">
+        <v>25</v>
+      </c>
+      <c r="AK4">
+        <v>27</v>
+      </c>
+      <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
+        <v>190</v>
+      </c>
+      <c r="AN4">
+        <v>19</v>
+      </c>
+      <c r="AO4">
+        <v>160</v>
+      </c>
+      <c r="AP4">
         <v>2.04</v>
       </c>
-      <c r="R4">
-        <v>1.2</v>
-      </c>
-      <c r="S4">
-        <v>2.92</v>
-      </c>
-      <c r="T4">
-        <v>1.01</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
-      <c r="V4">
-        <v>1.15</v>
-      </c>
-      <c r="W4">
-        <v>1.98</v>
-      </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
-      <c r="AC4">
-        <v>1000</v>
-      </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>1000</v>
-      </c>
-      <c r="AG4">
-        <v>1000</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>1.03</v>
-      </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AR4">
         <v>1.03</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AV4">
         <v>1.03</v>
@@ -1580,7 +1592,7 @@
         <v>1.03</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1646,7 +1658,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1654,16 +1666,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1678,7 +1690,7 @@
         <v>1000</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1690,22 +1702,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R5">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -1888,7 +1900,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1896,16 +1908,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -1926,16 +1938,16 @@
         <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
         <v>1.94</v>
@@ -1944,7 +1956,7 @@
         <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
         <v>2.52</v>
@@ -2130,7 +2142,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2138,16 +2150,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -2372,7 +2384,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2380,166 +2392,166 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G8">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
         <v>1.28</v>
       </c>
       <c r="S8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
         <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
         <v>1.03</v>
@@ -2557,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2614,7 +2626,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2622,16 +2634,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F9">
         <v>1.1</v>
@@ -2649,7 +2661,7 @@
         <v>1.1</v>
       </c>
       <c r="K9">
-        <v>870</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2658,22 +2670,22 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -2742,52 +2754,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2856,7 +2868,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2864,16 +2876,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F10">
         <v>1.1</v>
@@ -2891,7 +2903,7 @@
         <v>1.1</v>
       </c>
       <c r="K10">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2900,22 +2912,22 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S10">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
         <v>1.01</v>
@@ -2924,7 +2936,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
         <v>1.02</v>
@@ -2984,52 +2996,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3098,7 +3110,249 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>2.98</v>
+      </c>
+      <c r="G11">
+        <v>3.9</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>2.34</v>
+      </c>
+      <c r="J11">
+        <v>3.7</v>
+      </c>
+      <c r="K11">
+        <v>4.6</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>2.46</v>
+      </c>
+      <c r="O11">
+        <v>1.12</v>
+      </c>
+      <c r="P11">
+        <v>2.46</v>
+      </c>
+      <c r="Q11">
+        <v>1.43</v>
+      </c>
+      <c r="R11">
+        <v>1.64</v>
+      </c>
+      <c r="S11">
+        <v>2.06</v>
+      </c>
+      <c r="T11">
+        <v>1.01</v>
+      </c>
+      <c r="U11">
+        <v>1.01</v>
+      </c>
+      <c r="V11">
+        <v>1.74</v>
+      </c>
+      <c r="W11">
+        <v>1.34</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.03</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.03</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.01</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.01</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.01</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.01</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="119">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -298,6 +301,9 @@
     <t>15:00:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
@@ -328,6 +334,9 @@
     <t>Inter Toronto FC</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
@@ -358,7 +367,10 @@
     <t>FC Supra du Quebec</t>
   </si>
   <si>
-    <t>2026-10-05 12:39:35</t>
+    <t>FC Inter Turku</t>
+  </si>
+  <si>
+    <t>2026-10-05 14:56:23</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,22 +952,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F2">
         <v>2.88</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H2">
         <v>2.34</v>
@@ -964,70 +976,70 @@
         <v>2.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O2">
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
         <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S2">
         <v>2.24</v>
       </c>
       <c r="T2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U2">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
         <v>1.71</v>
       </c>
       <c r="W2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X2">
         <v>34</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2">
         <v>32</v>
@@ -1036,22 +1048,22 @@
         <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ2">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM2">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN2">
         <v>15.5</v>
@@ -1060,37 +1072,37 @@
         <v>11</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AS2">
         <v>22</v>
       </c>
       <c r="AT2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW2">
         <v>15</v>
       </c>
       <c r="AX2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA2">
         <v>17</v>
@@ -1108,73 +1120,73 @@
         <v>30</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ2">
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="CB2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,16 +1194,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F3">
         <v>11</v>
@@ -1209,7 +1221,7 @@
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1275,7 +1287,7 @@
         <v>130</v>
       </c>
       <c r="AG3">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AH3">
         <v>38</v>
@@ -1293,10 +1305,10 @@
         <v>230</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN3">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="AO3">
         <v>6.8</v>
@@ -1329,13 +1341,13 @@
         <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ3">
         <v>9.4</v>
       </c>
       <c r="BA3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1359,64 +1371,64 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,178 +1436,178 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T4">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="U4">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
+        <v>13</v>
+      </c>
+      <c r="Y4">
+        <v>13.5</v>
+      </c>
+      <c r="Z4">
+        <v>29</v>
+      </c>
+      <c r="AA4">
+        <v>95</v>
+      </c>
+      <c r="AB4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>16</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>15</v>
+      </c>
+      <c r="AG4">
+        <v>13.5</v>
+      </c>
+      <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>110</v>
+      </c>
+      <c r="AJ4">
+        <v>38</v>
+      </c>
+      <c r="AK4">
+        <v>34</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>29</v>
+      </c>
+      <c r="AO4">
+        <v>70</v>
+      </c>
+      <c r="AP4">
+        <v>9</v>
+      </c>
+      <c r="AQ4">
+        <v>9.4</v>
+      </c>
+      <c r="AR4">
+        <v>20</v>
+      </c>
+      <c r="AS4">
+        <v>6</v>
+      </c>
+      <c r="AT4">
+        <v>6.2</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>12.5</v>
+      </c>
+      <c r="AW4">
         <v>14.5</v>
       </c>
-      <c r="Y4">
+      <c r="AX4">
+        <v>10.5</v>
+      </c>
+      <c r="AY4">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4">
+        <v>16.5</v>
+      </c>
+      <c r="BA4">
+        <v>6</v>
+      </c>
+      <c r="BB4">
+        <v>5.5</v>
+      </c>
+      <c r="BC4">
         <v>19.5</v>
       </c>
-      <c r="Z4">
-        <v>55</v>
-      </c>
-      <c r="AA4">
-        <v>190</v>
-      </c>
-      <c r="AB4">
-        <v>7.6</v>
-      </c>
-      <c r="AC4">
-        <v>8.6</v>
-      </c>
-      <c r="AD4">
-        <v>27</v>
-      </c>
-      <c r="AE4">
-        <v>110</v>
-      </c>
-      <c r="AF4">
-        <v>11</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>28</v>
-      </c>
-      <c r="AI4">
-        <v>120</v>
-      </c>
-      <c r="AJ4">
-        <v>25</v>
-      </c>
-      <c r="AK4">
-        <v>27</v>
-      </c>
-      <c r="AL4">
-        <v>55</v>
-      </c>
-      <c r="AM4">
-        <v>190</v>
-      </c>
-      <c r="AN4">
-        <v>19</v>
-      </c>
-      <c r="AO4">
-        <v>160</v>
-      </c>
-      <c r="AP4">
-        <v>2.04</v>
-      </c>
-      <c r="AQ4">
-        <v>1.82</v>
-      </c>
-      <c r="AR4">
-        <v>1.03</v>
-      </c>
-      <c r="AS4">
-        <v>1.74</v>
-      </c>
-      <c r="AT4">
-        <v>1.29</v>
-      </c>
-      <c r="AU4">
-        <v>1.24</v>
-      </c>
-      <c r="AV4">
-        <v>1.03</v>
-      </c>
-      <c r="AW4">
-        <v>1.03</v>
-      </c>
-      <c r="AX4">
-        <v>1.03</v>
-      </c>
-      <c r="AY4">
-        <v>1.03</v>
-      </c>
-      <c r="AZ4">
-        <v>1.03</v>
-      </c>
-      <c r="BA4">
-        <v>1.03</v>
-      </c>
-      <c r="BB4">
-        <v>1.03</v>
-      </c>
-      <c r="BC4">
-        <v>1.03</v>
-      </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1658,7 +1670,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1666,16 +1678,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F5">
         <v>1.1</v>
@@ -1687,7 +1699,7 @@
         <v>1.1</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="J5">
         <v>1.12</v>
@@ -1900,7 +1912,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1908,16 +1920,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -1926,7 +1938,7 @@
         <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I6">
         <v>3.35</v>
@@ -1935,7 +1947,7 @@
         <v>3</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
         <v>1.28</v>
@@ -1947,7 +1959,7 @@
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>1.94</v>
@@ -2142,7 +2154,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2150,16 +2162,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -2384,7 +2396,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2392,34 +2404,34 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F8">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.33</v>
@@ -2431,13 +2443,13 @@
         <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P8">
         <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
         <v>1.28</v>
@@ -2446,16 +2458,16 @@
         <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
-        <v>1.92</v>
+        <v>1.02</v>
       </c>
       <c r="V8">
         <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X8">
         <v>15.5</v>
@@ -2512,64 +2524,64 @@
         <v>20</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH8">
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
@@ -2626,7 +2638,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2634,31 +2646,31 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F9">
         <v>1.1</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9">
         <v>1.1</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2868,7 +2880,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2876,31 +2888,31 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F10">
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>1.1</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -2918,7 +2930,7 @@
         <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q10">
         <v>1.43</v>
@@ -3110,7 +3122,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3118,19 +3130,19 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="G11">
         <v>3.9</v>
@@ -3145,7 +3157,7 @@
         <v>3.7</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3154,7 +3166,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="O11">
         <v>1.12</v>
@@ -3352,7 +3364,249 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>114</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12">
+        <v>4.3</v>
+      </c>
+      <c r="G12">
+        <v>4.7</v>
+      </c>
+      <c r="H12">
+        <v>1.87</v>
+      </c>
+      <c r="I12">
+        <v>1.94</v>
+      </c>
+      <c r="J12">
+        <v>3.8</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>1.32</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>4.3</v>
+      </c>
+      <c r="O12">
+        <v>1.27</v>
+      </c>
+      <c r="P12">
+        <v>2.14</v>
+      </c>
+      <c r="Q12">
+        <v>1.78</v>
+      </c>
+      <c r="R12">
+        <v>1.44</v>
+      </c>
+      <c r="S12">
+        <v>3.05</v>
+      </c>
+      <c r="T12">
+        <v>1.73</v>
+      </c>
+      <c r="U12">
+        <v>2.2</v>
+      </c>
+      <c r="V12">
+        <v>2.06</v>
+      </c>
+      <c r="W12">
+        <v>1.27</v>
+      </c>
+      <c r="X12">
+        <v>18.5</v>
+      </c>
+      <c r="Y12">
+        <v>10.5</v>
+      </c>
+      <c r="Z12">
+        <v>13</v>
+      </c>
+      <c r="AA12">
+        <v>22</v>
+      </c>
+      <c r="AB12">
+        <v>18</v>
+      </c>
+      <c r="AC12">
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <v>11</v>
+      </c>
+      <c r="AE12">
+        <v>19</v>
+      </c>
+      <c r="AF12">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>18.5</v>
+      </c>
+      <c r="AH12">
+        <v>18.5</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>120</v>
+      </c>
+      <c r="AK12">
+        <v>70</v>
+      </c>
+      <c r="AL12">
+        <v>70</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>65</v>
+      </c>
+      <c r="AO12">
+        <v>11.5</v>
+      </c>
+      <c r="AP12">
+        <v>15</v>
+      </c>
+      <c r="AQ12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR12">
+        <v>10.5</v>
+      </c>
+      <c r="AS12">
+        <v>17.5</v>
+      </c>
+      <c r="AT12">
+        <v>15</v>
+      </c>
+      <c r="AU12">
+        <v>8</v>
+      </c>
+      <c r="AV12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12">
+        <v>16</v>
+      </c>
+      <c r="AX12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY12">
+        <v>15</v>
+      </c>
+      <c r="AZ12">
+        <v>15.5</v>
+      </c>
+      <c r="BA12">
+        <v>8</v>
+      </c>
+      <c r="BB12">
+        <v>9.4</v>
+      </c>
+      <c r="BC12">
+        <v>32</v>
+      </c>
+      <c r="BD12">
+        <v>34</v>
+      </c>
+      <c r="BE12">
+        <v>9.4</v>
+      </c>
+      <c r="BF12">
+        <v>32</v>
+      </c>
+      <c r="BG12">
+        <v>10</v>
+      </c>
+      <c r="BH12">
+        <v>4.5</v>
+      </c>
+      <c r="BI12">
+        <v>2.74</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>6.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.32</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>5.2</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>2.32</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>2.32</v>
+      </c>
+      <c r="BT12">
+        <v>6.2</v>
+      </c>
+      <c r="BU12">
+        <v>3.4</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>2.32</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>2.32</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>2.32</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -370,7 +370,7 @@
     <t>FC Inter Turku</t>
   </si>
   <si>
-    <t>2026-10-05 14:56:23</t>
+    <t>2026-10-05 17:07:52</t>
   </si>
 </sst>
 </file>
@@ -964,22 +964,22 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="G2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
         <v>2.4</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.27</v>
@@ -991,139 +991,139 @@
         <v>6.4</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
+        <v>2.8</v>
+      </c>
+      <c r="Q2">
+        <v>1.52</v>
+      </c>
+      <c r="R2">
+        <v>1.76</v>
+      </c>
+      <c r="S2">
+        <v>2.28</v>
+      </c>
+      <c r="T2">
+        <v>1.49</v>
+      </c>
+      <c r="U2">
         <v>2.88</v>
       </c>
-      <c r="Q2">
-        <v>1.5</v>
-      </c>
-      <c r="R2">
-        <v>1.77</v>
-      </c>
-      <c r="S2">
-        <v>2.24</v>
-      </c>
-      <c r="T2">
-        <v>1.47</v>
-      </c>
-      <c r="U2">
-        <v>2.9</v>
-      </c>
       <c r="V2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AB2">
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2">
         <v>23</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ2">
-        <v>190</v>
+        <v>65</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>34</v>
       </c>
       <c r="AM2">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
         <v>11</v>
       </c>
       <c r="AP2">
+        <v>22</v>
+      </c>
+      <c r="AQ2">
+        <v>14.5</v>
+      </c>
+      <c r="AR2">
+        <v>16.5</v>
+      </c>
+      <c r="AS2">
+        <v>25</v>
+      </c>
+      <c r="AT2">
+        <v>18</v>
+      </c>
+      <c r="AU2">
+        <v>9</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>18.5</v>
+      </c>
+      <c r="AX2">
+        <v>21</v>
+      </c>
+      <c r="AY2">
+        <v>12</v>
+      </c>
+      <c r="AZ2">
+        <v>12.5</v>
+      </c>
+      <c r="BA2">
         <v>19.5</v>
       </c>
-      <c r="AQ2">
+      <c r="BB2">
+        <v>32</v>
+      </c>
+      <c r="BC2">
+        <v>21</v>
+      </c>
+      <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
+        <v>38</v>
+      </c>
+      <c r="BF2">
         <v>14</v>
       </c>
-      <c r="AR2">
-        <v>15</v>
-      </c>
-      <c r="AS2">
-        <v>22</v>
-      </c>
-      <c r="AT2">
-        <v>15.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>15</v>
-      </c>
-      <c r="AX2">
-        <v>17.5</v>
-      </c>
-      <c r="AY2">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2">
-        <v>11.5</v>
-      </c>
-      <c r="BA2">
-        <v>17</v>
-      </c>
-      <c r="BB2">
-        <v>36</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
-      <c r="BD2">
-        <v>19</v>
-      </c>
-      <c r="BE2">
-        <v>30</v>
-      </c>
-      <c r="BF2">
-        <v>12</v>
-      </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1209,19 +1209,19 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1230,7 +1230,7 @@
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O3">
         <v>1.32</v>
@@ -1239,7 +1239,7 @@
         <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
         <v>1.37</v>
@@ -1248,13 +1248,13 @@
         <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -1287,7 +1287,7 @@
         <v>130</v>
       </c>
       <c r="AG3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AH3">
         <v>38</v>
@@ -1308,7 +1308,7 @@
         <v>290</v>
       </c>
       <c r="AN3">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>6.8</v>
@@ -1323,31 +1323,31 @@
         <v>6.4</v>
       </c>
       <c r="AS3">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3">
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
         <v>18</v>
       </c>
       <c r="AZ3">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB3">
         <v>11.5</v>
@@ -1362,10 +1362,10 @@
         <v>11</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1448,37 +1448,37 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H4">
         <v>3.4</v>
       </c>
       <c r="I4">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J4">
         <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.38</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="Q4">
         <v>2.16</v>
@@ -1496,10 +1496,10 @@
         <v>1.89</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X4">
         <v>13</v>
@@ -1526,28 +1526,28 @@
         <v>60</v>
       </c>
       <c r="AF4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4">
         <v>29</v>
@@ -1565,7 +1565,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -1577,97 +1577,97 @@
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BB4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC4">
         <v>19.5</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
         <v>17</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
         <v>1000</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
         <v>1000</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
         <v>1000</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
         <v>1000</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1693,13 +1693,13 @@
         <v>1.1</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H5">
         <v>1.1</v>
       </c>
       <c r="I5">
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="J5">
         <v>1.12</v>
@@ -1714,13 +1714,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
         <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Q5">
         <v>1.42</v>
@@ -1732,16 +1732,16 @@
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1798,52 +1798,52 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -1855,61 +1855,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1974,10 +1974,10 @@
         <v>2.52</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
         <v>1.43</v>
@@ -2097,61 +2097,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2216,10 +2216,10 @@
         <v>2.28</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>2.22</v>
@@ -2339,61 +2339,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>118</v>
@@ -2449,7 +2449,7 @@
         <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
         <v>1.28</v>
@@ -2458,10 +2458,10 @@
         <v>3.1</v>
       </c>
       <c r="T8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U8">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.8</v>
@@ -2581,61 +2581,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2661,13 +2661,13 @@
         <v>1.1</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H9">
         <v>1.1</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J9">
         <v>1.12</v>
@@ -2682,16 +2682,16 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>1.02</v>
       </c>
       <c r="P9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R9">
         <v>1.08</v>
@@ -2700,16 +2700,16 @@
         <v>1.56</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2823,61 +2823,61 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2903,13 +2903,13 @@
         <v>1.1</v>
       </c>
       <c r="G10">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H10">
         <v>1.1</v>
       </c>
       <c r="I10">
-        <v>880</v>
+        <v>990</v>
       </c>
       <c r="J10">
         <v>1.12</v>
@@ -2924,7 +2924,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
         <v>1.02</v>
@@ -2933,7 +2933,7 @@
         <v>1.09</v>
       </c>
       <c r="Q10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R10">
         <v>1.08</v>
@@ -2942,16 +2942,16 @@
         <v>1.44</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3008,52 +3008,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3065,61 +3065,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3166,10 +3166,10 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.1</v>
+        <v>2.46</v>
       </c>
       <c r="O11">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="P11">
         <v>2.46</v>
@@ -3184,10 +3184,10 @@
         <v>2.06</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.74</v>
@@ -3307,61 +3307,61 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
         <v>1000</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>
@@ -3393,13 +3393,13 @@
         <v>1.87</v>
       </c>
       <c r="I12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
         <v>1.32</v>
@@ -3432,7 +3432,7 @@
         <v>2.2</v>
       </c>
       <c r="V12">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W12">
         <v>1.27</v>
@@ -3486,7 +3486,7 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO12">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -370,7 +370,7 @@
     <t>FC Inter Turku</t>
   </si>
   <si>
-    <t>2026-10-05 17:07:52</t>
+    <t>2026-10-05 19:18:38</t>
   </si>
 </sst>
 </file>
@@ -991,37 +991,37 @@
         <v>6.4</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q2">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T2">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="U2">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2">
         <v>29</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>21</v>
@@ -1033,13 +1033,13 @@
         <v>22</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2">
         <v>29</v>
@@ -1051,37 +1051,37 @@
         <v>14</v>
       </c>
       <c r="AI2">
+        <v>26</v>
+      </c>
+      <c r="AJ2">
+        <v>55</v>
+      </c>
+      <c r="AK2">
         <v>28</v>
       </c>
-      <c r="AJ2">
-        <v>65</v>
-      </c>
-      <c r="AK2">
-        <v>30</v>
-      </c>
       <c r="AL2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
+        <v>24</v>
+      </c>
+      <c r="AQ2">
+        <v>16</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
         <v>22</v>
-      </c>
-      <c r="AQ2">
-        <v>14.5</v>
-      </c>
-      <c r="AR2">
-        <v>16.5</v>
-      </c>
-      <c r="AS2">
-        <v>25</v>
       </c>
       <c r="AT2">
         <v>18</v>
@@ -1090,28 +1090,28 @@
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW2">
         <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2">
+        <v>13</v>
+      </c>
+      <c r="AZ2">
         <v>12</v>
       </c>
-      <c r="AZ2">
-        <v>12.5</v>
-      </c>
       <c r="BA2">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BB2">
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD2">
         <v>22</v>
@@ -1123,7 +1123,7 @@
         <v>14</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1209,19 +1209,19 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J3">
         <v>5.1</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
         <v>1.36</v>
@@ -1254,7 +1254,7 @@
         <v>1.61</v>
       </c>
       <c r="V3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -1275,7 +1275,7 @@
         <v>32</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1326,7 +1326,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>11</v>
@@ -1338,31 +1338,31 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>16</v>
+      </c>
+      <c r="AZ3">
+        <v>13</v>
+      </c>
+      <c r="BA3">
+        <v>19</v>
+      </c>
+      <c r="BB3">
+        <v>11</v>
+      </c>
+      <c r="BC3">
         <v>10.5</v>
       </c>
-      <c r="AY3">
-        <v>18</v>
-      </c>
-      <c r="AZ3">
-        <v>14</v>
-      </c>
-      <c r="BA3">
-        <v>19.5</v>
-      </c>
-      <c r="BB3">
-        <v>11.5</v>
-      </c>
-      <c r="BC3">
+      <c r="BD3">
+        <v>10.5</v>
+      </c>
+      <c r="BE3">
+        <v>10.5</v>
+      </c>
+      <c r="BF3">
         <v>11</v>
-      </c>
-      <c r="BD3">
-        <v>11</v>
-      </c>
-      <c r="BE3">
-        <v>11</v>
-      </c>
-      <c r="BF3">
-        <v>11.5</v>
       </c>
       <c r="BG3">
         <v>6</v>
@@ -1448,7 +1448,7 @@
         <v>109</v>
       </c>
       <c r="F4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
         <v>2.48</v>
@@ -1460,34 +1460,34 @@
         <v>4.1</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O4">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
         <v>1.9</v>
@@ -1690,13 +1690,13 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G5">
         <v>990</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I5">
         <v>990</v>
@@ -1729,7 +1729,7 @@
         <v>1.08</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1959,7 +1959,7 @@
         <v>3.5</v>
       </c>
       <c r="O6">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
         <v>1.94</v>
@@ -2040,52 +2040,52 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
         <v>1.01</v>
@@ -2282,52 +2282,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2658,13 +2658,13 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I9">
         <v>990</v>
@@ -2706,7 +2706,7 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -2766,52 +2766,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2900,13 +2900,13 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G10">
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I10">
         <v>990</v>
@@ -3142,13 +3142,13 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I11">
         <v>2.34</v>
@@ -3157,7 +3157,7 @@
         <v>3.7</v>
       </c>
       <c r="K11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3166,16 +3166,16 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
         <v>1.05</v>
       </c>
       <c r="P11">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="Q11">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
         <v>1.64</v>
@@ -3190,10 +3190,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3250,52 +3250,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3477,7 +3477,7 @@
         <v>120</v>
       </c>
       <c r="AK12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL12">
         <v>70</v>
@@ -3486,7 +3486,7 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO12">
         <v>11.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -304,6 +307,12 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
@@ -337,6 +346,12 @@
     <t>Gnistan</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Belouizdad</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
@@ -370,7 +385,13 @@
     <t>FC Inter Turku</t>
   </si>
   <si>
-    <t>2026-10-05 19:18:38</t>
+    <t>US Biskra</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>2026-10-05 21:30:43</t>
   </si>
 </sst>
 </file>
@@ -702,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -952,34 +973,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G2">
         <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.27</v>
@@ -1003,7 +1024,7 @@
         <v>1.79</v>
       </c>
       <c r="S2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T2">
         <v>1.46</v>
@@ -1012,7 +1033,7 @@
         <v>2.96</v>
       </c>
       <c r="V2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W2">
         <v>1.47</v>
@@ -1042,10 +1063,10 @@
         <v>22</v>
       </c>
       <c r="AF2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
         <v>14</v>
@@ -1057,7 +1078,7 @@
         <v>55</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>32</v>
@@ -1066,7 +1087,7 @@
         <v>55</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO2">
         <v>10.5</v>
@@ -1075,13 +1096,13 @@
         <v>24</v>
       </c>
       <c r="AQ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT2">
         <v>18</v>
@@ -1090,13 +1111,13 @@
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
+        <v>17.5</v>
+      </c>
+      <c r="AX2">
         <v>18.5</v>
-      </c>
-      <c r="AX2">
-        <v>20</v>
       </c>
       <c r="AY2">
         <v>13</v>
@@ -1105,16 +1126,16 @@
         <v>12</v>
       </c>
       <c r="BA2">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB2">
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BE2">
         <v>38</v>
@@ -1126,67 +1147,67 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI2">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK2">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.06</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS2">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>1.62</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY2">
-        <v>2.06</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA2">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1194,16 +1215,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F3">
         <v>11</v>
@@ -1215,10 +1236,10 @@
         <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K3">
         <v>5.8</v>
@@ -1254,7 +1275,7 @@
         <v>1.61</v>
       </c>
       <c r="V3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -1275,7 +1296,7 @@
         <v>32</v>
       </c>
       <c r="AC3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1326,7 +1347,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3">
         <v>11</v>
@@ -1338,31 +1359,31 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3">
         <v>16</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB3">
+        <v>11.5</v>
+      </c>
+      <c r="BC3">
         <v>11</v>
-      </c>
-      <c r="BC3">
-        <v>10.5</v>
       </c>
       <c r="BD3">
         <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
         <v>6</v>
@@ -1428,7 +1449,7 @@
         <v>1.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1436,16 +1457,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F4">
         <v>2.18</v>
@@ -1478,7 +1499,7 @@
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q4">
         <v>2.22</v>
@@ -1589,7 +1610,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
         <v>5.7</v>
@@ -1670,7 +1691,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1678,16 +1699,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F5">
         <v>1.12</v>
@@ -1738,10 +1759,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1912,7 +1933,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1920,16 +1941,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -2154,7 +2175,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2162,16 +2183,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F7">
         <v>4.7</v>
@@ -2396,7 +2417,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2404,16 +2425,16 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F8">
         <v>3.55</v>
@@ -2638,7 +2659,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2646,16 +2667,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F9">
         <v>1.12</v>
@@ -2880,7 +2901,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2888,16 +2909,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F10">
         <v>1.12</v>
@@ -2912,7 +2933,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -2948,10 +2969,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3122,7 +3143,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3130,34 +3151,34 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="G11">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="H11">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="I11">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="J11">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3166,13 +3187,13 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O11">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
         <v>1.44</v>
@@ -3190,10 +3211,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="W11">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3364,7 +3385,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3372,16 +3393,16 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F12">
         <v>4.3</v>
@@ -3417,7 +3438,7 @@
         <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R12">
         <v>1.44</v>
@@ -3477,7 +3498,7 @@
         <v>120</v>
       </c>
       <c r="AK12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL12">
         <v>70</v>
@@ -3606,7 +3627,491 @@
         <v>2.32</v>
       </c>
       <c r="CB12" t="s">
-        <v>118</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13">
+        <v>1.1</v>
+      </c>
+      <c r="G13">
+        <v>990</v>
+      </c>
+      <c r="H13">
+        <v>1.1</v>
+      </c>
+      <c r="I13">
+        <v>990</v>
+      </c>
+      <c r="J13">
+        <v>1.1</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13">
+        <v>1.01</v>
+      </c>
+      <c r="P13">
+        <v>1.08</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>1.08</v>
+      </c>
+      <c r="S13">
+        <v>1.05</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.01</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14">
+        <v>1.1</v>
+      </c>
+      <c r="G14">
+        <v>990</v>
+      </c>
+      <c r="H14">
+        <v>1.1</v>
+      </c>
+      <c r="I14">
+        <v>990</v>
+      </c>
+      <c r="J14">
+        <v>1.1</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.1</v>
+      </c>
+      <c r="O14">
+        <v>1.01</v>
+      </c>
+      <c r="P14">
+        <v>1.08</v>
+      </c>
+      <c r="Q14">
+        <v>1.01</v>
+      </c>
+      <c r="R14">
+        <v>1.08</v>
+      </c>
+      <c r="S14">
+        <v>1.05</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.01</v>
+      </c>
+      <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.04</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.04</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.04</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.04</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -391,7 +391,7 @@
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>2026-10-05 21:30:43</t>
+    <t>2026-10-05 23:41:44</t>
   </si>
 </sst>
 </file>
@@ -985,22 +985,22 @@
         <v>112</v>
       </c>
       <c r="F2">
+        <v>2.98</v>
+      </c>
+      <c r="G2">
         <v>3.05</v>
       </c>
-      <c r="G2">
-        <v>3.1</v>
-      </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I2">
         <v>2.38</v>
       </c>
       <c r="J2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
         <v>1.27</v>
@@ -1015,19 +1015,19 @@
         <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q2">
         <v>1.51</v>
       </c>
       <c r="R2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S2">
         <v>2.22</v>
       </c>
       <c r="T2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U2">
         <v>2.96</v>
@@ -1036,13 +1036,13 @@
         <v>1.72</v>
       </c>
       <c r="W2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
         <v>29</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z2">
         <v>21</v>
@@ -1051,7 +1051,7 @@
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1063,10 +1063,10 @@
         <v>22</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
         <v>14</v>
@@ -1102,7 +1102,7 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT2">
         <v>18</v>
@@ -1111,37 +1111,37 @@
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
         <v>12</v>
       </c>
       <c r="BA2">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD2">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BE2">
         <v>38</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
         <v>9.199999999999999</v>
@@ -1174,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR2">
         <v>26</v>
@@ -1186,25 +1186,25 @@
         <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
         <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX2">
         <v>22</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>14</v>
       </c>
       <c r="CA2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB2" t="s">
         <v>125</v>
@@ -1227,10 +1227,10 @@
         <v>113</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H3">
         <v>1.34</v>
@@ -1239,25 +1239,25 @@
         <v>1.36</v>
       </c>
       <c r="J3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O3">
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q3">
         <v>1.92</v>
@@ -1269,7 +1269,7 @@
         <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U3">
         <v>1.61</v>
@@ -1284,7 +1284,7 @@
         <v>16.5</v>
       </c>
       <c r="Y3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z3">
         <v>7.2</v>
@@ -1332,7 +1332,7 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP3">
         <v>14</v>
@@ -1347,7 +1347,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU3">
         <v>11</v>
@@ -1359,31 +1359,31 @@
         <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
+        <v>13</v>
+      </c>
+      <c r="BA3">
+        <v>19</v>
+      </c>
+      <c r="BB3">
         <v>12.5</v>
       </c>
-      <c r="BA3">
-        <v>18.5</v>
-      </c>
-      <c r="BB3">
+      <c r="BC3">
         <v>11.5</v>
       </c>
-      <c r="BC3">
+      <c r="BD3">
         <v>11</v>
       </c>
-      <c r="BD3">
-        <v>10.5</v>
-      </c>
       <c r="BE3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG3">
         <v>6</v>
@@ -1392,37 +1392,37 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="BT3">
         <v>1000</v>
@@ -1434,19 +1434,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>2.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="CB3" t="s">
         <v>125</v>
@@ -1469,22 +1469,22 @@
         <v>114</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G4">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1493,16 +1493,16 @@
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
         <v>1.24</v>
@@ -1511,16 +1511,16 @@
         <v>4.2</v>
       </c>
       <c r="T4">
+        <v>1.92</v>
+      </c>
+      <c r="U4">
         <v>1.9</v>
       </c>
-      <c r="U4">
-        <v>1.89</v>
-      </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>13</v>
@@ -1541,7 +1541,7 @@
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
         <v>60</v>
@@ -1559,10 +1559,10 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AK4">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AL4">
         <v>60</v>
@@ -1577,16 +1577,16 @@
         <v>70</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
@@ -1595,37 +1595,37 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="BB4">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BE4">
         <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
         <v>6.2</v>
@@ -1723,7 +1723,7 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1759,10 +1759,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2195,13 +2195,13 @@
         <v>117</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="G7">
-        <v>14</v>
+        <v>990</v>
       </c>
       <c r="H7">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="I7">
         <v>1.82</v>
@@ -2213,16 +2213,16 @@
         <v>10.5</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
         <v>2.42</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
         <v>2.04</v>
@@ -2437,22 +2437,22 @@
         <v>118</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L8">
         <v>1.33</v>
@@ -2470,7 +2470,7 @@
         <v>1.82</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
         <v>1.28</v>
@@ -2488,7 +2488,7 @@
         <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X8">
         <v>15.5</v>
@@ -2727,10 +2727,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2969,10 +2969,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3166,7 +3166,7 @@
         <v>2.72</v>
       </c>
       <c r="G11">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="H11">
         <v>2.18</v>
@@ -3175,7 +3175,7 @@
         <v>2.58</v>
       </c>
       <c r="J11">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
         <v>6.4</v>
@@ -3187,10 +3187,10 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.56</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
         <v>2.56</v>
@@ -3420,7 +3420,7 @@
         <v>3.85</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <v>1.32</v>
@@ -3438,7 +3438,7 @@
         <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R12">
         <v>1.44</v>
@@ -3447,7 +3447,7 @@
         <v>3.05</v>
       </c>
       <c r="T12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U12">
         <v>2.2</v>
@@ -3465,7 +3465,7 @@
         <v>10.5</v>
       </c>
       <c r="Z12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA12">
         <v>22</v>
@@ -3507,7 +3507,7 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO12">
         <v>11.5</v>
@@ -3537,7 +3537,7 @@
         <v>16</v>
       </c>
       <c r="AX12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY12">
         <v>15</v>
@@ -3546,10 +3546,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3558,7 +3558,7 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF12">
         <v>32</v>
@@ -3612,7 +3612,7 @@
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>2.32</v>
+        <v>7.2</v>
       </c>
       <c r="BX12">
         <v>1000</v>
@@ -3647,46 +3647,46 @@
         <v>123</v>
       </c>
       <c r="F13">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="G13">
-        <v>990</v>
+        <v>1.8</v>
       </c>
       <c r="H13">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>13.5</v>
       </c>
       <c r="J13">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R13">
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3695,10 +3695,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3713,7 +3713,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC13">
         <v>1000</v>
@@ -3812,7 +3812,7 @@
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
@@ -3889,58 +3889,58 @@
         <v>124</v>
       </c>
       <c r="F14">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>1.48</v>
       </c>
       <c r="H14">
-        <v>1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P14">
-        <v>1.08</v>
+        <v>1.66</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S14">
-        <v>1.05</v>
+        <v>2.96</v>
       </c>
       <c r="T14">
         <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="V14">
         <v>1.01</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4054,19 +4054,19 @@
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BN14">
         <v>1000</v>
@@ -4078,37 +4078,37 @@
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="CB14" t="s">
         <v>125</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="159">
   <si>
     <t>League</t>
   </si>
@@ -280,6 +280,12 @@
     <t>Algerian Ligue 1</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
     <t>2026-10-07</t>
   </si>
   <si>
@@ -313,6 +319,21 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Chicago Fire</t>
   </si>
   <si>
@@ -352,6 +373,45 @@
     <t>Belouizdad</t>
   </si>
   <si>
+    <t>Leones FC</t>
+  </si>
+  <si>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
+    <t>Red Bull Bragantino</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Operario PR</t>
+  </si>
+  <si>
+    <t>EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>Forge</t>
+  </si>
+  <si>
+    <t>Botafogo FR</t>
+  </si>
+  <si>
+    <t>Vila Nova</t>
+  </si>
+  <si>
+    <t>CRB</t>
+  </si>
+  <si>
+    <t>America MG</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
@@ -391,7 +451,46 @@
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>2026-10-05 23:41:44</t>
+    <t>Barranquilla</t>
+  </si>
+  <si>
+    <t>Union Magdalena</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Gremio</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Pacific</t>
+  </si>
+  <si>
+    <t>Vasco Da Gama</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>Fortaleza EC</t>
+  </si>
+  <si>
+    <t>2026-10-06 01:52:54</t>
   </si>
 </sst>
 </file>
@@ -723,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -973,22 +1072,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="F2">
         <v>2.98</v>
       </c>
       <c r="G2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>2.34</v>
@@ -1012,16 +1111,16 @@
         <v>6.4</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q2">
         <v>1.51</v>
       </c>
       <c r="R2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S2">
         <v>2.22</v>
@@ -1048,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="AA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB2">
         <v>21</v>
@@ -1066,7 +1165,7 @@
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>14</v>
@@ -1087,13 +1186,13 @@
         <v>55</v>
       </c>
       <c r="AN2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
         <v>10.5</v>
       </c>
       <c r="AP2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1102,37 +1201,37 @@
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT2">
         <v>18</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
         <v>18</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
         <v>12</v>
       </c>
       <c r="BA2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC2">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BD2">
         <v>25</v>
@@ -1156,7 +1255,7 @@
         <v>8.4</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1207,7 +1306,7 @@
         <v>7.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1215,16 +1314,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F3">
         <v>11.5</v>
@@ -1233,7 +1332,7 @@
         <v>13.5</v>
       </c>
       <c r="H3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I3">
         <v>1.36</v>
@@ -1245,31 +1344,31 @@
         <v>5.7</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O3">
         <v>1.32</v>
       </c>
       <c r="P3">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
         <v>1.61</v>
@@ -1347,7 +1446,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU3">
         <v>11</v>
@@ -1362,16 +1461,16 @@
         <v>12</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC3">
         <v>11.5</v>
@@ -1449,7 +1548,7 @@
         <v>1.08</v>
       </c>
       <c r="CB3" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1457,22 +1556,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="F4">
         <v>2.24</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
         <v>3.45</v>
@@ -1481,61 +1580,61 @@
         <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
         <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA4">
         <v>95</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1559,10 +1658,10 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AK4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL4">
         <v>60</v>
@@ -1577,7 +1676,7 @@
         <v>70</v>
       </c>
       <c r="AP4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
         <v>9.800000000000001</v>
@@ -1586,10 +1685,10 @@
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -1598,7 +1697,7 @@
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1610,25 +1709,25 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB4">
         <v>26</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
         <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1691,7 +1790,7 @@
         <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1699,16 +1798,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="F5">
         <v>1.12</v>
@@ -1723,7 +1822,7 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1759,10 +1858,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1933,7 +2032,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1941,16 +2040,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -2175,7 +2274,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2183,16 +2282,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="F7">
         <v>5.7</v>
@@ -2417,7 +2516,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2425,19 +2524,19 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="F8">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
         <v>4.6</v>
@@ -2452,7 +2551,7 @@
         <v>3.25</v>
       </c>
       <c r="K8">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.33</v>
@@ -2467,7 +2566,7 @@
         <v>1.31</v>
       </c>
       <c r="P8">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q8">
         <v>1.99</v>
@@ -2491,19 +2590,19 @@
         <v>1.28</v>
       </c>
       <c r="X8">
+        <v>16</v>
+      </c>
+      <c r="Y8">
+        <v>11</v>
+      </c>
+      <c r="Z8">
         <v>15.5</v>
       </c>
-      <c r="Y8">
-        <v>10.5</v>
-      </c>
-      <c r="Z8">
-        <v>15</v>
-      </c>
       <c r="AA8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC8">
         <v>9.199999999999999</v>
@@ -2518,7 +2617,7 @@
         <v>34</v>
       </c>
       <c r="AG8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH8">
         <v>22</v>
@@ -2536,67 +2635,67 @@
         <v>70</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN8">
         <v>65</v>
       </c>
       <c r="AO8">
+        <v>21</v>
+      </c>
+      <c r="AP8">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8">
+        <v>7.2</v>
+      </c>
+      <c r="AR8">
+        <v>10</v>
+      </c>
+      <c r="AS8">
+        <v>4.5</v>
+      </c>
+      <c r="AT8">
+        <v>10.5</v>
+      </c>
+      <c r="AU8">
+        <v>6.2</v>
+      </c>
+      <c r="AV8">
+        <v>8.4</v>
+      </c>
+      <c r="AW8">
         <v>20</v>
       </c>
-      <c r="AP8">
-        <v>3.9</v>
-      </c>
-      <c r="AQ8">
-        <v>3.5</v>
-      </c>
-      <c r="AR8">
-        <v>3.85</v>
-      </c>
-      <c r="AS8">
-        <v>4.4</v>
-      </c>
-      <c r="AT8">
-        <v>3.95</v>
-      </c>
-      <c r="AU8">
-        <v>3.3</v>
-      </c>
-      <c r="AV8">
-        <v>3.7</v>
-      </c>
-      <c r="AW8">
-        <v>4.4</v>
-      </c>
       <c r="AX8">
+        <v>4.6</v>
+      </c>
+      <c r="AY8">
+        <v>13.5</v>
+      </c>
+      <c r="AZ8">
+        <v>15.5</v>
+      </c>
+      <c r="BA8">
         <v>4.5</v>
       </c>
-      <c r="AY8">
-        <v>4.1</v>
-      </c>
-      <c r="AZ8">
-        <v>4.2</v>
-      </c>
-      <c r="BA8">
+      <c r="BB8">
         <v>4.7</v>
       </c>
-      <c r="BB8">
-        <v>4.9</v>
-      </c>
       <c r="BC8">
+        <v>4.6</v>
+      </c>
+      <c r="BD8">
+        <v>4.6</v>
+      </c>
+      <c r="BE8">
         <v>4.8</v>
       </c>
-      <c r="BD8">
-        <v>4.8</v>
-      </c>
-      <c r="BE8">
-        <v>5</v>
-      </c>
       <c r="BF8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG8">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2659,7 +2758,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2667,16 +2766,16 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="F9">
         <v>1.12</v>
@@ -2691,7 +2790,7 @@
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2727,10 +2826,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2901,7 +3000,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2909,16 +3008,16 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F10">
         <v>1.12</v>
@@ -2933,7 +3032,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="K10">
         <v>950</v>
@@ -2945,16 +3044,16 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O10">
         <v>1.02</v>
       </c>
       <c r="P10">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Q10">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="R10">
         <v>1.08</v>
@@ -2969,10 +3068,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3143,7 +3242,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3151,16 +3250,16 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="F11">
         <v>2.72</v>
@@ -3172,13 +3271,13 @@
         <v>2.18</v>
       </c>
       <c r="I11">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J11">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3187,10 +3286,10 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>2.56</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="P11">
         <v>2.56</v>
@@ -3211,10 +3310,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3385,7 +3484,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3393,16 +3492,16 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="F12">
         <v>4.3</v>
@@ -3438,7 +3537,7 @@
         <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R12">
         <v>1.44</v>
@@ -3507,7 +3606,7 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO12">
         <v>11.5</v>
@@ -3537,7 +3636,7 @@
         <v>16</v>
       </c>
       <c r="AX12">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
         <v>15</v>
@@ -3546,7 +3645,7 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BB12">
         <v>9.800000000000001</v>
@@ -3558,7 +3657,7 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>9.6</v>
+        <v>38</v>
       </c>
       <c r="BF12">
         <v>32</v>
@@ -3627,7 +3726,7 @@
         <v>2.32</v>
       </c>
       <c r="CB12" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3635,34 +3734,34 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="F13">
         <v>1.62</v>
       </c>
       <c r="G13">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>13.5</v>
+        <v>870</v>
       </c>
       <c r="J13">
         <v>3.3</v>
       </c>
       <c r="K13">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3695,10 +3794,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W13">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3713,7 +3812,7 @@
         <v>1000</v>
       </c>
       <c r="AB13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
         <v>1000</v>
@@ -3869,7 +3968,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3877,16 +3976,16 @@
         <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="F14">
         <v>1.31</v>
@@ -3925,7 +4024,7 @@
         <v>1.98</v>
       </c>
       <c r="R14">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S14">
         <v>2.96</v>
@@ -4072,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BP14">
         <v>1000</v>
@@ -4111,7 +4210,3153 @@
         <v>1.27</v>
       </c>
       <c r="CB14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F15">
+        <v>1.97</v>
+      </c>
+      <c r="G15">
+        <v>2.44</v>
+      </c>
+      <c r="H15">
+        <v>3.2</v>
+      </c>
+      <c r="I15">
+        <v>5.3</v>
+      </c>
+      <c r="J15">
+        <v>3.25</v>
+      </c>
+      <c r="K15">
+        <v>5.5</v>
+      </c>
+      <c r="L15">
+        <v>1.01</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>2.56</v>
+      </c>
+      <c r="O15">
+        <v>1.38</v>
+      </c>
+      <c r="P15">
+        <v>1.6</v>
+      </c>
+      <c r="Q15">
+        <v>1.9</v>
+      </c>
+      <c r="R15">
+        <v>1.17</v>
+      </c>
+      <c r="S15">
+        <v>2.62</v>
+      </c>
+      <c r="T15">
+        <v>1.12</v>
+      </c>
+      <c r="U15">
+        <v>1.12</v>
+      </c>
+      <c r="V15">
+        <v>1.25</v>
+      </c>
+      <c r="W15">
+        <v>1.73</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16">
+        <v>3.2</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>2.12</v>
+      </c>
+      <c r="I16">
+        <v>2.54</v>
+      </c>
+      <c r="J16">
+        <v>3.1</v>
+      </c>
+      <c r="K16">
+        <v>4.6</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>3.15</v>
+      </c>
+      <c r="O16">
+        <v>1.36</v>
+      </c>
+      <c r="P16">
+        <v>1.7</v>
+      </c>
+      <c r="Q16">
+        <v>2.04</v>
+      </c>
+      <c r="R16">
+        <v>1.2</v>
+      </c>
+      <c r="S16">
+        <v>2.86</v>
+      </c>
+      <c r="T16">
+        <v>1.11</v>
+      </c>
+      <c r="U16">
+        <v>1.11</v>
+      </c>
+      <c r="V16">
+        <v>1.65</v>
+      </c>
+      <c r="W16">
+        <v>1.33</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.04</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.04</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.04</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.04</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.04</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17">
+        <v>1.85</v>
+      </c>
+      <c r="G17">
+        <v>1.9</v>
+      </c>
+      <c r="H17">
+        <v>4.5</v>
+      </c>
+      <c r="I17">
+        <v>4.7</v>
+      </c>
+      <c r="J17">
+        <v>3.85</v>
+      </c>
+      <c r="K17">
+        <v>4.1</v>
+      </c>
+      <c r="L17">
+        <v>1.37</v>
+      </c>
+      <c r="M17">
+        <v>1.02</v>
+      </c>
+      <c r="N17">
+        <v>3.85</v>
+      </c>
+      <c r="O17">
+        <v>1.26</v>
+      </c>
+      <c r="P17">
+        <v>2.04</v>
+      </c>
+      <c r="Q17">
+        <v>1.72</v>
+      </c>
+      <c r="R17">
+        <v>1.41</v>
+      </c>
+      <c r="S17">
+        <v>2.92</v>
+      </c>
+      <c r="T17">
+        <v>1.67</v>
+      </c>
+      <c r="U17">
+        <v>2.08</v>
+      </c>
+      <c r="V17">
+        <v>1.27</v>
+      </c>
+      <c r="W17">
+        <v>2.1</v>
+      </c>
+      <c r="X17">
+        <v>22</v>
+      </c>
+      <c r="Y17">
+        <v>18.5</v>
+      </c>
+      <c r="Z17">
+        <v>42</v>
+      </c>
+      <c r="AA17">
+        <v>120</v>
+      </c>
+      <c r="AB17">
+        <v>10.5</v>
+      </c>
+      <c r="AC17">
+        <v>9</v>
+      </c>
+      <c r="AD17">
+        <v>18.5</v>
+      </c>
+      <c r="AE17">
+        <v>65</v>
+      </c>
+      <c r="AF17">
+        <v>15</v>
+      </c>
+      <c r="AG17">
+        <v>10.5</v>
+      </c>
+      <c r="AH17">
+        <v>22</v>
+      </c>
+      <c r="AI17">
+        <v>70</v>
+      </c>
+      <c r="AJ17">
+        <v>26</v>
+      </c>
+      <c r="AK17">
+        <v>24</v>
+      </c>
+      <c r="AL17">
+        <v>40</v>
+      </c>
+      <c r="AM17">
+        <v>110</v>
+      </c>
+      <c r="AN17">
+        <v>11</v>
+      </c>
+      <c r="AO17">
+        <v>65</v>
+      </c>
+      <c r="AP17">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17">
+        <v>15.5</v>
+      </c>
+      <c r="AR17">
+        <v>6.2</v>
+      </c>
+      <c r="AS17">
+        <v>6.8</v>
+      </c>
+      <c r="AT17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU17">
+        <v>8</v>
+      </c>
+      <c r="AV17">
+        <v>15</v>
+      </c>
+      <c r="AW17">
+        <v>6.6</v>
+      </c>
+      <c r="AX17">
+        <v>10.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>16</v>
+      </c>
+      <c r="BA17">
+        <v>6.6</v>
+      </c>
+      <c r="BB17">
+        <v>5.7</v>
+      </c>
+      <c r="BC17">
+        <v>16.5</v>
+      </c>
+      <c r="BD17">
+        <v>6.2</v>
+      </c>
+      <c r="BE17">
+        <v>6.8</v>
+      </c>
+      <c r="BF17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG17">
+        <v>6.6</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.36</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.33</v>
+      </c>
+      <c r="BN17">
+        <v>6</v>
+      </c>
+      <c r="BO17">
+        <v>3.35</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>2</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.33</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>5.3</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.33</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.33</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.33</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18">
+        <v>2.3</v>
+      </c>
+      <c r="G18">
+        <v>2.38</v>
+      </c>
+      <c r="H18">
+        <v>3.45</v>
+      </c>
+      <c r="I18">
+        <v>3.7</v>
+      </c>
+      <c r="J18">
+        <v>3.35</v>
+      </c>
+      <c r="K18">
+        <v>3.45</v>
+      </c>
+      <c r="L18">
+        <v>1.43</v>
+      </c>
+      <c r="M18">
+        <v>1.09</v>
+      </c>
+      <c r="N18">
+        <v>3.25</v>
+      </c>
+      <c r="O18">
+        <v>1.4</v>
+      </c>
+      <c r="P18">
+        <v>1.76</v>
+      </c>
+      <c r="Q18">
+        <v>2.18</v>
+      </c>
+      <c r="R18">
+        <v>1.28</v>
+      </c>
+      <c r="S18">
+        <v>3.95</v>
+      </c>
+      <c r="T18">
+        <v>1.92</v>
+      </c>
+      <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
+        <v>1.37</v>
+      </c>
+      <c r="W18">
+        <v>1.72</v>
+      </c>
+      <c r="X18">
+        <v>12</v>
+      </c>
+      <c r="Y18">
+        <v>12</v>
+      </c>
+      <c r="Z18">
+        <v>25</v>
+      </c>
+      <c r="AA18">
+        <v>85</v>
+      </c>
+      <c r="AB18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC18">
+        <v>7.6</v>
+      </c>
+      <c r="AD18">
+        <v>15.5</v>
+      </c>
+      <c r="AE18">
+        <v>48</v>
+      </c>
+      <c r="AF18">
+        <v>13.5</v>
+      </c>
+      <c r="AG18">
+        <v>12</v>
+      </c>
+      <c r="AH18">
+        <v>21</v>
+      </c>
+      <c r="AI18">
+        <v>70</v>
+      </c>
+      <c r="AJ18">
+        <v>32</v>
+      </c>
+      <c r="AK18">
+        <v>28</v>
+      </c>
+      <c r="AL18">
+        <v>60</v>
+      </c>
+      <c r="AM18">
+        <v>150</v>
+      </c>
+      <c r="AN18">
+        <v>23</v>
+      </c>
+      <c r="AO18">
+        <v>55</v>
+      </c>
+      <c r="AP18">
+        <v>10</v>
+      </c>
+      <c r="AQ18">
+        <v>10.5</v>
+      </c>
+      <c r="AR18">
+        <v>21</v>
+      </c>
+      <c r="AS18">
+        <v>10</v>
+      </c>
+      <c r="AT18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU18">
+        <v>7</v>
+      </c>
+      <c r="AV18">
+        <v>13.5</v>
+      </c>
+      <c r="AW18">
+        <v>38</v>
+      </c>
+      <c r="AX18">
+        <v>12</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>17.5</v>
+      </c>
+      <c r="BA18">
+        <v>10</v>
+      </c>
+      <c r="BB18">
+        <v>25</v>
+      </c>
+      <c r="BC18">
+        <v>19</v>
+      </c>
+      <c r="BD18">
+        <v>38</v>
+      </c>
+      <c r="BE18">
+        <v>10.5</v>
+      </c>
+      <c r="BF18">
+        <v>19</v>
+      </c>
+      <c r="BG18">
+        <v>9.6</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>2.62</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>2.36</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>2.66</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.87</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>2.66</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>2.66</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>2.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>2.66</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>2.66</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>2.66</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19">
+        <v>2.4</v>
+      </c>
+      <c r="G19">
+        <v>2.54</v>
+      </c>
+      <c r="H19">
+        <v>3.05</v>
+      </c>
+      <c r="I19">
+        <v>3.4</v>
+      </c>
+      <c r="J19">
+        <v>3.5</v>
+      </c>
+      <c r="K19">
+        <v>3.65</v>
+      </c>
+      <c r="L19">
+        <v>1.37</v>
+      </c>
+      <c r="M19">
+        <v>1.07</v>
+      </c>
+      <c r="N19">
+        <v>3.75</v>
+      </c>
+      <c r="O19">
+        <v>1.3</v>
+      </c>
+      <c r="P19">
+        <v>1.87</v>
+      </c>
+      <c r="Q19">
+        <v>1.84</v>
+      </c>
+      <c r="R19">
+        <v>1.35</v>
+      </c>
+      <c r="S19">
+        <v>3.05</v>
+      </c>
+      <c r="T19">
+        <v>1.67</v>
+      </c>
+      <c r="U19">
+        <v>2.08</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.65</v>
+      </c>
+      <c r="X19">
+        <v>15</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>24</v>
+      </c>
+      <c r="AA19">
+        <v>60</v>
+      </c>
+      <c r="AB19">
+        <v>11</v>
+      </c>
+      <c r="AC19">
+        <v>8</v>
+      </c>
+      <c r="AD19">
+        <v>14</v>
+      </c>
+      <c r="AE19">
+        <v>40</v>
+      </c>
+      <c r="AF19">
+        <v>16</v>
+      </c>
+      <c r="AG19">
+        <v>12</v>
+      </c>
+      <c r="AH19">
+        <v>18</v>
+      </c>
+      <c r="AI19">
+        <v>46</v>
+      </c>
+      <c r="AJ19">
+        <v>36</v>
+      </c>
+      <c r="AK19">
+        <v>27</v>
+      </c>
+      <c r="AL19">
+        <v>40</v>
+      </c>
+      <c r="AM19">
+        <v>110</v>
+      </c>
+      <c r="AN19">
+        <v>20</v>
+      </c>
+      <c r="AO19">
+        <v>34</v>
+      </c>
+      <c r="AP19">
+        <v>12.5</v>
+      </c>
+      <c r="AQ19">
+        <v>11.5</v>
+      </c>
+      <c r="AR19">
+        <v>19</v>
+      </c>
+      <c r="AS19">
+        <v>10</v>
+      </c>
+      <c r="AT19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU19">
+        <v>7.4</v>
+      </c>
+      <c r="AV19">
+        <v>12.5</v>
+      </c>
+      <c r="AW19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX19">
+        <v>13.5</v>
+      </c>
+      <c r="AY19">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19">
+        <v>15</v>
+      </c>
+      <c r="BA19">
+        <v>9.6</v>
+      </c>
+      <c r="BB19">
+        <v>9</v>
+      </c>
+      <c r="BC19">
+        <v>23</v>
+      </c>
+      <c r="BD19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE19">
+        <v>11</v>
+      </c>
+      <c r="BF19">
+        <v>17</v>
+      </c>
+      <c r="BG19">
+        <v>9</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.51</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>2.18</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>2.5</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.82</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>2.5</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>2.5</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.92</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>2.5</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>2.5</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>2.5</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20">
+        <v>2.12</v>
+      </c>
+      <c r="G20">
+        <v>2.3</v>
+      </c>
+      <c r="H20">
+        <v>3.75</v>
+      </c>
+      <c r="I20">
+        <v>4.4</v>
+      </c>
+      <c r="J20">
+        <v>3.25</v>
+      </c>
+      <c r="K20">
+        <v>3.8</v>
+      </c>
+      <c r="L20">
+        <v>1.47</v>
+      </c>
+      <c r="M20">
+        <v>1.06</v>
+      </c>
+      <c r="N20">
+        <v>2.96</v>
+      </c>
+      <c r="O20">
+        <v>1.42</v>
+      </c>
+      <c r="P20">
+        <v>1.63</v>
+      </c>
+      <c r="Q20">
+        <v>2.26</v>
+      </c>
+      <c r="R20">
+        <v>1.23</v>
+      </c>
+      <c r="S20">
+        <v>4.1</v>
+      </c>
+      <c r="T20">
+        <v>1.89</v>
+      </c>
+      <c r="U20">
+        <v>1.9</v>
+      </c>
+      <c r="V20">
+        <v>1.3</v>
+      </c>
+      <c r="W20">
+        <v>1.76</v>
+      </c>
+      <c r="X20">
+        <v>970</v>
+      </c>
+      <c r="Y20">
+        <v>970</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>970</v>
+      </c>
+      <c r="AC20">
+        <v>970</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.31</v>
+      </c>
+      <c r="AQ20">
+        <v>1.32</v>
+      </c>
+      <c r="AR20">
+        <v>1.41</v>
+      </c>
+      <c r="AS20">
+        <v>1.41</v>
+      </c>
+      <c r="AT20">
+        <v>1.27</v>
+      </c>
+      <c r="AU20">
+        <v>5.6</v>
+      </c>
+      <c r="AV20">
+        <v>1.41</v>
+      </c>
+      <c r="AW20">
+        <v>1.41</v>
+      </c>
+      <c r="AX20">
+        <v>1.41</v>
+      </c>
+      <c r="AY20">
+        <v>1.41</v>
+      </c>
+      <c r="AZ20">
+        <v>1.41</v>
+      </c>
+      <c r="BA20">
+        <v>1.41</v>
+      </c>
+      <c r="BB20">
+        <v>1.41</v>
+      </c>
+      <c r="BC20">
+        <v>1.41</v>
+      </c>
+      <c r="BD20">
+        <v>1.41</v>
+      </c>
+      <c r="BE20">
+        <v>1.41</v>
+      </c>
+      <c r="BF20">
+        <v>1.41</v>
+      </c>
+      <c r="BG20">
+        <v>1.41</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.04</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.49</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
         <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F21">
+        <v>1.95</v>
+      </c>
+      <c r="G21">
+        <v>2.16</v>
+      </c>
+      <c r="H21">
+        <v>3.9</v>
+      </c>
+      <c r="I21">
+        <v>4.7</v>
+      </c>
+      <c r="J21">
+        <v>3.1</v>
+      </c>
+      <c r="K21">
+        <v>4.1</v>
+      </c>
+      <c r="L21">
+        <v>1.46</v>
+      </c>
+      <c r="M21">
+        <v>1.09</v>
+      </c>
+      <c r="N21">
+        <v>3.3</v>
+      </c>
+      <c r="O21">
+        <v>1.4</v>
+      </c>
+      <c r="P21">
+        <v>1.68</v>
+      </c>
+      <c r="Q21">
+        <v>2.1</v>
+      </c>
+      <c r="R21">
+        <v>1.25</v>
+      </c>
+      <c r="S21">
+        <v>3.9</v>
+      </c>
+      <c r="T21">
+        <v>1.87</v>
+      </c>
+      <c r="U21">
+        <v>1.84</v>
+      </c>
+      <c r="V21">
+        <v>1.28</v>
+      </c>
+      <c r="W21">
+        <v>1.86</v>
+      </c>
+      <c r="X21">
+        <v>12</v>
+      </c>
+      <c r="Y21">
+        <v>15.5</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>970</v>
+      </c>
+      <c r="AC21">
+        <v>8.6</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>13</v>
+      </c>
+      <c r="AG21">
+        <v>11.5</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ21">
+        <v>10.5</v>
+      </c>
+      <c r="AR21">
+        <v>2.06</v>
+      </c>
+      <c r="AS21">
+        <v>2.06</v>
+      </c>
+      <c r="AT21">
+        <v>6.6</v>
+      </c>
+      <c r="AU21">
+        <v>6.4</v>
+      </c>
+      <c r="AV21">
+        <v>2.06</v>
+      </c>
+      <c r="AW21">
+        <v>2.06</v>
+      </c>
+      <c r="AX21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21">
+        <v>1.75</v>
+      </c>
+      <c r="AZ21">
+        <v>2.06</v>
+      </c>
+      <c r="BA21">
+        <v>2.06</v>
+      </c>
+      <c r="BB21">
+        <v>2.06</v>
+      </c>
+      <c r="BC21">
+        <v>2.06</v>
+      </c>
+      <c r="BD21">
+        <v>2.06</v>
+      </c>
+      <c r="BE21">
+        <v>2.06</v>
+      </c>
+      <c r="BF21">
+        <v>2.06</v>
+      </c>
+      <c r="BG21">
+        <v>2.06</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.23</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.04</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.04</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.45</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.04</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.04</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.96</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.04</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.04</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.04</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22">
+        <v>1.67</v>
+      </c>
+      <c r="G22">
+        <v>1.78</v>
+      </c>
+      <c r="H22">
+        <v>5.3</v>
+      </c>
+      <c r="I22">
+        <v>6.6</v>
+      </c>
+      <c r="J22">
+        <v>3.95</v>
+      </c>
+      <c r="K22">
+        <v>4.3</v>
+      </c>
+      <c r="L22">
+        <v>1.4</v>
+      </c>
+      <c r="M22">
+        <v>1.06</v>
+      </c>
+      <c r="N22">
+        <v>3.55</v>
+      </c>
+      <c r="O22">
+        <v>1.31</v>
+      </c>
+      <c r="P22">
+        <v>1.9</v>
+      </c>
+      <c r="Q22">
+        <v>1.87</v>
+      </c>
+      <c r="R22">
+        <v>1.34</v>
+      </c>
+      <c r="S22">
+        <v>3.1</v>
+      </c>
+      <c r="T22">
+        <v>1.8</v>
+      </c>
+      <c r="U22">
+        <v>1.92</v>
+      </c>
+      <c r="V22">
+        <v>1.17</v>
+      </c>
+      <c r="W22">
+        <v>2.28</v>
+      </c>
+      <c r="X22">
+        <v>950</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>970</v>
+      </c>
+      <c r="AC22">
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>970</v>
+      </c>
+      <c r="AG22">
+        <v>970</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>970</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>10</v>
+      </c>
+      <c r="AQ22">
+        <v>11</v>
+      </c>
+      <c r="AR22">
+        <v>1.57</v>
+      </c>
+      <c r="AS22">
+        <v>1.57</v>
+      </c>
+      <c r="AT22">
+        <v>6.4</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>1.57</v>
+      </c>
+      <c r="AW22">
+        <v>1.57</v>
+      </c>
+      <c r="AX22">
+        <v>9.4</v>
+      </c>
+      <c r="AY22">
+        <v>9</v>
+      </c>
+      <c r="AZ22">
+        <v>1.57</v>
+      </c>
+      <c r="BA22">
+        <v>1.57</v>
+      </c>
+      <c r="BB22">
+        <v>11</v>
+      </c>
+      <c r="BC22">
+        <v>11</v>
+      </c>
+      <c r="BD22">
+        <v>1.57</v>
+      </c>
+      <c r="BE22">
+        <v>1.57</v>
+      </c>
+      <c r="BF22">
+        <v>7.4</v>
+      </c>
+      <c r="BG22">
+        <v>1.57</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.26</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.87</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.87</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.36</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.87</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.87</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.87</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.87</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.87</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.87</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23">
+        <v>1.2</v>
+      </c>
+      <c r="G23">
+        <v>1.4</v>
+      </c>
+      <c r="H23">
+        <v>6.6</v>
+      </c>
+      <c r="I23">
+        <v>990</v>
+      </c>
+      <c r="J23">
+        <v>6</v>
+      </c>
+      <c r="K23">
+        <v>950</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>1.1</v>
+      </c>
+      <c r="O23">
+        <v>1.12</v>
+      </c>
+      <c r="P23">
+        <v>2.72</v>
+      </c>
+      <c r="Q23">
+        <v>1.13</v>
+      </c>
+      <c r="R23">
+        <v>1.76</v>
+      </c>
+      <c r="S23">
+        <v>1.94</v>
+      </c>
+      <c r="T23">
+        <v>1.11</v>
+      </c>
+      <c r="U23">
+        <v>1.11</v>
+      </c>
+      <c r="V23">
+        <v>1.01</v>
+      </c>
+      <c r="W23">
+        <v>3.5</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23">
+        <v>1.01</v>
+      </c>
+      <c r="AR23">
+        <v>1.01</v>
+      </c>
+      <c r="AS23">
+        <v>1.01</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>1.01</v>
+      </c>
+      <c r="AV23">
+        <v>1.01</v>
+      </c>
+      <c r="AW23">
+        <v>1.01</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23">
+        <v>1.01</v>
+      </c>
+      <c r="BA23">
+        <v>1.01</v>
+      </c>
+      <c r="BB23">
+        <v>1.01</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.04</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.04</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24">
+        <v>2.8</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>2.52</v>
+      </c>
+      <c r="I24">
+        <v>2.68</v>
+      </c>
+      <c r="J24">
+        <v>3.55</v>
+      </c>
+      <c r="K24">
+        <v>3.75</v>
+      </c>
+      <c r="L24">
+        <v>1.33</v>
+      </c>
+      <c r="M24">
+        <v>1.06</v>
+      </c>
+      <c r="N24">
+        <v>4.3</v>
+      </c>
+      <c r="O24">
+        <v>1.27</v>
+      </c>
+      <c r="P24">
+        <v>2.12</v>
+      </c>
+      <c r="Q24">
+        <v>1.79</v>
+      </c>
+      <c r="R24">
+        <v>1.44</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24">
+        <v>1.67</v>
+      </c>
+      <c r="U24">
+        <v>2.32</v>
+      </c>
+      <c r="V24">
+        <v>1.59</v>
+      </c>
+      <c r="W24">
+        <v>1.5</v>
+      </c>
+      <c r="X24">
+        <v>21</v>
+      </c>
+      <c r="Y24">
+        <v>13</v>
+      </c>
+      <c r="Z24">
+        <v>18.5</v>
+      </c>
+      <c r="AA24">
+        <v>46</v>
+      </c>
+      <c r="AB24">
+        <v>14</v>
+      </c>
+      <c r="AC24">
+        <v>8.4</v>
+      </c>
+      <c r="AD24">
+        <v>12.5</v>
+      </c>
+      <c r="AE24">
+        <v>29</v>
+      </c>
+      <c r="AF24">
+        <v>22</v>
+      </c>
+      <c r="AG24">
+        <v>13.5</v>
+      </c>
+      <c r="AH24">
+        <v>16.5</v>
+      </c>
+      <c r="AI24">
+        <v>50</v>
+      </c>
+      <c r="AJ24">
+        <v>55</v>
+      </c>
+      <c r="AK24">
+        <v>34</v>
+      </c>
+      <c r="AL24">
+        <v>46</v>
+      </c>
+      <c r="AM24">
+        <v>100</v>
+      </c>
+      <c r="AN24">
+        <v>24</v>
+      </c>
+      <c r="AO24">
+        <v>19.5</v>
+      </c>
+      <c r="AP24">
+        <v>15</v>
+      </c>
+      <c r="AQ24">
+        <v>11</v>
+      </c>
+      <c r="AR24">
+        <v>15.5</v>
+      </c>
+      <c r="AS24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT24">
+        <v>11.5</v>
+      </c>
+      <c r="AU24">
+        <v>7.6</v>
+      </c>
+      <c r="AV24">
+        <v>10.5</v>
+      </c>
+      <c r="AW24">
+        <v>7.4</v>
+      </c>
+      <c r="AX24">
+        <v>18</v>
+      </c>
+      <c r="AY24">
+        <v>11.5</v>
+      </c>
+      <c r="AZ24">
+        <v>14</v>
+      </c>
+      <c r="BA24">
+        <v>7.8</v>
+      </c>
+      <c r="BB24">
+        <v>30</v>
+      </c>
+      <c r="BC24">
+        <v>7.6</v>
+      </c>
+      <c r="BD24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF24">
+        <v>16.5</v>
+      </c>
+      <c r="BG24">
+        <v>16</v>
+      </c>
+      <c r="BH24">
+        <v>4.5</v>
+      </c>
+      <c r="BI24">
+        <v>2.96</v>
+      </c>
+      <c r="BJ24">
+        <v>1000</v>
+      </c>
+      <c r="BK24">
+        <v>5.7</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>2.38</v>
+      </c>
+      <c r="BN24">
+        <v>1000</v>
+      </c>
+      <c r="BO24">
+        <v>4.1</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>2.38</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
+        <v>2.38</v>
+      </c>
+      <c r="BT24">
+        <v>8</v>
+      </c>
+      <c r="BU24">
+        <v>4</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>2.38</v>
+      </c>
+      <c r="BZ24">
+        <v>1000</v>
+      </c>
+      <c r="CA24">
+        <v>2.38</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25">
+        <v>2.2</v>
+      </c>
+      <c r="G25">
+        <v>2.34</v>
+      </c>
+      <c r="H25">
+        <v>3.95</v>
+      </c>
+      <c r="I25">
+        <v>4.4</v>
+      </c>
+      <c r="J25">
+        <v>3.05</v>
+      </c>
+      <c r="K25">
+        <v>3.25</v>
+      </c>
+      <c r="L25">
+        <v>1.52</v>
+      </c>
+      <c r="M25">
+        <v>1.12</v>
+      </c>
+      <c r="N25">
+        <v>2.74</v>
+      </c>
+      <c r="O25">
+        <v>1.52</v>
+      </c>
+      <c r="P25">
+        <v>1.57</v>
+      </c>
+      <c r="Q25">
+        <v>2.58</v>
+      </c>
+      <c r="R25">
+        <v>1.21</v>
+      </c>
+      <c r="S25">
+        <v>5.3</v>
+      </c>
+      <c r="T25">
+        <v>2.1</v>
+      </c>
+      <c r="U25">
+        <v>1.8</v>
+      </c>
+      <c r="V25">
+        <v>1.29</v>
+      </c>
+      <c r="W25">
+        <v>1.74</v>
+      </c>
+      <c r="X25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y25">
+        <v>11.5</v>
+      </c>
+      <c r="Z25">
+        <v>36</v>
+      </c>
+      <c r="AA25">
+        <v>120</v>
+      </c>
+      <c r="AB25">
+        <v>7.4</v>
+      </c>
+      <c r="AC25">
+        <v>7.4</v>
+      </c>
+      <c r="AD25">
+        <v>19</v>
+      </c>
+      <c r="AE25">
+        <v>85</v>
+      </c>
+      <c r="AF25">
+        <v>15.5</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <v>28</v>
+      </c>
+      <c r="AI25">
+        <v>110</v>
+      </c>
+      <c r="AJ25">
+        <v>38</v>
+      </c>
+      <c r="AK25">
+        <v>38</v>
+      </c>
+      <c r="AL25">
+        <v>70</v>
+      </c>
+      <c r="AM25">
+        <v>220</v>
+      </c>
+      <c r="AN25">
+        <v>38</v>
+      </c>
+      <c r="AO25">
+        <v>120</v>
+      </c>
+      <c r="AP25">
+        <v>8</v>
+      </c>
+      <c r="AQ25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR25">
+        <v>6.6</v>
+      </c>
+      <c r="AS25">
+        <v>7.4</v>
+      </c>
+      <c r="AT25">
+        <v>6.4</v>
+      </c>
+      <c r="AU25">
+        <v>6.4</v>
+      </c>
+      <c r="AV25">
+        <v>15.5</v>
+      </c>
+      <c r="AW25">
+        <v>7.2</v>
+      </c>
+      <c r="AX25">
+        <v>11</v>
+      </c>
+      <c r="AY25">
+        <v>10</v>
+      </c>
+      <c r="AZ25">
+        <v>6.2</v>
+      </c>
+      <c r="BA25">
+        <v>7.4</v>
+      </c>
+      <c r="BB25">
+        <v>6.6</v>
+      </c>
+      <c r="BC25">
+        <v>6.6</v>
+      </c>
+      <c r="BD25">
+        <v>7.2</v>
+      </c>
+      <c r="BE25">
+        <v>7.2</v>
+      </c>
+      <c r="BF25">
+        <v>21</v>
+      </c>
+      <c r="BG25">
+        <v>7</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.04</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.54</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <v>2.26</v>
+      </c>
+      <c r="H26">
+        <v>3.45</v>
+      </c>
+      <c r="I26">
+        <v>4.4</v>
+      </c>
+      <c r="J26">
+        <v>3.15</v>
+      </c>
+      <c r="K26">
+        <v>4.2</v>
+      </c>
+      <c r="L26">
+        <v>1.41</v>
+      </c>
+      <c r="M26">
+        <v>1.04</v>
+      </c>
+      <c r="N26">
+        <v>3.35</v>
+      </c>
+      <c r="O26">
+        <v>1.33</v>
+      </c>
+      <c r="P26">
+        <v>1.78</v>
+      </c>
+      <c r="Q26">
+        <v>1.92</v>
+      </c>
+      <c r="R26">
+        <v>1.29</v>
+      </c>
+      <c r="S26">
+        <v>3.3</v>
+      </c>
+      <c r="T26">
+        <v>1.73</v>
+      </c>
+      <c r="U26">
+        <v>1.99</v>
+      </c>
+      <c r="V26">
+        <v>1.29</v>
+      </c>
+      <c r="W26">
+        <v>1.8</v>
+      </c>
+      <c r="X26">
+        <v>950</v>
+      </c>
+      <c r="Y26">
+        <v>950</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>970</v>
+      </c>
+      <c r="AC26">
+        <v>970</v>
+      </c>
+      <c r="AD26">
+        <v>950</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>32</v>
+      </c>
+      <c r="AG26">
+        <v>950</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>9</v>
+      </c>
+      <c r="AQ26">
+        <v>1.37</v>
+      </c>
+      <c r="AR26">
+        <v>1.43</v>
+      </c>
+      <c r="AS26">
+        <v>1.43</v>
+      </c>
+      <c r="AT26">
+        <v>6.8</v>
+      </c>
+      <c r="AU26">
+        <v>5.9</v>
+      </c>
+      <c r="AV26">
+        <v>1.41</v>
+      </c>
+      <c r="AW26">
+        <v>1.43</v>
+      </c>
+      <c r="AX26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY26">
+        <v>7.6</v>
+      </c>
+      <c r="AZ26">
+        <v>1.43</v>
+      </c>
+      <c r="BA26">
+        <v>1.43</v>
+      </c>
+      <c r="BB26">
+        <v>1.43</v>
+      </c>
+      <c r="BC26">
+        <v>1.43</v>
+      </c>
+      <c r="BD26">
+        <v>1.43</v>
+      </c>
+      <c r="BE26">
+        <v>1.43</v>
+      </c>
+      <c r="BF26">
+        <v>9</v>
+      </c>
+      <c r="BG26">
+        <v>1.43</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>2</v>
+      </c>
+      <c r="BJ26">
+        <v>13.5</v>
+      </c>
+      <c r="BK26">
+        <v>6.4</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>2</v>
+      </c>
+      <c r="BN26">
+        <v>5.4</v>
+      </c>
+      <c r="BO26">
+        <v>4</v>
+      </c>
+      <c r="BP26">
+        <v>22</v>
+      </c>
+      <c r="BQ26">
+        <v>1.84</v>
+      </c>
+      <c r="BR26">
+        <v>42</v>
+      </c>
+      <c r="BS26">
+        <v>1.91</v>
+      </c>
+      <c r="BT26">
+        <v>9.4</v>
+      </c>
+      <c r="BU26">
+        <v>5.7</v>
+      </c>
+      <c r="BV26">
+        <v>44</v>
+      </c>
+      <c r="BW26">
+        <v>1.92</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.94</v>
+      </c>
+      <c r="BZ26">
+        <v>38</v>
+      </c>
+      <c r="CA26">
+        <v>1.9</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27">
+        <v>4.3</v>
+      </c>
+      <c r="G27">
+        <v>4.7</v>
+      </c>
+      <c r="H27">
+        <v>1.96</v>
+      </c>
+      <c r="I27">
+        <v>2.06</v>
+      </c>
+      <c r="J27">
+        <v>3.55</v>
+      </c>
+      <c r="K27">
+        <v>3.75</v>
+      </c>
+      <c r="L27">
+        <v>1.4</v>
+      </c>
+      <c r="M27">
+        <v>1.08</v>
+      </c>
+      <c r="N27">
+        <v>3.4</v>
+      </c>
+      <c r="O27">
+        <v>1.38</v>
+      </c>
+      <c r="P27">
+        <v>1.8</v>
+      </c>
+      <c r="Q27">
+        <v>2.06</v>
+      </c>
+      <c r="R27">
+        <v>1.32</v>
+      </c>
+      <c r="S27">
+        <v>3.85</v>
+      </c>
+      <c r="T27">
+        <v>1.89</v>
+      </c>
+      <c r="U27">
+        <v>1.99</v>
+      </c>
+      <c r="V27">
+        <v>1.94</v>
+      </c>
+      <c r="W27">
+        <v>1.27</v>
+      </c>
+      <c r="X27">
+        <v>14.5</v>
+      </c>
+      <c r="Y27">
+        <v>9.6</v>
+      </c>
+      <c r="Z27">
+        <v>14</v>
+      </c>
+      <c r="AA27">
+        <v>28</v>
+      </c>
+      <c r="AB27">
+        <v>16.5</v>
+      </c>
+      <c r="AC27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>12.5</v>
+      </c>
+      <c r="AE27">
+        <v>27</v>
+      </c>
+      <c r="AF27">
+        <v>38</v>
+      </c>
+      <c r="AG27">
+        <v>21</v>
+      </c>
+      <c r="AH27">
+        <v>23</v>
+      </c>
+      <c r="AI27">
+        <v>48</v>
+      </c>
+      <c r="AJ27">
+        <v>120</v>
+      </c>
+      <c r="AK27">
+        <v>75</v>
+      </c>
+      <c r="AL27">
+        <v>80</v>
+      </c>
+      <c r="AM27">
+        <v>140</v>
+      </c>
+      <c r="AN27">
+        <v>90</v>
+      </c>
+      <c r="AO27">
+        <v>17.5</v>
+      </c>
+      <c r="AP27">
+        <v>11</v>
+      </c>
+      <c r="AQ27">
+        <v>7.4</v>
+      </c>
+      <c r="AR27">
+        <v>10.5</v>
+      </c>
+      <c r="AS27">
+        <v>20</v>
+      </c>
+      <c r="AT27">
+        <v>12.5</v>
+      </c>
+      <c r="AU27">
+        <v>7.2</v>
+      </c>
+      <c r="AV27">
+        <v>9.4</v>
+      </c>
+      <c r="AW27">
+        <v>20</v>
+      </c>
+      <c r="AX27">
+        <v>5.5</v>
+      </c>
+      <c r="AY27">
+        <v>15.5</v>
+      </c>
+      <c r="AZ27">
+        <v>17.5</v>
+      </c>
+      <c r="BA27">
+        <v>5.6</v>
+      </c>
+      <c r="BB27">
+        <v>5.6</v>
+      </c>
+      <c r="BC27">
+        <v>5.9</v>
+      </c>
+      <c r="BD27">
+        <v>5.9</v>
+      </c>
+      <c r="BE27">
+        <v>5.7</v>
+      </c>
+      <c r="BF27">
+        <v>6</v>
+      </c>
+      <c r="BG27">
+        <v>14.5</v>
+      </c>
+      <c r="BH27">
+        <v>1000</v>
+      </c>
+      <c r="BI27">
+        <v>1.04</v>
+      </c>
+      <c r="BJ27">
+        <v>1000</v>
+      </c>
+      <c r="BK27">
+        <v>1.04</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>1.04</v>
+      </c>
+      <c r="BN27">
+        <v>1000</v>
+      </c>
+      <c r="BO27">
+        <v>1.04</v>
+      </c>
+      <c r="BP27">
+        <v>1000</v>
+      </c>
+      <c r="BQ27">
+        <v>1.04</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>1.04</v>
+      </c>
+      <c r="BT27">
+        <v>1000</v>
+      </c>
+      <c r="BU27">
+        <v>1.04</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>1.04</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>1.04</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>1.04</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -490,7 +490,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 01:52:54</t>
+    <t>2026-10-06 04:04:29</t>
   </si>
 </sst>
 </file>
@@ -1084,16 +1084,16 @@
         <v>132</v>
       </c>
       <c r="F2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="H2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1108,64 +1108,64 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
         <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="S2">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="U2">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V2">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB2">
         <v>21</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <v>14</v>
@@ -1177,76 +1177,76 @@
         <v>55</v>
       </c>
       <c r="AK2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL2">
         <v>32</v>
       </c>
       <c r="AM2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO2">
         <v>10.5</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AT2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV2">
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY2">
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
         <v>9.199999999999999</v>
       </c>
       <c r="BH2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI2">
         <v>4.3</v>
@@ -1261,7 +1261,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1279,10 +1279,10 @@
         <v>26</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU2">
         <v>5.3</v>
@@ -1297,7 +1297,7 @@
         <v>22</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>14</v>
@@ -1326,16 +1326,16 @@
         <v>133</v>
       </c>
       <c r="F3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
         <v>1.35</v>
       </c>
       <c r="I3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="J3">
         <v>5.3</v>
@@ -1353,49 +1353,49 @@
         <v>4</v>
       </c>
       <c r="O3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V3">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="W3">
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AA3">
         <v>10.5</v>
       </c>
       <c r="AB3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1404,70 +1404,70 @@
         <v>17.5</v>
       </c>
       <c r="AF3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AG3">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AH3">
         <v>38</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>1000</v>
       </c>
       <c r="AK3">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AL3">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AM3">
         <v>290</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AO3">
+        <v>6.8</v>
+      </c>
+      <c r="AP3">
+        <v>14.5</v>
+      </c>
+      <c r="AQ3">
         <v>6.6</v>
       </c>
-      <c r="AP3">
-        <v>14</v>
-      </c>
-      <c r="AQ3">
-        <v>6.4</v>
-      </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AY3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB3">
         <v>12</v>
@@ -1476,76 +1476,76 @@
         <v>11.5</v>
       </c>
       <c r="BD3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE3">
         <v>11.5</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI3">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.08</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.08</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BO3">
-        <v>2.44</v>
+        <v>7.6</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.08</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.08</v>
+        <v>13</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BU3">
-        <v>1.51</v>
+        <v>3.25</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW3">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BY3">
-        <v>1.08</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA3">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>158</v>
@@ -1574,13 +1574,13 @@
         <v>2.38</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
         <v>3.8</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
         <v>3.5</v>
@@ -1595,28 +1595,28 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="U4">
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
         <v>1.73</v>
@@ -1625,7 +1625,7 @@
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
         <v>27</v>
@@ -1649,7 +1649,7 @@
         <v>14.5</v>
       </c>
       <c r="AG4">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>21</v>
@@ -1658,10 +1658,10 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL4">
         <v>60</v>
@@ -1685,7 +1685,7 @@
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1697,46 +1697,46 @@
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BD4">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF4">
         <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
         <v>1.04</v>
@@ -1748,43 +1748,43 @@
         <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
         <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS4">
         <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
         <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY4">
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA4">
         <v>1.04</v>
@@ -1822,10 +1822,10 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1858,10 +1858,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2061,7 +2061,7 @@
         <v>2.68</v>
       </c>
       <c r="I6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2076,19 +2076,19 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P6">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S6">
         <v>2.52</v>
@@ -2297,7 +2297,7 @@
         <v>5.7</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>14.5</v>
       </c>
       <c r="H7">
         <v>1.38</v>
@@ -2309,7 +2309,7 @@
         <v>3.7</v>
       </c>
       <c r="K7">
-        <v>10.5</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>1.23</v>
@@ -2318,13 +2318,13 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7">
         <v>1.52</v>
@@ -2336,16 +2336,16 @@
         <v>2.28</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V7">
         <v>2.22</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2536,70 +2536,70 @@
         <v>138</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
         <v>2.24</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L8">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P8">
         <v>1.84</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R8">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
         <v>1.74</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V8">
         <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB8">
         <v>16</v>
@@ -2641,10 +2641,10 @@
         <v>65</v>
       </c>
       <c r="AO8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ8">
         <v>7.2</v>
@@ -2665,97 +2665,97 @@
         <v>8.4</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="AX8">
         <v>4.6</v>
       </c>
       <c r="AY8">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AZ8">
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB8">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE8">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="s">
         <v>158</v>
@@ -2790,10 +2790,10 @@
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2826,10 +2826,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3026,16 +3026,16 @@
         <v>990</v>
       </c>
       <c r="H10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I10">
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3044,7 +3044,7 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O10">
         <v>1.02</v>
@@ -3068,10 +3068,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3265,16 +3265,16 @@
         <v>2.72</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
         <v>2.52</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
         <v>4.7</v>
@@ -3286,88 +3286,88 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.56</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="S11">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.68</v>
       </c>
       <c r="V11">
         <v>1.65</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP11">
         <v>1.01</v>
@@ -3522,10 +3522,10 @@
         <v>4</v>
       </c>
       <c r="L12">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
         <v>4.3</v>
@@ -3537,16 +3537,16 @@
         <v>2.14</v>
       </c>
       <c r="Q12">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
         <v>1.44</v>
       </c>
       <c r="S12">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T12">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U12">
         <v>2.2</v>
@@ -3570,10 +3570,10 @@
         <v>22</v>
       </c>
       <c r="AB12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12">
         <v>11</v>
@@ -3600,7 +3600,7 @@
         <v>70</v>
       </c>
       <c r="AL12">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM12">
         <v>110</v>
@@ -3645,10 +3645,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB12">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3657,73 +3657,73 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF12">
         <v>32</v>
       </c>
       <c r="BG12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BI12">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM12">
-        <v>2.32</v>
+        <v>6.4</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO12">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ12">
-        <v>2.32</v>
+        <v>5.9</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS12">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="BT12">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BU12">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW12">
         <v>7.2</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY12">
-        <v>2.32</v>
+        <v>5.6</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA12">
-        <v>2.32</v>
+        <v>5.7</v>
       </c>
       <c r="CB12" t="s">
         <v>158</v>
@@ -3746,19 +3746,19 @@
         <v>143</v>
       </c>
       <c r="F13">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G13">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I13">
-        <v>870</v>
+        <v>9.4</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
         <v>3.85</v>
@@ -3767,145 +3767,145 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N13">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="P13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q13">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="V13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W13">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3917,13 +3917,13 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -3935,37 +3935,37 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="CB13" t="s">
         <v>158</v>
@@ -3988,226 +3988,226 @@
         <v>144</v>
       </c>
       <c r="F14">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="H14">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>15.5</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="K14">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="L14">
+        <v>1.4</v>
+      </c>
+      <c r="M14">
+        <v>1.07</v>
+      </c>
+      <c r="N14">
+        <v>3.4</v>
+      </c>
+      <c r="O14">
         <v>1.35</v>
       </c>
-      <c r="M14">
-        <v>1.03</v>
-      </c>
-      <c r="N14">
-        <v>2.74</v>
-      </c>
-      <c r="O14">
-        <v>1.38</v>
-      </c>
       <c r="P14">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q14">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R14">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S14">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U14">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W14">
+        <v>3.3</v>
+      </c>
+      <c r="X14">
+        <v>16</v>
+      </c>
+      <c r="Y14">
+        <v>34</v>
+      </c>
+      <c r="Z14">
+        <v>140</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>7.4</v>
+      </c>
+      <c r="AC14">
+        <v>13.5</v>
+      </c>
+      <c r="AD14">
+        <v>55</v>
+      </c>
+      <c r="AE14">
+        <v>330</v>
+      </c>
+      <c r="AF14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>44</v>
+      </c>
+      <c r="AI14">
+        <v>270</v>
+      </c>
+      <c r="AJ14">
+        <v>13</v>
+      </c>
+      <c r="AK14">
+        <v>21</v>
+      </c>
+      <c r="AL14">
+        <v>65</v>
+      </c>
+      <c r="AM14">
+        <v>340</v>
+      </c>
+      <c r="AN14">
+        <v>9.4</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14">
+        <v>4.4</v>
+      </c>
+      <c r="AR14">
+        <v>4.9</v>
+      </c>
+      <c r="AS14">
+        <v>5.1</v>
+      </c>
+      <c r="AT14">
+        <v>5.5</v>
+      </c>
+      <c r="AU14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV14">
+        <v>4.7</v>
+      </c>
+      <c r="AW14">
+        <v>5.1</v>
+      </c>
+      <c r="AX14">
+        <v>6</v>
+      </c>
+      <c r="AY14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14">
+        <v>4.6</v>
+      </c>
+      <c r="BA14">
+        <v>5</v>
+      </c>
+      <c r="BB14">
+        <v>8.6</v>
+      </c>
+      <c r="BC14">
+        <v>13.5</v>
+      </c>
+      <c r="BD14">
+        <v>4.8</v>
+      </c>
+      <c r="BE14">
+        <v>5.1</v>
+      </c>
+      <c r="BF14">
+        <v>6.4</v>
+      </c>
+      <c r="BG14">
+        <v>5.1</v>
+      </c>
+      <c r="BH14">
+        <v>3.75</v>
+      </c>
+      <c r="BI14">
+        <v>2.78</v>
+      </c>
+      <c r="BJ14">
+        <v>16</v>
+      </c>
+      <c r="BK14">
+        <v>4.4</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>6</v>
+      </c>
+      <c r="BN14">
+        <v>3.95</v>
+      </c>
+      <c r="BO14">
         <v>3.1</v>
       </c>
-      <c r="X14">
-        <v>1000</v>
-      </c>
-      <c r="Y14">
-        <v>1000</v>
-      </c>
-      <c r="Z14">
-        <v>1000</v>
-      </c>
-      <c r="AA14">
-        <v>1000</v>
-      </c>
-      <c r="AB14">
-        <v>1000</v>
-      </c>
-      <c r="AC14">
-        <v>1000</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>1000</v>
-      </c>
-      <c r="AG14">
-        <v>1000</v>
-      </c>
-      <c r="AH14">
-        <v>1000</v>
-      </c>
-      <c r="AI14">
-        <v>1000</v>
-      </c>
-      <c r="AJ14">
-        <v>1000</v>
-      </c>
-      <c r="AK14">
-        <v>1000</v>
-      </c>
-      <c r="AL14">
-        <v>1000</v>
-      </c>
-      <c r="AM14">
-        <v>1000</v>
-      </c>
-      <c r="AN14">
-        <v>1000</v>
-      </c>
-      <c r="AO14">
-        <v>1000</v>
-      </c>
-      <c r="AP14">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14">
-        <v>1.01</v>
-      </c>
-      <c r="AR14">
-        <v>1.01</v>
-      </c>
-      <c r="AS14">
-        <v>1.01</v>
-      </c>
-      <c r="AT14">
-        <v>1.01</v>
-      </c>
-      <c r="AU14">
-        <v>1.01</v>
-      </c>
-      <c r="AV14">
-        <v>1.01</v>
-      </c>
-      <c r="AW14">
-        <v>1.01</v>
-      </c>
-      <c r="AX14">
-        <v>1.01</v>
-      </c>
-      <c r="AY14">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14">
-        <v>1.01</v>
-      </c>
-      <c r="BA14">
-        <v>1.01</v>
-      </c>
-      <c r="BB14">
-        <v>1.01</v>
-      </c>
-      <c r="BC14">
-        <v>1.01</v>
-      </c>
-      <c r="BD14">
-        <v>1.01</v>
-      </c>
-      <c r="BE14">
-        <v>1.01</v>
-      </c>
-      <c r="BF14">
-        <v>1.01</v>
-      </c>
-      <c r="BG14">
-        <v>1.01</v>
-      </c>
-      <c r="BH14">
-        <v>1000</v>
-      </c>
-      <c r="BI14">
-        <v>1.27</v>
-      </c>
-      <c r="BJ14">
-        <v>1000</v>
-      </c>
-      <c r="BK14">
-        <v>1.27</v>
-      </c>
-      <c r="BL14">
-        <v>1000</v>
-      </c>
-      <c r="BM14">
-        <v>1.27</v>
-      </c>
-      <c r="BN14">
-        <v>1000</v>
-      </c>
-      <c r="BO14">
-        <v>2.76</v>
-      </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ14">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS14">
-        <v>1.27</v>
+        <v>5.2</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BU14">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.27</v>
+        <v>5.9</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.27</v>
+        <v>5.8</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA14">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="CB14" t="s">
         <v>158</v>
@@ -4230,175 +4230,175 @@
         <v>145</v>
       </c>
       <c r="F15">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G15">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="H15">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I15">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N15">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="O15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P15">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
+        <v>3.55</v>
+      </c>
+      <c r="T15">
+        <v>1.78</v>
+      </c>
+      <c r="U15">
+        <v>1.98</v>
+      </c>
+      <c r="V15">
+        <v>1.28</v>
+      </c>
+      <c r="W15">
+        <v>1.83</v>
+      </c>
+      <c r="X15">
+        <v>14</v>
+      </c>
+      <c r="Y15">
+        <v>14</v>
+      </c>
+      <c r="Z15">
+        <v>36</v>
+      </c>
+      <c r="AA15">
+        <v>110</v>
+      </c>
+      <c r="AB15">
+        <v>8.6</v>
+      </c>
+      <c r="AC15">
+        <v>8</v>
+      </c>
+      <c r="AD15">
+        <v>17.5</v>
+      </c>
+      <c r="AE15">
+        <v>70</v>
+      </c>
+      <c r="AF15">
+        <v>13</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>80</v>
+      </c>
+      <c r="AJ15">
+        <v>27</v>
+      </c>
+      <c r="AK15">
+        <v>25</v>
+      </c>
+      <c r="AL15">
+        <v>50</v>
+      </c>
+      <c r="AM15">
+        <v>140</v>
+      </c>
+      <c r="AN15">
+        <v>22</v>
+      </c>
+      <c r="AO15">
+        <v>80</v>
+      </c>
+      <c r="AP15">
+        <v>4.9</v>
+      </c>
+      <c r="AQ15">
+        <v>4.9</v>
+      </c>
+      <c r="AR15">
+        <v>6.2</v>
+      </c>
+      <c r="AS15">
+        <v>7</v>
+      </c>
+      <c r="AT15">
+        <v>4</v>
+      </c>
+      <c r="AU15">
+        <v>3.85</v>
+      </c>
+      <c r="AV15">
+        <v>5.2</v>
+      </c>
+      <c r="AW15">
+        <v>6.8</v>
+      </c>
+      <c r="AX15">
+        <v>4.7</v>
+      </c>
+      <c r="AY15">
+        <v>4.7</v>
+      </c>
+      <c r="AZ15">
+        <v>5.6</v>
+      </c>
+      <c r="BA15">
+        <v>6.8</v>
+      </c>
+      <c r="BB15">
+        <v>5.8</v>
+      </c>
+      <c r="BC15">
+        <v>5.7</v>
+      </c>
+      <c r="BD15">
+        <v>6.4</v>
+      </c>
+      <c r="BE15">
+        <v>7</v>
+      </c>
+      <c r="BF15">
+        <v>5.6</v>
+      </c>
+      <c r="BG15">
+        <v>6.8</v>
+      </c>
+      <c r="BH15">
+        <v>3.5</v>
+      </c>
+      <c r="BI15">
         <v>2.62</v>
       </c>
-      <c r="T15">
-        <v>1.12</v>
-      </c>
-      <c r="U15">
-        <v>1.12</v>
-      </c>
-      <c r="V15">
-        <v>1.25</v>
-      </c>
-      <c r="W15">
-        <v>1.73</v>
-      </c>
-      <c r="X15">
-        <v>1000</v>
-      </c>
-      <c r="Y15">
-        <v>1000</v>
-      </c>
-      <c r="Z15">
-        <v>1000</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>1000</v>
-      </c>
-      <c r="AC15">
-        <v>1000</v>
-      </c>
-      <c r="AD15">
-        <v>1000</v>
-      </c>
-      <c r="AE15">
-        <v>1000</v>
-      </c>
-      <c r="AF15">
-        <v>1000</v>
-      </c>
-      <c r="AG15">
-        <v>1000</v>
-      </c>
-      <c r="AH15">
-        <v>1000</v>
-      </c>
-      <c r="AI15">
-        <v>1000</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>1000</v>
-      </c>
-      <c r="AL15">
-        <v>1000</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>1000</v>
-      </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15">
-        <v>1.01</v>
-      </c>
-      <c r="AR15">
-        <v>1.01</v>
-      </c>
-      <c r="AS15">
-        <v>1.01</v>
-      </c>
-      <c r="AT15">
-        <v>1.01</v>
-      </c>
-      <c r="AU15">
-        <v>1.01</v>
-      </c>
-      <c r="AV15">
-        <v>1.01</v>
-      </c>
-      <c r="AW15">
-        <v>1.01</v>
-      </c>
-      <c r="AX15">
-        <v>1.01</v>
-      </c>
-      <c r="AY15">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15">
-        <v>1.01</v>
-      </c>
-      <c r="BA15">
-        <v>1.01</v>
-      </c>
-      <c r="BB15">
-        <v>1.01</v>
-      </c>
-      <c r="BC15">
-        <v>1.01</v>
-      </c>
-      <c r="BD15">
-        <v>1.01</v>
-      </c>
-      <c r="BE15">
-        <v>1.01</v>
-      </c>
-      <c r="BF15">
-        <v>1.01</v>
-      </c>
-      <c r="BG15">
-        <v>1.01</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK15">
         <v>1.04</v>
@@ -4410,43 +4410,43 @@
         <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO15">
         <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ15">
         <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS15">
         <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU15">
         <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW15">
         <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY15">
         <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA15">
         <v>1.04</v>
@@ -4472,166 +4472,166 @@
         <v>146</v>
       </c>
       <c r="F16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16">
+        <v>2.2</v>
+      </c>
+      <c r="I16">
+        <v>2.48</v>
+      </c>
+      <c r="J16">
+        <v>3.2</v>
+      </c>
+      <c r="K16">
+        <v>3.7</v>
+      </c>
+      <c r="L16">
+        <v>1.02</v>
+      </c>
+      <c r="M16">
+        <v>1.08</v>
+      </c>
+      <c r="N16">
+        <v>3.2</v>
+      </c>
+      <c r="O16">
+        <v>1.37</v>
+      </c>
+      <c r="P16">
+        <v>1.72</v>
+      </c>
+      <c r="Q16">
         <v>2.12</v>
       </c>
-      <c r="I16">
-        <v>2.54</v>
-      </c>
-      <c r="J16">
-        <v>3.1</v>
-      </c>
-      <c r="K16">
-        <v>4.6</v>
-      </c>
-      <c r="L16">
-        <v>1.01</v>
-      </c>
-      <c r="M16">
-        <v>1.01</v>
-      </c>
-      <c r="N16">
-        <v>3.15</v>
-      </c>
-      <c r="O16">
-        <v>1.36</v>
-      </c>
-      <c r="P16">
-        <v>1.7</v>
-      </c>
-      <c r="Q16">
-        <v>2.04</v>
-      </c>
       <c r="R16">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S16">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V16">
+        <v>1.67</v>
+      </c>
+      <c r="W16">
+        <v>1.34</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>9.4</v>
+      </c>
+      <c r="Z16">
+        <v>15</v>
+      </c>
+      <c r="AA16">
+        <v>34</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>8</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>29</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>16</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>75</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>65</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.83</v>
+      </c>
+      <c r="AQ16">
+        <v>1.54</v>
+      </c>
+      <c r="AR16">
+        <v>1.64</v>
+      </c>
+      <c r="AS16">
+        <v>1.74</v>
+      </c>
+      <c r="AT16">
+        <v>1.83</v>
+      </c>
+      <c r="AU16">
+        <v>1.49</v>
+      </c>
+      <c r="AV16">
+        <v>1.83</v>
+      </c>
+      <c r="AW16">
+        <v>1.73</v>
+      </c>
+      <c r="AX16">
+        <v>1.84</v>
+      </c>
+      <c r="AY16">
         <v>1.65</v>
       </c>
-      <c r="W16">
-        <v>1.33</v>
-      </c>
-      <c r="X16">
-        <v>1000</v>
-      </c>
-      <c r="Y16">
-        <v>1000</v>
-      </c>
-      <c r="Z16">
-        <v>1000</v>
-      </c>
-      <c r="AA16">
-        <v>1000</v>
-      </c>
-      <c r="AB16">
-        <v>1000</v>
-      </c>
-      <c r="AC16">
-        <v>1000</v>
-      </c>
-      <c r="AD16">
-        <v>1000</v>
-      </c>
-      <c r="AE16">
-        <v>1000</v>
-      </c>
-      <c r="AF16">
-        <v>1000</v>
-      </c>
-      <c r="AG16">
-        <v>1000</v>
-      </c>
-      <c r="AH16">
-        <v>1000</v>
-      </c>
-      <c r="AI16">
-        <v>1000</v>
-      </c>
-      <c r="AJ16">
-        <v>1000</v>
-      </c>
-      <c r="AK16">
-        <v>1000</v>
-      </c>
-      <c r="AL16">
-        <v>1000</v>
-      </c>
-      <c r="AM16">
-        <v>1000</v>
-      </c>
-      <c r="AN16">
-        <v>1000</v>
-      </c>
-      <c r="AO16">
-        <v>1000</v>
-      </c>
-      <c r="AP16">
-        <v>1.01</v>
-      </c>
-      <c r="AQ16">
-        <v>1.01</v>
-      </c>
-      <c r="AR16">
-        <v>1.01</v>
-      </c>
-      <c r="AS16">
-        <v>1.01</v>
-      </c>
-      <c r="AT16">
-        <v>1.01</v>
-      </c>
-      <c r="AU16">
-        <v>1.01</v>
-      </c>
-      <c r="AV16">
-        <v>1.01</v>
-      </c>
-      <c r="AW16">
-        <v>1.01</v>
-      </c>
-      <c r="AX16">
-        <v>1.01</v>
-      </c>
-      <c r="AY16">
-        <v>1.01</v>
-      </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4714,13 +4714,13 @@
         <v>147</v>
       </c>
       <c r="F17">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G17">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I17">
         <v>4.7</v>
@@ -4735,37 +4735,37 @@
         <v>1.37</v>
       </c>
       <c r="M17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O17">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q17">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="T17">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="U17">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
         <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X17">
         <v>22</v>
@@ -4774,10 +4774,10 @@
         <v>18.5</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA17">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB17">
         <v>10.5</v>
@@ -4792,7 +4792,7 @@
         <v>65</v>
       </c>
       <c r="AF17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG17">
         <v>10.5</v>
@@ -4801,7 +4801,7 @@
         <v>22</v>
       </c>
       <c r="AI17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ17">
         <v>26</v>
@@ -4810,7 +4810,7 @@
         <v>24</v>
       </c>
       <c r="AL17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM17">
         <v>110</v>
@@ -4819,7 +4819,7 @@
         <v>11</v>
       </c>
       <c r="AO17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP17">
         <v>15.5</v>
@@ -4828,10 +4828,10 @@
         <v>15.5</v>
       </c>
       <c r="AR17">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS17">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT17">
         <v>9.199999999999999</v>
@@ -4840,10 +4840,10 @@
         <v>8</v>
       </c>
       <c r="AV17">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW17">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX17">
         <v>10.5</v>
@@ -4852,37 +4852,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17">
+        <v>15.5</v>
+      </c>
+      <c r="BA17">
+        <v>7.2</v>
+      </c>
+      <c r="BB17">
         <v>16</v>
-      </c>
-      <c r="BA17">
-        <v>6.6</v>
-      </c>
-      <c r="BB17">
-        <v>5.7</v>
       </c>
       <c r="BC17">
         <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE17">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF17">
         <v>9.800000000000001</v>
       </c>
       <c r="BG17">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI17">
-        <v>1.36</v>
+        <v>3.4</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
         <v>6</v>
@@ -4891,49 +4891,49 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.33</v>
+        <v>5.4</v>
       </c>
       <c r="BN17">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO17">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ17">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>1.33</v>
+        <v>4.8</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU17">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW17">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY17">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA17">
-        <v>1.33</v>
+        <v>4.6</v>
       </c>
       <c r="CB17" t="s">
         <v>158</v>
@@ -4959,22 +4959,22 @@
         <v>2.3</v>
       </c>
       <c r="G18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H18">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I18">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J18">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K18">
         <v>3.45</v>
       </c>
       <c r="L18">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M18">
         <v>1.09</v>
@@ -4986,7 +4986,7 @@
         <v>1.4</v>
       </c>
       <c r="P18">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q18">
         <v>2.18</v>
@@ -4995,19 +4995,19 @@
         <v>1.28</v>
       </c>
       <c r="S18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="T18">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U18">
         <v>2</v>
       </c>
       <c r="V18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X18">
         <v>12</v>
@@ -5034,7 +5034,7 @@
         <v>48</v>
       </c>
       <c r="AF18">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG18">
         <v>12</v>
@@ -5076,7 +5076,7 @@
         <v>10</v>
       </c>
       <c r="AT18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU18">
         <v>7</v>
@@ -5085,10 +5085,10 @@
         <v>13.5</v>
       </c>
       <c r="AW18">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY18">
         <v>10.5</v>
@@ -5097,16 +5097,16 @@
         <v>17.5</v>
       </c>
       <c r="BA18">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BC18">
         <v>19</v>
       </c>
       <c r="BD18">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="BE18">
         <v>10.5</v>
@@ -5115,67 +5115,67 @@
         <v>19</v>
       </c>
       <c r="BG18">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI18">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>2.36</v>
+        <v>5.1</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.66</v>
+        <v>7.6</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO18">
-        <v>1.87</v>
+        <v>4.5</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ18">
-        <v>2.66</v>
+        <v>13</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS18">
-        <v>2.66</v>
+        <v>6.6</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU18">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW18">
-        <v>2.66</v>
+        <v>6.6</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY18">
-        <v>2.66</v>
+        <v>7</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA18">
-        <v>2.66</v>
+        <v>6.6</v>
       </c>
       <c r="CB18" t="s">
         <v>158</v>
@@ -5198,16 +5198,16 @@
         <v>149</v>
       </c>
       <c r="F19">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G19">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J19">
         <v>3.5</v>
@@ -5222,34 +5222,34 @@
         <v>1.07</v>
       </c>
       <c r="N19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P19">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q19">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R19">
         <v>1.35</v>
       </c>
       <c r="S19">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T19">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="U19">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
         <v>1.43</v>
       </c>
       <c r="W19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X19">
         <v>15</v>
@@ -5273,7 +5273,7 @@
         <v>14</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19">
         <v>16</v>
@@ -5303,7 +5303,7 @@
         <v>20</v>
       </c>
       <c r="AO19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP19">
         <v>12.5</v>
@@ -5348,7 +5348,7 @@
         <v>23</v>
       </c>
       <c r="BD19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE19">
         <v>11</v>
@@ -5357,7 +5357,7 @@
         <v>17</v>
       </c>
       <c r="BG19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5440,226 +5440,226 @@
         <v>150</v>
       </c>
       <c r="F20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G20">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H20">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J20">
         <v>3.25</v>
       </c>
       <c r="K20">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>1.42</v>
       </c>
       <c r="P20">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
         <v>2.26</v>
       </c>
       <c r="R20">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S20">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T20">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X20">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y20">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB20">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC20">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP20">
-        <v>1.31</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20">
-        <v>1.32</v>
+        <v>10.5</v>
       </c>
       <c r="AR20">
-        <v>1.41</v>
+        <v>20</v>
       </c>
       <c r="AS20">
-        <v>1.41</v>
+        <v>5.5</v>
       </c>
       <c r="AT20">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="AU20">
+        <v>6.6</v>
+      </c>
+      <c r="AV20">
+        <v>14.5</v>
+      </c>
+      <c r="AW20">
+        <v>5.3</v>
+      </c>
+      <c r="AX20">
+        <v>11</v>
+      </c>
+      <c r="AY20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ20">
+        <v>17</v>
+      </c>
+      <c r="BA20">
+        <v>5.4</v>
+      </c>
+      <c r="BB20">
+        <v>4.9</v>
+      </c>
+      <c r="BC20">
+        <v>4.9</v>
+      </c>
+      <c r="BD20">
+        <v>38</v>
+      </c>
+      <c r="BE20">
         <v>5.6</v>
       </c>
-      <c r="AV20">
-        <v>1.41</v>
-      </c>
-      <c r="AW20">
-        <v>1.41</v>
-      </c>
-      <c r="AX20">
-        <v>1.41</v>
-      </c>
-      <c r="AY20">
-        <v>1.41</v>
-      </c>
-      <c r="AZ20">
-        <v>1.41</v>
-      </c>
-      <c r="BA20">
-        <v>1.41</v>
-      </c>
-      <c r="BB20">
-        <v>1.41</v>
-      </c>
-      <c r="BC20">
-        <v>1.41</v>
-      </c>
-      <c r="BD20">
-        <v>1.41</v>
-      </c>
-      <c r="BE20">
-        <v>1.41</v>
-      </c>
       <c r="BF20">
-        <v>1.41</v>
+        <v>19</v>
       </c>
       <c r="BG20">
-        <v>1.41</v>
+        <v>5.4</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO20">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB20" t="s">
         <v>158</v>
@@ -5682,22 +5682,22 @@
         <v>151</v>
       </c>
       <c r="F21">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L21">
         <v>1.46</v>
@@ -5706,22 +5706,22 @@
         <v>1.09</v>
       </c>
       <c r="N21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O21">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q21">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T21">
         <v>1.87</v>
@@ -5730,34 +5730,34 @@
         <v>1.84</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y21">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB21">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF21">
         <v>13</v>
@@ -5766,82 +5766,82 @@
         <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP21">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ21">
+        <v>11</v>
+      </c>
+      <c r="AR21">
+        <v>8.4</v>
+      </c>
+      <c r="AS21">
+        <v>10</v>
+      </c>
+      <c r="AT21">
+        <v>7.4</v>
+      </c>
+      <c r="AU21">
+        <v>6.8</v>
+      </c>
+      <c r="AV21">
+        <v>14.5</v>
+      </c>
+      <c r="AW21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX21">
         <v>10.5</v>
       </c>
-      <c r="AR21">
-        <v>2.06</v>
-      </c>
-      <c r="AS21">
-        <v>2.06</v>
-      </c>
-      <c r="AT21">
-        <v>6.6</v>
-      </c>
-      <c r="AU21">
-        <v>6.4</v>
-      </c>
-      <c r="AV21">
-        <v>2.06</v>
-      </c>
-      <c r="AW21">
-        <v>2.06</v>
-      </c>
-      <c r="AX21">
+      <c r="AY21">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY21">
-        <v>1.75</v>
-      </c>
       <c r="AZ21">
-        <v>2.06</v>
+        <v>17</v>
       </c>
       <c r="BA21">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BB21">
-        <v>2.06</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC21">
-        <v>2.06</v>
+        <v>21</v>
       </c>
       <c r="BD21">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE21">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BF21">
-        <v>2.06</v>
+        <v>17.5</v>
       </c>
       <c r="BG21">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5883,7 +5883,7 @@
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
         <v>1000</v>
@@ -5924,16 +5924,16 @@
         <v>152</v>
       </c>
       <c r="F22">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G22">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H22">
         <v>5.3</v>
       </c>
       <c r="I22">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="J22">
         <v>3.95</v>
@@ -5948,7 +5948,7 @@
         <v>1.06</v>
       </c>
       <c r="N22">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O22">
         <v>1.31</v>
@@ -5957,32 +5957,32 @@
         <v>1.9</v>
       </c>
       <c r="Q22">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R22">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T22">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="U22">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
         <v>2.28</v>
       </c>
       <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
         <v>950</v>
       </c>
-      <c r="Y22">
-        <v>1000</v>
-      </c>
       <c r="Z22">
         <v>1000</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>1000</v>
       </c>
       <c r="AB22">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AC22">
         <v>11</v>
@@ -5999,19 +5999,19 @@
         <v>1000</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF22">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ22">
         <v>1000</v>
@@ -6038,34 +6038,34 @@
         <v>11</v>
       </c>
       <c r="AR22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AS22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AT22">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU22">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AW22">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AX22">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY22">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AZ22">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="BA22">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="BB22">
         <v>11</v>
@@ -6074,16 +6074,16 @@
         <v>11</v>
       </c>
       <c r="BD22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="BE22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="BF22">
         <v>7.4</v>
       </c>
       <c r="BG22">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6166,22 +6166,22 @@
         <v>153</v>
       </c>
       <c r="F23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G23">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="H23">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I23">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="J23">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6202,7 +6202,7 @@
         <v>1.13</v>
       </c>
       <c r="R23">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="S23">
         <v>1.94</v>
@@ -6214,10 +6214,10 @@
         <v>1.11</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6408,7 +6408,7 @@
         <v>154</v>
       </c>
       <c r="F24">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -6417,7 +6417,7 @@
         <v>2.52</v>
       </c>
       <c r="I24">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J24">
         <v>3.55</v>
@@ -6426,7 +6426,7 @@
         <v>3.75</v>
       </c>
       <c r="L24">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M24">
         <v>1.06</v>
@@ -6441,7 +6441,7 @@
         <v>2.12</v>
       </c>
       <c r="Q24">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R24">
         <v>1.44</v>
@@ -6525,7 +6525,7 @@
         <v>15.5</v>
       </c>
       <c r="AS24">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT24">
         <v>11.5</v>
@@ -6537,7 +6537,7 @@
         <v>10.5</v>
       </c>
       <c r="AW24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX24">
         <v>18</v>
@@ -6549,19 +6549,19 @@
         <v>14</v>
       </c>
       <c r="BA24">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB24">
         <v>30</v>
       </c>
       <c r="BC24">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD24">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF24">
         <v>16.5</v>
@@ -6570,64 +6570,64 @@
         <v>16</v>
       </c>
       <c r="BH24">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="BI24">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK24">
+        <v>7.8</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>6.6</v>
+      </c>
+      <c r="BN24">
+        <v>7.2</v>
+      </c>
+      <c r="BO24">
+        <v>5.4</v>
+      </c>
+      <c r="BP24">
+        <v>26</v>
+      </c>
+      <c r="BQ24">
+        <v>5.8</v>
+      </c>
+      <c r="BR24">
+        <v>38</v>
+      </c>
+      <c r="BS24">
+        <v>5.9</v>
+      </c>
+      <c r="BT24">
         <v>5.7</v>
       </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>2.38</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>4.1</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>2.38</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>2.38</v>
-      </c>
-      <c r="BT24">
-        <v>8</v>
-      </c>
       <c r="BU24">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW24">
         <v>9.199999999999999</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY24">
-        <v>2.38</v>
+        <v>5.8</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA24">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="s">
         <v>158</v>
@@ -6650,10 +6650,10 @@
         <v>155</v>
       </c>
       <c r="F25">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G25">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H25">
         <v>3.95</v>
@@ -6668,13 +6668,13 @@
         <v>3.25</v>
       </c>
       <c r="L25">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M25">
         <v>1.12</v>
       </c>
       <c r="N25">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O25">
         <v>1.52</v>
@@ -6683,25 +6683,25 @@
         <v>1.57</v>
       </c>
       <c r="Q25">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R25">
         <v>1.21</v>
       </c>
       <c r="S25">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T25">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U25">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X25">
         <v>9.199999999999999</v>
@@ -6710,7 +6710,7 @@
         <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA25">
         <v>120</v>
@@ -6725,16 +6725,16 @@
         <v>19</v>
       </c>
       <c r="AE25">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF25">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG25">
         <v>12</v>
       </c>
       <c r="AH25">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI25">
         <v>110</v>
@@ -6764,10 +6764,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR25">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS25">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT25">
         <v>6.4</v>
@@ -6779,7 +6779,7 @@
         <v>15.5</v>
       </c>
       <c r="AW25">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX25">
         <v>11</v>
@@ -6788,88 +6788,88 @@
         <v>10</v>
       </c>
       <c r="AZ25">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA25">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB25">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC25">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD25">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE25">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF25">
         <v>21</v>
       </c>
       <c r="BG25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI25">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO25">
-        <v>1.54</v>
+        <v>4.3</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB25" t="s">
         <v>158</v>
@@ -6892,175 +6892,175 @@
         <v>156</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H26">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I26">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="J26">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M26">
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P26">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T26">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="U26">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
         <v>1.8</v>
       </c>
       <c r="X26">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Y26">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB26">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF26">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="AG26">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM26">
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP26">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ26">
-        <v>1.37</v>
+        <v>12</v>
       </c>
       <c r="AR26">
-        <v>1.43</v>
+        <v>8</v>
       </c>
       <c r="AS26">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="AT26">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AV26">
-        <v>1.41</v>
+        <v>13.5</v>
       </c>
       <c r="AW26">
-        <v>1.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX26">
+        <v>12</v>
+      </c>
+      <c r="AY26">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26">
+        <v>16</v>
+      </c>
+      <c r="BA26">
+        <v>10</v>
+      </c>
+      <c r="BB26">
+        <v>8</v>
+      </c>
+      <c r="BC26">
+        <v>21</v>
+      </c>
+      <c r="BD26">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY26">
-        <v>7.6</v>
-      </c>
-      <c r="AZ26">
-        <v>1.43</v>
-      </c>
-      <c r="BA26">
-        <v>1.43</v>
-      </c>
-      <c r="BB26">
-        <v>1.43</v>
-      </c>
-      <c r="BC26">
-        <v>1.43</v>
-      </c>
-      <c r="BD26">
-        <v>1.43</v>
-      </c>
       <c r="BE26">
-        <v>1.43</v>
+        <v>11</v>
       </c>
       <c r="BF26">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BG26">
-        <v>1.43</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI26">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="BJ26">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK26">
         <v>6.4</v>
@@ -7069,49 +7069,49 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>2</v>
+        <v>16.5</v>
       </c>
       <c r="BN26">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO26">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BP26">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BQ26">
-        <v>1.84</v>
+        <v>8.6</v>
       </c>
       <c r="BR26">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.91</v>
+        <v>11.5</v>
       </c>
       <c r="BT26">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="BU26">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BV26">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BW26">
-        <v>1.92</v>
+        <v>11.5</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.94</v>
+        <v>13</v>
       </c>
       <c r="BZ26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.9</v>
+        <v>11</v>
       </c>
       <c r="CB26" t="s">
         <v>158</v>
@@ -7134,16 +7134,16 @@
         <v>157</v>
       </c>
       <c r="F27">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H27">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J27">
         <v>3.55</v>
@@ -7152,7 +7152,7 @@
         <v>3.75</v>
       </c>
       <c r="L27">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M27">
         <v>1.08</v>
@@ -7170,19 +7170,19 @@
         <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S27">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T27">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U27">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W27">
         <v>1.27</v>
@@ -7191,13 +7191,13 @@
         <v>14.5</v>
       </c>
       <c r="Y27">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z27">
         <v>14</v>
       </c>
       <c r="AA27">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB27">
         <v>16.5</v>
@@ -7209,7 +7209,7 @@
         <v>12.5</v>
       </c>
       <c r="AE27">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF27">
         <v>38</v>
@@ -7221,13 +7221,13 @@
         <v>23</v>
       </c>
       <c r="AI27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ27">
         <v>120</v>
       </c>
       <c r="AK27">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL27">
         <v>80</v>
@@ -7236,10 +7236,10 @@
         <v>140</v>
       </c>
       <c r="AN27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO27">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP27">
         <v>11</v>
@@ -7251,7 +7251,7 @@
         <v>10.5</v>
       </c>
       <c r="AS27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT27">
         <v>12.5</v>
@@ -7266,7 +7266,7 @@
         <v>20</v>
       </c>
       <c r="AX27">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY27">
         <v>15.5</v>
@@ -7275,85 +7275,85 @@
         <v>17.5</v>
       </c>
       <c r="BA27">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB27">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC27">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD27">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE27">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF27">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG27">
         <v>14.5</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB27" t="s">
         <v>158</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="161">
   <si>
     <t>League</t>
   </si>
@@ -370,6 +370,9 @@
     <t>CS Constantine</t>
   </si>
   <si>
+    <t>ES Ben Aknoun</t>
+  </si>
+  <si>
     <t>Belouizdad</t>
   </si>
   <si>
@@ -448,6 +451,9 @@
     <t>US Biskra</t>
   </si>
   <si>
+    <t>JS El Biar</t>
+  </si>
+  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
@@ -490,7 +496,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 04:04:29</t>
+    <t>2026-10-06 06:16:18</t>
   </si>
 </sst>
 </file>
@@ -822,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1081,7 +1087,7 @@
         <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F2">
         <v>3.05</v>
@@ -1108,34 +1114,34 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T2">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U2">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V2">
         <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X2">
         <v>28</v>
@@ -1147,13 +1153,13 @@
         <v>20</v>
       </c>
       <c r="AA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB2">
         <v>21</v>
       </c>
       <c r="AC2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2">
         <v>12</v>
@@ -1171,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="AI2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ2">
         <v>55</v>
@@ -1186,19 +1192,19 @@
         <v>50</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
       </c>
       <c r="AR2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS2">
         <v>29</v>
@@ -1225,7 +1231,7 @@
         <v>13</v>
       </c>
       <c r="BA2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB2">
         <v>46</v>
@@ -1240,13 +1246,13 @@
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI2">
         <v>4.3</v>
@@ -1258,10 +1264,10 @@
         <v>7.4</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1273,13 +1279,13 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR2">
         <v>26</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
         <v>5.8</v>
@@ -1288,10 +1294,10 @@
         <v>5.3</v>
       </c>
       <c r="BV2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX2">
         <v>22</v>
@@ -1300,13 +1306,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1323,85 +1329,85 @@
         <v>107</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3">
         <v>11</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I3">
+        <v>1.37</v>
+      </c>
+      <c r="J3">
+        <v>5.4</v>
+      </c>
+      <c r="K3">
+        <v>5.9</v>
+      </c>
+      <c r="L3">
         <v>1.38</v>
       </c>
-      <c r="J3">
-        <v>5.3</v>
-      </c>
-      <c r="K3">
-        <v>5.7</v>
-      </c>
-      <c r="L3">
-        <v>1.4</v>
-      </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R3">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W3">
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
         <v>7.4</v>
       </c>
       <c r="AA3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF3">
         <v>120</v>
@@ -1419,19 +1425,19 @@
         <v>1000</v>
       </c>
       <c r="AK3">
+        <v>250</v>
+      </c>
+      <c r="AL3">
+        <v>190</v>
+      </c>
+      <c r="AM3">
         <v>260</v>
       </c>
-      <c r="AL3">
-        <v>210</v>
-      </c>
-      <c r="AM3">
-        <v>290</v>
-      </c>
       <c r="AN3">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AO3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
@@ -1446,7 +1452,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
@@ -1455,22 +1461,22 @@
         <v>9.6</v>
       </c>
       <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>11.5</v>
+      </c>
+      <c r="AY3">
+        <v>17</v>
+      </c>
+      <c r="AZ3">
         <v>15</v>
       </c>
-      <c r="AX3">
-        <v>42</v>
-      </c>
-      <c r="AY3">
-        <v>18.5</v>
-      </c>
-      <c r="AZ3">
-        <v>16</v>
-      </c>
       <c r="BA3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC3">
         <v>11.5</v>
@@ -1485,46 +1491,46 @@
         <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH3">
+        <v>3.75</v>
+      </c>
+      <c r="BI3">
+        <v>3.35</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
+        <v>6.8</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>13</v>
+      </c>
+      <c r="BN3">
+        <v>15</v>
+      </c>
+      <c r="BO3">
+        <v>7.2</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>12.5</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>12.5</v>
+      </c>
+      <c r="BT3">
         <v>3.6</v>
-      </c>
-      <c r="BI3">
-        <v>3.2</v>
-      </c>
-      <c r="BJ3">
-        <v>14</v>
-      </c>
-      <c r="BK3">
-        <v>7.2</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>14</v>
-      </c>
-      <c r="BN3">
-        <v>15.5</v>
-      </c>
-      <c r="BO3">
-        <v>7.6</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>13</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>13</v>
-      </c>
-      <c r="BT3">
-        <v>3.55</v>
       </c>
       <c r="BU3">
         <v>3.25</v>
@@ -1536,19 +1542,19 @@
         <v>7</v>
       </c>
       <c r="BX3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1565,25 +1571,25 @@
         <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F4">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1595,58 +1601,58 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="U4">
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="X4">
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
         <v>27</v>
       </c>
       <c r="AA4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
         <v>60</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
         <v>12</v>
@@ -1658,16 +1664,16 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AK4">
+        <v>34</v>
+      </c>
+      <c r="AL4">
         <v>65</v>
       </c>
-      <c r="AL4">
-        <v>60</v>
-      </c>
       <c r="AM4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN4">
         <v>29</v>
@@ -1679,13 +1685,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1697,7 +1703,7 @@
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
@@ -1709,10 +1715,10 @@
         <v>17</v>
       </c>
       <c r="BA4">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC4">
         <v>17.5</v>
@@ -1727,10 +1733,10 @@
         <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI4">
         <v>2.42</v>
@@ -1739,58 +1745,58 @@
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1807,22 +1813,22 @@
         <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F5">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1.69</v>
       </c>
       <c r="H5">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>17.5</v>
       </c>
       <c r="J5">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
         <v>85</v>
@@ -1831,37 +1837,37 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
+        <v>2.66</v>
+      </c>
+      <c r="O5">
+        <v>1.06</v>
+      </c>
+      <c r="P5">
+        <v>1.61</v>
+      </c>
+      <c r="Q5">
+        <v>2.12</v>
+      </c>
+      <c r="R5">
+        <v>1.19</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>1.12</v>
+      </c>
+      <c r="U5">
+        <v>1.12</v>
+      </c>
+      <c r="V5">
         <v>1.1</v>
       </c>
-      <c r="O5">
-        <v>1.02</v>
-      </c>
-      <c r="P5">
-        <v>1.1</v>
-      </c>
-      <c r="Q5">
-        <v>1.42</v>
-      </c>
-      <c r="R5">
-        <v>1.08</v>
-      </c>
-      <c r="S5">
-        <v>1.42</v>
-      </c>
-      <c r="T5">
-        <v>1.11</v>
-      </c>
-      <c r="U5">
-        <v>1.11</v>
-      </c>
-      <c r="V5">
-        <v>1.09</v>
-      </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1972,7 +1978,7 @@
         <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
         <v>1.04</v>
@@ -1981,58 +1987,58 @@
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="CB5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2049,7 +2055,7 @@
         <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F6">
         <v>2.5</v>
@@ -2079,7 +2085,7 @@
         <v>3.55</v>
       </c>
       <c r="O6">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
         <v>1.96</v>
@@ -2274,7 +2280,7 @@
         <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2291,10 +2297,10 @@
         <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F7">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="G7">
         <v>14.5</v>
@@ -2303,13 +2309,13 @@
         <v>1.38</v>
       </c>
       <c r="I7">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="J7">
         <v>3.7</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="L7">
         <v>1.23</v>
@@ -2318,10 +2324,10 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P7">
         <v>2.06</v>
@@ -2342,10 +2348,10 @@
         <v>1.12</v>
       </c>
       <c r="V7">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="W7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2516,7 +2522,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2533,13 +2539,13 @@
         <v>112</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F8">
         <v>3.65</v>
       </c>
       <c r="G8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H8">
         <v>2.04</v>
@@ -2581,13 +2587,13 @@
         <v>1.74</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="V8">
         <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X8">
         <v>15.5</v>
@@ -2758,7 +2764,7 @@
         <v>4.9</v>
       </c>
       <c r="CB8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2775,7 +2781,7 @@
         <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F9">
         <v>1.12</v>
@@ -2790,7 +2796,7 @@
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="K9">
         <v>85</v>
@@ -3000,7 +3006,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3017,7 +3023,7 @@
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F10">
         <v>1.12</v>
@@ -3032,7 +3038,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="K10">
         <v>85</v>
@@ -3242,7 +3248,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3259,25 +3265,25 @@
         <v>115</v>
       </c>
       <c r="E11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F11">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="G11">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H11">
         <v>2.2</v>
       </c>
       <c r="I11">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J11">
         <v>3.6</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3286,37 +3292,37 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R11">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S11">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="T11">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.68</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y11">
         <v>22</v>
@@ -3328,7 +3334,7 @@
         <v>40</v>
       </c>
       <c r="AB11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC11">
         <v>13</v>
@@ -3355,7 +3361,7 @@
         <v>55</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL11">
         <v>36</v>
@@ -3364,16 +3370,16 @@
         <v>60</v>
       </c>
       <c r="AN11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO11">
         <v>13</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR11">
         <v>1.01</v>
@@ -3385,25 +3391,25 @@
         <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3412,7 +3418,7 @@
         <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
@@ -3421,7 +3427,7 @@
         <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3484,7 +3490,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3501,61 +3507,61 @@
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H12">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="I12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="J12">
         <v>3.85</v>
       </c>
       <c r="K12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q12">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T12">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U12">
         <v>2.2</v>
       </c>
       <c r="V12">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X12">
         <v>18.5</v>
@@ -3567,16 +3573,16 @@
         <v>12.5</v>
       </c>
       <c r="AA12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB12">
         <v>18.5</v>
       </c>
       <c r="AC12">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE12">
         <v>19</v>
@@ -3594,7 +3600,7 @@
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK12">
         <v>70</v>
@@ -3606,16 +3612,16 @@
         <v>110</v>
       </c>
       <c r="AN12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO12">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP12">
         <v>15</v>
       </c>
       <c r="AQ12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR12">
         <v>10.5</v>
@@ -3630,13 +3636,13 @@
         <v>8</v>
       </c>
       <c r="AV12">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW12">
         <v>16</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY12">
         <v>15</v>
@@ -3645,10 +3651,10 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB12">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC12">
         <v>32</v>
@@ -3657,16 +3663,16 @@
         <v>34</v>
       </c>
       <c r="BE12">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF12">
         <v>32</v>
       </c>
       <c r="BG12">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI12">
         <v>3.4</v>
@@ -3684,13 +3690,13 @@
         <v>6.4</v>
       </c>
       <c r="BN12">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO12">
         <v>7</v>
       </c>
       <c r="BP12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ12">
         <v>5.9</v>
@@ -3705,28 +3711,28 @@
         <v>4.7</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW12">
         <v>7.2</v>
       </c>
       <c r="BX12">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY12">
+        <v>5.5</v>
+      </c>
+      <c r="BZ12">
+        <v>24</v>
+      </c>
+      <c r="CA12">
         <v>5.6</v>
       </c>
-      <c r="BZ12">
-        <v>25</v>
-      </c>
-      <c r="CA12">
-        <v>5.7</v>
-      </c>
       <c r="CB12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3743,25 +3749,25 @@
         <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F13">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="G13">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H13">
         <v>6.8</v>
       </c>
       <c r="I13">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3770,16 +3776,16 @@
         <v>1.12</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
         <v>1.46</v>
       </c>
       <c r="P13">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R13">
         <v>1.18</v>
@@ -3788,22 +3794,22 @@
         <v>5.4</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X13">
         <v>10.5</v>
       </c>
       <c r="Y13">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="Z13">
         <v>75</v>
@@ -3812,10 +3818,10 @@
         <v>380</v>
       </c>
       <c r="AB13">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD13">
         <v>38</v>
@@ -3824,7 +3830,7 @@
         <v>220</v>
       </c>
       <c r="AF13">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG13">
         <v>13.5</v>
@@ -3836,7 +3842,7 @@
         <v>230</v>
       </c>
       <c r="AJ13">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK13">
         <v>30</v>
@@ -3860,22 +3866,22 @@
         <v>12</v>
       </c>
       <c r="AR13">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AS13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT13">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AU13">
         <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AW13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX13">
         <v>7.2</v>
@@ -3884,10 +3890,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ13">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
@@ -3896,16 +3902,16 @@
         <v>18</v>
       </c>
       <c r="BD13">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF13">
         <v>13.5</v>
       </c>
       <c r="BG13">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3917,13 +3923,13 @@
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -3935,40 +3941,40 @@
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="CB13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3979,480 +3985,480 @@
         <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>118</v>
       </c>
       <c r="E14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="G14">
-        <v>1.43</v>
+        <v>2.66</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="I14">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="J14">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="K14">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
         <v>119</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F15">
+        <v>1.36</v>
+      </c>
+      <c r="G15">
+        <v>1.43</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>15.5</v>
+      </c>
+      <c r="J15">
+        <v>4.6</v>
+      </c>
+      <c r="K15">
+        <v>5.9</v>
+      </c>
+      <c r="L15">
+        <v>1.41</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.4</v>
+      </c>
+      <c r="O15">
+        <v>1.35</v>
+      </c>
+      <c r="P15">
+        <v>1.81</v>
+      </c>
+      <c r="Q15">
         <v>2.02</v>
       </c>
-      <c r="G15">
-        <v>2.2</v>
-      </c>
-      <c r="H15">
-        <v>3.7</v>
-      </c>
-      <c r="I15">
-        <v>4.8</v>
-      </c>
-      <c r="J15">
+      <c r="R15">
+        <v>1.3</v>
+      </c>
+      <c r="S15">
+        <v>3.65</v>
+      </c>
+      <c r="T15">
+        <v>2.36</v>
+      </c>
+      <c r="U15">
+        <v>1.53</v>
+      </c>
+      <c r="V15">
+        <v>1.07</v>
+      </c>
+      <c r="W15">
         <v>3.3</v>
       </c>
-      <c r="K15">
-        <v>3.7</v>
-      </c>
-      <c r="L15">
-        <v>1.4</v>
-      </c>
-      <c r="M15">
-        <v>1.08</v>
-      </c>
-      <c r="N15">
-        <v>3.15</v>
-      </c>
-      <c r="O15">
-        <v>1.37</v>
-      </c>
-      <c r="P15">
-        <v>1.71</v>
-      </c>
-      <c r="Q15">
-        <v>2</v>
-      </c>
-      <c r="R15">
-        <v>1.25</v>
-      </c>
-      <c r="S15">
-        <v>3.55</v>
-      </c>
-      <c r="T15">
-        <v>1.78</v>
-      </c>
-      <c r="U15">
-        <v>1.98</v>
-      </c>
-      <c r="V15">
-        <v>1.28</v>
-      </c>
-      <c r="W15">
-        <v>1.83</v>
-      </c>
       <c r="X15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y15">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="Z15">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AA15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AE15">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AF15">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="AG15">
         <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AI15">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AK15">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AL15">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM15">
-        <v>140</v>
+        <v>340</v>
       </c>
       <c r="AN15">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="AO15">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR15">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT15">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AU15">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
+        <v>5.5</v>
+      </c>
+      <c r="AW15">
+        <v>6</v>
+      </c>
+      <c r="AX15">
+        <v>6</v>
+      </c>
+      <c r="AY15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>5.3</v>
+      </c>
+      <c r="BA15">
+        <v>5.9</v>
+      </c>
+      <c r="BB15">
+        <v>8.6</v>
+      </c>
+      <c r="BC15">
+        <v>13.5</v>
+      </c>
+      <c r="BD15">
+        <v>5.5</v>
+      </c>
+      <c r="BE15">
+        <v>6</v>
+      </c>
+      <c r="BF15">
+        <v>6.4</v>
+      </c>
+      <c r="BG15">
+        <v>6</v>
+      </c>
+      <c r="BH15">
+        <v>3.75</v>
+      </c>
+      <c r="BI15">
+        <v>2.78</v>
+      </c>
+      <c r="BJ15">
+        <v>16</v>
+      </c>
+      <c r="BK15">
+        <v>4.4</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>6</v>
+      </c>
+      <c r="BN15">
+        <v>3.95</v>
+      </c>
+      <c r="BO15">
+        <v>3.1</v>
+      </c>
+      <c r="BP15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ15">
+        <v>3.75</v>
+      </c>
+      <c r="BR15">
+        <v>36</v>
+      </c>
+      <c r="BS15">
         <v>5.2</v>
       </c>
-      <c r="AW15">
-        <v>6.8</v>
-      </c>
-      <c r="AX15">
+      <c r="BT15">
+        <v>16.5</v>
+      </c>
+      <c r="BU15">
+        <v>4.4</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>5.9</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>5.8</v>
+      </c>
+      <c r="BZ15">
+        <v>21</v>
+      </c>
+      <c r="CA15">
         <v>4.7</v>
       </c>
-      <c r="AY15">
-        <v>4.7</v>
-      </c>
-      <c r="AZ15">
-        <v>5.6</v>
-      </c>
-      <c r="BA15">
-        <v>6.8</v>
-      </c>
-      <c r="BB15">
-        <v>5.8</v>
-      </c>
-      <c r="BC15">
-        <v>5.7</v>
-      </c>
-      <c r="BD15">
-        <v>6.4</v>
-      </c>
-      <c r="BE15">
-        <v>7</v>
-      </c>
-      <c r="BF15">
-        <v>5.6</v>
-      </c>
-      <c r="BG15">
-        <v>6.8</v>
-      </c>
-      <c r="BH15">
-        <v>3.5</v>
-      </c>
-      <c r="BI15">
-        <v>2.62</v>
-      </c>
-      <c r="BJ15">
-        <v>12</v>
-      </c>
-      <c r="BK15">
-        <v>1.04</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>1.04</v>
-      </c>
-      <c r="BN15">
-        <v>5.4</v>
-      </c>
-      <c r="BO15">
-        <v>1.04</v>
-      </c>
-      <c r="BP15">
-        <v>18</v>
-      </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>38</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>8.4</v>
-      </c>
-      <c r="BU15">
-        <v>1.04</v>
-      </c>
-      <c r="BV15">
-        <v>42</v>
-      </c>
-      <c r="BW15">
-        <v>1.04</v>
-      </c>
-      <c r="BX15">
-        <v>60</v>
-      </c>
-      <c r="BY15">
-        <v>1.04</v>
-      </c>
-      <c r="BZ15">
-        <v>36</v>
-      </c>
-      <c r="CA15">
-        <v>1.04</v>
-      </c>
       <c r="CB15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4463,480 +4469,480 @@
         <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
         <v>120</v>
       </c>
       <c r="E16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F16">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="G16">
+        <v>2.12</v>
+      </c>
+      <c r="H16">
+        <v>3.85</v>
+      </c>
+      <c r="I16">
         <v>4</v>
       </c>
-      <c r="H16">
-        <v>2.2</v>
-      </c>
-      <c r="I16">
-        <v>2.48</v>
-      </c>
       <c r="J16">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
         <v>3.7</v>
       </c>
       <c r="L16">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="M16">
         <v>1.08</v>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
         <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q16">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R16">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S16">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T16">
         <v>1.83</v>
       </c>
       <c r="U16">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="V16">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y16">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="Z16">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AA16">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC16">
         <v>8</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG16">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ16">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL16">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP16">
-        <v>1.83</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16">
-        <v>1.54</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>1.64</v>
+        <v>6.2</v>
       </c>
       <c r="AS16">
-        <v>1.74</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>1.83</v>
+        <v>6.6</v>
       </c>
       <c r="AU16">
-        <v>1.49</v>
+        <v>3.9</v>
       </c>
       <c r="AV16">
-        <v>1.83</v>
+        <v>5.3</v>
       </c>
       <c r="AW16">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>1.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16">
-        <v>1.65</v>
+        <v>8.4</v>
       </c>
       <c r="AZ16">
-        <v>1.83</v>
+        <v>5.7</v>
       </c>
       <c r="BA16">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>1.79</v>
+        <v>20</v>
       </c>
       <c r="BC16">
-        <v>1.84</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>1.79</v>
+        <v>6.6</v>
       </c>
       <c r="BE16">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>1.84</v>
+        <v>14.5</v>
       </c>
       <c r="BG16">
-        <v>1.84</v>
+        <v>7</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
         <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
         <v>121</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F17">
-        <v>1.86</v>
+        <v>3.9</v>
       </c>
       <c r="G17">
-        <v>1.92</v>
+        <v>4.4</v>
       </c>
       <c r="H17">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>2.26</v>
       </c>
       <c r="J17">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L17">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="M17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N17">
-        <v>4.3</v>
+        <v>2.52</v>
       </c>
       <c r="O17">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="P17">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>1.22</v>
+      </c>
+      <c r="S17">
+        <v>2.82</v>
+      </c>
+      <c r="T17">
+        <v>1.99</v>
+      </c>
+      <c r="U17">
+        <v>1.87</v>
+      </c>
+      <c r="V17">
         <v>1.8</v>
       </c>
-      <c r="R17">
-        <v>1.44</v>
-      </c>
-      <c r="S17">
-        <v>3.05</v>
-      </c>
-      <c r="T17">
-        <v>1.74</v>
-      </c>
-      <c r="U17">
-        <v>2.2</v>
-      </c>
-      <c r="V17">
-        <v>1.27</v>
-      </c>
       <c r="W17">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="X17">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="Y17">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z17">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="AB17">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD17">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE17">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AF17">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AG17">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AH17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI17">
         <v>65</v>
       </c>
       <c r="AJ17">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="AK17">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AL17">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AM17">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AN17">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="AO17">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AP17">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR17">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS17">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AT17">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AU17">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>15.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AX17">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY17">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AZ17">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA17">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB17">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD17">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE17">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BF17">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BG17">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="BH17">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4953,232 +4959,232 @@
         <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F18">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="G18">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="H18">
+        <v>4.4</v>
+      </c>
+      <c r="I18">
+        <v>4.7</v>
+      </c>
+      <c r="J18">
+        <v>3.9</v>
+      </c>
+      <c r="K18">
+        <v>4.1</v>
+      </c>
+      <c r="L18">
+        <v>1.37</v>
+      </c>
+      <c r="M18">
+        <v>1.05</v>
+      </c>
+      <c r="N18">
+        <v>4.3</v>
+      </c>
+      <c r="O18">
+        <v>1.26</v>
+      </c>
+      <c r="P18">
+        <v>2.12</v>
+      </c>
+      <c r="Q18">
+        <v>1.72</v>
+      </c>
+      <c r="R18">
+        <v>1.44</v>
+      </c>
+      <c r="S18">
+        <v>3.05</v>
+      </c>
+      <c r="T18">
+        <v>1.75</v>
+      </c>
+      <c r="U18">
+        <v>2.22</v>
+      </c>
+      <c r="V18">
+        <v>1.27</v>
+      </c>
+      <c r="W18">
+        <v>2.08</v>
+      </c>
+      <c r="X18">
+        <v>22</v>
+      </c>
+      <c r="Y18">
+        <v>18.5</v>
+      </c>
+      <c r="Z18">
+        <v>40</v>
+      </c>
+      <c r="AA18">
+        <v>110</v>
+      </c>
+      <c r="AB18">
+        <v>10.5</v>
+      </c>
+      <c r="AC18">
+        <v>9</v>
+      </c>
+      <c r="AD18">
+        <v>18.5</v>
+      </c>
+      <c r="AE18">
+        <v>65</v>
+      </c>
+      <c r="AF18">
+        <v>13</v>
+      </c>
+      <c r="AG18">
+        <v>10.5</v>
+      </c>
+      <c r="AH18">
+        <v>22</v>
+      </c>
+      <c r="AI18">
+        <v>65</v>
+      </c>
+      <c r="AJ18">
+        <v>26</v>
+      </c>
+      <c r="AK18">
+        <v>24</v>
+      </c>
+      <c r="AL18">
+        <v>40</v>
+      </c>
+      <c r="AM18">
+        <v>110</v>
+      </c>
+      <c r="AN18">
+        <v>11</v>
+      </c>
+      <c r="AO18">
+        <v>60</v>
+      </c>
+      <c r="AP18">
+        <v>15.5</v>
+      </c>
+      <c r="AQ18">
+        <v>15.5</v>
+      </c>
+      <c r="AR18">
+        <v>6.8</v>
+      </c>
+      <c r="AS18">
+        <v>7.6</v>
+      </c>
+      <c r="AT18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18">
+        <v>8</v>
+      </c>
+      <c r="AV18">
+        <v>15</v>
+      </c>
+      <c r="AW18">
+        <v>7.4</v>
+      </c>
+      <c r="AX18">
+        <v>10.5</v>
+      </c>
+      <c r="AY18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18">
+        <v>15.5</v>
+      </c>
+      <c r="BA18">
+        <v>7.4</v>
+      </c>
+      <c r="BB18">
+        <v>18</v>
+      </c>
+      <c r="BC18">
+        <v>16.5</v>
+      </c>
+      <c r="BD18">
+        <v>6.8</v>
+      </c>
+      <c r="BE18">
+        <v>7.6</v>
+      </c>
+      <c r="BF18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG18">
+        <v>7.2</v>
+      </c>
+      <c r="BH18">
+        <v>4.3</v>
+      </c>
+      <c r="BI18">
         <v>3.4</v>
       </c>
-      <c r="I18">
-        <v>3.65</v>
-      </c>
-      <c r="J18">
-        <v>3.3</v>
-      </c>
-      <c r="K18">
-        <v>3.45</v>
-      </c>
-      <c r="L18">
-        <v>1.49</v>
-      </c>
-      <c r="M18">
-        <v>1.09</v>
-      </c>
-      <c r="N18">
-        <v>3.25</v>
-      </c>
-      <c r="O18">
-        <v>1.4</v>
-      </c>
-      <c r="P18">
-        <v>1.72</v>
-      </c>
-      <c r="Q18">
-        <v>2.18</v>
-      </c>
-      <c r="R18">
-        <v>1.28</v>
-      </c>
-      <c r="S18">
-        <v>4.1</v>
-      </c>
-      <c r="T18">
-        <v>1.91</v>
-      </c>
-      <c r="U18">
-        <v>2</v>
-      </c>
-      <c r="V18">
-        <v>1.38</v>
-      </c>
-      <c r="W18">
-        <v>1.71</v>
-      </c>
-      <c r="X18">
-        <v>12</v>
-      </c>
-      <c r="Y18">
-        <v>12</v>
-      </c>
-      <c r="Z18">
+      <c r="BJ18">
+        <v>11.5</v>
+      </c>
+      <c r="BK18">
+        <v>6</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>5.4</v>
+      </c>
+      <c r="BN18">
+        <v>4.7</v>
+      </c>
+      <c r="BO18">
+        <v>4.2</v>
+      </c>
+      <c r="BP18">
+        <v>15</v>
+      </c>
+      <c r="BQ18">
+        <v>7.4</v>
+      </c>
+      <c r="BR18">
+        <v>32</v>
+      </c>
+      <c r="BS18">
+        <v>4.8</v>
+      </c>
+      <c r="BT18">
+        <v>9.6</v>
+      </c>
+      <c r="BU18">
+        <v>7</v>
+      </c>
+      <c r="BV18">
+        <v>44</v>
+      </c>
+      <c r="BW18">
+        <v>5</v>
+      </c>
+      <c r="BX18">
+        <v>55</v>
+      </c>
+      <c r="BY18">
+        <v>5.1</v>
+      </c>
+      <c r="BZ18">
         <v>25</v>
       </c>
-      <c r="AA18">
-        <v>85</v>
-      </c>
-      <c r="AB18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC18">
-        <v>7.6</v>
-      </c>
-      <c r="AD18">
-        <v>15.5</v>
-      </c>
-      <c r="AE18">
-        <v>48</v>
-      </c>
-      <c r="AF18">
-        <v>14</v>
-      </c>
-      <c r="AG18">
-        <v>12</v>
-      </c>
-      <c r="AH18">
-        <v>21</v>
-      </c>
-      <c r="AI18">
-        <v>70</v>
-      </c>
-      <c r="AJ18">
-        <v>32</v>
-      </c>
-      <c r="AK18">
-        <v>28</v>
-      </c>
-      <c r="AL18">
-        <v>60</v>
-      </c>
-      <c r="AM18">
-        <v>150</v>
-      </c>
-      <c r="AN18">
-        <v>23</v>
-      </c>
-      <c r="AO18">
-        <v>55</v>
-      </c>
-      <c r="AP18">
-        <v>10</v>
-      </c>
-      <c r="AQ18">
-        <v>10.5</v>
-      </c>
-      <c r="AR18">
-        <v>21</v>
-      </c>
-      <c r="AS18">
-        <v>10</v>
-      </c>
-      <c r="AT18">
-        <v>8.4</v>
-      </c>
-      <c r="AU18">
-        <v>7</v>
-      </c>
-      <c r="AV18">
-        <v>13.5</v>
-      </c>
-      <c r="AW18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX18">
-        <v>12.5</v>
-      </c>
-      <c r="AY18">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18">
-        <v>17.5</v>
-      </c>
-      <c r="BA18">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB18">
-        <v>21</v>
-      </c>
-      <c r="BC18">
-        <v>19</v>
-      </c>
-      <c r="BD18">
-        <v>9.6</v>
-      </c>
-      <c r="BE18">
-        <v>10.5</v>
-      </c>
-      <c r="BF18">
-        <v>19</v>
-      </c>
-      <c r="BG18">
-        <v>9.4</v>
-      </c>
-      <c r="BH18">
-        <v>3.1</v>
-      </c>
-      <c r="BI18">
-        <v>2.78</v>
-      </c>
-      <c r="BJ18">
-        <v>12.5</v>
-      </c>
-      <c r="BK18">
-        <v>5.1</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>7.6</v>
-      </c>
-      <c r="BN18">
-        <v>5</v>
-      </c>
-      <c r="BO18">
-        <v>4.5</v>
-      </c>
-      <c r="BP18">
-        <v>21</v>
-      </c>
-      <c r="BQ18">
-        <v>13</v>
-      </c>
-      <c r="BR18">
-        <v>40</v>
-      </c>
-      <c r="BS18">
-        <v>6.6</v>
-      </c>
-      <c r="BT18">
-        <v>7.8</v>
-      </c>
-      <c r="BU18">
-        <v>6</v>
-      </c>
-      <c r="BV18">
-        <v>40</v>
-      </c>
-      <c r="BW18">
-        <v>6.6</v>
-      </c>
-      <c r="BX18">
-        <v>60</v>
-      </c>
-      <c r="BY18">
-        <v>7</v>
-      </c>
-      <c r="BZ18">
-        <v>40</v>
-      </c>
       <c r="CA18">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="CB18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5195,237 +5201,237 @@
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F19">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H19">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="I19">
+        <v>3.65</v>
+      </c>
+      <c r="J19">
         <v>3.3</v>
       </c>
-      <c r="J19">
-        <v>3.5</v>
-      </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="M19">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="P19">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="Q19">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="R19">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S19">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="X19">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA19">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AB19">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD19">
+        <v>15.5</v>
+      </c>
+      <c r="AE19">
+        <v>48</v>
+      </c>
+      <c r="AF19">
         <v>14</v>
-      </c>
-      <c r="AE19">
-        <v>38</v>
-      </c>
-      <c r="AF19">
-        <v>16</v>
       </c>
       <c r="AG19">
         <v>12</v>
       </c>
       <c r="AH19">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI19">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AJ19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK19">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AP19">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR19">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS19">
         <v>10</v>
       </c>
       <c r="AT19">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW19">
         <v>9.199999999999999</v>
       </c>
       <c r="AX19">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
         <v>10.5</v>
       </c>
       <c r="AZ19">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB19">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="BC19">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BD19">
+        <v>38</v>
+      </c>
+      <c r="BE19">
+        <v>10.5</v>
+      </c>
+      <c r="BF19">
+        <v>19</v>
+      </c>
+      <c r="BG19">
         <v>9.4</v>
       </c>
-      <c r="BE19">
-        <v>11</v>
-      </c>
-      <c r="BF19">
-        <v>17</v>
-      </c>
-      <c r="BG19">
+      <c r="BH19">
+        <v>3.05</v>
+      </c>
+      <c r="BI19">
+        <v>2.84</v>
+      </c>
+      <c r="BJ19">
+        <v>12.5</v>
+      </c>
+      <c r="BK19">
+        <v>5.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
         <v>8.800000000000001</v>
       </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.51</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>2.18</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>2.5</v>
-      </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO19">
-        <v>1.82</v>
+        <v>4.5</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ19">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS19">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU19">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW19">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY19">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA19">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="CB19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
         <v>90</v>
@@ -5437,232 +5443,232 @@
         <v>124</v>
       </c>
       <c r="E20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F20">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="H20">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="I20">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J20">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K20">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="O20">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="P20">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="R20">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="T20">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="U20">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="X20">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y20">
         <v>13</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AA20">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AC20">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AE20">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AF20">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG20">
         <v>12</v>
       </c>
       <c r="AH20">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AI20">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AJ20">
         <v>36</v>
       </c>
       <c r="AK20">
+        <v>27</v>
+      </c>
+      <c r="AL20">
+        <v>40</v>
+      </c>
+      <c r="AM20">
+        <v>110</v>
+      </c>
+      <c r="AN20">
+        <v>20</v>
+      </c>
+      <c r="AO20">
         <v>32</v>
       </c>
-      <c r="AL20">
-        <v>60</v>
-      </c>
-      <c r="AM20">
-        <v>170</v>
-      </c>
-      <c r="AN20">
-        <v>29</v>
-      </c>
-      <c r="AO20">
-        <v>90</v>
-      </c>
       <c r="AP20">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AQ20">
+        <v>11.5</v>
+      </c>
+      <c r="AR20">
+        <v>19</v>
+      </c>
+      <c r="AS20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU20">
+        <v>7.4</v>
+      </c>
+      <c r="AV20">
+        <v>12.5</v>
+      </c>
+      <c r="AW20">
+        <v>9</v>
+      </c>
+      <c r="AX20">
+        <v>13.5</v>
+      </c>
+      <c r="AY20">
         <v>10.5</v>
       </c>
-      <c r="AR20">
-        <v>20</v>
-      </c>
-      <c r="AS20">
-        <v>5.5</v>
-      </c>
-      <c r="AT20">
-        <v>7</v>
-      </c>
-      <c r="AU20">
-        <v>6.6</v>
-      </c>
-      <c r="AV20">
-        <v>14.5</v>
-      </c>
-      <c r="AW20">
-        <v>5.3</v>
-      </c>
-      <c r="AX20">
-        <v>11</v>
-      </c>
-      <c r="AY20">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ20">
+        <v>15</v>
+      </c>
+      <c r="BA20">
+        <v>9.4</v>
+      </c>
+      <c r="BB20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC20">
+        <v>23</v>
+      </c>
+      <c r="BD20">
+        <v>9</v>
+      </c>
+      <c r="BE20">
+        <v>10.5</v>
+      </c>
+      <c r="BF20">
         <v>17</v>
       </c>
-      <c r="BA20">
-        <v>5.4</v>
-      </c>
-      <c r="BB20">
-        <v>4.9</v>
-      </c>
-      <c r="BC20">
-        <v>4.9</v>
-      </c>
-      <c r="BD20">
-        <v>38</v>
-      </c>
-      <c r="BE20">
-        <v>5.6</v>
-      </c>
-      <c r="BF20">
-        <v>19</v>
-      </c>
       <c r="BG20">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH20">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="BJ20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>7.8</v>
+        <v>2.18</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="BN20">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.2</v>
+        <v>1.82</v>
       </c>
       <c r="BP20">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="BR20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="BT20">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="BV20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="BX20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="BZ20">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5679,19 +5685,19 @@
         <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F21">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="I21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J21">
         <v>3.25</v>
@@ -5700,336 +5706,336 @@
         <v>3.55</v>
       </c>
       <c r="L21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M21">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O21">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P21">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R21">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T21">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="X21">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z21">
+        <v>34</v>
+      </c>
+      <c r="AA21">
+        <v>110</v>
+      </c>
+      <c r="AB21">
+        <v>8.6</v>
+      </c>
+      <c r="AC21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21">
+        <v>17.5</v>
+      </c>
+      <c r="AE21">
+        <v>70</v>
+      </c>
+      <c r="AF21">
+        <v>15.5</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>26</v>
+      </c>
+      <c r="AI21">
+        <v>90</v>
+      </c>
+      <c r="AJ21">
+        <v>36</v>
+      </c>
+      <c r="AK21">
         <v>32</v>
       </c>
-      <c r="AA21">
-        <v>120</v>
-      </c>
-      <c r="AB21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>7.6</v>
-      </c>
-      <c r="AD21">
-        <v>18</v>
-      </c>
-      <c r="AE21">
-        <v>65</v>
-      </c>
-      <c r="AF21">
-        <v>13</v>
-      </c>
-      <c r="AG21">
-        <v>11.5</v>
-      </c>
-      <c r="AH21">
-        <v>21</v>
-      </c>
-      <c r="AI21">
-        <v>75</v>
-      </c>
-      <c r="AJ21">
+      <c r="AL21">
+        <v>60</v>
+      </c>
+      <c r="AM21">
+        <v>170</v>
+      </c>
+      <c r="AN21">
         <v>29</v>
       </c>
-      <c r="AK21">
-        <v>27</v>
-      </c>
-      <c r="AL21">
-        <v>48</v>
-      </c>
-      <c r="AM21">
-        <v>160</v>
-      </c>
-      <c r="AN21">
-        <v>21</v>
-      </c>
       <c r="AO21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP21">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="AS21">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AT21">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
         <v>14.5</v>
       </c>
       <c r="AW21">
+        <v>5.3</v>
+      </c>
+      <c r="AX21">
+        <v>11</v>
+      </c>
+      <c r="AY21">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AX21">
-        <v>10.5</v>
-      </c>
-      <c r="AY21">
-        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
         <v>17</v>
       </c>
       <c r="BA21">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="BB21">
+        <v>5</v>
+      </c>
+      <c r="BC21">
+        <v>4.9</v>
+      </c>
+      <c r="BD21">
+        <v>38</v>
+      </c>
+      <c r="BE21">
+        <v>5.6</v>
+      </c>
+      <c r="BF21">
+        <v>19</v>
+      </c>
+      <c r="BG21">
+        <v>5.4</v>
+      </c>
+      <c r="BH21">
+        <v>3.45</v>
+      </c>
+      <c r="BI21">
+        <v>2.42</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>7.8</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>6</v>
+      </c>
+      <c r="BN21">
+        <v>4.8</v>
+      </c>
+      <c r="BO21">
+        <v>4.2</v>
+      </c>
+      <c r="BP21">
+        <v>21</v>
+      </c>
+      <c r="BQ21">
+        <v>4.8</v>
+      </c>
+      <c r="BR21">
+        <v>44</v>
+      </c>
+      <c r="BS21">
+        <v>5.4</v>
+      </c>
+      <c r="BT21">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC21">
-        <v>21</v>
-      </c>
-      <c r="BD21">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE21">
-        <v>10</v>
-      </c>
-      <c r="BF21">
-        <v>17.5</v>
-      </c>
-      <c r="BG21">
-        <v>10</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.23</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.04</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.04</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.45</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.04</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.04</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s">
         <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F22">
+        <v>2.12</v>
+      </c>
+      <c r="G22">
+        <v>2.24</v>
+      </c>
+      <c r="H22">
+        <v>3.9</v>
+      </c>
+      <c r="I22">
+        <v>4.2</v>
+      </c>
+      <c r="J22">
+        <v>3.25</v>
+      </c>
+      <c r="K22">
+        <v>3.55</v>
+      </c>
+      <c r="L22">
+        <v>1.46</v>
+      </c>
+      <c r="M22">
+        <v>1.09</v>
+      </c>
+      <c r="N22">
+        <v>2.98</v>
+      </c>
+      <c r="O22">
+        <v>1.4</v>
+      </c>
+      <c r="P22">
         <v>1.71</v>
       </c>
-      <c r="G22">
-        <v>1.77</v>
-      </c>
-      <c r="H22">
-        <v>5.3</v>
-      </c>
-      <c r="I22">
-        <v>5.8</v>
-      </c>
-      <c r="J22">
-        <v>3.95</v>
-      </c>
-      <c r="K22">
-        <v>4.3</v>
-      </c>
-      <c r="L22">
-        <v>1.4</v>
-      </c>
-      <c r="M22">
-        <v>1.06</v>
-      </c>
-      <c r="N22">
+      <c r="Q22">
+        <v>2.22</v>
+      </c>
+      <c r="R22">
+        <v>1.23</v>
+      </c>
+      <c r="S22">
         <v>3.85</v>
       </c>
-      <c r="O22">
+      <c r="T22">
+        <v>1.94</v>
+      </c>
+      <c r="U22">
+        <v>1.95</v>
+      </c>
+      <c r="V22">
         <v>1.31</v>
       </c>
-      <c r="P22">
-        <v>1.9</v>
-      </c>
-      <c r="Q22">
-        <v>1.86</v>
-      </c>
-      <c r="R22">
-        <v>1.39</v>
-      </c>
-      <c r="S22">
-        <v>3.2</v>
-      </c>
-      <c r="T22">
-        <v>1.88</v>
-      </c>
-      <c r="U22">
-        <v>2.04</v>
-      </c>
-      <c r="V22">
-        <v>1.21</v>
-      </c>
       <c r="W22">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y22">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB22">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC22">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE22">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AF22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH22">
+        <v>21</v>
+      </c>
+      <c r="AI22">
+        <v>75</v>
+      </c>
+      <c r="AJ22">
+        <v>29</v>
+      </c>
+      <c r="AK22">
+        <v>28</v>
+      </c>
+      <c r="AL22">
+        <v>48</v>
+      </c>
+      <c r="AM22">
+        <v>160</v>
+      </c>
+      <c r="AN22">
         <v>22</v>
       </c>
-      <c r="AI22">
-        <v>95</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>970</v>
-      </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP22">
         <v>10</v>
@@ -6038,120 +6044,120 @@
         <v>11</v>
       </c>
       <c r="AR22">
-        <v>2.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="AT22">
         <v>7.4</v>
       </c>
       <c r="AU22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV22">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="AW22">
-        <v>2.08</v>
+        <v>9.6</v>
       </c>
       <c r="AX22">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY22">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22">
-        <v>2.02</v>
+        <v>17.5</v>
       </c>
       <c r="BA22">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="BB22">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC22">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD22">
-        <v>2.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE22">
-        <v>2.12</v>
+        <v>10.5</v>
       </c>
       <c r="BF22">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BG22">
-        <v>2.12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
         <v>90</v>
@@ -6163,67 +6169,67 @@
         <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F23">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="G23">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="H23">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="I23">
-        <v>16</v>
+        <v>5.7</v>
       </c>
       <c r="J23">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="O23">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="P23">
-        <v>2.72</v>
+        <v>1.9</v>
       </c>
       <c r="Q23">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="R23">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="W23">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z23">
         <v>1000</v>
@@ -6235,25 +6241,25 @@
         <v>1000</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD23">
         <v>1000</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ23">
         <v>1000</v>
@@ -6268,374 +6274,374 @@
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="CB23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
         <v>128</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F24">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1.31</v>
       </c>
       <c r="H24">
-        <v>2.52</v>
+        <v>10.5</v>
       </c>
       <c r="I24">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="J24">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="K24">
-        <v>3.75</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>5.8</v>
+      </c>
+      <c r="O24">
+        <v>1.11</v>
+      </c>
+      <c r="P24">
+        <v>2.72</v>
+      </c>
+      <c r="Q24">
+        <v>1.13</v>
+      </c>
+      <c r="R24">
+        <v>1.79</v>
+      </c>
+      <c r="S24">
+        <v>1.94</v>
+      </c>
+      <c r="T24">
+        <v>1.11</v>
+      </c>
+      <c r="U24">
+        <v>1.11</v>
+      </c>
+      <c r="V24">
         <v>1.06</v>
       </c>
-      <c r="N24">
-        <v>4.3</v>
-      </c>
-      <c r="O24">
-        <v>1.27</v>
-      </c>
-      <c r="P24">
-        <v>2.12</v>
-      </c>
-      <c r="Q24">
-        <v>1.74</v>
-      </c>
-      <c r="R24">
-        <v>1.44</v>
-      </c>
-      <c r="S24">
-        <v>3</v>
-      </c>
-      <c r="T24">
-        <v>1.67</v>
-      </c>
-      <c r="U24">
-        <v>2.32</v>
-      </c>
-      <c r="V24">
-        <v>1.59</v>
-      </c>
       <c r="W24">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="X24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B25" t="s">
         <v>90</v>
@@ -6647,232 +6653,232 @@
         <v>129</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F25">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>2.52</v>
+      </c>
+      <c r="I25">
+        <v>2.7</v>
+      </c>
+      <c r="J25">
+        <v>3.55</v>
+      </c>
+      <c r="K25">
+        <v>3.75</v>
+      </c>
+      <c r="L25">
+        <v>1.37</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>4.3</v>
+      </c>
+      <c r="O25">
+        <v>1.27</v>
+      </c>
+      <c r="P25">
+        <v>2.12</v>
+      </c>
+      <c r="Q25">
+        <v>1.76</v>
+      </c>
+      <c r="R25">
+        <v>1.44</v>
+      </c>
+      <c r="S25">
+        <v>3</v>
+      </c>
+      <c r="T25">
+        <v>1.67</v>
+      </c>
+      <c r="U25">
         <v>2.32</v>
       </c>
-      <c r="H25">
-        <v>3.95</v>
-      </c>
-      <c r="I25">
-        <v>4.4</v>
-      </c>
-      <c r="J25">
-        <v>3.05</v>
-      </c>
-      <c r="K25">
-        <v>3.25</v>
-      </c>
-      <c r="L25">
-        <v>1.56</v>
-      </c>
-      <c r="M25">
-        <v>1.12</v>
-      </c>
-      <c r="N25">
-        <v>2.68</v>
-      </c>
-      <c r="O25">
-        <v>1.52</v>
-      </c>
-      <c r="P25">
-        <v>1.57</v>
-      </c>
-      <c r="Q25">
-        <v>2.52</v>
-      </c>
-      <c r="R25">
-        <v>1.21</v>
-      </c>
-      <c r="S25">
-        <v>5.2</v>
-      </c>
-      <c r="T25">
-        <v>2.08</v>
-      </c>
-      <c r="U25">
-        <v>1.79</v>
-      </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="W25">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="X25">
+        <v>21</v>
+      </c>
+      <c r="Y25">
+        <v>13</v>
+      </c>
+      <c r="Z25">
+        <v>19</v>
+      </c>
+      <c r="AA25">
+        <v>46</v>
+      </c>
+      <c r="AB25">
+        <v>14</v>
+      </c>
+      <c r="AC25">
+        <v>8.4</v>
+      </c>
+      <c r="AD25">
+        <v>12.5</v>
+      </c>
+      <c r="AE25">
+        <v>29</v>
+      </c>
+      <c r="AF25">
+        <v>22</v>
+      </c>
+      <c r="AG25">
+        <v>13.5</v>
+      </c>
+      <c r="AH25">
+        <v>16.5</v>
+      </c>
+      <c r="AI25">
+        <v>50</v>
+      </c>
+      <c r="AJ25">
+        <v>55</v>
+      </c>
+      <c r="AK25">
+        <v>34</v>
+      </c>
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>100</v>
+      </c>
+      <c r="AN25">
+        <v>24</v>
+      </c>
+      <c r="AO25">
+        <v>19.5</v>
+      </c>
+      <c r="AP25">
+        <v>15</v>
+      </c>
+      <c r="AQ25">
+        <v>11</v>
+      </c>
+      <c r="AR25">
+        <v>15.5</v>
+      </c>
+      <c r="AS25">
+        <v>8.6</v>
+      </c>
+      <c r="AT25">
+        <v>11.5</v>
+      </c>
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
+        <v>10.5</v>
+      </c>
+      <c r="AW25">
+        <v>7.6</v>
+      </c>
+      <c r="AX25">
+        <v>18</v>
+      </c>
+      <c r="AY25">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB25">
+        <v>30</v>
+      </c>
+      <c r="BC25">
+        <v>8</v>
+      </c>
+      <c r="BD25">
+        <v>8.6</v>
+      </c>
+      <c r="BE25">
+        <v>9.4</v>
+      </c>
+      <c r="BF25">
+        <v>16.5</v>
+      </c>
+      <c r="BG25">
+        <v>16</v>
+      </c>
+      <c r="BH25">
+        <v>3.7</v>
+      </c>
+      <c r="BI25">
+        <v>3.35</v>
+      </c>
+      <c r="BJ25">
+        <v>11</v>
+      </c>
+      <c r="BK25">
+        <v>7.8</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>6.6</v>
+      </c>
+      <c r="BN25">
+        <v>7.2</v>
+      </c>
+      <c r="BO25">
+        <v>5.4</v>
+      </c>
+      <c r="BP25">
+        <v>26</v>
+      </c>
+      <c r="BQ25">
+        <v>5.8</v>
+      </c>
+      <c r="BR25">
+        <v>38</v>
+      </c>
+      <c r="BS25">
+        <v>5.9</v>
+      </c>
+      <c r="BT25">
+        <v>5.7</v>
+      </c>
+      <c r="BU25">
+        <v>5.1</v>
+      </c>
+      <c r="BV25">
+        <v>23</v>
+      </c>
+      <c r="BW25">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y25">
-        <v>11.5</v>
-      </c>
-      <c r="Z25">
-        <v>34</v>
-      </c>
-      <c r="AA25">
-        <v>120</v>
-      </c>
-      <c r="AB25">
-        <v>7.4</v>
-      </c>
-      <c r="AC25">
-        <v>7.4</v>
-      </c>
-      <c r="AD25">
-        <v>19</v>
-      </c>
-      <c r="AE25">
-        <v>80</v>
-      </c>
-      <c r="AF25">
-        <v>13.5</v>
-      </c>
-      <c r="AG25">
-        <v>12</v>
-      </c>
-      <c r="AH25">
-        <v>25</v>
-      </c>
-      <c r="AI25">
-        <v>110</v>
-      </c>
-      <c r="AJ25">
-        <v>38</v>
-      </c>
-      <c r="AK25">
-        <v>38</v>
-      </c>
-      <c r="AL25">
-        <v>70</v>
-      </c>
-      <c r="AM25">
-        <v>220</v>
-      </c>
-      <c r="AN25">
-        <v>38</v>
-      </c>
-      <c r="AO25">
-        <v>120</v>
-      </c>
-      <c r="AP25">
-        <v>8</v>
-      </c>
-      <c r="AQ25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR25">
-        <v>7</v>
-      </c>
-      <c r="AS25">
-        <v>8</v>
-      </c>
-      <c r="AT25">
-        <v>6.4</v>
-      </c>
-      <c r="AU25">
-        <v>6.4</v>
-      </c>
-      <c r="AV25">
-        <v>15.5</v>
-      </c>
-      <c r="AW25">
-        <v>7.8</v>
-      </c>
-      <c r="AX25">
-        <v>11</v>
-      </c>
-      <c r="AY25">
-        <v>10</v>
-      </c>
-      <c r="AZ25">
-        <v>6.6</v>
-      </c>
-      <c r="BA25">
-        <v>8</v>
-      </c>
-      <c r="BB25">
-        <v>7.2</v>
-      </c>
-      <c r="BC25">
-        <v>7.2</v>
-      </c>
-      <c r="BD25">
-        <v>7.6</v>
-      </c>
-      <c r="BE25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF25">
-        <v>21</v>
-      </c>
-      <c r="BG25">
-        <v>8</v>
-      </c>
-      <c r="BH25">
-        <v>2.78</v>
-      </c>
-      <c r="BI25">
-        <v>2.54</v>
-      </c>
-      <c r="BJ25">
-        <v>11.5</v>
-      </c>
-      <c r="BK25">
-        <v>6.6</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>15</v>
-      </c>
-      <c r="BN25">
-        <v>4.8</v>
-      </c>
-      <c r="BO25">
-        <v>4.3</v>
-      </c>
-      <c r="BP25">
-        <v>28</v>
-      </c>
-      <c r="BQ25">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR25">
-        <v>60</v>
-      </c>
-      <c r="BS25">
-        <v>11.5</v>
-      </c>
-      <c r="BT25">
-        <v>7.2</v>
-      </c>
-      <c r="BU25">
-        <v>5</v>
-      </c>
-      <c r="BV25">
-        <v>55</v>
-      </c>
-      <c r="BW25">
-        <v>11.5</v>
-      </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY25">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="BZ25">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="CA25">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="CB25" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6889,214 +6895,214 @@
         <v>130</v>
       </c>
       <c r="E26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F26">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="G26">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H26">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="I26">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="L26">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="N26">
-        <v>3.65</v>
+        <v>2.68</v>
       </c>
       <c r="O26">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="P26">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="Q26">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="R26">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S26">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="T26">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="U26">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="X26">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y26">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
+        <v>34</v>
+      </c>
+      <c r="AA26">
+        <v>120</v>
+      </c>
+      <c r="AB26">
+        <v>7.4</v>
+      </c>
+      <c r="AC26">
+        <v>7.4</v>
+      </c>
+      <c r="AD26">
+        <v>19</v>
+      </c>
+      <c r="AE26">
+        <v>80</v>
+      </c>
+      <c r="AF26">
+        <v>13.5</v>
+      </c>
+      <c r="AG26">
+        <v>12</v>
+      </c>
+      <c r="AH26">
+        <v>25</v>
+      </c>
+      <c r="AI26">
+        <v>110</v>
+      </c>
+      <c r="AJ26">
+        <v>38</v>
+      </c>
+      <c r="AK26">
+        <v>38</v>
+      </c>
+      <c r="AL26">
+        <v>70</v>
+      </c>
+      <c r="AM26">
+        <v>220</v>
+      </c>
+      <c r="AN26">
+        <v>38</v>
+      </c>
+      <c r="AO26">
+        <v>120</v>
+      </c>
+      <c r="AP26">
+        <v>8</v>
+      </c>
+      <c r="AQ26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR26">
+        <v>7</v>
+      </c>
+      <c r="AS26">
+        <v>8</v>
+      </c>
+      <c r="AT26">
+        <v>6.4</v>
+      </c>
+      <c r="AU26">
+        <v>6.4</v>
+      </c>
+      <c r="AV26">
+        <v>15.5</v>
+      </c>
+      <c r="AW26">
+        <v>7.8</v>
+      </c>
+      <c r="AX26">
+        <v>11</v>
+      </c>
+      <c r="AY26">
+        <v>10</v>
+      </c>
+      <c r="AZ26">
+        <v>6.6</v>
+      </c>
+      <c r="BA26">
+        <v>8</v>
+      </c>
+      <c r="BB26">
+        <v>7.2</v>
+      </c>
+      <c r="BC26">
+        <v>7.2</v>
+      </c>
+      <c r="BD26">
+        <v>7.6</v>
+      </c>
+      <c r="BE26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF26">
+        <v>21</v>
+      </c>
+      <c r="BG26">
+        <v>8</v>
+      </c>
+      <c r="BH26">
+        <v>2.78</v>
+      </c>
+      <c r="BI26">
+        <v>2.54</v>
+      </c>
+      <c r="BJ26">
+        <v>11.5</v>
+      </c>
+      <c r="BK26">
+        <v>6.6</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>15</v>
+      </c>
+      <c r="BN26">
+        <v>4.8</v>
+      </c>
+      <c r="BO26">
+        <v>4.3</v>
+      </c>
+      <c r="BP26">
         <v>28</v>
       </c>
-      <c r="AA26">
-        <v>75</v>
-      </c>
-      <c r="AB26">
-        <v>9.4</v>
-      </c>
-      <c r="AC26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD26">
-        <v>16</v>
-      </c>
-      <c r="AE26">
-        <v>48</v>
-      </c>
-      <c r="AF26">
-        <v>14</v>
-      </c>
-      <c r="AG26">
-        <v>11</v>
-      </c>
-      <c r="AH26">
-        <v>18.5</v>
-      </c>
-      <c r="AI26">
-        <v>80</v>
-      </c>
-      <c r="AJ26">
-        <v>28</v>
-      </c>
-      <c r="AK26">
-        <v>24</v>
-      </c>
-      <c r="AL26">
-        <v>40</v>
-      </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>18</v>
-      </c>
-      <c r="AO26">
-        <v>50</v>
-      </c>
-      <c r="AP26">
-        <v>12</v>
-      </c>
-      <c r="AQ26">
-        <v>12</v>
-      </c>
-      <c r="AR26">
-        <v>8</v>
-      </c>
-      <c r="AS26">
-        <v>10</v>
-      </c>
-      <c r="AT26">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU26">
-        <v>7</v>
-      </c>
-      <c r="AV26">
-        <v>13.5</v>
-      </c>
-      <c r="AW26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX26">
-        <v>12</v>
-      </c>
-      <c r="AY26">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26">
-        <v>16</v>
-      </c>
-      <c r="BA26">
-        <v>10</v>
-      </c>
-      <c r="BB26">
-        <v>8</v>
-      </c>
-      <c r="BC26">
-        <v>21</v>
-      </c>
-      <c r="BD26">
+      <c r="BQ26">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE26">
-        <v>11</v>
-      </c>
-      <c r="BF26">
-        <v>15.5</v>
-      </c>
-      <c r="BG26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH26">
-        <v>3.3</v>
-      </c>
-      <c r="BI26">
-        <v>3.05</v>
-      </c>
-      <c r="BJ26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK26">
-        <v>6.4</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>16.5</v>
-      </c>
-      <c r="BN26">
-        <v>4.9</v>
-      </c>
-      <c r="BO26">
-        <v>4.4</v>
-      </c>
-      <c r="BP26">
-        <v>16</v>
-      </c>
-      <c r="BQ26">
-        <v>8.6</v>
-      </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS26">
         <v>11.5</v>
       </c>
       <c r="BT26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU26">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV26">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BW26">
         <v>11.5</v>
@@ -7105,16 +7111,16 @@
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA26">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7131,232 +7137,474 @@
         <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F27">
-        <v>4.2</v>
+        <v>2.18</v>
       </c>
       <c r="G27">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="H27">
-        <v>1.97</v>
+        <v>3.6</v>
       </c>
       <c r="I27">
-        <v>2.08</v>
+        <v>3.9</v>
       </c>
       <c r="J27">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M27">
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O27">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P27">
+        <v>1.86</v>
+      </c>
+      <c r="Q27">
+        <v>2.04</v>
+      </c>
+      <c r="R27">
+        <v>1.34</v>
+      </c>
+      <c r="S27">
+        <v>3.65</v>
+      </c>
+      <c r="T27">
+        <v>1.82</v>
+      </c>
+      <c r="U27">
+        <v>2.08</v>
+      </c>
+      <c r="V27">
+        <v>1.35</v>
+      </c>
+      <c r="W27">
+        <v>1.77</v>
+      </c>
+      <c r="X27">
+        <v>13.5</v>
+      </c>
+      <c r="Y27">
+        <v>13</v>
+      </c>
+      <c r="Z27">
+        <v>26</v>
+      </c>
+      <c r="AA27">
+        <v>95</v>
+      </c>
+      <c r="AB27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27">
+        <v>7.8</v>
+      </c>
+      <c r="AD27">
+        <v>16</v>
+      </c>
+      <c r="AE27">
+        <v>50</v>
+      </c>
+      <c r="AF27">
+        <v>14</v>
+      </c>
+      <c r="AG27">
+        <v>11.5</v>
+      </c>
+      <c r="AH27">
+        <v>18.5</v>
+      </c>
+      <c r="AI27">
+        <v>60</v>
+      </c>
+      <c r="AJ27">
+        <v>36</v>
+      </c>
+      <c r="AK27">
+        <v>25</v>
+      </c>
+      <c r="AL27">
+        <v>40</v>
+      </c>
+      <c r="AM27">
+        <v>120</v>
+      </c>
+      <c r="AN27">
+        <v>21</v>
+      </c>
+      <c r="AO27">
+        <v>55</v>
+      </c>
+      <c r="AP27">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27">
+        <v>11.5</v>
+      </c>
+      <c r="AR27">
+        <v>23</v>
+      </c>
+      <c r="AS27">
+        <v>10.5</v>
+      </c>
+      <c r="AT27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27">
+        <v>7</v>
+      </c>
+      <c r="AV27">
+        <v>14</v>
+      </c>
+      <c r="AW27">
+        <v>9.6</v>
+      </c>
+      <c r="AX27">
+        <v>12</v>
+      </c>
+      <c r="AY27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ27">
+        <v>16</v>
+      </c>
+      <c r="BA27">
+        <v>10</v>
+      </c>
+      <c r="BB27">
+        <v>9</v>
+      </c>
+      <c r="BC27">
+        <v>8</v>
+      </c>
+      <c r="BD27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE27">
+        <v>10.5</v>
+      </c>
+      <c r="BF27">
+        <v>15.5</v>
+      </c>
+      <c r="BG27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH27">
+        <v>3.25</v>
+      </c>
+      <c r="BI27">
+        <v>3.05</v>
+      </c>
+      <c r="BJ27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK27">
+        <v>6.4</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>17</v>
+      </c>
+      <c r="BN27">
+        <v>4.9</v>
+      </c>
+      <c r="BO27">
+        <v>4.4</v>
+      </c>
+      <c r="BP27">
+        <v>16</v>
+      </c>
+      <c r="BQ27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR27">
+        <v>32</v>
+      </c>
+      <c r="BS27">
+        <v>12</v>
+      </c>
+      <c r="BT27">
+        <v>7</v>
+      </c>
+      <c r="BU27">
+        <v>5.1</v>
+      </c>
+      <c r="BV27">
+        <v>32</v>
+      </c>
+      <c r="BW27">
+        <v>12</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>13</v>
+      </c>
+      <c r="BZ27">
+        <v>28</v>
+      </c>
+      <c r="CA27">
+        <v>11.5</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28">
+        <v>4.3</v>
+      </c>
+      <c r="G28">
+        <v>4.9</v>
+      </c>
+      <c r="H28">
+        <v>1.9</v>
+      </c>
+      <c r="I28">
+        <v>2.04</v>
+      </c>
+      <c r="J28">
+        <v>3.6</v>
+      </c>
+      <c r="K28">
+        <v>3.9</v>
+      </c>
+      <c r="L28">
+        <v>1.39</v>
+      </c>
+      <c r="M28">
+        <v>1.08</v>
+      </c>
+      <c r="N28">
+        <v>3.3</v>
+      </c>
+      <c r="O28">
+        <v>1.37</v>
+      </c>
+      <c r="P28">
         <v>1.8</v>
       </c>
-      <c r="Q27">
+      <c r="Q28">
         <v>2.06</v>
       </c>
-      <c r="R27">
+      <c r="R28">
         <v>1.31</v>
       </c>
-      <c r="S27">
-        <v>3.75</v>
-      </c>
-      <c r="T27">
-        <v>1.9</v>
-      </c>
-      <c r="U27">
-        <v>2</v>
-      </c>
-      <c r="V27">
-        <v>1.93</v>
-      </c>
-      <c r="W27">
+      <c r="S28">
+        <v>3.7</v>
+      </c>
+      <c r="T28">
+        <v>1.89</v>
+      </c>
+      <c r="U28">
+        <v>1.96</v>
+      </c>
+      <c r="V28">
+        <v>1.96</v>
+      </c>
+      <c r="W28">
         <v>1.27</v>
       </c>
-      <c r="X27">
-        <v>14.5</v>
-      </c>
-      <c r="Y27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z27">
-        <v>14</v>
-      </c>
-      <c r="AA27">
+      <c r="X28">
+        <v>15</v>
+      </c>
+      <c r="Y28">
+        <v>8.6</v>
+      </c>
+      <c r="Z28">
+        <v>13.5</v>
+      </c>
+      <c r="AA28">
         <v>25</v>
       </c>
-      <c r="AB27">
-        <v>16.5</v>
-      </c>
-      <c r="AC27">
+      <c r="AB28">
+        <v>17</v>
+      </c>
+      <c r="AC28">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <v>12.5</v>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <v>24</v>
       </c>
-      <c r="AF27">
+      <c r="AF28">
         <v>38</v>
       </c>
-      <c r="AG27">
-        <v>21</v>
-      </c>
-      <c r="AH27">
-        <v>23</v>
-      </c>
-      <c r="AI27">
+      <c r="AG28">
+        <v>19</v>
+      </c>
+      <c r="AH28">
+        <v>24</v>
+      </c>
+      <c r="AI28">
         <v>44</v>
       </c>
-      <c r="AJ27">
+      <c r="AJ28">
         <v>120</v>
       </c>
-      <c r="AK27">
+      <c r="AK28">
         <v>70</v>
       </c>
-      <c r="AL27">
+      <c r="AL28">
         <v>80</v>
       </c>
-      <c r="AM27">
+      <c r="AM28">
         <v>140</v>
       </c>
-      <c r="AN27">
+      <c r="AN28">
         <v>85</v>
       </c>
-      <c r="AO27">
+      <c r="AO28">
+        <v>18</v>
+      </c>
+      <c r="AP28">
+        <v>11</v>
+      </c>
+      <c r="AQ28">
+        <v>7.2</v>
+      </c>
+      <c r="AR28">
+        <v>10</v>
+      </c>
+      <c r="AS28">
         <v>19.5</v>
       </c>
-      <c r="AP27">
-        <v>11</v>
-      </c>
-      <c r="AQ27">
-        <v>7.4</v>
-      </c>
-      <c r="AR27">
-        <v>10.5</v>
-      </c>
-      <c r="AS27">
-        <v>21</v>
-      </c>
-      <c r="AT27">
+      <c r="AT28">
         <v>12.5</v>
       </c>
-      <c r="AU27">
+      <c r="AU28">
         <v>7.2</v>
       </c>
-      <c r="AV27">
-        <v>9.4</v>
-      </c>
-      <c r="AW27">
-        <v>20</v>
-      </c>
-      <c r="AX27">
+      <c r="AV28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW28">
+        <v>19</v>
+      </c>
+      <c r="AX28">
         <v>6</v>
       </c>
-      <c r="AY27">
+      <c r="AY28">
         <v>15.5</v>
       </c>
-      <c r="AZ27">
+      <c r="AZ28">
         <v>17.5</v>
       </c>
-      <c r="BA27">
+      <c r="BA28">
         <v>6.2</v>
       </c>
-      <c r="BB27">
-        <v>6</v>
-      </c>
-      <c r="BC27">
+      <c r="BB28">
+        <v>6.4</v>
+      </c>
+      <c r="BC28">
         <v>6.6</v>
       </c>
-      <c r="BD27">
+      <c r="BD28">
         <v>6.6</v>
       </c>
-      <c r="BE27">
-        <v>6</v>
-      </c>
-      <c r="BF27">
+      <c r="BE28">
+        <v>6.4</v>
+      </c>
+      <c r="BF28">
         <v>6.6</v>
       </c>
-      <c r="BG27">
-        <v>14.5</v>
-      </c>
-      <c r="BH27">
+      <c r="BG28">
+        <v>13.5</v>
+      </c>
+      <c r="BH28">
         <v>3.6</v>
       </c>
-      <c r="BI27">
-        <v>2.66</v>
-      </c>
-      <c r="BJ27">
+      <c r="BI28">
+        <v>2.68</v>
+      </c>
+      <c r="BJ28">
         <v>12</v>
       </c>
-      <c r="BK27">
+      <c r="BK28">
         <v>3.9</v>
       </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
         <v>5.6</v>
       </c>
-      <c r="BN27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO27">
-        <v>6</v>
-      </c>
-      <c r="BP27">
-        <v>46</v>
-      </c>
-      <c r="BQ27">
+      <c r="BN28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO28">
+        <v>3.6</v>
+      </c>
+      <c r="BP28">
+        <v>48</v>
+      </c>
+      <c r="BQ28">
+        <v>5.2</v>
+      </c>
+      <c r="BR28">
+        <v>65</v>
+      </c>
+      <c r="BS28">
+        <v>5.3</v>
+      </c>
+      <c r="BT28">
         <v>5.1</v>
       </c>
-      <c r="BR27">
-        <v>60</v>
-      </c>
-      <c r="BS27">
-        <v>5.2</v>
-      </c>
-      <c r="BT27">
-        <v>5.2</v>
-      </c>
-      <c r="BU27">
-        <v>3.7</v>
-      </c>
-      <c r="BV27">
-        <v>17</v>
-      </c>
-      <c r="BW27">
-        <v>4.3</v>
-      </c>
-      <c r="BX27">
+      <c r="BU28">
+        <v>3.9</v>
+      </c>
+      <c r="BV28">
+        <v>16</v>
+      </c>
+      <c r="BW28">
+        <v>4.2</v>
+      </c>
+      <c r="BX28">
         <v>36</v>
       </c>
-      <c r="BY27">
+      <c r="BY28">
+        <v>5</v>
+      </c>
+      <c r="BZ28">
+        <v>32</v>
+      </c>
+      <c r="CA28">
         <v>4.9</v>
       </c>
-      <c r="BZ27">
-        <v>34</v>
-      </c>
-      <c r="CA27">
-        <v>4.9</v>
-      </c>
-      <c r="CB27" t="s">
-        <v>158</v>
+      <c r="CB28" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -496,7 +496,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 06:16:18</t>
+    <t>2026-10-06 08:27:28</t>
   </si>
 </sst>
 </file>
@@ -1090,16 +1090,16 @@
         <v>133</v>
       </c>
       <c r="F2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1114,46 +1114,46 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
+        <v>1.79</v>
+      </c>
+      <c r="S2">
+        <v>2.22</v>
+      </c>
+      <c r="T2">
+        <v>1.47</v>
+      </c>
+      <c r="U2">
+        <v>3</v>
+      </c>
+      <c r="V2">
         <v>1.76</v>
       </c>
-      <c r="S2">
-        <v>2.24</v>
-      </c>
-      <c r="T2">
-        <v>1.48</v>
-      </c>
-      <c r="U2">
-        <v>2.94</v>
-      </c>
-      <c r="V2">
-        <v>1.75</v>
-      </c>
       <c r="W2">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X2">
         <v>28</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>20</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB2">
         <v>21</v>
@@ -1165,16 +1165,16 @@
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AG2">
         <v>14</v>
       </c>
       <c r="AH2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI2">
         <v>25</v>
@@ -1183,7 +1183,7 @@
         <v>55</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL2">
         <v>32</v>
@@ -1192,13 +1192,13 @@
         <v>50</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AO2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
         <v>15.5</v>
@@ -1210,106 +1210,106 @@
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU2">
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
         <v>22</v>
       </c>
       <c r="BB2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BC2">
         <v>25</v>
       </c>
       <c r="BD2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BJ2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>2.78</v>
       </c>
       <c r="BL2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>3.35</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BR2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="BT2">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.3</v>
+        <v>2.42</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>7.4</v>
+        <v>3.35</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BZ2">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="CB2" t="s">
         <v>160</v>
@@ -1332,7 +1332,7 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -1341,19 +1341,19 @@
         <v>1.34</v>
       </c>
       <c r="I3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="K3">
         <v>5.9</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>4.1</v>
@@ -1362,10 +1362,10 @@
         <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R3">
         <v>1.41</v>
@@ -1374,184 +1374,184 @@
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V3">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="W3">
         <v>1.08</v>
       </c>
       <c r="X3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AA3">
         <v>10</v>
       </c>
       <c r="AB3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AC3">
         <v>13</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF3">
         <v>120</v>
       </c>
       <c r="AG3">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AH3">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AK3">
         <v>250</v>
       </c>
       <c r="AL3">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AM3">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN3">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="AO3">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP3">
         <v>14.5</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT3">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AU3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV3">
         <v>9.6</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AZ3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BA3">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BB3">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC3">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD3">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE3">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>1.34</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.25</v>
+        <v>1.33</v>
       </c>
       <c r="BV3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BX3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>160</v>
@@ -1577,7 +1577,7 @@
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H4">
         <v>3.3</v>
@@ -1586,10 +1586,10 @@
         <v>3.45</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -1613,13 +1613,13 @@
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -1628,172 +1628,172 @@
         <v>1.68</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="Z4">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="AA4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AD4">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>95</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>3.35</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="AS4">
-        <v>26</v>
+        <v>17.5</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>2.78</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>2.56</v>
       </c>
       <c r="AV4">
-        <v>13</v>
+        <v>1.19</v>
       </c>
       <c r="AW4">
-        <v>7.8</v>
+        <v>1.21</v>
       </c>
       <c r="AX4">
-        <v>11.5</v>
+        <v>1.2</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>1.21</v>
       </c>
       <c r="BB4">
-        <v>7.2</v>
+        <v>1.21</v>
       </c>
       <c r="BC4">
-        <v>17.5</v>
+        <v>1.2</v>
       </c>
       <c r="BD4">
-        <v>38</v>
+        <v>1.21</v>
       </c>
       <c r="BE4">
-        <v>8.4</v>
+        <v>1.21</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>1.21</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>1.21</v>
       </c>
       <c r="BH4">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>160</v>
@@ -1816,58 +1816,58 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.69</v>
+        <v>990</v>
       </c>
       <c r="H5">
         <v>1.1</v>
       </c>
       <c r="I5">
-        <v>17.5</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="K5">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
-        <v>1.06</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>1.12</v>
+        <v>1.59</v>
       </c>
       <c r="V5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W5">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1924,13 +1924,13 @@
         <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS5">
         <v>1.01</v>
@@ -1942,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
@@ -1954,31 +1954,31 @@
         <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BE5">
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
         <v>1.04</v>
@@ -1987,55 +1987,55 @@
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>160</v>
@@ -2058,52 +2058,52 @@
         <v>137</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G6">
         <v>3.1</v>
       </c>
       <c r="H6">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
       <c r="K6">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>1.94</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R6">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V6">
         <v>1.43</v>
@@ -2300,31 +2300,31 @@
         <v>138</v>
       </c>
       <c r="F7">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="G7">
-        <v>14.5</v>
+        <v>990</v>
       </c>
       <c r="H7">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="I7">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
         <v>1.21</v>
@@ -2333,25 +2333,25 @@
         <v>2.06</v>
       </c>
       <c r="Q7">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="S7">
-        <v>2.28</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2542,226 +2542,226 @@
         <v>139</v>
       </c>
       <c r="F8">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>1.12</v>
       </c>
       <c r="K8">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.07</v>
       </c>
       <c r="N8">
-        <v>3.35</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.12</v>
       </c>
       <c r="Q8">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="R8">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="S8">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U8">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W8">
         <v>1.31</v>
       </c>
       <c r="X8">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="AQ8">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="AX8">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="AZ8">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>4.9</v>
+        <v>1.02</v>
       </c>
       <c r="BE8">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>160</v>
@@ -2784,19 +2784,19 @@
         <v>140</v>
       </c>
       <c r="F9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G9">
         <v>990</v>
       </c>
       <c r="H9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I9">
         <v>990</v>
       </c>
       <c r="J9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="K9">
         <v>85</v>
@@ -2832,10 +2832,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3026,7 +3026,7 @@
         <v>141</v>
       </c>
       <c r="F10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G10">
         <v>990</v>
@@ -3038,7 +3038,7 @@
         <v>990</v>
       </c>
       <c r="J10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="K10">
         <v>85</v>
@@ -3074,10 +3074,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3268,46 +3268,46 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>2.66</v>
+        <v>1.12</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>1.12</v>
       </c>
       <c r="I11">
-        <v>2.64</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>1.12</v>
       </c>
       <c r="K11">
-        <v>6.8</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>1.68</v>
       </c>
       <c r="O11">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>1.69</v>
       </c>
       <c r="Q11">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="R11">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="S11">
-        <v>2.08</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3316,70 +3316,70 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
         <v>1.01</v>
@@ -3391,25 +3391,25 @@
         <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
         <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>1.01</v>
@@ -3418,7 +3418,7 @@
         <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
@@ -3427,7 +3427,7 @@
         <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3519,217 +3519,217 @@
         <v>1.82</v>
       </c>
       <c r="I12">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M12">
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W12">
         <v>1.26</v>
       </c>
       <c r="X12">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y12">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z12">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA12">
-        <v>21</v>
+        <v>640</v>
       </c>
       <c r="AB12">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC12">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD12">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AF12">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AG12">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH12">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="AJ12">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AK12">
-        <v>70</v>
+        <v>320</v>
       </c>
       <c r="AL12">
+        <v>330</v>
+      </c>
+      <c r="AM12">
+        <v>100</v>
+      </c>
+      <c r="AN12">
         <v>65</v>
       </c>
-      <c r="AM12">
-        <v>110</v>
-      </c>
-      <c r="AN12">
-        <v>70</v>
-      </c>
       <c r="AO12">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP12">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR12">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS12">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT12">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU12">
+        <v>6.8</v>
+      </c>
+      <c r="AV12">
         <v>8</v>
       </c>
-      <c r="AV12">
-        <v>9</v>
-      </c>
       <c r="AW12">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AX12">
-        <v>16</v>
+        <v>1.89</v>
       </c>
       <c r="AY12">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="BA12">
-        <v>15</v>
+        <v>1.88</v>
       </c>
       <c r="BB12">
-        <v>10.5</v>
+        <v>1.95</v>
       </c>
       <c r="BC12">
-        <v>32</v>
+        <v>1.93</v>
       </c>
       <c r="BD12">
-        <v>34</v>
+        <v>1.93</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>1.95</v>
       </c>
       <c r="BF12">
-        <v>32</v>
+        <v>1.93</v>
       </c>
       <c r="BG12">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BH12">
+        <v>4.5</v>
+      </c>
+      <c r="BI12">
+        <v>3.1</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>2.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>2.36</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.96</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>2.36</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>2.36</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
         <v>3.75</v>
       </c>
-      <c r="BI12">
-        <v>3.4</v>
-      </c>
-      <c r="BJ12">
-        <v>11.5</v>
-      </c>
-      <c r="BK12">
-        <v>8.4</v>
-      </c>
-      <c r="BL12">
-        <v>130</v>
-      </c>
-      <c r="BM12">
-        <v>6.4</v>
-      </c>
-      <c r="BN12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO12">
-        <v>7</v>
-      </c>
-      <c r="BP12">
-        <v>46</v>
-      </c>
-      <c r="BQ12">
-        <v>5.9</v>
-      </c>
-      <c r="BR12">
-        <v>55</v>
-      </c>
-      <c r="BS12">
-        <v>6</v>
-      </c>
-      <c r="BT12">
-        <v>4.7</v>
-      </c>
-      <c r="BU12">
-        <v>4.1</v>
-      </c>
       <c r="BV12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>7.2</v>
+        <v>2.36</v>
       </c>
       <c r="BX12">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="BZ12">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>2.36</v>
       </c>
       <c r="CB12" t="s">
         <v>160</v>
@@ -3752,184 +3752,184 @@
         <v>144</v>
       </c>
       <c r="F13">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="H13">
-        <v>6.8</v>
+        <v>1.12</v>
       </c>
       <c r="I13">
-        <v>8.6</v>
+        <v>990</v>
       </c>
       <c r="J13">
-        <v>3.3</v>
+        <v>1.12</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.52</v>
+        <v>1.51</v>
       </c>
       <c r="O13">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="P13">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="Q13">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>5.4</v>
+        <v>2.46</v>
       </c>
       <c r="T13">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="U13">
         <v>1.5</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="W13">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
         <v>1000</v>
       </c>
       <c r="BI13">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
         <v>1000</v>
@@ -3947,13 +3947,13 @@
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
@@ -3971,7 +3971,7 @@
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>160</v>
@@ -3994,19 +3994,19 @@
         <v>145</v>
       </c>
       <c r="F14">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="G14">
-        <v>2.66</v>
+        <v>600</v>
       </c>
       <c r="H14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I14">
-        <v>4.4</v>
+        <v>870</v>
       </c>
       <c r="J14">
-        <v>2.88</v>
+        <v>1.12</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4236,226 +4236,226 @@
         <v>146</v>
       </c>
       <c r="F15">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="G15">
         <v>1.43</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="I15">
-        <v>15.5</v>
+        <v>990</v>
       </c>
       <c r="J15">
-        <v>4.6</v>
+        <v>1.12</v>
       </c>
       <c r="K15">
-        <v>5.9</v>
+        <v>950</v>
       </c>
       <c r="L15">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.81</v>
+        <v>1.09</v>
       </c>
       <c r="Q15">
-        <v>2.02</v>
+        <v>1.34</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="S15">
-        <v>3.65</v>
+        <v>1.05</v>
       </c>
       <c r="T15">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="U15">
         <v>1.53</v>
       </c>
       <c r="V15">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
         <v>3.3</v>
       </c>
       <c r="X15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>160</v>
@@ -4478,226 +4478,226 @@
         <v>147</v>
       </c>
       <c r="F16">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="G16">
-        <v>2.12</v>
+        <v>600</v>
       </c>
       <c r="H16">
-        <v>3.85</v>
+        <v>1.12</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J16">
-        <v>3.55</v>
+        <v>1.12</v>
       </c>
       <c r="K16">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.08</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="O16">
         <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="S16">
-        <v>3.35</v>
+        <v>1.05</v>
       </c>
       <c r="T16">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="X16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>160</v>
@@ -4720,166 +4720,166 @@
         <v>148</v>
       </c>
       <c r="F17">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G17">
-        <v>4.4</v>
+        <v>600</v>
       </c>
       <c r="H17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I17">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="J17">
-        <v>3.15</v>
+        <v>1.12</v>
       </c>
       <c r="K17">
-        <v>3.45</v>
+        <v>500</v>
       </c>
       <c r="L17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N17">
-        <v>2.52</v>
+        <v>1.13</v>
       </c>
       <c r="O17">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P17">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="R17">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="S17">
-        <v>2.82</v>
+        <v>1.05</v>
       </c>
       <c r="T17">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W17">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4962,7 +4962,7 @@
         <v>149</v>
       </c>
       <c r="F18">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G18">
         <v>1.92</v>
@@ -4974,7 +4974,7 @@
         <v>4.7</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
         <v>4.1</v>
@@ -4992,13 +4992,13 @@
         <v>1.26</v>
       </c>
       <c r="P18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="R18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S18">
         <v>3.05</v>
@@ -5016,172 +5016,172 @@
         <v>2.08</v>
       </c>
       <c r="X18">
+        <v>970</v>
+      </c>
+      <c r="Y18">
         <v>22</v>
-      </c>
-      <c r="Y18">
-        <v>18.5</v>
       </c>
       <c r="Z18">
         <v>40</v>
       </c>
       <c r="AA18">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AC18">
         <v>9</v>
       </c>
       <c r="AD18">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG18">
         <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>25</v>
+      </c>
+      <c r="AK18">
+        <v>23</v>
+      </c>
+      <c r="AL18">
+        <v>38</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>12.5</v>
+      </c>
+      <c r="AO18">
         <v>65</v>
       </c>
-      <c r="AJ18">
-        <v>26</v>
-      </c>
-      <c r="AK18">
-        <v>24</v>
-      </c>
-      <c r="AL18">
-        <v>40</v>
-      </c>
-      <c r="AM18">
-        <v>110</v>
-      </c>
-      <c r="AN18">
-        <v>11</v>
-      </c>
-      <c r="AO18">
-        <v>60</v>
-      </c>
       <c r="AP18">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AQ18">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR18">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AS18">
+        <v>4.8</v>
+      </c>
+      <c r="AT18">
+        <v>8.4</v>
+      </c>
+      <c r="AU18">
         <v>7.6</v>
       </c>
-      <c r="AT18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18">
-        <v>8</v>
-      </c>
       <c r="AV18">
+        <v>14.5</v>
+      </c>
+      <c r="AW18">
+        <v>4.8</v>
+      </c>
+      <c r="AX18">
+        <v>9.4</v>
+      </c>
+      <c r="AY18">
+        <v>8.6</v>
+      </c>
+      <c r="AZ18">
         <v>15</v>
       </c>
-      <c r="AW18">
-        <v>7.4</v>
-      </c>
-      <c r="AX18">
-        <v>10.5</v>
-      </c>
-      <c r="AY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18">
-        <v>15.5</v>
-      </c>
       <c r="BA18">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB18">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="BC18">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD18">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BE18">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF18">
         <v>9.800000000000001</v>
       </c>
       <c r="BG18">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH18">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>1.89</v>
       </c>
       <c r="BP18">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="BR18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="BV18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>160</v>
@@ -5207,67 +5207,67 @@
         <v>2.32</v>
       </c>
       <c r="G19">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I19">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J19">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K19">
         <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M19">
         <v>1.09</v>
       </c>
       <c r="N19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P19">
         <v>1.76</v>
       </c>
       <c r="Q19">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19">
         <v>4.1</v>
       </c>
       <c r="T19">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V19">
         <v>1.38</v>
       </c>
       <c r="W19">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z19">
         <v>25</v>
       </c>
       <c r="AA19">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
         <v>9.199999999999999</v>
@@ -5276,154 +5276,154 @@
         <v>7.6</v>
       </c>
       <c r="AD19">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE19">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="AF19">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG19">
         <v>12</v>
       </c>
       <c r="AH19">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI19">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK19">
+        <v>50</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>9.4</v>
+      </c>
+      <c r="AQ19">
+        <v>9.4</v>
+      </c>
+      <c r="AR19">
+        <v>6.2</v>
+      </c>
+      <c r="AS19">
+        <v>23</v>
+      </c>
+      <c r="AT19">
+        <v>8</v>
+      </c>
+      <c r="AU19">
+        <v>6.8</v>
+      </c>
+      <c r="AV19">
+        <v>12</v>
+      </c>
+      <c r="AW19">
+        <v>13.5</v>
+      </c>
+      <c r="AX19">
+        <v>12</v>
+      </c>
+      <c r="AY19">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19">
+        <v>17</v>
+      </c>
+      <c r="BA19">
         <v>28</v>
       </c>
-      <c r="AL19">
-        <v>60</v>
-      </c>
-      <c r="AM19">
-        <v>150</v>
-      </c>
-      <c r="AN19">
-        <v>23</v>
-      </c>
-      <c r="AO19">
-        <v>55</v>
-      </c>
-      <c r="AP19">
-        <v>10</v>
-      </c>
-      <c r="AQ19">
-        <v>10.5</v>
-      </c>
-      <c r="AR19">
-        <v>21</v>
-      </c>
-      <c r="AS19">
-        <v>10</v>
-      </c>
-      <c r="AT19">
+      <c r="BB19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC19">
         <v>8.4</v>
       </c>
-      <c r="AU19">
-        <v>7</v>
-      </c>
-      <c r="AV19">
-        <v>13.5</v>
-      </c>
-      <c r="AW19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX19">
-        <v>12.5</v>
-      </c>
-      <c r="AY19">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19">
-        <v>17.5</v>
-      </c>
-      <c r="BA19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB19">
-        <v>25</v>
-      </c>
-      <c r="BC19">
-        <v>19</v>
-      </c>
       <c r="BD19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="BE19">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="BF19">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="BG19">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH19">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI19">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>2.94</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="BP19">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="BR19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="BV19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>160</v>
@@ -5446,7 +5446,7 @@
         <v>151</v>
       </c>
       <c r="F20">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G20">
         <v>2.5</v>
@@ -5458,25 +5458,25 @@
         <v>3.3</v>
       </c>
       <c r="J20">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M20">
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O20">
         <v>1.31</v>
       </c>
       <c r="P20">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5485,13 +5485,13 @@
         <v>1.37</v>
       </c>
       <c r="S20">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V20">
         <v>1.43</v>
@@ -5503,169 +5503,169 @@
         <v>15</v>
       </c>
       <c r="Y20">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z20">
         <v>24</v>
       </c>
       <c r="AA20">
+        <v>70</v>
+      </c>
+      <c r="AB20">
+        <v>11.5</v>
+      </c>
+      <c r="AC20">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>14.5</v>
+      </c>
+      <c r="AE20">
+        <v>42</v>
+      </c>
+      <c r="AF20">
+        <v>970</v>
+      </c>
+      <c r="AG20">
+        <v>13</v>
+      </c>
+      <c r="AH20">
+        <v>970</v>
+      </c>
+      <c r="AI20">
         <v>60</v>
       </c>
-      <c r="AB20">
-        <v>11</v>
-      </c>
-      <c r="AC20">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD20">
+      <c r="AJ20">
+        <v>40</v>
+      </c>
+      <c r="AK20">
+        <v>36</v>
+      </c>
+      <c r="AL20">
+        <v>50</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>970</v>
+      </c>
+      <c r="AO20">
+        <v>34</v>
+      </c>
+      <c r="AP20">
+        <v>12.5</v>
+      </c>
+      <c r="AQ20">
+        <v>10</v>
+      </c>
+      <c r="AR20">
+        <v>6.2</v>
+      </c>
+      <c r="AS20">
         <v>14</v>
       </c>
-      <c r="AE20">
-        <v>38</v>
-      </c>
-      <c r="AF20">
-        <v>16</v>
-      </c>
-      <c r="AG20">
+      <c r="AT20">
+        <v>9</v>
+      </c>
+      <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>10</v>
+      </c>
+      <c r="AW20">
+        <v>9.6</v>
+      </c>
+      <c r="AX20">
         <v>12</v>
       </c>
-      <c r="AH20">
-        <v>18</v>
-      </c>
-      <c r="AI20">
-        <v>46</v>
-      </c>
-      <c r="AJ20">
-        <v>36</v>
-      </c>
-      <c r="AK20">
-        <v>27</v>
-      </c>
-      <c r="AL20">
-        <v>40</v>
-      </c>
-      <c r="AM20">
-        <v>110</v>
-      </c>
-      <c r="AN20">
-        <v>20</v>
-      </c>
-      <c r="AO20">
-        <v>32</v>
-      </c>
-      <c r="AP20">
-        <v>13</v>
-      </c>
-      <c r="AQ20">
-        <v>11.5</v>
-      </c>
-      <c r="AR20">
-        <v>19</v>
-      </c>
-      <c r="AS20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU20">
-        <v>7.4</v>
-      </c>
-      <c r="AV20">
-        <v>12.5</v>
-      </c>
-      <c r="AW20">
-        <v>9</v>
-      </c>
-      <c r="AX20">
-        <v>13.5</v>
-      </c>
       <c r="AY20">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
         <v>15</v>
       </c>
       <c r="BA20">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BB20">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC20">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="BD20">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BE20">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF20">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.51</v>
+        <v>2.98</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>160</v>
@@ -5688,22 +5688,22 @@
         <v>152</v>
       </c>
       <c r="F21">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H21">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="I21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K21">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L21">
         <v>1.48</v>
@@ -5712,202 +5712,202 @@
         <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="O21">
         <v>1.42</v>
       </c>
       <c r="P21">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="R21">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="S21">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="T21">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
         <v>1.79</v>
       </c>
       <c r="X21">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y21">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="Z21">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AA21">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD21">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE21">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AH21">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI21">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AK21">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="AL21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="AR21">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="AS21">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="AT21">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU21">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV21">
-        <v>14.5</v>
+        <v>1.9</v>
       </c>
       <c r="AW21">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="AX21">
-        <v>11</v>
+        <v>1.82</v>
       </c>
       <c r="AY21">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>17</v>
+        <v>5.6</v>
       </c>
       <c r="BA21">
-        <v>5.4</v>
+        <v>1.95</v>
       </c>
       <c r="BB21">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BC21">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD21">
-        <v>38</v>
+        <v>1.95</v>
       </c>
       <c r="BE21">
-        <v>5.6</v>
+        <v>1.96</v>
       </c>
       <c r="BF21">
-        <v>19</v>
+        <v>1.96</v>
       </c>
       <c r="BG21">
-        <v>5.4</v>
+        <v>1.96</v>
       </c>
       <c r="BH21">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>160</v>
@@ -5933,175 +5933,175 @@
         <v>2.12</v>
       </c>
       <c r="G22">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H22">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I22">
         <v>4.2</v>
       </c>
       <c r="J22">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L22">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M22">
         <v>1.09</v>
       </c>
       <c r="N22">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="O22">
         <v>1.4</v>
       </c>
       <c r="P22">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q22">
         <v>2.22</v>
       </c>
       <c r="R22">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S22">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T22">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U22">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="V22">
         <v>1.31</v>
       </c>
       <c r="W22">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="X22">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y22">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z22">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AA22">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC22">
         <v>7.6</v>
       </c>
       <c r="AD22">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG22">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="AI22">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK22">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AL22">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO22">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="AQ22">
-        <v>11</v>
+        <v>3.65</v>
       </c>
       <c r="AR22">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AS22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AT22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU22">
         <v>6.8</v>
       </c>
       <c r="AV22">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="AW22">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AX22">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="AY22">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ22">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BB22">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BC22">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BD22">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BE22">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="BF22">
-        <v>18.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG22">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BL22">
         <v>1000</v>
@@ -6113,7 +6113,7 @@
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="BP22">
         <v>1000</v>
@@ -6131,7 +6131,7 @@
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BV22">
         <v>1000</v>
@@ -6178,10 +6178,10 @@
         <v>1.77</v>
       </c>
       <c r="H23">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I23">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J23">
         <v>3.95</v>
@@ -6196,28 +6196,28 @@
         <v>1.06</v>
       </c>
       <c r="N23">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23">
+        <v>1.89</v>
+      </c>
+      <c r="R23">
+        <v>1.39</v>
+      </c>
+      <c r="S23">
+        <v>3.3</v>
+      </c>
+      <c r="T23">
         <v>1.9</v>
       </c>
-      <c r="Q23">
-        <v>1.86</v>
-      </c>
-      <c r="R23">
-        <v>1.32</v>
-      </c>
-      <c r="S23">
-        <v>3.05</v>
-      </c>
-      <c r="T23">
-        <v>1.88</v>
-      </c>
       <c r="U23">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
         <v>1.21</v>
@@ -6226,172 +6226,172 @@
         <v>2.28</v>
       </c>
       <c r="X23">
+        <v>18.5</v>
+      </c>
+      <c r="Y23">
+        <v>970</v>
+      </c>
+      <c r="Z23">
+        <v>55</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>9.6</v>
+      </c>
+      <c r="AC23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD23">
         <v>950</v>
       </c>
-      <c r="Y23">
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>10.5</v>
+      </c>
+      <c r="AG23">
+        <v>10.5</v>
+      </c>
+      <c r="AH23">
         <v>950</v>
       </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>1000</v>
-      </c>
-      <c r="AC23">
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
         <v>970</v>
       </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>95</v>
-      </c>
-      <c r="AF23">
-        <v>11</v>
-      </c>
-      <c r="AG23">
-        <v>970</v>
-      </c>
-      <c r="AH23">
+      <c r="AK23">
         <v>22</v>
       </c>
-      <c r="AI23">
-        <v>95</v>
-      </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM23">
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AR23">
-        <v>1.69</v>
+        <v>9.4</v>
       </c>
       <c r="AS23">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="AT23">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU23">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>1.68</v>
+        <v>16</v>
       </c>
       <c r="AW23">
-        <v>1.66</v>
+        <v>22</v>
       </c>
       <c r="AX23">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="BA23">
-        <v>1.66</v>
+        <v>5.3</v>
       </c>
       <c r="BB23">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC23">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BD23">
-        <v>1.69</v>
+        <v>9.4</v>
       </c>
       <c r="BE23">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="BF23">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG23">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="CB23" t="s">
         <v>160</v>
@@ -6414,22 +6414,22 @@
         <v>155</v>
       </c>
       <c r="F24">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
-        <v>1.31</v>
+        <v>990</v>
       </c>
       <c r="H24">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
-        <v>16</v>
+        <v>990</v>
       </c>
       <c r="J24">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="K24">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6438,22 +6438,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="O24">
         <v>1.11</v>
       </c>
       <c r="P24">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
         <v>1.13</v>
       </c>
       <c r="R24">
-        <v>1.79</v>
+        <v>1.08</v>
       </c>
       <c r="S24">
-        <v>1.94</v>
+        <v>1.13</v>
       </c>
       <c r="T24">
         <v>1.11</v>
@@ -6462,10 +6462,10 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W24">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6656,226 +6656,226 @@
         <v>156</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H25">
         <v>2.52</v>
       </c>
       <c r="I25">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="J25">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K25">
         <v>3.75</v>
       </c>
       <c r="L25">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
         <v>1.06</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P25">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q25">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R25">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S25">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U25">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="W25">
         <v>1.5</v>
       </c>
       <c r="X25">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z25">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AD25">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE25">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH25">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI25">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25">
+        <v>8.6</v>
+      </c>
+      <c r="AR25">
         <v>11</v>
       </c>
-      <c r="AR25">
-        <v>15.5</v>
-      </c>
       <c r="AS25">
+        <v>1.31</v>
+      </c>
+      <c r="AT25">
+        <v>9</v>
+      </c>
+      <c r="AU25">
+        <v>6</v>
+      </c>
+      <c r="AV25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW25">
+        <v>1.31</v>
+      </c>
+      <c r="AX25">
+        <v>12</v>
+      </c>
+      <c r="AY25">
         <v>8.6</v>
       </c>
-      <c r="AT25">
+      <c r="AZ25">
+        <v>10</v>
+      </c>
+      <c r="BA25">
+        <v>1.31</v>
+      </c>
+      <c r="BB25">
+        <v>1.31</v>
+      </c>
+      <c r="BC25">
+        <v>1.31</v>
+      </c>
+      <c r="BD25">
+        <v>1.31</v>
+      </c>
+      <c r="BE25">
+        <v>1.31</v>
+      </c>
+      <c r="BF25">
+        <v>1.31</v>
+      </c>
+      <c r="BG25">
         <v>11.5</v>
       </c>
-      <c r="AU25">
-        <v>7.6</v>
-      </c>
-      <c r="AV25">
-        <v>10.5</v>
-      </c>
-      <c r="AW25">
-        <v>7.6</v>
-      </c>
-      <c r="AX25">
-        <v>18</v>
-      </c>
-      <c r="AY25">
-        <v>11.5</v>
-      </c>
-      <c r="AZ25">
-        <v>14</v>
-      </c>
-      <c r="BA25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB25">
-        <v>30</v>
-      </c>
-      <c r="BC25">
-        <v>8</v>
-      </c>
-      <c r="BD25">
-        <v>8.6</v>
-      </c>
-      <c r="BE25">
-        <v>9.4</v>
-      </c>
-      <c r="BF25">
-        <v>16.5</v>
-      </c>
-      <c r="BG25">
-        <v>16</v>
-      </c>
       <c r="BH25">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.35</v>
+        <v>1.43</v>
       </c>
       <c r="BJ25">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>7.8</v>
+        <v>2.18</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>6.6</v>
+        <v>2.18</v>
       </c>
       <c r="BN25">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>5.4</v>
+        <v>1.67</v>
       </c>
       <c r="BP25">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>5.8</v>
+        <v>2.18</v>
       </c>
       <c r="BR25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="BT25">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>5.1</v>
+        <v>1.64</v>
       </c>
       <c r="BV25">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW25">
-        <v>9.199999999999999</v>
+        <v>2.18</v>
       </c>
       <c r="BX25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>5.8</v>
+        <v>2.18</v>
       </c>
       <c r="BZ25">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="CB25" t="s">
         <v>160</v>
@@ -6898,25 +6898,25 @@
         <v>157</v>
       </c>
       <c r="F26">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H26">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J26">
         <v>3.05</v>
       </c>
       <c r="K26">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L26">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="M26">
         <v>1.12</v>
@@ -6925,7 +6925,7 @@
         <v>2.68</v>
       </c>
       <c r="O26">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P26">
         <v>1.56</v>
@@ -6937,187 +6937,187 @@
         <v>1.2</v>
       </c>
       <c r="S26">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T26">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U26">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V26">
         <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X26">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y26">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC26">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD26">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE26">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>8</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>9.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="AR26">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="AS26">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="AT26">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV26">
-        <v>15.5</v>
+        <v>2.32</v>
       </c>
       <c r="AW26">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="AX26">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="AZ26">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="BA26">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="BB26">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="BC26">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="BD26">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="BE26">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="BF26">
-        <v>21</v>
+        <v>2.6</v>
       </c>
       <c r="BG26">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="BH26">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA26">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
         <v>160</v>
@@ -7140,226 +7140,226 @@
         <v>158</v>
       </c>
       <c r="F27">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G27">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H27">
+        <v>3.5</v>
+      </c>
+      <c r="I27">
+        <v>3.75</v>
+      </c>
+      <c r="J27">
+        <v>3.35</v>
+      </c>
+      <c r="K27">
         <v>3.6</v>
       </c>
-      <c r="I27">
-        <v>3.9</v>
-      </c>
-      <c r="J27">
-        <v>3.4</v>
-      </c>
-      <c r="K27">
-        <v>3.65</v>
-      </c>
       <c r="L27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M27">
         <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
         <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q27">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S27">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T27">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U27">
         <v>2.08</v>
       </c>
       <c r="V27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X27">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y27">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA27">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC27">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD27">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AG27">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH27">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL27">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN27">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AO27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>11.5</v>
+        <v>2.68</v>
       </c>
       <c r="AQ27">
-        <v>11.5</v>
+        <v>2.66</v>
       </c>
       <c r="AR27">
-        <v>23</v>
+        <v>2.92</v>
       </c>
       <c r="AS27">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="AT27">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AU27">
-        <v>7</v>
+        <v>2.28</v>
       </c>
       <c r="AV27">
-        <v>14</v>
+        <v>2.76</v>
       </c>
       <c r="AW27">
-        <v>9.6</v>
+        <v>3.25</v>
       </c>
       <c r="AX27">
-        <v>12</v>
+        <v>2.72</v>
       </c>
       <c r="AY27">
-        <v>9.800000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="AZ27">
-        <v>16</v>
+        <v>2.82</v>
       </c>
       <c r="BA27">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="BB27">
-        <v>9</v>
+        <v>3.25</v>
       </c>
       <c r="BC27">
-        <v>8</v>
+        <v>2.92</v>
       </c>
       <c r="BD27">
-        <v>9.199999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="BE27">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="BF27">
-        <v>15.5</v>
+        <v>2.84</v>
       </c>
       <c r="BG27">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="BH27">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI27">
-        <v>3.05</v>
+        <v>1.26</v>
       </c>
       <c r="BJ27">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>4.4</v>
+        <v>1.47</v>
       </c>
       <c r="BP27">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA27">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="s">
         <v>160</v>
@@ -7382,16 +7382,16 @@
         <v>159</v>
       </c>
       <c r="F28">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G28">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H28">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I28">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J28">
         <v>3.6</v>
@@ -7400,13 +7400,13 @@
         <v>3.9</v>
       </c>
       <c r="L28">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M28">
         <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O28">
         <v>1.37</v>
@@ -7415,7 +7415,7 @@
         <v>1.8</v>
       </c>
       <c r="Q28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R28">
         <v>1.31</v>
@@ -7430,178 +7430,178 @@
         <v>1.96</v>
       </c>
       <c r="V28">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W28">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X28">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y28">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Z28">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AA28">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AC28">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD28">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AH28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AP28">
-        <v>11</v>
+        <v>2.34</v>
       </c>
       <c r="AQ28">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="AR28">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="AS28">
-        <v>19.5</v>
+        <v>2.8</v>
       </c>
       <c r="AT28">
-        <v>12.5</v>
+        <v>2.34</v>
       </c>
       <c r="AU28">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="AV28">
-        <v>9.199999999999999</v>
+        <v>2.26</v>
       </c>
       <c r="AW28">
-        <v>19</v>
+        <v>2.8</v>
       </c>
       <c r="AX28">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="AY28">
-        <v>15.5</v>
+        <v>2.44</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>2.78</v>
       </c>
       <c r="BA28">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="BB28">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="BC28">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BD28">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BE28">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="BF28">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BG28">
-        <v>13.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH28">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>160</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -496,7 +496,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 08:27:28</t>
+    <t>2026-10-06 10:38:39</t>
   </si>
 </sst>
 </file>
@@ -1090,73 +1090,73 @@
         <v>133</v>
       </c>
       <c r="F2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I2">
         <v>2.3</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="R2">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="S2">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="T2">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V2">
         <v>1.76</v>
       </c>
       <c r="W2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1165,10 +1165,10 @@
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG2">
         <v>14</v>
@@ -1177,139 +1177,139 @@
         <v>13</v>
       </c>
       <c r="AI2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ2">
         <v>55</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AN2">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS2">
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AU2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
         <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC2">
         <v>25</v>
       </c>
       <c r="BD2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BF2">
         <v>13</v>
       </c>
       <c r="BG2">
+        <v>8.4</v>
+      </c>
+      <c r="BH2">
+        <v>5.2</v>
+      </c>
+      <c r="BI2">
+        <v>4.6</v>
+      </c>
+      <c r="BJ2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK2">
+        <v>7.4</v>
+      </c>
+      <c r="BL2">
+        <v>60</v>
+      </c>
+      <c r="BM2">
+        <v>11.5</v>
+      </c>
+      <c r="BN2">
+        <v>7</v>
+      </c>
+      <c r="BO2">
+        <v>6.2</v>
+      </c>
+      <c r="BP2">
+        <v>21</v>
+      </c>
+      <c r="BQ2">
         <v>9</v>
       </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>4</v>
-      </c>
-      <c r="BJ2">
-        <v>1000</v>
-      </c>
-      <c r="BK2">
-        <v>2.78</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>3.35</v>
-      </c>
-      <c r="BN2">
-        <v>1000</v>
-      </c>
-      <c r="BO2">
-        <v>2.6</v>
-      </c>
-      <c r="BP2">
-        <v>1000</v>
-      </c>
-      <c r="BQ2">
-        <v>4.2</v>
-      </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS2">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW2">
-        <v>3.35</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY2">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA2">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>160</v>
@@ -1332,34 +1332,34 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>13</v>
       </c>
       <c r="H3">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="K3">
         <v>5.9</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3">
         <v>2.08</v>
@@ -1377,7 +1377,7 @@
         <v>2.4</v>
       </c>
       <c r="U3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
         <v>3.85</v>
@@ -1389,16 +1389,16 @@
         <v>18</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AC3">
         <v>13</v>
@@ -1413,34 +1413,34 @@
         <v>120</v>
       </c>
       <c r="AG3">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AH3">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AI3">
         <v>50</v>
       </c>
       <c r="AJ3">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="AK3">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AL3">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AM3">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN3">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AO3">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AP3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
         <v>6.8</v>
@@ -1455,103 +1455,103 @@
         <v>27</v>
       </c>
       <c r="AU3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>14</v>
+      </c>
+      <c r="AY3">
+        <v>38</v>
+      </c>
+      <c r="AZ3">
+        <v>32</v>
+      </c>
+      <c r="BA3">
+        <v>42</v>
+      </c>
+      <c r="BB3">
+        <v>14</v>
+      </c>
+      <c r="BC3">
+        <v>14</v>
+      </c>
+      <c r="BD3">
+        <v>14</v>
+      </c>
+      <c r="BE3">
+        <v>14</v>
+      </c>
+      <c r="BF3">
+        <v>14.5</v>
+      </c>
+      <c r="BG3">
+        <v>5.8</v>
+      </c>
+      <c r="BH3">
+        <v>3.7</v>
+      </c>
+      <c r="BI3">
+        <v>3.35</v>
+      </c>
+      <c r="BJ3">
+        <v>14</v>
+      </c>
+      <c r="BK3">
+        <v>7</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>13.5</v>
+      </c>
+      <c r="BN3">
+        <v>15.5</v>
+      </c>
+      <c r="BO3">
+        <v>7.6</v>
+      </c>
+      <c r="BP3">
+        <v>130</v>
+      </c>
+      <c r="BQ3">
+        <v>13</v>
+      </c>
+      <c r="BR3">
+        <v>120</v>
+      </c>
+      <c r="BS3">
+        <v>13</v>
+      </c>
+      <c r="BT3">
+        <v>3.6</v>
+      </c>
+      <c r="BU3">
+        <v>3.25</v>
+      </c>
+      <c r="BV3">
+        <v>7.8</v>
+      </c>
+      <c r="BW3">
+        <v>7</v>
+      </c>
+      <c r="BX3">
+        <v>29</v>
+      </c>
+      <c r="BY3">
         <v>9.6</v>
       </c>
-      <c r="AW3">
-        <v>14.5</v>
-      </c>
-      <c r="AX3">
-        <v>5.6</v>
-      </c>
-      <c r="AY3">
-        <v>40</v>
-      </c>
-      <c r="AZ3">
-        <v>30</v>
-      </c>
-      <c r="BA3">
-        <v>5.3</v>
-      </c>
-      <c r="BB3">
-        <v>5.7</v>
-      </c>
-      <c r="BC3">
-        <v>5.6</v>
-      </c>
-      <c r="BD3">
-        <v>5.6</v>
-      </c>
-      <c r="BE3">
-        <v>5.6</v>
-      </c>
-      <c r="BF3">
-        <v>5.7</v>
-      </c>
-      <c r="BG3">
-        <v>5.9</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>1.34</v>
-      </c>
-      <c r="BJ3">
-        <v>1000</v>
-      </c>
-      <c r="BK3">
-        <v>2</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>1.04</v>
-      </c>
-      <c r="BN3">
-        <v>1000</v>
-      </c>
-      <c r="BO3">
-        <v>1.04</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>1.04</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>1.04</v>
-      </c>
-      <c r="BT3">
-        <v>1000</v>
-      </c>
-      <c r="BU3">
-        <v>1.33</v>
-      </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>2</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>1.04</v>
-      </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="s">
         <v>160</v>
@@ -1574,13 +1574,13 @@
         <v>135</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G4">
         <v>2.48</v>
       </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I4">
         <v>3.45</v>
@@ -1589,7 +1589,7 @@
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
         <v>1.67</v>
@@ -1613,13 +1613,13 @@
         <v>1.24</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -1628,172 +1628,172 @@
         <v>1.68</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>16</v>
+      </c>
+      <c r="AE4">
+        <v>60</v>
+      </c>
+      <c r="AF4">
+        <v>15.5</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>25</v>
+      </c>
+      <c r="AI4">
+        <v>80</v>
+      </c>
+      <c r="AJ4">
+        <v>42</v>
+      </c>
+      <c r="AK4">
+        <v>38</v>
+      </c>
+      <c r="AL4">
+        <v>60</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
         <v>34</v>
       </c>
-      <c r="AD4">
-        <v>950</v>
-      </c>
-      <c r="AE4">
-        <v>240</v>
-      </c>
-      <c r="AF4">
-        <v>95</v>
-      </c>
-      <c r="AG4">
-        <v>950</v>
-      </c>
-      <c r="AH4">
-        <v>950</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>200</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP4">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>3.35</v>
+        <v>9.4</v>
       </c>
       <c r="AR4">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AT4">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>2.56</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>1.19</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>1.21</v>
+        <v>21</v>
       </c>
       <c r="AX4">
-        <v>1.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>1.2</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="BB4">
-        <v>1.21</v>
+        <v>6</v>
       </c>
       <c r="BC4">
-        <v>1.2</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>1.21</v>
+        <v>14.5</v>
       </c>
       <c r="BE4">
-        <v>1.21</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>1.21</v>
+        <v>20</v>
       </c>
       <c r="BG4">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB4" t="s">
         <v>160</v>
@@ -1816,226 +1816,226 @@
         <v>136</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
         <v>1.59</v>
       </c>
       <c r="V5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP5">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="AQ5">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="AR5">
-        <v>1.02</v>
+        <v>4.9</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV5">
-        <v>1.02</v>
+        <v>4.6</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ5">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB5">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="BC5">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BD5">
-        <v>1.02</v>
+        <v>4.8</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF5">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="CB5" t="s">
         <v>160</v>
@@ -2058,166 +2058,166 @@
         <v>137</v>
       </c>
       <c r="F6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
+        <v>2.66</v>
+      </c>
+      <c r="H6">
+        <v>2.9</v>
+      </c>
+      <c r="I6">
         <v>3.1</v>
       </c>
-      <c r="H6">
-        <v>2.8</v>
-      </c>
-      <c r="I6">
-        <v>3.35</v>
-      </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>1.94</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S6">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T6">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2300,79 +2300,79 @@
         <v>138</v>
       </c>
       <c r="F7">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="H7">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="I7">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q7">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB7">
         <v>1000</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2405,61 +2405,61 @@
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2542,166 +2542,166 @@
         <v>139</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G8">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="H8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J8">
-        <v>1.12</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
+        <v>3.45</v>
+      </c>
+      <c r="O8">
+        <v>1.33</v>
+      </c>
+      <c r="P8">
+        <v>1.87</v>
+      </c>
+      <c r="Q8">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>1.33</v>
+      </c>
+      <c r="S8">
+        <v>3.55</v>
+      </c>
+      <c r="T8">
         <v>1.8</v>
       </c>
-      <c r="O8">
-        <v>1.34</v>
-      </c>
-      <c r="P8">
-        <v>1.12</v>
-      </c>
-      <c r="Q8">
-        <v>1.34</v>
-      </c>
-      <c r="R8">
-        <v>1.09</v>
-      </c>
-      <c r="S8">
-        <v>1.05</v>
-      </c>
-      <c r="T8">
-        <v>1.71</v>
-      </c>
       <c r="U8">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V8">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W8">
         <v>1.31</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP8">
-        <v>1.02</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8">
-        <v>1.02</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY8">
-        <v>1.02</v>
+        <v>13.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD8">
-        <v>1.02</v>
+        <v>5</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2784,58 +2784,58 @@
         <v>140</v>
       </c>
       <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>3.75</v>
+      </c>
+      <c r="H9">
+        <v>2.38</v>
+      </c>
+      <c r="I9">
+        <v>110</v>
+      </c>
+      <c r="J9">
+        <v>1.12</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>1.56</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>2.34</v>
+      </c>
+      <c r="O9">
+        <v>1.56</v>
+      </c>
+      <c r="P9">
+        <v>1.45</v>
+      </c>
+      <c r="Q9">
+        <v>2.64</v>
+      </c>
+      <c r="R9">
         <v>1.13</v>
       </c>
-      <c r="G9">
-        <v>990</v>
-      </c>
-      <c r="H9">
-        <v>1.13</v>
-      </c>
-      <c r="I9">
-        <v>990</v>
-      </c>
-      <c r="J9">
-        <v>1.22</v>
-      </c>
-      <c r="K9">
-        <v>85</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>1.1</v>
-      </c>
-      <c r="O9">
-        <v>1.02</v>
-      </c>
-      <c r="P9">
-        <v>1.09</v>
-      </c>
-      <c r="Q9">
-        <v>1.54</v>
-      </c>
-      <c r="R9">
-        <v>1.08</v>
-      </c>
       <c r="S9">
-        <v>1.56</v>
+        <v>4.8</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3026,46 +3026,46 @@
         <v>141</v>
       </c>
       <c r="F10">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="G10">
-        <v>990</v>
+        <v>2.08</v>
       </c>
       <c r="H10">
-        <v>1.13</v>
+        <v>3.9</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>6.2</v>
       </c>
       <c r="J10">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>85</v>
+        <v>5.3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10">
-        <v>1.13</v>
+        <v>2.74</v>
       </c>
       <c r="O10">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P10">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="Q10">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="R10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3074,10 +3074,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3268,46 +3268,46 @@
         <v>142</v>
       </c>
       <c r="F11">
-        <v>1.12</v>
+        <v>2.68</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>3.35</v>
       </c>
       <c r="H11">
-        <v>1.12</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>2.54</v>
       </c>
       <c r="J11">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.68</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
+        <v>2.5</v>
+      </c>
+      <c r="Q11">
+        <v>1.45</v>
+      </c>
+      <c r="R11">
         <v>1.69</v>
       </c>
-      <c r="Q11">
-        <v>1.04</v>
-      </c>
-      <c r="R11">
-        <v>1.12</v>
-      </c>
       <c r="S11">
-        <v>1.05</v>
+        <v>2.14</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3316,10 +3316,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3510,22 +3510,22 @@
         <v>143</v>
       </c>
       <c r="F12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G12">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="I12">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="J12">
         <v>3.95</v>
       </c>
       <c r="K12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>1.32</v>
@@ -3534,202 +3534,202 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
         <v>1.25</v>
       </c>
       <c r="P12">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T12">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="V12">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="W12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X12">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z12">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AA12">
-        <v>640</v>
+        <v>21</v>
       </c>
       <c r="AB12">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC12">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AE12">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AF12">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AG12">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH12">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>110</v>
       </c>
       <c r="AK12">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="AL12">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="AM12">
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO12">
+        <v>11.5</v>
+      </c>
+      <c r="AP12">
+        <v>15.5</v>
+      </c>
+      <c r="AQ12">
+        <v>9.4</v>
+      </c>
+      <c r="AR12">
+        <v>10.5</v>
+      </c>
+      <c r="AS12">
+        <v>18</v>
+      </c>
+      <c r="AT12">
+        <v>16</v>
+      </c>
+      <c r="AU12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW12">
+        <v>16</v>
+      </c>
+      <c r="AX12">
+        <v>16.5</v>
+      </c>
+      <c r="AY12">
+        <v>15.5</v>
+      </c>
+      <c r="AZ12">
+        <v>15.5</v>
+      </c>
+      <c r="BA12">
+        <v>15</v>
+      </c>
+      <c r="BB12">
+        <v>36</v>
+      </c>
+      <c r="BC12">
+        <v>24</v>
+      </c>
+      <c r="BD12">
+        <v>26</v>
+      </c>
+      <c r="BE12">
+        <v>38</v>
+      </c>
+      <c r="BF12">
+        <v>34</v>
+      </c>
+      <c r="BG12">
+        <v>9.4</v>
+      </c>
+      <c r="BH12">
+        <v>3.95</v>
+      </c>
+      <c r="BI12">
+        <v>3.2</v>
+      </c>
+      <c r="BJ12">
+        <v>13</v>
+      </c>
+      <c r="BK12">
+        <v>7.6</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>4.6</v>
+      </c>
+      <c r="BN12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO12">
+        <v>6.6</v>
+      </c>
+      <c r="BP12">
+        <v>50</v>
+      </c>
+      <c r="BQ12">
+        <v>4.2</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>4.3</v>
+      </c>
+      <c r="BT12">
+        <v>5.4</v>
+      </c>
+      <c r="BU12">
+        <v>3.9</v>
+      </c>
+      <c r="BV12">
         <v>17.5</v>
       </c>
-      <c r="AP12">
-        <v>13.5</v>
-      </c>
-      <c r="AQ12">
-        <v>8.6</v>
-      </c>
-      <c r="AR12">
-        <v>8.4</v>
-      </c>
-      <c r="AS12">
-        <v>13.5</v>
-      </c>
-      <c r="AT12">
-        <v>14</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>8</v>
-      </c>
-      <c r="AW12">
-        <v>12</v>
-      </c>
-      <c r="AX12">
-        <v>1.89</v>
-      </c>
-      <c r="AY12">
-        <v>11</v>
-      </c>
-      <c r="AZ12">
-        <v>11</v>
-      </c>
-      <c r="BA12">
-        <v>1.88</v>
-      </c>
-      <c r="BB12">
-        <v>1.95</v>
-      </c>
-      <c r="BC12">
-        <v>1.93</v>
-      </c>
-      <c r="BD12">
-        <v>1.93</v>
-      </c>
-      <c r="BE12">
-        <v>1.95</v>
-      </c>
-      <c r="BF12">
-        <v>1.93</v>
-      </c>
-      <c r="BG12">
-        <v>7.2</v>
-      </c>
-      <c r="BH12">
-        <v>4.5</v>
-      </c>
-      <c r="BI12">
-        <v>3.1</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>2.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>2.36</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.96</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>2.36</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>2.36</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>3.75</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
       <c r="BW12">
-        <v>2.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY12">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA12">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="s">
         <v>160</v>
@@ -3752,19 +3752,19 @@
         <v>144</v>
       </c>
       <c r="F13">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G13">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="H13">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>9.6</v>
       </c>
       <c r="J13">
-        <v>1.12</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
         <v>3.85</v>
@@ -3773,37 +3773,37 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>1.09</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R13">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="S13">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3914,64 +3914,64 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="CB13" t="s">
         <v>160</v>
@@ -3994,22 +3994,22 @@
         <v>145</v>
       </c>
       <c r="F14">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>2.6</v>
       </c>
       <c r="H14">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>4.1</v>
       </c>
       <c r="J14">
-        <v>1.12</v>
+        <v>2.94</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4236,22 +4236,22 @@
         <v>146</v>
       </c>
       <c r="F15">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="G15">
         <v>1.43</v>
       </c>
       <c r="H15">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>990</v>
+        <v>15.5</v>
       </c>
       <c r="J15">
-        <v>1.12</v>
+        <v>4.6</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4260,160 +4260,160 @@
         <v>1.07</v>
       </c>
       <c r="N15">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O15">
         <v>1.34</v>
       </c>
       <c r="P15">
-        <v>1.09</v>
+        <v>1.82</v>
       </c>
       <c r="Q15">
-        <v>1.34</v>
+        <v>2.02</v>
       </c>
       <c r="R15">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="T15">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
         <v>1.53</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W15">
         <v>3.3</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BN15">
         <v>1000</v>
@@ -4425,37 +4425,37 @@
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="CB15" t="s">
         <v>160</v>
@@ -4478,49 +4478,49 @@
         <v>147</v>
       </c>
       <c r="F16">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="G16">
-        <v>600</v>
+        <v>2.26</v>
       </c>
       <c r="H16">
-        <v>1.12</v>
+        <v>3.8</v>
       </c>
       <c r="I16">
         <v>3.9</v>
       </c>
       <c r="J16">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N16">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
         <v>1.37</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="R16">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="S16">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U16">
         <v>1.11</v>
@@ -4529,115 +4529,115 @@
         <v>1.34</v>
       </c>
       <c r="W16">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4720,166 +4720,166 @@
         <v>148</v>
       </c>
       <c r="F17">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>4.6</v>
       </c>
       <c r="H17">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I17">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="J17">
+        <v>2.94</v>
+      </c>
+      <c r="K17">
+        <v>3.35</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
         <v>1.12</v>
       </c>
-      <c r="K17">
-        <v>500</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.09</v>
-      </c>
       <c r="N17">
-        <v>1.13</v>
+        <v>2.66</v>
       </c>
       <c r="O17">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="P17">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="Q17">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="R17">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="S17">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V17">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4965,7 +4965,7 @@
         <v>1.86</v>
       </c>
       <c r="G18">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H18">
         <v>4.4</v>
@@ -4986,10 +4986,10 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P18">
         <v>2.14</v>
@@ -4998,7 +4998,7 @@
         <v>1.81</v>
       </c>
       <c r="R18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S18">
         <v>3.05</v>
@@ -5016,28 +5016,28 @@
         <v>2.08</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y18">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Z18">
         <v>40</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB18">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC18">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF18">
         <v>12.5</v>
@@ -5046,142 +5046,142 @@
         <v>10.5</v>
       </c>
       <c r="AH18">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ18">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AK18">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL18">
         <v>38</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN18">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AO18">
         <v>65</v>
       </c>
       <c r="AP18">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS18">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AT18">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV18">
         <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AX18">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY18">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
         <v>15</v>
       </c>
       <c r="BA18">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="BB18">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BC18">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE18">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF18">
         <v>9.800000000000001</v>
       </c>
       <c r="BG18">
+        <v>10</v>
+      </c>
+      <c r="BH18">
+        <v>3.7</v>
+      </c>
+      <c r="BI18">
+        <v>3.4</v>
+      </c>
+      <c r="BJ18">
+        <v>11.5</v>
+      </c>
+      <c r="BK18">
         <v>4.5</v>
       </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.72</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
-      <c r="BK18">
-        <v>2.5</v>
-      </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO18">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ18">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU18">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB18" t="s">
         <v>160</v>
@@ -5207,16 +5207,16 @@
         <v>2.32</v>
       </c>
       <c r="G19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H19">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I19">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J19">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K19">
         <v>3.4</v>
@@ -5240,19 +5240,19 @@
         <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19">
         <v>4.1</v>
       </c>
       <c r="T19">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U19">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
         <v>1.7</v>
@@ -5261,13 +5261,13 @@
         <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z19">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB19">
         <v>9.199999999999999</v>
@@ -5276,106 +5276,106 @@
         <v>7.6</v>
       </c>
       <c r="AD19">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE19">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="AF19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG19">
         <v>12</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK19">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR19">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="AS19">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AT19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19">
         <v>6.8</v>
       </c>
       <c r="AV19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW19">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="AX19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY19">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19">
+        <v>17.5</v>
+      </c>
+      <c r="BA19">
+        <v>25</v>
+      </c>
+      <c r="BB19">
+        <v>13</v>
+      </c>
+      <c r="BC19">
+        <v>19</v>
+      </c>
+      <c r="BD19">
+        <v>38</v>
+      </c>
+      <c r="BE19">
+        <v>10.5</v>
+      </c>
+      <c r="BF19">
         <v>17</v>
       </c>
-      <c r="BA19">
-        <v>28</v>
-      </c>
-      <c r="BB19">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC19">
-        <v>8.4</v>
-      </c>
-      <c r="BD19">
-        <v>16</v>
-      </c>
-      <c r="BE19">
-        <v>4.5</v>
-      </c>
-      <c r="BF19">
-        <v>4.5</v>
-      </c>
       <c r="BG19">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH19">
         <v>3</v>
       </c>
       <c r="BI19">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5387,25 +5387,25 @@
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BV19">
         <v>1000</v>
@@ -5449,13 +5449,13 @@
         <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J20">
         <v>3.45</v>
@@ -5470,7 +5470,7 @@
         <v>1.07</v>
       </c>
       <c r="N20">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
         <v>1.31</v>
@@ -5479,25 +5479,25 @@
         <v>1.98</v>
       </c>
       <c r="Q20">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
         <v>1.37</v>
       </c>
       <c r="S20">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T20">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U20">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
         <v>1.43</v>
       </c>
       <c r="W20">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X20">
         <v>15</v>
@@ -5509,10 +5509,10 @@
         <v>24</v>
       </c>
       <c r="AA20">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -5521,151 +5521,151 @@
         <v>14.5</v>
       </c>
       <c r="AE20">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF20">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AG20">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AI20">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ20">
+        <v>36</v>
+      </c>
+      <c r="AK20">
+        <v>27</v>
+      </c>
+      <c r="AL20">
         <v>40</v>
       </c>
-      <c r="AK20">
-        <v>36</v>
-      </c>
-      <c r="AL20">
-        <v>50</v>
-      </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AO20">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP20">
         <v>12.5</v>
       </c>
       <c r="AQ20">
+        <v>11.5</v>
+      </c>
+      <c r="AR20">
+        <v>19</v>
+      </c>
+      <c r="AS20">
         <v>10</v>
       </c>
-      <c r="AR20">
-        <v>6.2</v>
-      </c>
-      <c r="AS20">
-        <v>14</v>
-      </c>
       <c r="AT20">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW20">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20">
         <v>15</v>
       </c>
       <c r="BA20">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20">
+        <v>15.5</v>
+      </c>
+      <c r="BC20">
+        <v>23</v>
+      </c>
+      <c r="BD20">
+        <v>17</v>
+      </c>
+      <c r="BE20">
+        <v>11</v>
+      </c>
+      <c r="BF20">
+        <v>16.5</v>
+      </c>
+      <c r="BG20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH20">
+        <v>3.4</v>
+      </c>
+      <c r="BI20">
+        <v>3.15</v>
+      </c>
+      <c r="BJ20">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC20">
-        <v>7.6</v>
-      </c>
-      <c r="BD20">
+      <c r="BK20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>16</v>
+      </c>
+      <c r="BN20">
+        <v>5.3</v>
+      </c>
+      <c r="BO20">
+        <v>4.9</v>
+      </c>
+      <c r="BP20">
+        <v>19</v>
+      </c>
+      <c r="BQ20">
+        <v>9.4</v>
+      </c>
+      <c r="BR20">
+        <v>32</v>
+      </c>
+      <c r="BS20">
+        <v>11.5</v>
+      </c>
+      <c r="BT20">
+        <v>6.2</v>
+      </c>
+      <c r="BU20">
+        <v>5.7</v>
+      </c>
+      <c r="BV20">
+        <v>26</v>
+      </c>
+      <c r="BW20">
+        <v>10.5</v>
+      </c>
+      <c r="BX20">
+        <v>38</v>
+      </c>
+      <c r="BY20">
+        <v>12.5</v>
+      </c>
+      <c r="BZ20">
+        <v>27</v>
+      </c>
+      <c r="CA20">
         <v>11</v>
-      </c>
-      <c r="BE20">
-        <v>7.2</v>
-      </c>
-      <c r="BF20">
-        <v>14.5</v>
-      </c>
-      <c r="BG20">
-        <v>6</v>
-      </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>2.98</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>2.78</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>2.28</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>3.95</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>2.46</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>160</v>
@@ -5688,226 +5688,226 @@
         <v>152</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="G21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
+        <v>3.85</v>
+      </c>
+      <c r="I21">
+        <v>4.3</v>
+      </c>
+      <c r="J21">
+        <v>3.25</v>
+      </c>
+      <c r="K21">
         <v>3.55</v>
       </c>
-      <c r="I21">
-        <v>4.8</v>
-      </c>
-      <c r="J21">
-        <v>3.05</v>
-      </c>
-      <c r="K21">
-        <v>3.8</v>
-      </c>
       <c r="L21">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M21">
         <v>1.1</v>
       </c>
       <c r="N21">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="O21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P21">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="Q21">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R21">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S21">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="T21">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="U21">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W21">
         <v>1.79</v>
       </c>
       <c r="X21">
+        <v>11</v>
+      </c>
+      <c r="Y21">
         <v>12.5</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
+        <v>32</v>
+      </c>
+      <c r="AA21">
+        <v>110</v>
+      </c>
+      <c r="AB21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC21">
+        <v>7.8</v>
+      </c>
+      <c r="AD21">
+        <v>17.5</v>
+      </c>
+      <c r="AE21">
+        <v>70</v>
+      </c>
+      <c r="AF21">
+        <v>13</v>
+      </c>
+      <c r="AG21">
+        <v>11.5</v>
+      </c>
+      <c r="AH21">
+        <v>26</v>
+      </c>
+      <c r="AI21">
+        <v>90</v>
+      </c>
+      <c r="AJ21">
+        <v>36</v>
+      </c>
+      <c r="AK21">
+        <v>34</v>
+      </c>
+      <c r="AL21">
+        <v>60</v>
+      </c>
+      <c r="AM21">
+        <v>170</v>
+      </c>
+      <c r="AN21">
+        <v>29</v>
+      </c>
+      <c r="AO21">
+        <v>90</v>
+      </c>
+      <c r="AP21">
+        <v>9.6</v>
+      </c>
+      <c r="AQ21">
+        <v>10.5</v>
+      </c>
+      <c r="AR21">
+        <v>6.6</v>
+      </c>
+      <c r="AS21">
+        <v>7.8</v>
+      </c>
+      <c r="AT21">
+        <v>7</v>
+      </c>
+      <c r="AU21">
+        <v>6.8</v>
+      </c>
+      <c r="AV21">
+        <v>14.5</v>
+      </c>
+      <c r="AW21">
         <v>23</v>
       </c>
-      <c r="Z21">
-        <v>95</v>
-      </c>
-      <c r="AA21">
-        <v>1000</v>
-      </c>
-      <c r="AB21">
+      <c r="AX21">
+        <v>11</v>
+      </c>
+      <c r="AY21">
         <v>9.800000000000001</v>
       </c>
-      <c r="AC21">
-        <v>9</v>
-      </c>
-      <c r="AD21">
-        <v>970</v>
-      </c>
-      <c r="AE21">
-        <v>1000</v>
-      </c>
-      <c r="AF21">
-        <v>27</v>
-      </c>
-      <c r="AG21">
-        <v>18.5</v>
-      </c>
-      <c r="AH21">
-        <v>950</v>
-      </c>
-      <c r="AI21">
-        <v>1000</v>
-      </c>
-      <c r="AJ21">
-        <v>140</v>
-      </c>
-      <c r="AK21">
-        <v>130</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>1000</v>
-      </c>
-      <c r="AP21">
+      <c r="AZ21">
+        <v>18</v>
+      </c>
+      <c r="BA21">
+        <v>7.6</v>
+      </c>
+      <c r="BB21">
+        <v>6.8</v>
+      </c>
+      <c r="BC21">
+        <v>6.6</v>
+      </c>
+      <c r="BD21">
+        <v>7.2</v>
+      </c>
+      <c r="BE21">
         <v>7.4</v>
       </c>
-      <c r="AQ21">
-        <v>1.8</v>
-      </c>
-      <c r="AR21">
+      <c r="BF21">
+        <v>17</v>
+      </c>
+      <c r="BG21">
+        <v>7.6</v>
+      </c>
+      <c r="BH21">
+        <v>3.45</v>
+      </c>
+      <c r="BI21">
+        <v>2.72</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>4.4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>5.4</v>
+      </c>
+      <c r="BN21">
+        <v>5.7</v>
+      </c>
+      <c r="BO21">
+        <v>4.3</v>
+      </c>
+      <c r="BP21">
+        <v>25</v>
+      </c>
+      <c r="BQ21">
+        <v>4.2</v>
+      </c>
+      <c r="BR21">
+        <v>50</v>
+      </c>
+      <c r="BS21">
+        <v>4.8</v>
+      </c>
+      <c r="BT21">
+        <v>8.6</v>
+      </c>
+      <c r="BU21">
+        <v>5.6</v>
+      </c>
+      <c r="BV21">
+        <v>50</v>
+      </c>
+      <c r="BW21">
+        <v>4.8</v>
+      </c>
+      <c r="BX21">
+        <v>75</v>
+      </c>
+      <c r="BY21">
+        <v>5</v>
+      </c>
+      <c r="BZ21">
+        <v>44</v>
+      </c>
+      <c r="CA21">
         <v>4.9</v>
-      </c>
-      <c r="AS21">
-        <v>1.95</v>
-      </c>
-      <c r="AT21">
-        <v>6.6</v>
-      </c>
-      <c r="AU21">
-        <v>6</v>
-      </c>
-      <c r="AV21">
-        <v>1.9</v>
-      </c>
-      <c r="AW21">
-        <v>1.95</v>
-      </c>
-      <c r="AX21">
-        <v>1.82</v>
-      </c>
-      <c r="AY21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ21">
-        <v>5.6</v>
-      </c>
-      <c r="BA21">
-        <v>1.95</v>
-      </c>
-      <c r="BB21">
-        <v>6.4</v>
-      </c>
-      <c r="BC21">
-        <v>6</v>
-      </c>
-      <c r="BD21">
-        <v>1.95</v>
-      </c>
-      <c r="BE21">
-        <v>1.96</v>
-      </c>
-      <c r="BF21">
-        <v>1.96</v>
-      </c>
-      <c r="BG21">
-        <v>1.96</v>
-      </c>
-      <c r="BH21">
-        <v>1000</v>
-      </c>
-      <c r="BI21">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21">
-        <v>1000</v>
-      </c>
-      <c r="BK21">
-        <v>1.04</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>1.04</v>
-      </c>
-      <c r="BN21">
-        <v>1000</v>
-      </c>
-      <c r="BO21">
-        <v>1.04</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>1.04</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>1.04</v>
-      </c>
-      <c r="BT21">
-        <v>1000</v>
-      </c>
-      <c r="BU21">
-        <v>1.04</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>1.04</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>1.04</v>
-      </c>
-      <c r="BZ21">
-        <v>1000</v>
-      </c>
-      <c r="CA21">
-        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>160</v>
@@ -5930,22 +5930,22 @@
         <v>153</v>
       </c>
       <c r="F22">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="G22">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="H22">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I22">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J22">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L22">
         <v>1.47</v>
@@ -5954,202 +5954,202 @@
         <v>1.09</v>
       </c>
       <c r="N22">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O22">
         <v>1.4</v>
       </c>
       <c r="P22">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R22">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S22">
         <v>4.2</v>
       </c>
       <c r="T22">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U22">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="X22">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y22">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z22">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC22">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF22">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AG22">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH22">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ22">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK22">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN22">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP22">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="AR22">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS22">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU22">
         <v>6.8</v>
       </c>
       <c r="AV22">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="AW22">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="AX22">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AY22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>9.4</v>
+      </c>
+      <c r="BA22">
+        <v>26</v>
+      </c>
+      <c r="BB22">
+        <v>7.8</v>
+      </c>
+      <c r="BC22">
+        <v>7.6</v>
+      </c>
+      <c r="BD22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE22">
         <v>10</v>
       </c>
-      <c r="AZ22">
-        <v>4.1</v>
-      </c>
-      <c r="BA22">
-        <v>5</v>
-      </c>
-      <c r="BB22">
-        <v>5.4</v>
-      </c>
-      <c r="BC22">
-        <v>5.9</v>
-      </c>
-      <c r="BD22">
-        <v>14</v>
-      </c>
-      <c r="BE22">
-        <v>5</v>
-      </c>
       <c r="BF22">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BG22">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI22">
-        <v>1.26</v>
+        <v>2.8</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK22">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO22">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU22">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB22" t="s">
         <v>160</v>
@@ -6172,7 +6172,7 @@
         <v>154</v>
       </c>
       <c r="F23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G23">
         <v>1.77</v>
@@ -6181,7 +6181,7 @@
         <v>5.2</v>
       </c>
       <c r="I23">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J23">
         <v>3.95</v>
@@ -6205,7 +6205,7 @@
         <v>2</v>
       </c>
       <c r="Q23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R23">
         <v>1.39</v>
@@ -6214,10 +6214,10 @@
         <v>3.3</v>
       </c>
       <c r="T23">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V23">
         <v>1.21</v>
@@ -6226,13 +6226,13 @@
         <v>2.28</v>
       </c>
       <c r="X23">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y23">
         <v>970</v>
       </c>
       <c r="Z23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA23">
         <v>1000</v>
@@ -6274,7 +6274,7 @@
         <v>1000</v>
       </c>
       <c r="AN23">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AO23">
         <v>1000</v>
@@ -6286,10 +6286,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT23">
         <v>7.6</v>
@@ -6298,10 +6298,10 @@
         <v>7.4</v>
       </c>
       <c r="AV23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX23">
         <v>8.6</v>
@@ -6310,10 +6310,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BA23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB23">
         <v>14</v>
@@ -6322,22 +6322,22 @@
         <v>15</v>
       </c>
       <c r="BD23">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF23">
         <v>8</v>
       </c>
       <c r="BG23">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="BJ23">
         <v>1000</v>
@@ -6349,49 +6349,49 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BN23">
         <v>1000</v>
       </c>
       <c r="BO23">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BP23">
         <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BT23">
         <v>1000</v>
       </c>
       <c r="BU23">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="CB23" t="s">
         <v>160</v>
@@ -6414,22 +6414,22 @@
         <v>155</v>
       </c>
       <c r="F24">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="G24">
-        <v>990</v>
+        <v>1.31</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="I24">
-        <v>990</v>
+        <v>16.5</v>
       </c>
       <c r="J24">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="K24">
-        <v>950</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6438,19 +6438,19 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="O24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q24">
         <v>1.13</v>
       </c>
       <c r="R24">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="S24">
         <v>1.13</v>
@@ -6462,118 +6462,118 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH24">
         <v>1000</v>
@@ -6656,19 +6656,19 @@
         <v>156</v>
       </c>
       <c r="F25">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="G25">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="H25">
         <v>2.52</v>
       </c>
       <c r="I25">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="J25">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K25">
         <v>3.75</v>
@@ -6680,202 +6680,202 @@
         <v>1.06</v>
       </c>
       <c r="N25">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O25">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="Q25">
         <v>1.73</v>
       </c>
       <c r="R25">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S25">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T25">
+        <v>1.67</v>
+      </c>
+      <c r="U25">
+        <v>2.34</v>
+      </c>
+      <c r="V25">
         <v>1.6</v>
-      </c>
-      <c r="U25">
-        <v>2.2</v>
-      </c>
-      <c r="V25">
-        <v>1.52</v>
       </c>
       <c r="W25">
         <v>1.5</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y25">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB25">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AC25">
+        <v>8.4</v>
+      </c>
+      <c r="AD25">
+        <v>12.5</v>
+      </c>
+      <c r="AE25">
+        <v>29</v>
+      </c>
+      <c r="AF25">
+        <v>22</v>
+      </c>
+      <c r="AG25">
+        <v>13.5</v>
+      </c>
+      <c r="AH25">
+        <v>16.5</v>
+      </c>
+      <c r="AI25">
+        <v>44</v>
+      </c>
+      <c r="AJ25">
+        <v>55</v>
+      </c>
+      <c r="AK25">
+        <v>38</v>
+      </c>
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>90</v>
+      </c>
+      <c r="AN25">
+        <v>25</v>
+      </c>
+      <c r="AO25">
+        <v>20</v>
+      </c>
+      <c r="AP25">
+        <v>15</v>
+      </c>
+      <c r="AQ25">
+        <v>11</v>
+      </c>
+      <c r="AR25">
+        <v>16</v>
+      </c>
+      <c r="AS25">
+        <v>8</v>
+      </c>
+      <c r="AT25">
         <v>12</v>
       </c>
-      <c r="AD25">
-        <v>970</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>970</v>
-      </c>
-      <c r="AH25">
-        <v>970</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
+      <c r="AU25">
+        <v>7.6</v>
+      </c>
+      <c r="AV25">
         <v>10.5</v>
       </c>
-      <c r="AQ25">
-        <v>8.6</v>
-      </c>
-      <c r="AR25">
-        <v>11</v>
-      </c>
-      <c r="AS25">
-        <v>1.31</v>
-      </c>
-      <c r="AT25">
-        <v>9</v>
-      </c>
-      <c r="AU25">
-        <v>6</v>
-      </c>
-      <c r="AV25">
+      <c r="AW25">
+        <v>18.5</v>
+      </c>
+      <c r="AX25">
+        <v>17</v>
+      </c>
+      <c r="AY25">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>25</v>
+      </c>
+      <c r="BB25">
+        <v>8.4</v>
+      </c>
+      <c r="BC25">
+        <v>23</v>
+      </c>
+      <c r="BD25">
         <v>8.199999999999999</v>
       </c>
-      <c r="AW25">
-        <v>1.31</v>
-      </c>
-      <c r="AX25">
-        <v>12</v>
-      </c>
-      <c r="AY25">
-        <v>8.6</v>
-      </c>
-      <c r="AZ25">
-        <v>10</v>
-      </c>
-      <c r="BA25">
-        <v>1.31</v>
-      </c>
-      <c r="BB25">
-        <v>1.31</v>
-      </c>
-      <c r="BC25">
-        <v>1.31</v>
-      </c>
-      <c r="BD25">
-        <v>1.31</v>
-      </c>
       <c r="BE25">
-        <v>1.31</v>
+        <v>34</v>
       </c>
       <c r="BF25">
-        <v>1.31</v>
+        <v>16</v>
       </c>
       <c r="BG25">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BH25">
         <v>1000</v>
       </c>
       <c r="BI25">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
       </c>
       <c r="BK25">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BN25">
         <v>1000</v>
       </c>
       <c r="BO25">
-        <v>1.67</v>
+        <v>5.1</v>
       </c>
       <c r="BP25">
         <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BT25">
         <v>1000</v>
       </c>
       <c r="BU25">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="BZ25">
         <v>1000</v>
       </c>
       <c r="CA25">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="CB25" t="s">
         <v>160</v>
@@ -6901,10 +6901,10 @@
         <v>2.2</v>
       </c>
       <c r="G26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H26">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I26">
         <v>4.3</v>
@@ -6919,7 +6919,7 @@
         <v>1.56</v>
       </c>
       <c r="M26">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N26">
         <v>2.68</v>
@@ -6928,16 +6928,16 @@
         <v>1.51</v>
       </c>
       <c r="P26">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q26">
         <v>2.56</v>
       </c>
       <c r="R26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S26">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T26">
         <v>2.1</v>
@@ -6952,172 +6952,172 @@
         <v>1.76</v>
       </c>
       <c r="X26">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y26">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB26">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC26">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD26">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF26">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG26">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
-        <v>2.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26">
-        <v>2.6</v>
+        <v>20</v>
       </c>
       <c r="AS26">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU26">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>2.32</v>
+        <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="AX26">
-        <v>2.22</v>
+        <v>11</v>
       </c>
       <c r="AY26">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA26">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB26">
-        <v>2.6</v>
+        <v>12</v>
       </c>
       <c r="BC26">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD26">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="BE26">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF26">
-        <v>2.6</v>
+        <v>21</v>
       </c>
       <c r="BG26">
-        <v>2.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH26">
         <v>1000</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="CB26" t="s">
         <v>160</v>
@@ -7140,19 +7140,19 @@
         <v>158</v>
       </c>
       <c r="F27">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G27">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="H27">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I27">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J27">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7170,7 +7170,7 @@
         <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q27">
         <v>2.06</v>
@@ -7182,184 +7182,184 @@
         <v>3.7</v>
       </c>
       <c r="T27">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U27">
         <v>2.08</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="X27">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y27">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z27">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AA27">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB27">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD27">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF27">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG27">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH27">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI27">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ27">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK27">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL27">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM27">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN27">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP27">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27">
-        <v>2.66</v>
+        <v>11.5</v>
       </c>
       <c r="AR27">
-        <v>2.92</v>
+        <v>22</v>
       </c>
       <c r="AS27">
-        <v>3.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT27">
-        <v>2.5</v>
+        <v>8.4</v>
       </c>
       <c r="AU27">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="AV27">
-        <v>2.76</v>
+        <v>14</v>
       </c>
       <c r="AW27">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX27">
-        <v>2.72</v>
+        <v>5.9</v>
       </c>
       <c r="AY27">
-        <v>2.62</v>
+        <v>10</v>
       </c>
       <c r="AZ27">
-        <v>2.82</v>
+        <v>16.5</v>
       </c>
       <c r="BA27">
-        <v>3.25</v>
+        <v>22</v>
       </c>
       <c r="BB27">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BC27">
-        <v>2.92</v>
+        <v>7.2</v>
       </c>
       <c r="BD27">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="BF27">
-        <v>2.84</v>
+        <v>15</v>
       </c>
       <c r="BG27">
-        <v>3.25</v>
+        <v>34</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="CB27" t="s">
         <v>160</v>
@@ -7382,31 +7382,31 @@
         <v>159</v>
       </c>
       <c r="F28">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H28">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I28">
         <v>2</v>
       </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L28">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M28">
         <v>1.08</v>
       </c>
       <c r="N28">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O28">
         <v>1.37</v>
@@ -7415,19 +7415,19 @@
         <v>1.8</v>
       </c>
       <c r="Q28">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R28">
         <v>1.31</v>
       </c>
       <c r="S28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T28">
         <v>1.89</v>
       </c>
       <c r="U28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V28">
         <v>2</v>
@@ -7436,172 +7436,172 @@
         <v>1.26</v>
       </c>
       <c r="X28">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y28">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="Z28">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB28">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC28">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD28">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG28">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO28">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AP28">
-        <v>2.34</v>
+        <v>11</v>
       </c>
       <c r="AQ28">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="AR28">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="AS28">
-        <v>2.8</v>
+        <v>19.5</v>
       </c>
       <c r="AT28">
-        <v>2.34</v>
+        <v>12.5</v>
       </c>
       <c r="AU28">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV28">
-        <v>2.26</v>
+        <v>9.4</v>
       </c>
       <c r="AW28">
-        <v>2.8</v>
+        <v>18.5</v>
       </c>
       <c r="AX28">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="AY28">
-        <v>2.44</v>
+        <v>15.5</v>
       </c>
       <c r="AZ28">
-        <v>2.78</v>
+        <v>17.5</v>
       </c>
       <c r="BA28">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB28">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC28">
-        <v>2.8</v>
+        <v>23</v>
       </c>
       <c r="BD28">
-        <v>2.8</v>
+        <v>28</v>
       </c>
       <c r="BE28">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF28">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG28">
-        <v>2.38</v>
+        <v>13.5</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI28">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK28">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO28">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU28">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB28" t="s">
         <v>160</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="175">
   <si>
     <t>League</t>
   </si>
@@ -274,12 +274,21 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Nigerian Premier League</t>
+  </si>
+  <si>
+    <t>Peruvian Segunda Division</t>
+  </si>
+  <si>
     <t>Finnish Veikkausliiga</t>
   </si>
   <si>
     <t>Algerian Ligue 1</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Colombian Primera B</t>
   </si>
   <si>
@@ -310,15 +319,24 @@
     <t>15:00:00</t>
   </si>
   <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:00:00</t>
   </si>
   <si>
@@ -364,6 +382,12 @@
     <t>Inter Toronto FC</t>
   </si>
   <si>
+    <t>Shooting Stars</t>
+  </si>
+  <si>
+    <t>AD Cantolao</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
@@ -373,9 +397,15 @@
     <t>ES Ben Aknoun</t>
   </si>
   <si>
+    <t>Sport Huancayo Res</t>
+  </si>
+  <si>
     <t>Belouizdad</t>
   </si>
   <si>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
     <t>Leones FC</t>
   </si>
   <si>
@@ -445,6 +475,12 @@
     <t>FC Supra du Quebec</t>
   </si>
   <si>
+    <t>Kano Pillars FC</t>
+  </si>
+  <si>
+    <t>Santos FC de Ica</t>
+  </si>
+  <si>
     <t>FC Inter Turku</t>
   </si>
   <si>
@@ -454,9 +490,15 @@
     <t>JS El Biar</t>
   </si>
   <si>
+    <t>Club ADA Jaén</t>
+  </si>
+  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>CD Cuenca Juniors</t>
+  </si>
+  <si>
     <t>Barranquilla</t>
   </si>
   <si>
@@ -496,7 +538,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 10:38:39</t>
+    <t>2026-10-06 12:50:18</t>
   </si>
 </sst>
 </file>
@@ -828,7 +870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1078,16 +1120,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F2">
         <v>3.05</v>
@@ -1096,10 +1138,10 @@
         <v>3.15</v>
       </c>
       <c r="H2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
         <v>4.1</v>
@@ -1117,19 +1159,19 @@
         <v>7.6</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
         <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="T2">
         <v>1.43</v>
@@ -1138,7 +1180,7 @@
         <v>3.15</v>
       </c>
       <c r="V2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
         <v>1.46</v>
@@ -1171,7 +1213,7 @@
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>13</v>
@@ -1189,7 +1231,7 @@
         <v>28</v>
       </c>
       <c r="AM2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AN2">
         <v>14.5</v>
@@ -1198,7 +1240,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ2">
         <v>17.5</v>
@@ -1210,7 +1252,7 @@
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2">
         <v>10</v>
@@ -1228,7 +1270,7 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2">
         <v>21</v>
@@ -1243,31 +1285,31 @@
         <v>24</v>
       </c>
       <c r="BE2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>5.2</v>
       </c>
       <c r="BI2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ2">
         <v>8.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>60</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>7</v>
@@ -1276,43 +1318,43 @@
         <v>6.2</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>24</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
         <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>12</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1320,16 +1362,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -1347,10 +1389,10 @@
         <v>5.6</v>
       </c>
       <c r="K3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1374,7 +1416,7 @@
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U3">
         <v>1.67</v>
@@ -1392,7 +1434,7 @@
         <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA3">
         <v>9.800000000000001</v>
@@ -1422,7 +1464,7 @@
         <v>50</v>
       </c>
       <c r="AJ3">
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="AK3">
         <v>260</v>
@@ -1434,10 +1476,10 @@
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AO3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP3">
         <v>15.5</v>
@@ -1464,7 +1506,7 @@
         <v>14</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY3">
         <v>38</v>
@@ -1476,19 +1518,19 @@
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF3">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
         <v>5.8</v>
@@ -1503,13 +1545,13 @@
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
         <v>15.5</v>
@@ -1521,7 +1563,7 @@
         <v>130</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BR3">
         <v>120</v>
@@ -1539,22 +1581,22 @@
         <v>7.8</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX3">
         <v>29</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA3">
         <v>7.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1562,22 +1604,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F4">
         <v>2.36</v>
       </c>
       <c r="G4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H4">
         <v>3.35</v>
@@ -1592,34 +1634,34 @@
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
         <v>1.4</v>
@@ -1628,19 +1670,19 @@
         <v>1.68</v>
       </c>
       <c r="X4">
+        <v>10.5</v>
+      </c>
+      <c r="Y4">
         <v>11.5</v>
       </c>
-      <c r="Y4">
-        <v>12</v>
-      </c>
       <c r="Z4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1649,115 +1691,115 @@
         <v>16</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>80</v>
       </c>
       <c r="AJ4">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AK4">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP4">
         <v>9</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA4">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BD4">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH4">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
         <v>24</v>
@@ -1766,37 +1808,37 @@
         <v>4.1</v>
       </c>
       <c r="BR4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS4">
+        <v>4.5</v>
+      </c>
+      <c r="BT4">
+        <v>8</v>
+      </c>
+      <c r="BU4">
+        <v>5</v>
+      </c>
+      <c r="BV4">
+        <v>42</v>
+      </c>
+      <c r="BW4">
         <v>4.4</v>
       </c>
-      <c r="BT4">
-        <v>7.8</v>
-      </c>
-      <c r="BU4">
-        <v>4.9</v>
-      </c>
-      <c r="BV4">
-        <v>38</v>
-      </c>
-      <c r="BW4">
-        <v>4.3</v>
-      </c>
       <c r="BX4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY4">
+        <v>4.6</v>
+      </c>
+      <c r="BZ4">
+        <v>50</v>
+      </c>
+      <c r="CA4">
         <v>4.5</v>
       </c>
-      <c r="BZ4">
-        <v>46</v>
-      </c>
-      <c r="CA4">
-        <v>4.4</v>
-      </c>
       <c r="CB4" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1804,19 +1846,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G5">
         <v>1.66</v>
@@ -1834,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
         <v>1.09</v>
@@ -1846,7 +1888,7 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1861,13 +1903,13 @@
         <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="V5">
         <v>1.1</v>
       </c>
       <c r="W5">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1978,67 +2020,67 @@
         <v>5.1</v>
       </c>
       <c r="BH5">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BI5">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK5">
-        <v>1.44</v>
+        <v>4.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.44</v>
+        <v>6.6</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO5">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS5">
-        <v>1.44</v>
+        <v>5.9</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU5">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.44</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA5">
-        <v>1.44</v>
+        <v>5.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2046,85 +2088,85 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="R6">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
         <v>23</v>
       </c>
       <c r="AA6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2133,7 +2175,7 @@
         <v>14.5</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6">
         <v>21</v>
@@ -2145,7 +2187,7 @@
         <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
         <v>42</v>
@@ -2154,31 +2196,31 @@
         <v>29</v>
       </c>
       <c r="AL6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6">
         <v>15.5</v>
       </c>
       <c r="AS6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU6">
         <v>7.2</v>
@@ -2187,7 +2229,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AX6">
         <v>14.5</v>
@@ -2199,88 +2241,88 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
+        <v>5.6</v>
+      </c>
+      <c r="BE6">
+        <v>5.5</v>
+      </c>
+      <c r="BF6">
+        <v>14.5</v>
+      </c>
+      <c r="BG6">
+        <v>16</v>
+      </c>
+      <c r="BH6">
+        <v>4.4</v>
+      </c>
+      <c r="BI6">
+        <v>3.15</v>
+      </c>
+      <c r="BJ6">
+        <v>10.5</v>
+      </c>
+      <c r="BK6">
+        <v>3.55</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
         <v>5.2</v>
       </c>
-      <c r="BE6">
-        <v>5.1</v>
-      </c>
-      <c r="BF6">
-        <v>15.5</v>
-      </c>
-      <c r="BG6">
-        <v>17.5</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2288,67 +2330,67 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G7">
         <v>7.4</v>
       </c>
       <c r="H7">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="I7">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="W7">
         <v>1.16</v>
@@ -2357,10 +2399,10 @@
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AA7">
         <v>970</v>
@@ -2372,10 +2414,10 @@
         <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF7">
         <v>1000</v>
@@ -2408,13 +2450,13 @@
         <v>970</v>
       </c>
       <c r="AP7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AQ7">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR7">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AS7">
         <v>10.5</v>
@@ -2423,40 +2465,40 @@
         <v>14.5</v>
       </c>
       <c r="AU7">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AV7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW7">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AX7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AY7">
-        <v>2.04</v>
+        <v>16</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BB7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BC7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BD7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BE7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BF7">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BG7">
         <v>5.6</v>
@@ -2522,7 +2564,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2530,34 +2572,34 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F8">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I8">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J8">
         <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.42</v>
@@ -2566,13 +2608,13 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
         <v>1.33</v>
       </c>
       <c r="P8">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2590,13 +2632,13 @@
         <v>2.04</v>
       </c>
       <c r="V8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X8">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
         <v>11</v>
@@ -2620,13 +2662,13 @@
         <v>28</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG8">
         <v>18.5</v>
       </c>
       <c r="AH8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI8">
         <v>46</v>
@@ -2650,7 +2692,7 @@
         <v>21</v>
       </c>
       <c r="AP8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
         <v>8</v>
@@ -2668,13 +2710,13 @@
         <v>7</v>
       </c>
       <c r="AV8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2683,25 +2725,25 @@
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB8">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BD8">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE8">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BG8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2764,7 +2806,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2772,70 +2814,70 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="H9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>3.3</v>
       </c>
       <c r="J9">
         <v>1.12</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L9">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="O9">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="Q9">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
         <v>1.13</v>
       </c>
       <c r="S9">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="T9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3006,7 +3048,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3014,37 +3056,37 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="F10">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="G10">
         <v>2.08</v>
       </c>
       <c r="H10">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J10">
         <v>3.15</v>
       </c>
       <c r="K10">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10">
         <v>1.06</v>
@@ -3053,7 +3095,7 @@
         <v>2.74</v>
       </c>
       <c r="O10">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="P10">
         <v>1.63</v>
@@ -3062,7 +3104,7 @@
         <v>2.14</v>
       </c>
       <c r="R10">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="S10">
         <v>3.05</v>
@@ -3074,7 +3116,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W10">
         <v>1.92</v>
@@ -3248,7 +3290,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3256,40 +3298,40 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F11">
+        <v>2.46</v>
+      </c>
+      <c r="G11">
         <v>2.68</v>
       </c>
-      <c r="G11">
-        <v>3.35</v>
-      </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -3298,136 +3340,136 @@
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q11">
+        <v>1.46</v>
+      </c>
+      <c r="R11">
+        <v>1.71</v>
+      </c>
+      <c r="S11">
+        <v>2.12</v>
+      </c>
+      <c r="T11">
         <v>1.45</v>
       </c>
-      <c r="R11">
-        <v>1.69</v>
-      </c>
-      <c r="S11">
-        <v>2.14</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3490,7 +3532,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3498,241 +3540,241 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F12">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.88</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.95</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L12">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="R12">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S12">
-        <v>2.92</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3740,70 +3782,70 @@
         <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F13">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
-        <v>1.77</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="I13">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
         <v>1.08</v>
       </c>
-      <c r="N13">
-        <v>2.4</v>
-      </c>
       <c r="O13">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P13">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="Q13">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3914,1035 +3956,1035 @@
         <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
         <v>1000</v>
       </c>
       <c r="BK13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
         <v>1000</v>
       </c>
       <c r="BO13">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
         <v>1000</v>
       </c>
       <c r="BU13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>4.3</v>
+      </c>
+      <c r="H14">
+        <v>1.93</v>
+      </c>
+      <c r="I14">
+        <v>1.99</v>
+      </c>
+      <c r="J14">
+        <v>3.9</v>
+      </c>
+      <c r="K14">
+        <v>4.1</v>
+      </c>
+      <c r="L14">
+        <v>1.33</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>4.4</v>
+      </c>
+      <c r="O14">
+        <v>1.27</v>
+      </c>
+      <c r="P14">
+        <v>2.16</v>
+      </c>
+      <c r="Q14">
+        <v>1.8</v>
+      </c>
+      <c r="R14">
+        <v>1.46</v>
+      </c>
+      <c r="S14">
+        <v>2.96</v>
+      </c>
+      <c r="T14">
+        <v>1.74</v>
+      </c>
+      <c r="U14">
+        <v>2.26</v>
+      </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
+      <c r="W14">
+        <v>1.3</v>
+      </c>
+      <c r="X14">
+        <v>18</v>
+      </c>
+      <c r="Y14">
+        <v>11</v>
+      </c>
+      <c r="Z14">
+        <v>13</v>
+      </c>
+      <c r="AA14">
+        <v>23</v>
+      </c>
+      <c r="AB14">
+        <v>17</v>
+      </c>
+      <c r="AC14">
+        <v>9</v>
+      </c>
+      <c r="AD14">
+        <v>10.5</v>
+      </c>
+      <c r="AE14">
+        <v>19.5</v>
+      </c>
+      <c r="AF14">
+        <v>34</v>
+      </c>
+      <c r="AG14">
+        <v>17</v>
+      </c>
+      <c r="AH14">
+        <v>17.5</v>
+      </c>
+      <c r="AI14">
+        <v>32</v>
+      </c>
+      <c r="AJ14">
         <v>90</v>
       </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F14">
-        <v>2.32</v>
-      </c>
-      <c r="G14">
-        <v>2.6</v>
-      </c>
-      <c r="H14">
-        <v>3.4</v>
-      </c>
-      <c r="I14">
-        <v>4.1</v>
-      </c>
-      <c r="J14">
-        <v>2.94</v>
-      </c>
-      <c r="K14">
-        <v>3.3</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
       <c r="AK14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD14">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BF14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BI14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ14">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BK14">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL14">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BN14">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BO14">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BP14">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BQ14">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BR14">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="BS14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BT14">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BU14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BW14">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BZ14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="CB14" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="F15">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="G15">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="I15">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="O15">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="P15">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="Q15">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S15">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="T15">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V15">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="W15">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="X15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
         <v>1000</v>
       </c>
       <c r="AB15">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI15">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BJ15">
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BN15">
         <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BP15">
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="CB15" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="F16">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G16">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="H16">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I16">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J16">
+        <v>2.94</v>
+      </c>
+      <c r="K16">
         <v>3.3</v>
       </c>
-      <c r="K16">
-        <v>3.65</v>
-      </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="G17">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="H17">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="I17">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="J17">
-        <v>2.94</v>
+        <v>1.1</v>
       </c>
       <c r="K17">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.66</v>
+        <v>1.08</v>
       </c>
       <c r="O17">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P17">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="Q17">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="S17">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
         <v>1000</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
         <v>1000</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4950,1059 +4992,1059 @@
         <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F18">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="G18">
-        <v>1.91</v>
+        <v>1.43</v>
       </c>
       <c r="H18">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="J18">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="L18">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M18">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O18">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="Q18">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="R18">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="T18">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="U18">
-        <v>2.22</v>
+        <v>1.53</v>
       </c>
       <c r="V18">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="W18">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="X18">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Y18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z18">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="AA18">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
+        <v>7.4</v>
+      </c>
+      <c r="AC18">
+        <v>13.5</v>
+      </c>
+      <c r="AD18">
+        <v>55</v>
+      </c>
+      <c r="AE18">
+        <v>330</v>
+      </c>
+      <c r="AF18">
+        <v>7.4</v>
+      </c>
+      <c r="AG18">
+        <v>12.5</v>
+      </c>
+      <c r="AH18">
+        <v>44</v>
+      </c>
+      <c r="AI18">
+        <v>270</v>
+      </c>
+      <c r="AJ18">
+        <v>13</v>
+      </c>
+      <c r="AK18">
+        <v>18.5</v>
+      </c>
+      <c r="AL18">
+        <v>65</v>
+      </c>
+      <c r="AM18">
+        <v>340</v>
+      </c>
+      <c r="AN18">
+        <v>8.6</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
         <v>10.5</v>
       </c>
-      <c r="AC18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD18">
-        <v>18.5</v>
-      </c>
-      <c r="AE18">
-        <v>65</v>
-      </c>
-      <c r="AF18">
-        <v>12.5</v>
-      </c>
-      <c r="AG18">
-        <v>10.5</v>
-      </c>
-      <c r="AH18">
-        <v>19</v>
-      </c>
-      <c r="AI18">
-        <v>70</v>
-      </c>
-      <c r="AJ18">
-        <v>40</v>
-      </c>
-      <c r="AK18">
-        <v>19.5</v>
-      </c>
-      <c r="AL18">
-        <v>38</v>
-      </c>
-      <c r="AM18">
-        <v>110</v>
-      </c>
-      <c r="AN18">
-        <v>11</v>
-      </c>
-      <c r="AO18">
-        <v>65</v>
-      </c>
-      <c r="AP18">
-        <v>15.5</v>
-      </c>
       <c r="AQ18">
-        <v>16</v>
+        <v>5.1</v>
       </c>
       <c r="AR18">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AS18">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AT18">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="AU18">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AV18">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX18">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AY18">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="BA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BB18">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC18">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD18">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BE18">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BF18">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BG18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BH18">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="BJ18">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>7</v>
+        <v>1.29</v>
       </c>
       <c r="BN18">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>5.1</v>
+        <v>1.29</v>
       </c>
       <c r="BR18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>6</v>
+        <v>1.29</v>
       </c>
       <c r="BT18">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>7.2</v>
+        <v>1.29</v>
       </c>
       <c r="BV18">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="BX18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>6.6</v>
+        <v>1.29</v>
       </c>
       <c r="BZ18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>5.7</v>
+        <v>1.29</v>
       </c>
       <c r="CB18" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F19">
-        <v>2.32</v>
+        <v>1.49</v>
       </c>
       <c r="G19">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="H19">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="I19">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="J19">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="L19">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>2.52</v>
+      </c>
+      <c r="O19">
+        <v>1.55</v>
+      </c>
+      <c r="P19">
+        <v>1.38</v>
+      </c>
+      <c r="Q19">
+        <v>2.36</v>
+      </c>
+      <c r="R19">
         <v>1.09</v>
       </c>
-      <c r="N19">
-        <v>3.2</v>
-      </c>
-      <c r="O19">
-        <v>1.4</v>
-      </c>
-      <c r="P19">
-        <v>1.76</v>
-      </c>
-      <c r="Q19">
-        <v>2.2</v>
-      </c>
-      <c r="R19">
-        <v>1.29</v>
-      </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="T19">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="W19">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="X19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR19">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AS19">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT19">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU19">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV19">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW19">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX19">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY19">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA19">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BB19">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC19">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BD19">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE19">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF19">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
         <v>1000</v>
       </c>
       <c r="BK19">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
         <v>1000</v>
       </c>
       <c r="BO19">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
         <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F20">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="G20">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="H20">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="I20">
+        <v>3.9</v>
+      </c>
+      <c r="J20">
         <v>3.35</v>
-      </c>
-      <c r="J20">
-        <v>3.45</v>
       </c>
       <c r="K20">
         <v>3.6</v>
       </c>
       <c r="L20">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="M20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N20">
+        <v>3.2</v>
+      </c>
+      <c r="O20">
+        <v>1.39</v>
+      </c>
+      <c r="P20">
+        <v>1.73</v>
+      </c>
+      <c r="Q20">
+        <v>2.12</v>
+      </c>
+      <c r="R20">
+        <v>1.28</v>
+      </c>
+      <c r="S20">
         <v>3.9</v>
       </c>
-      <c r="O20">
-        <v>1.31</v>
-      </c>
-      <c r="P20">
-        <v>1.98</v>
-      </c>
-      <c r="Q20">
-        <v>1.91</v>
-      </c>
-      <c r="R20">
-        <v>1.37</v>
-      </c>
-      <c r="S20">
-        <v>3.35</v>
-      </c>
       <c r="T20">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="X20">
+        <v>14</v>
+      </c>
+      <c r="Y20">
         <v>15</v>
       </c>
-      <c r="Y20">
-        <v>13.5</v>
-      </c>
       <c r="Z20">
+        <v>34</v>
+      </c>
+      <c r="AA20">
+        <v>100</v>
+      </c>
+      <c r="AB20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC20">
+        <v>9</v>
+      </c>
+      <c r="AD20">
+        <v>19</v>
+      </c>
+      <c r="AE20">
+        <v>65</v>
+      </c>
+      <c r="AF20">
+        <v>15</v>
+      </c>
+      <c r="AG20">
+        <v>12.5</v>
+      </c>
+      <c r="AH20">
+        <v>23</v>
+      </c>
+      <c r="AI20">
+        <v>75</v>
+      </c>
+      <c r="AJ20">
+        <v>32</v>
+      </c>
+      <c r="AK20">
+        <v>29</v>
+      </c>
+      <c r="AL20">
+        <v>50</v>
+      </c>
+      <c r="AM20">
+        <v>140</v>
+      </c>
+      <c r="AN20">
         <v>24</v>
       </c>
-      <c r="AA20">
-        <v>60</v>
-      </c>
-      <c r="AB20">
-        <v>11</v>
-      </c>
-      <c r="AC20">
-        <v>8</v>
-      </c>
-      <c r="AD20">
+      <c r="AO20">
+        <v>75</v>
+      </c>
+      <c r="AP20">
+        <v>10.5</v>
+      </c>
+      <c r="AQ20">
+        <v>10</v>
+      </c>
+      <c r="AR20">
+        <v>4.5</v>
+      </c>
+      <c r="AS20">
+        <v>5</v>
+      </c>
+      <c r="AT20">
+        <v>7.4</v>
+      </c>
+      <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
         <v>14.5</v>
       </c>
-      <c r="AE20">
-        <v>38</v>
-      </c>
-      <c r="AF20">
+      <c r="AW20">
+        <v>4.8</v>
+      </c>
+      <c r="AX20">
+        <v>10</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
         <v>17</v>
       </c>
-      <c r="AG20">
-        <v>11.5</v>
-      </c>
-      <c r="AH20">
-        <v>17.5</v>
-      </c>
-      <c r="AI20">
-        <v>46</v>
-      </c>
-      <c r="AJ20">
-        <v>36</v>
-      </c>
-      <c r="AK20">
-        <v>27</v>
-      </c>
-      <c r="AL20">
-        <v>40</v>
-      </c>
-      <c r="AM20">
-        <v>110</v>
-      </c>
-      <c r="AN20">
-        <v>19.5</v>
-      </c>
-      <c r="AO20">
-        <v>32</v>
-      </c>
-      <c r="AP20">
-        <v>12.5</v>
-      </c>
-      <c r="AQ20">
-        <v>11.5</v>
-      </c>
-      <c r="AR20">
+      <c r="BA20">
+        <v>4.9</v>
+      </c>
+      <c r="BB20">
+        <v>21</v>
+      </c>
+      <c r="BC20">
         <v>19</v>
       </c>
-      <c r="AS20">
-        <v>10</v>
-      </c>
-      <c r="AT20">
-        <v>9.6</v>
-      </c>
-      <c r="AU20">
-        <v>7.2</v>
-      </c>
-      <c r="AV20">
-        <v>12.5</v>
-      </c>
-      <c r="AW20">
-        <v>16</v>
-      </c>
-      <c r="AX20">
-        <v>14.5</v>
-      </c>
-      <c r="AY20">
-        <v>10.5</v>
-      </c>
-      <c r="AZ20">
+      <c r="BD20">
+        <v>4.7</v>
+      </c>
+      <c r="BE20">
+        <v>5</v>
+      </c>
+      <c r="BF20">
         <v>15</v>
       </c>
-      <c r="BA20">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB20">
-        <v>15.5</v>
-      </c>
-      <c r="BC20">
-        <v>23</v>
-      </c>
-      <c r="BD20">
-        <v>17</v>
-      </c>
-      <c r="BE20">
-        <v>11</v>
-      </c>
-      <c r="BF20">
-        <v>16.5</v>
-      </c>
       <c r="BG20">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BH20">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F21">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>4.1</v>
       </c>
       <c r="H21">
-        <v>3.85</v>
+        <v>2.22</v>
       </c>
       <c r="I21">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K21">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M21">
         <v>1.1</v>
       </c>
       <c r="N21">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O21">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Q21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R21">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T21">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U21">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="W21">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="X21">
         <v>11</v>
       </c>
       <c r="Y21">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z21">
+        <v>15</v>
+      </c>
+      <c r="AA21">
+        <v>36</v>
+      </c>
+      <c r="AB21">
+        <v>14</v>
+      </c>
+      <c r="AC21">
+        <v>9</v>
+      </c>
+      <c r="AD21">
+        <v>14</v>
+      </c>
+      <c r="AE21">
         <v>32</v>
       </c>
-      <c r="AA21">
-        <v>110</v>
-      </c>
-      <c r="AB21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC21">
-        <v>7.8</v>
-      </c>
-      <c r="AD21">
-        <v>17.5</v>
-      </c>
-      <c r="AE21">
+      <c r="AF21">
+        <v>32</v>
+      </c>
+      <c r="AG21">
+        <v>17</v>
+      </c>
+      <c r="AH21">
+        <v>25</v>
+      </c>
+      <c r="AI21">
+        <v>60</v>
+      </c>
+      <c r="AJ21">
+        <v>100</v>
+      </c>
+      <c r="AK21">
         <v>70</v>
       </c>
-      <c r="AF21">
-        <v>13</v>
-      </c>
-      <c r="AG21">
-        <v>11.5</v>
-      </c>
-      <c r="AH21">
-        <v>26</v>
-      </c>
-      <c r="AI21">
-        <v>90</v>
-      </c>
-      <c r="AJ21">
-        <v>36</v>
-      </c>
-      <c r="AK21">
-        <v>34</v>
-      </c>
       <c r="AL21">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AM21">
         <v>170</v>
       </c>
       <c r="AN21">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AO21">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="AP21">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AR21">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="AS21">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AT21">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AU21">
+        <v>5.6</v>
+      </c>
+      <c r="AV21">
+        <v>8.6</v>
+      </c>
+      <c r="AW21">
+        <v>21</v>
+      </c>
+      <c r="AX21">
+        <v>21</v>
+      </c>
+      <c r="AY21">
+        <v>13.5</v>
+      </c>
+      <c r="AZ21">
+        <v>17</v>
+      </c>
+      <c r="BA21">
+        <v>5.1</v>
+      </c>
+      <c r="BB21">
+        <v>5.3</v>
+      </c>
+      <c r="BC21">
+        <v>5.2</v>
+      </c>
+      <c r="BD21">
+        <v>5.3</v>
+      </c>
+      <c r="BE21">
+        <v>5.5</v>
+      </c>
+      <c r="BF21">
+        <v>5.3</v>
+      </c>
+      <c r="BG21">
+        <v>20</v>
+      </c>
+      <c r="BH21">
+        <v>3.05</v>
+      </c>
+      <c r="BI21">
+        <v>2.4</v>
+      </c>
+      <c r="BJ21">
+        <v>11</v>
+      </c>
+      <c r="BK21">
+        <v>5.4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>10</v>
+      </c>
+      <c r="BN21">
+        <v>7.2</v>
+      </c>
+      <c r="BO21">
+        <v>5.2</v>
+      </c>
+      <c r="BP21">
+        <v>38</v>
+      </c>
+      <c r="BQ21">
+        <v>8.4</v>
+      </c>
+      <c r="BR21">
+        <v>55</v>
+      </c>
+      <c r="BS21">
+        <v>9</v>
+      </c>
+      <c r="BT21">
+        <v>5.1</v>
+      </c>
+      <c r="BU21">
+        <v>3.75</v>
+      </c>
+      <c r="BV21">
+        <v>19</v>
+      </c>
+      <c r="BW21">
         <v>6.8</v>
       </c>
-      <c r="AV21">
-        <v>14.5</v>
-      </c>
-      <c r="AW21">
-        <v>23</v>
-      </c>
-      <c r="AX21">
-        <v>11</v>
-      </c>
-      <c r="AY21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21">
-        <v>18</v>
-      </c>
-      <c r="BA21">
-        <v>7.6</v>
-      </c>
-      <c r="BB21">
-        <v>6.8</v>
-      </c>
-      <c r="BC21">
-        <v>6.6</v>
-      </c>
-      <c r="BD21">
-        <v>7.2</v>
-      </c>
-      <c r="BE21">
-        <v>7.4</v>
-      </c>
-      <c r="BF21">
-        <v>17</v>
-      </c>
-      <c r="BG21">
-        <v>7.6</v>
-      </c>
-      <c r="BH21">
-        <v>3.45</v>
-      </c>
-      <c r="BI21">
-        <v>2.72</v>
-      </c>
-      <c r="BJ21">
-        <v>12.5</v>
-      </c>
-      <c r="BK21">
-        <v>4.4</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>5.4</v>
-      </c>
-      <c r="BN21">
-        <v>5.7</v>
-      </c>
-      <c r="BO21">
-        <v>4.3</v>
-      </c>
-      <c r="BP21">
-        <v>25</v>
-      </c>
-      <c r="BQ21">
-        <v>4.2</v>
-      </c>
-      <c r="BR21">
-        <v>50</v>
-      </c>
-      <c r="BS21">
-        <v>4.8</v>
-      </c>
-      <c r="BT21">
-        <v>8.6</v>
-      </c>
-      <c r="BU21">
-        <v>5.6</v>
-      </c>
-      <c r="BV21">
-        <v>50</v>
-      </c>
-      <c r="BW21">
-        <v>4.8</v>
-      </c>
       <c r="BX21">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BY21">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="BZ21">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="CA21">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="CB21" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F22">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="G22">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="H22">
+        <v>4.4</v>
+      </c>
+      <c r="I22">
+        <v>4.7</v>
+      </c>
+      <c r="J22">
+        <v>3.85</v>
+      </c>
+      <c r="K22">
         <v>4.1</v>
       </c>
-      <c r="I22">
-        <v>4.5</v>
-      </c>
-      <c r="J22">
-        <v>3.25</v>
-      </c>
-      <c r="K22">
-        <v>3.55</v>
-      </c>
       <c r="L22">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="M22">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O22">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="P22">
+        <v>2.14</v>
+      </c>
+      <c r="Q22">
+        <v>1.81</v>
+      </c>
+      <c r="R22">
+        <v>1.45</v>
+      </c>
+      <c r="S22">
+        <v>3.05</v>
+      </c>
+      <c r="T22">
         <v>1.75</v>
       </c>
-      <c r="Q22">
-        <v>2.2</v>
-      </c>
-      <c r="R22">
-        <v>1.29</v>
-      </c>
-      <c r="S22">
-        <v>4.2</v>
-      </c>
-      <c r="T22">
-        <v>2</v>
-      </c>
       <c r="U22">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="V22">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W22">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="X22">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Y22">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="Z22">
+        <v>40</v>
+      </c>
+      <c r="AA22">
+        <v>120</v>
+      </c>
+      <c r="AB22">
+        <v>10.5</v>
+      </c>
+      <c r="AC22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD22">
         <v>32</v>
-      </c>
-      <c r="AA22">
-        <v>95</v>
-      </c>
-      <c r="AB22">
-        <v>8.4</v>
-      </c>
-      <c r="AC22">
-        <v>7.8</v>
-      </c>
-      <c r="AD22">
-        <v>18.5</v>
       </c>
       <c r="AE22">
         <v>65</v>
@@ -6011,874 +6053,874 @@
         <v>12.5</v>
       </c>
       <c r="AG22">
+        <v>10.5</v>
+      </c>
+      <c r="AH22">
+        <v>34</v>
+      </c>
+      <c r="AI22">
+        <v>70</v>
+      </c>
+      <c r="AJ22">
+        <v>40</v>
+      </c>
+      <c r="AK22">
+        <v>19.5</v>
+      </c>
+      <c r="AL22">
+        <v>38</v>
+      </c>
+      <c r="AM22">
+        <v>110</v>
+      </c>
+      <c r="AN22">
+        <v>11</v>
+      </c>
+      <c r="AO22">
+        <v>65</v>
+      </c>
+      <c r="AP22">
+        <v>14.5</v>
+      </c>
+      <c r="AQ22">
+        <v>16</v>
+      </c>
+      <c r="AR22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS22">
+        <v>11</v>
+      </c>
+      <c r="AT22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>14.5</v>
+      </c>
+      <c r="AW22">
+        <v>10</v>
+      </c>
+      <c r="AX22">
+        <v>9.4</v>
+      </c>
+      <c r="AY22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ22">
+        <v>15</v>
+      </c>
+      <c r="BA22">
+        <v>10</v>
+      </c>
+      <c r="BB22">
+        <v>16.5</v>
+      </c>
+      <c r="BC22">
+        <v>15</v>
+      </c>
+      <c r="BD22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE22">
+        <v>10.5</v>
+      </c>
+      <c r="BF22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG22">
+        <v>10</v>
+      </c>
+      <c r="BH22">
+        <v>3.7</v>
+      </c>
+      <c r="BI22">
+        <v>3.4</v>
+      </c>
+      <c r="BJ22">
         <v>11.5</v>
       </c>
-      <c r="AH22">
-        <v>21</v>
-      </c>
-      <c r="AI22">
-        <v>80</v>
-      </c>
-      <c r="AJ22">
-        <v>27</v>
-      </c>
-      <c r="AK22">
-        <v>26</v>
-      </c>
-      <c r="AL22">
-        <v>55</v>
-      </c>
-      <c r="AM22">
-        <v>160</v>
-      </c>
-      <c r="AN22">
-        <v>20</v>
-      </c>
-      <c r="AO22">
-        <v>75</v>
-      </c>
-      <c r="AP22">
-        <v>10</v>
-      </c>
-      <c r="AQ22">
-        <v>11</v>
-      </c>
-      <c r="AR22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT22">
-        <v>7.4</v>
-      </c>
-      <c r="AU22">
-        <v>6.8</v>
-      </c>
-      <c r="AV22">
-        <v>15</v>
-      </c>
-      <c r="AW22">
-        <v>9.4</v>
-      </c>
-      <c r="AX22">
-        <v>10.5</v>
-      </c>
-      <c r="AY22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ22">
-        <v>9.4</v>
-      </c>
-      <c r="BA22">
-        <v>26</v>
-      </c>
-      <c r="BB22">
-        <v>7.8</v>
-      </c>
-      <c r="BC22">
-        <v>7.6</v>
-      </c>
-      <c r="BD22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE22">
-        <v>10</v>
-      </c>
-      <c r="BF22">
-        <v>17</v>
-      </c>
-      <c r="BG22">
-        <v>9.6</v>
-      </c>
-      <c r="BH22">
-        <v>3.1</v>
-      </c>
-      <c r="BI22">
-        <v>2.8</v>
-      </c>
-      <c r="BJ22">
-        <v>11</v>
-      </c>
       <c r="BK22">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BN22">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO22">
         <v>4.2</v>
       </c>
       <c r="BP22">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BQ22">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BR22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS22">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BT22">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BU22">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV22">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW22">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BX22">
         <v>55</v>
       </c>
       <c r="BY22">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BZ22">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="CA22">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="CB22" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="F23">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="G23">
-        <v>1.77</v>
+        <v>2.44</v>
       </c>
       <c r="H23">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="I23">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="J23">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="K23">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L23">
+        <v>1.5</v>
+      </c>
+      <c r="M23">
+        <v>1.09</v>
+      </c>
+      <c r="N23">
+        <v>3.25</v>
+      </c>
+      <c r="O23">
         <v>1.4</v>
       </c>
-      <c r="M23">
-        <v>1.06</v>
-      </c>
-      <c r="N23">
-        <v>3.9</v>
-      </c>
-      <c r="O23">
-        <v>1.3</v>
-      </c>
       <c r="P23">
+        <v>1.76</v>
+      </c>
+      <c r="Q23">
+        <v>2.2</v>
+      </c>
+      <c r="R23">
+        <v>1.29</v>
+      </c>
+      <c r="S23">
+        <v>4</v>
+      </c>
+      <c r="T23">
+        <v>1.92</v>
+      </c>
+      <c r="U23">
         <v>2</v>
       </c>
-      <c r="Q23">
-        <v>1.9</v>
-      </c>
-      <c r="R23">
+      <c r="V23">
         <v>1.39</v>
       </c>
-      <c r="S23">
-        <v>3.3</v>
-      </c>
-      <c r="T23">
-        <v>1.89</v>
-      </c>
-      <c r="U23">
-        <v>2.04</v>
-      </c>
-      <c r="V23">
-        <v>1.21</v>
-      </c>
       <c r="W23">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="X23">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y23">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Z23">
+        <v>25</v>
+      </c>
+      <c r="AA23">
+        <v>85</v>
+      </c>
+      <c r="AB23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC23">
+        <v>7.6</v>
+      </c>
+      <c r="AD23">
+        <v>15.5</v>
+      </c>
+      <c r="AE23">
+        <v>55</v>
+      </c>
+      <c r="AF23">
+        <v>14.5</v>
+      </c>
+      <c r="AG23">
+        <v>12</v>
+      </c>
+      <c r="AH23">
+        <v>21</v>
+      </c>
+      <c r="AI23">
+        <v>70</v>
+      </c>
+      <c r="AJ23">
+        <v>34</v>
+      </c>
+      <c r="AK23">
+        <v>29</v>
+      </c>
+      <c r="AL23">
         <v>50</v>
       </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>9.6</v>
-      </c>
-      <c r="AC23">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD23">
-        <v>950</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
+      <c r="AM23">
+        <v>150</v>
+      </c>
+      <c r="AN23">
+        <v>24</v>
+      </c>
+      <c r="AO23">
+        <v>55</v>
+      </c>
+      <c r="AP23">
+        <v>10</v>
+      </c>
+      <c r="AQ23">
         <v>10.5</v>
       </c>
-      <c r="AG23">
+      <c r="AR23">
+        <v>20</v>
+      </c>
+      <c r="AS23">
+        <v>32</v>
+      </c>
+      <c r="AT23">
+        <v>8.4</v>
+      </c>
+      <c r="AU23">
+        <v>6.8</v>
+      </c>
+      <c r="AV23">
+        <v>13</v>
+      </c>
+      <c r="AW23">
+        <v>20</v>
+      </c>
+      <c r="AX23">
+        <v>12.5</v>
+      </c>
+      <c r="AY23">
         <v>10.5</v>
-      </c>
-      <c r="AH23">
-        <v>950</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>970</v>
-      </c>
-      <c r="AK23">
-        <v>22</v>
-      </c>
-      <c r="AL23">
-        <v>42</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>970</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>12.5</v>
-      </c>
-      <c r="AQ23">
-        <v>14.5</v>
-      </c>
-      <c r="AR23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS23">
-        <v>4.5</v>
-      </c>
-      <c r="AT23">
-        <v>7.6</v>
-      </c>
-      <c r="AU23">
-        <v>7.4</v>
-      </c>
-      <c r="AV23">
-        <v>15.5</v>
-      </c>
-      <c r="AW23">
-        <v>21</v>
-      </c>
-      <c r="AX23">
-        <v>8.6</v>
-      </c>
-      <c r="AY23">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
         <v>17</v>
       </c>
       <c r="BA23">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BB23">
         <v>14</v>
       </c>
       <c r="BC23">
+        <v>19.5</v>
+      </c>
+      <c r="BD23">
+        <v>20</v>
+      </c>
+      <c r="BE23">
+        <v>10.5</v>
+      </c>
+      <c r="BF23">
+        <v>17</v>
+      </c>
+      <c r="BG23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH23">
+        <v>3.2</v>
+      </c>
+      <c r="BI23">
+        <v>2.68</v>
+      </c>
+      <c r="BJ23">
         <v>15</v>
       </c>
-      <c r="BD23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE23">
+      <c r="BK23">
+        <v>7.8</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>4.8</v>
+      </c>
+      <c r="BN23">
+        <v>6</v>
+      </c>
+      <c r="BO23">
+        <v>2.68</v>
+      </c>
+      <c r="BP23">
+        <v>25</v>
+      </c>
+      <c r="BQ23">
+        <v>4</v>
+      </c>
+      <c r="BR23">
+        <v>50</v>
+      </c>
+      <c r="BS23">
+        <v>4.4</v>
+      </c>
+      <c r="BT23">
+        <v>7.8</v>
+      </c>
+      <c r="BU23">
+        <v>5.5</v>
+      </c>
+      <c r="BV23">
+        <v>46</v>
+      </c>
+      <c r="BW23">
+        <v>4.3</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
         <v>4.5</v>
       </c>
-      <c r="BF23">
-        <v>8</v>
-      </c>
-      <c r="BG23">
-        <v>4.5</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
-      <c r="BI23">
-        <v>1.54</v>
-      </c>
-      <c r="BJ23">
-        <v>1000</v>
-      </c>
-      <c r="BK23">
-        <v>2.32</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>1.06</v>
-      </c>
-      <c r="BN23">
-        <v>1000</v>
-      </c>
-      <c r="BO23">
-        <v>1.7</v>
-      </c>
-      <c r="BP23">
-        <v>1000</v>
-      </c>
-      <c r="BQ23">
-        <v>2.64</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>1.06</v>
-      </c>
-      <c r="BT23">
-        <v>1000</v>
-      </c>
-      <c r="BU23">
-        <v>2.18</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.06</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.06</v>
-      </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA23">
-        <v>1.06</v>
+        <v>4.4</v>
       </c>
       <c r="CB23" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F24">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="G24">
-        <v>1.31</v>
+        <v>2.52</v>
       </c>
       <c r="H24">
+        <v>3.1</v>
+      </c>
+      <c r="I24">
+        <v>3.3</v>
+      </c>
+      <c r="J24">
+        <v>3.45</v>
+      </c>
+      <c r="K24">
+        <v>3.6</v>
+      </c>
+      <c r="L24">
+        <v>1.41</v>
+      </c>
+      <c r="M24">
+        <v>1.07</v>
+      </c>
+      <c r="N24">
+        <v>3.85</v>
+      </c>
+      <c r="O24">
+        <v>1.32</v>
+      </c>
+      <c r="P24">
+        <v>1.97</v>
+      </c>
+      <c r="Q24">
+        <v>1.95</v>
+      </c>
+      <c r="R24">
+        <v>1.38</v>
+      </c>
+      <c r="S24">
+        <v>3.35</v>
+      </c>
+      <c r="T24">
+        <v>1.76</v>
+      </c>
+      <c r="U24">
+        <v>2.22</v>
+      </c>
+      <c r="V24">
+        <v>1.43</v>
+      </c>
+      <c r="W24">
+        <v>1.66</v>
+      </c>
+      <c r="X24">
+        <v>14.5</v>
+      </c>
+      <c r="Y24">
+        <v>13.5</v>
+      </c>
+      <c r="Z24">
+        <v>23</v>
+      </c>
+      <c r="AA24">
+        <v>60</v>
+      </c>
+      <c r="AB24">
+        <v>11</v>
+      </c>
+      <c r="AC24">
+        <v>8</v>
+      </c>
+      <c r="AD24">
+        <v>14.5</v>
+      </c>
+      <c r="AE24">
+        <v>38</v>
+      </c>
+      <c r="AF24">
+        <v>16.5</v>
+      </c>
+      <c r="AG24">
+        <v>11.5</v>
+      </c>
+      <c r="AH24">
+        <v>17.5</v>
+      </c>
+      <c r="AI24">
+        <v>46</v>
+      </c>
+      <c r="AJ24">
+        <v>36</v>
+      </c>
+      <c r="AK24">
+        <v>27</v>
+      </c>
+      <c r="AL24">
+        <v>40</v>
+      </c>
+      <c r="AM24">
+        <v>110</v>
+      </c>
+      <c r="AN24">
+        <v>20</v>
+      </c>
+      <c r="AO24">
+        <v>32</v>
+      </c>
+      <c r="AP24">
+        <v>13</v>
+      </c>
+      <c r="AQ24">
+        <v>11.5</v>
+      </c>
+      <c r="AR24">
+        <v>19</v>
+      </c>
+      <c r="AS24">
         <v>10.5</v>
-      </c>
-      <c r="I24">
-        <v>16.5</v>
-      </c>
-      <c r="J24">
-        <v>6.4</v>
-      </c>
-      <c r="K24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L24">
-        <v>1.01</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>6.6</v>
-      </c>
-      <c r="O24">
-        <v>1.13</v>
-      </c>
-      <c r="P24">
-        <v>2.32</v>
-      </c>
-      <c r="Q24">
-        <v>1.13</v>
-      </c>
-      <c r="R24">
-        <v>1.33</v>
-      </c>
-      <c r="S24">
-        <v>1.13</v>
-      </c>
-      <c r="T24">
-        <v>1.11</v>
-      </c>
-      <c r="U24">
-        <v>1.11</v>
-      </c>
-      <c r="V24">
-        <v>1.06</v>
-      </c>
-      <c r="W24">
-        <v>4.2</v>
-      </c>
-      <c r="X24">
-        <v>42</v>
-      </c>
-      <c r="Y24">
-        <v>950</v>
-      </c>
-      <c r="Z24">
-        <v>150</v>
-      </c>
-      <c r="AA24">
-        <v>520</v>
-      </c>
-      <c r="AB24">
-        <v>15</v>
-      </c>
-      <c r="AC24">
-        <v>19.5</v>
-      </c>
-      <c r="AD24">
-        <v>55</v>
-      </c>
-      <c r="AE24">
-        <v>210</v>
-      </c>
-      <c r="AF24">
-        <v>11.5</v>
-      </c>
-      <c r="AG24">
-        <v>14</v>
-      </c>
-      <c r="AH24">
-        <v>36</v>
-      </c>
-      <c r="AI24">
-        <v>150</v>
-      </c>
-      <c r="AJ24">
-        <v>12</v>
-      </c>
-      <c r="AK24">
-        <v>16</v>
-      </c>
-      <c r="AL24">
-        <v>38</v>
-      </c>
-      <c r="AM24">
-        <v>150</v>
-      </c>
-      <c r="AN24">
-        <v>4</v>
-      </c>
-      <c r="AO24">
-        <v>220</v>
-      </c>
-      <c r="AP24">
-        <v>4.8</v>
-      </c>
-      <c r="AQ24">
-        <v>4.9</v>
-      </c>
-      <c r="AR24">
-        <v>5.2</v>
-      </c>
-      <c r="AS24">
-        <v>5.3</v>
       </c>
       <c r="AT24">
         <v>9.800000000000001</v>
       </c>
       <c r="AU24">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AV24">
+        <v>12.5</v>
+      </c>
+      <c r="AW24">
+        <v>15.5</v>
+      </c>
+      <c r="AX24">
+        <v>14</v>
+      </c>
+      <c r="AY24">
+        <v>10.5</v>
+      </c>
+      <c r="AZ24">
+        <v>15</v>
+      </c>
+      <c r="BA24">
+        <v>10</v>
+      </c>
+      <c r="BB24">
+        <v>15</v>
+      </c>
+      <c r="BC24">
+        <v>23</v>
+      </c>
+      <c r="BD24">
+        <v>16.5</v>
+      </c>
+      <c r="BE24">
+        <v>12</v>
+      </c>
+      <c r="BF24">
+        <v>16.5</v>
+      </c>
+      <c r="BG24">
+        <v>9.4</v>
+      </c>
+      <c r="BH24">
+        <v>3.4</v>
+      </c>
+      <c r="BI24">
+        <v>3.15</v>
+      </c>
+      <c r="BJ24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>14</v>
+      </c>
+      <c r="BN24">
+        <v>5.4</v>
+      </c>
+      <c r="BO24">
         <v>4.9</v>
       </c>
-      <c r="AW24">
-        <v>5.3</v>
-      </c>
-      <c r="AX24">
-        <v>7.6</v>
-      </c>
-      <c r="AY24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24">
-        <v>4.7</v>
-      </c>
-      <c r="BA24">
-        <v>5.2</v>
-      </c>
-      <c r="BB24">
-        <v>8</v>
-      </c>
-      <c r="BC24">
+      <c r="BP24">
+        <v>19</v>
+      </c>
+      <c r="BQ24">
+        <v>8.6</v>
+      </c>
+      <c r="BR24">
+        <v>32</v>
+      </c>
+      <c r="BS24">
         <v>10.5</v>
       </c>
-      <c r="BD24">
-        <v>4.7</v>
-      </c>
-      <c r="BE24">
-        <v>5.2</v>
-      </c>
-      <c r="BF24">
-        <v>2.92</v>
-      </c>
-      <c r="BG24">
-        <v>5.3</v>
-      </c>
-      <c r="BH24">
-        <v>1000</v>
-      </c>
-      <c r="BI24">
-        <v>1.04</v>
-      </c>
-      <c r="BJ24">
-        <v>1000</v>
-      </c>
-      <c r="BK24">
-        <v>1.04</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>1.04</v>
-      </c>
-      <c r="BN24">
-        <v>1000</v>
-      </c>
-      <c r="BO24">
-        <v>1.04</v>
-      </c>
-      <c r="BP24">
-        <v>1000</v>
-      </c>
-      <c r="BQ24">
-        <v>1.04</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>1.04</v>
-      </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB24" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="G25">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="H25">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="I25">
-        <v>2.68</v>
+        <v>4.2</v>
       </c>
       <c r="J25">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K25">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="O25">
+        <v>1.43</v>
+      </c>
+      <c r="P25">
+        <v>1.69</v>
+      </c>
+      <c r="Q25">
+        <v>2.28</v>
+      </c>
+      <c r="R25">
         <v>1.26</v>
       </c>
-      <c r="P25">
-        <v>2.12</v>
-      </c>
-      <c r="Q25">
-        <v>1.73</v>
-      </c>
-      <c r="R25">
-        <v>1.45</v>
-      </c>
       <c r="S25">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="T25">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="U25">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="V25">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="W25">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="X25">
-        <v>17.5</v>
+        <v>11</v>
       </c>
       <c r="Y25">
         <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AA25">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AB25">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD25">
+        <v>17.5</v>
+      </c>
+      <c r="AE25">
+        <v>70</v>
+      </c>
+      <c r="AF25">
+        <v>13</v>
+      </c>
+      <c r="AG25">
+        <v>11.5</v>
+      </c>
+      <c r="AH25">
+        <v>26</v>
+      </c>
+      <c r="AI25">
+        <v>90</v>
+      </c>
+      <c r="AJ25">
+        <v>36</v>
+      </c>
+      <c r="AK25">
+        <v>34</v>
+      </c>
+      <c r="AL25">
+        <v>60</v>
+      </c>
+      <c r="AM25">
+        <v>170</v>
+      </c>
+      <c r="AN25">
+        <v>29</v>
+      </c>
+      <c r="AO25">
+        <v>90</v>
+      </c>
+      <c r="AP25">
+        <v>9.6</v>
+      </c>
+      <c r="AQ25">
+        <v>10.5</v>
+      </c>
+      <c r="AR25">
+        <v>6.6</v>
+      </c>
+      <c r="AS25">
+        <v>7.8</v>
+      </c>
+      <c r="AT25">
+        <v>7</v>
+      </c>
+      <c r="AU25">
+        <v>6.8</v>
+      </c>
+      <c r="AV25">
+        <v>14.5</v>
+      </c>
+      <c r="AW25">
+        <v>22</v>
+      </c>
+      <c r="AX25">
+        <v>11</v>
+      </c>
+      <c r="AY25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ25">
+        <v>18</v>
+      </c>
+      <c r="BA25">
+        <v>7.8</v>
+      </c>
+      <c r="BB25">
+        <v>6.8</v>
+      </c>
+      <c r="BC25">
+        <v>6.6</v>
+      </c>
+      <c r="BD25">
+        <v>7.4</v>
+      </c>
+      <c r="BE25">
+        <v>8</v>
+      </c>
+      <c r="BF25">
+        <v>17</v>
+      </c>
+      <c r="BG25">
+        <v>7.8</v>
+      </c>
+      <c r="BH25">
+        <v>3.45</v>
+      </c>
+      <c r="BI25">
+        <v>2.72</v>
+      </c>
+      <c r="BJ25">
         <v>12.5</v>
       </c>
-      <c r="AE25">
-        <v>29</v>
-      </c>
-      <c r="AF25">
-        <v>22</v>
-      </c>
-      <c r="AG25">
-        <v>13.5</v>
-      </c>
-      <c r="AH25">
-        <v>16.5</v>
-      </c>
-      <c r="AI25">
+      <c r="BK25">
+        <v>3.95</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>4.8</v>
+      </c>
+      <c r="BN25">
+        <v>5.7</v>
+      </c>
+      <c r="BO25">
+        <v>4.3</v>
+      </c>
+      <c r="BP25">
+        <v>21</v>
+      </c>
+      <c r="BQ25">
+        <v>4</v>
+      </c>
+      <c r="BR25">
         <v>44</v>
       </c>
-      <c r="AJ25">
-        <v>55</v>
-      </c>
-      <c r="AK25">
-        <v>38</v>
-      </c>
-      <c r="AL25">
-        <v>46</v>
-      </c>
-      <c r="AM25">
-        <v>90</v>
-      </c>
-      <c r="AN25">
-        <v>25</v>
-      </c>
-      <c r="AO25">
-        <v>20</v>
-      </c>
-      <c r="AP25">
-        <v>15</v>
-      </c>
-      <c r="AQ25">
-        <v>11</v>
-      </c>
-      <c r="AR25">
-        <v>16</v>
-      </c>
-      <c r="AS25">
-        <v>8</v>
-      </c>
-      <c r="AT25">
-        <v>12</v>
-      </c>
-      <c r="AU25">
-        <v>7.6</v>
-      </c>
-      <c r="AV25">
-        <v>10.5</v>
-      </c>
-      <c r="AW25">
-        <v>18.5</v>
-      </c>
-      <c r="AX25">
-        <v>17</v>
-      </c>
-      <c r="AY25">
-        <v>11.5</v>
-      </c>
-      <c r="AZ25">
-        <v>14</v>
-      </c>
-      <c r="BA25">
-        <v>25</v>
-      </c>
-      <c r="BB25">
-        <v>8.4</v>
-      </c>
-      <c r="BC25">
-        <v>23</v>
-      </c>
-      <c r="BD25">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE25">
-        <v>34</v>
-      </c>
-      <c r="BF25">
-        <v>16</v>
-      </c>
-      <c r="BG25">
-        <v>16</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>3.05</v>
-      </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
-        <v>2.16</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>2.62</v>
-      </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
-        <v>5.1</v>
-      </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
-        <v>2.62</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
       <c r="BS25">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU25">
-        <v>1.88</v>
+        <v>5.4</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW25">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY25">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA25">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="CB25" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6886,725 +6928,1693 @@
         <v>81</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F26">
+        <v>1.97</v>
+      </c>
+      <c r="G26">
+        <v>2.02</v>
+      </c>
+      <c r="H26">
+        <v>4.5</v>
+      </c>
+      <c r="I26">
+        <v>4.8</v>
+      </c>
+      <c r="J26">
+        <v>3.4</v>
+      </c>
+      <c r="K26">
+        <v>3.55</v>
+      </c>
+      <c r="L26">
+        <v>1.47</v>
+      </c>
+      <c r="M26">
+        <v>1.09</v>
+      </c>
+      <c r="N26">
+        <v>3.25</v>
+      </c>
+      <c r="O26">
+        <v>1.41</v>
+      </c>
+      <c r="P26">
+        <v>1.74</v>
+      </c>
+      <c r="Q26">
         <v>2.2</v>
       </c>
-      <c r="G26">
-        <v>2.32</v>
-      </c>
-      <c r="H26">
-        <v>3.95</v>
-      </c>
-      <c r="I26">
-        <v>4.3</v>
-      </c>
-      <c r="J26">
-        <v>3.05</v>
-      </c>
-      <c r="K26">
-        <v>3.3</v>
-      </c>
-      <c r="L26">
-        <v>1.56</v>
-      </c>
-      <c r="M26">
-        <v>1.11</v>
-      </c>
-      <c r="N26">
-        <v>2.68</v>
-      </c>
-      <c r="O26">
-        <v>1.51</v>
-      </c>
-      <c r="P26">
-        <v>1.57</v>
-      </c>
-      <c r="Q26">
-        <v>2.56</v>
-      </c>
       <c r="R26">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="S26">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="T26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W26">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="X26">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="Y26">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Z26">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA26">
         <v>120</v>
       </c>
       <c r="AB26">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD26">
+        <v>18.5</v>
+      </c>
+      <c r="AE26">
+        <v>130</v>
+      </c>
+      <c r="AF26">
+        <v>11.5</v>
+      </c>
+      <c r="AG26">
+        <v>11.5</v>
+      </c>
+      <c r="AH26">
+        <v>22</v>
+      </c>
+      <c r="AI26">
+        <v>80</v>
+      </c>
+      <c r="AJ26">
+        <v>40</v>
+      </c>
+      <c r="AK26">
+        <v>25</v>
+      </c>
+      <c r="AL26">
+        <v>50</v>
+      </c>
+      <c r="AM26">
+        <v>160</v>
+      </c>
+      <c r="AN26">
+        <v>18.5</v>
+      </c>
+      <c r="AO26">
+        <v>90</v>
+      </c>
+      <c r="AP26">
+        <v>10</v>
+      </c>
+      <c r="AQ26">
+        <v>12</v>
+      </c>
+      <c r="AR26">
+        <v>9.4</v>
+      </c>
+      <c r="AS26">
+        <v>11.5</v>
+      </c>
+      <c r="AT26">
+        <v>7.2</v>
+      </c>
+      <c r="AU26">
+        <v>7</v>
+      </c>
+      <c r="AV26">
+        <v>16</v>
+      </c>
+      <c r="AW26">
+        <v>10.5</v>
+      </c>
+      <c r="AX26">
+        <v>10</v>
+      </c>
+      <c r="AY26">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26">
+        <v>18</v>
+      </c>
+      <c r="BA26">
+        <v>11</v>
+      </c>
+      <c r="BB26">
+        <v>11</v>
+      </c>
+      <c r="BC26">
+        <v>20</v>
+      </c>
+      <c r="BD26">
+        <v>10</v>
+      </c>
+      <c r="BE26">
+        <v>12</v>
+      </c>
+      <c r="BF26">
+        <v>16</v>
+      </c>
+      <c r="BG26">
+        <v>11</v>
+      </c>
+      <c r="BH26">
+        <v>3.1</v>
+      </c>
+      <c r="BI26">
+        <v>2.84</v>
+      </c>
+      <c r="BJ26">
+        <v>11</v>
+      </c>
+      <c r="BK26">
+        <v>6.2</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>12.5</v>
+      </c>
+      <c r="BN26">
+        <v>4.6</v>
+      </c>
+      <c r="BO26">
+        <v>4.1</v>
+      </c>
+      <c r="BP26">
+        <v>15.5</v>
+      </c>
+      <c r="BQ26">
+        <v>7.2</v>
+      </c>
+      <c r="BR26">
         <v>34</v>
       </c>
-      <c r="AE26">
-        <v>85</v>
-      </c>
-      <c r="AF26">
-        <v>13</v>
-      </c>
-      <c r="AG26">
-        <v>12</v>
-      </c>
-      <c r="AH26">
-        <v>55</v>
-      </c>
-      <c r="AI26">
-        <v>110</v>
-      </c>
-      <c r="AJ26">
-        <v>38</v>
-      </c>
-      <c r="AK26">
+      <c r="BS26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT26">
+        <v>7.8</v>
+      </c>
+      <c r="BU26">
+        <v>6.8</v>
+      </c>
+      <c r="BV26">
+        <v>44</v>
+      </c>
+      <c r="BW26">
+        <v>10.5</v>
+      </c>
+      <c r="BX26">
+        <v>60</v>
+      </c>
+      <c r="BY26">
+        <v>11</v>
+      </c>
+      <c r="BZ26">
         <v>34</v>
       </c>
-      <c r="AL26">
-        <v>70</v>
-      </c>
-      <c r="AM26">
-        <v>220</v>
-      </c>
-      <c r="AN26">
-        <v>36</v>
-      </c>
-      <c r="AO26">
-        <v>120</v>
-      </c>
-      <c r="AP26">
-        <v>8</v>
-      </c>
-      <c r="AQ26">
+      <c r="CA26">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR26">
-        <v>20</v>
-      </c>
-      <c r="AS26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT26">
-        <v>6.4</v>
-      </c>
-      <c r="AU26">
-        <v>6.4</v>
-      </c>
-      <c r="AV26">
-        <v>15.5</v>
-      </c>
-      <c r="AW26">
-        <v>9</v>
-      </c>
-      <c r="AX26">
-        <v>11</v>
-      </c>
-      <c r="AY26">
-        <v>10</v>
-      </c>
-      <c r="AZ26">
-        <v>16.5</v>
-      </c>
-      <c r="BA26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB26">
-        <v>12</v>
-      </c>
-      <c r="BC26">
-        <v>7.8</v>
-      </c>
-      <c r="BD26">
-        <v>9</v>
-      </c>
-      <c r="BE26">
-        <v>9.4</v>
-      </c>
-      <c r="BF26">
-        <v>21</v>
-      </c>
-      <c r="BG26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH26">
-        <v>1000</v>
-      </c>
-      <c r="BI26">
-        <v>1.77</v>
-      </c>
-      <c r="BJ26">
-        <v>16</v>
-      </c>
-      <c r="BK26">
-        <v>1.62</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>1.77</v>
-      </c>
-      <c r="BN26">
-        <v>5.6</v>
-      </c>
-      <c r="BO26">
-        <v>3.85</v>
-      </c>
-      <c r="BP26">
-        <v>28</v>
-      </c>
-      <c r="BQ26">
-        <v>1.67</v>
-      </c>
-      <c r="BR26">
-        <v>1000</v>
-      </c>
-      <c r="BS26">
-        <v>1.76</v>
-      </c>
-      <c r="BT26">
-        <v>10</v>
-      </c>
-      <c r="BU26">
-        <v>4.6</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>1.76</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>1.77</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>1.76</v>
-      </c>
       <c r="CB26" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27">
+        <v>1.71</v>
+      </c>
+      <c r="G27">
+        <v>1.77</v>
+      </c>
+      <c r="H27">
+        <v>5.2</v>
+      </c>
+      <c r="I27">
+        <v>5.7</v>
+      </c>
+      <c r="J27">
+        <v>3.95</v>
+      </c>
+      <c r="K27">
+        <v>4.3</v>
+      </c>
+      <c r="L27">
+        <v>1.4</v>
+      </c>
+      <c r="M27">
+        <v>1.06</v>
+      </c>
+      <c r="N27">
+        <v>3.95</v>
+      </c>
+      <c r="O27">
+        <v>1.31</v>
+      </c>
+      <c r="P27">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>1.89</v>
+      </c>
+      <c r="R27">
+        <v>1.4</v>
+      </c>
+      <c r="S27">
+        <v>3.3</v>
+      </c>
+      <c r="T27">
+        <v>1.89</v>
+      </c>
+      <c r="U27">
+        <v>2.04</v>
+      </c>
+      <c r="V27">
+        <v>1.21</v>
+      </c>
+      <c r="W27">
+        <v>2.3</v>
+      </c>
+      <c r="X27">
+        <v>16</v>
+      </c>
+      <c r="Y27">
+        <v>19</v>
+      </c>
+      <c r="Z27">
+        <v>80</v>
+      </c>
+      <c r="AA27">
+        <v>170</v>
+      </c>
+      <c r="AB27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>22</v>
+      </c>
+      <c r="AE27">
         <v>90</v>
       </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" t="s">
-        <v>158</v>
-      </c>
-      <c r="F27">
-        <v>2.1</v>
-      </c>
-      <c r="G27">
-        <v>2.18</v>
-      </c>
-      <c r="H27">
-        <v>3.9</v>
-      </c>
-      <c r="I27">
-        <v>4.2</v>
-      </c>
-      <c r="J27">
-        <v>3.45</v>
-      </c>
-      <c r="K27">
-        <v>3.6</v>
-      </c>
-      <c r="L27">
-        <v>1.44</v>
-      </c>
-      <c r="M27">
-        <v>1.08</v>
-      </c>
-      <c r="N27">
-        <v>3.5</v>
-      </c>
-      <c r="O27">
-        <v>1.36</v>
-      </c>
-      <c r="P27">
-        <v>1.85</v>
-      </c>
-      <c r="Q27">
-        <v>2.06</v>
-      </c>
-      <c r="R27">
-        <v>1.33</v>
-      </c>
-      <c r="S27">
-        <v>3.7</v>
-      </c>
-      <c r="T27">
-        <v>1.84</v>
-      </c>
-      <c r="U27">
-        <v>2.08</v>
-      </c>
-      <c r="V27">
-        <v>1.33</v>
-      </c>
-      <c r="W27">
-        <v>1.82</v>
-      </c>
-      <c r="X27">
-        <v>13.5</v>
-      </c>
-      <c r="Y27">
-        <v>13.5</v>
-      </c>
-      <c r="Z27">
-        <v>70</v>
-      </c>
-      <c r="AA27">
+      <c r="AF27">
+        <v>10.5</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+      <c r="AH27">
+        <v>21</v>
+      </c>
+      <c r="AI27">
         <v>90</v>
       </c>
-      <c r="AB27">
+      <c r="AJ27">
+        <v>19</v>
+      </c>
+      <c r="AK27">
+        <v>19</v>
+      </c>
+      <c r="AL27">
+        <v>75</v>
+      </c>
+      <c r="AM27">
+        <v>140</v>
+      </c>
+      <c r="AN27">
+        <v>10.5</v>
+      </c>
+      <c r="AO27">
+        <v>110</v>
+      </c>
+      <c r="AP27">
+        <v>14</v>
+      </c>
+      <c r="AQ27">
+        <v>14.5</v>
+      </c>
+      <c r="AR27">
+        <v>10.5</v>
+      </c>
+      <c r="AS27">
+        <v>13</v>
+      </c>
+      <c r="AT27">
+        <v>7.8</v>
+      </c>
+      <c r="AU27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27">
+        <v>16</v>
+      </c>
+      <c r="AW27">
+        <v>12</v>
+      </c>
+      <c r="AX27">
+        <v>9.6</v>
+      </c>
+      <c r="AY27">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC27">
-        <v>8</v>
-      </c>
-      <c r="AD27">
-        <v>19</v>
-      </c>
-      <c r="AE27">
-        <v>60</v>
-      </c>
-      <c r="AF27">
-        <v>14</v>
-      </c>
-      <c r="AG27">
-        <v>11.5</v>
-      </c>
-      <c r="AH27">
-        <v>18.5</v>
-      </c>
-      <c r="AI27">
-        <v>70</v>
-      </c>
-      <c r="AJ27">
-        <v>29</v>
-      </c>
-      <c r="AK27">
-        <v>25</v>
-      </c>
-      <c r="AL27">
-        <v>40</v>
-      </c>
-      <c r="AM27">
-        <v>120</v>
-      </c>
-      <c r="AN27">
-        <v>18</v>
-      </c>
-      <c r="AO27">
-        <v>60</v>
-      </c>
-      <c r="AP27">
-        <v>11.5</v>
-      </c>
-      <c r="AQ27">
-        <v>11.5</v>
-      </c>
-      <c r="AR27">
-        <v>22</v>
-      </c>
-      <c r="AS27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT27">
+      <c r="AZ27">
         <v>8.4</v>
       </c>
-      <c r="AU27">
-        <v>7</v>
-      </c>
-      <c r="AV27">
-        <v>14</v>
-      </c>
-      <c r="AW27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX27">
-        <v>5.9</v>
-      </c>
-      <c r="AY27">
+      <c r="BA27">
+        <v>12</v>
+      </c>
+      <c r="BB27">
+        <v>14.5</v>
+      </c>
+      <c r="BC27">
+        <v>15</v>
+      </c>
+      <c r="BD27">
         <v>10</v>
       </c>
-      <c r="AZ27">
-        <v>16.5</v>
-      </c>
-      <c r="BA27">
-        <v>22</v>
-      </c>
-      <c r="BB27">
-        <v>7.6</v>
-      </c>
-      <c r="BC27">
-        <v>7.2</v>
-      </c>
-      <c r="BD27">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE27">
+        <v>12.5</v>
+      </c>
+      <c r="BF27">
         <v>9.4</v>
       </c>
-      <c r="BF27">
-        <v>15</v>
-      </c>
       <c r="BG27">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="BJ27">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="BN27">
         <v>1000</v>
       </c>
       <c r="BO27">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="BP27">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="BR27">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="BT27">
         <v>1000</v>
       </c>
       <c r="BU27">
-        <v>5.5</v>
+        <v>2.16</v>
       </c>
       <c r="BV27">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
       </c>
       <c r="CA27">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="CB27" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28">
+        <v>1.22</v>
+      </c>
+      <c r="G28">
+        <v>1.3</v>
+      </c>
+      <c r="H28">
+        <v>10.5</v>
+      </c>
+      <c r="I28">
+        <v>16.5</v>
+      </c>
+      <c r="J28">
+        <v>6.4</v>
+      </c>
+      <c r="K28">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>6.6</v>
+      </c>
+      <c r="O28">
+        <v>1.13</v>
+      </c>
+      <c r="P28">
+        <v>2.8</v>
+      </c>
+      <c r="Q28">
+        <v>1.13</v>
+      </c>
+      <c r="R28">
+        <v>1.79</v>
+      </c>
+      <c r="S28">
+        <v>1.53</v>
+      </c>
+      <c r="T28">
+        <v>1.11</v>
+      </c>
+      <c r="U28">
+        <v>1.11</v>
+      </c>
+      <c r="V28">
+        <v>1.06</v>
+      </c>
+      <c r="W28">
+        <v>4.2</v>
+      </c>
+      <c r="X28">
+        <v>42</v>
+      </c>
+      <c r="Y28">
+        <v>950</v>
+      </c>
+      <c r="Z28">
+        <v>150</v>
+      </c>
+      <c r="AA28">
+        <v>520</v>
+      </c>
+      <c r="AB28">
+        <v>15</v>
+      </c>
+      <c r="AC28">
+        <v>19.5</v>
+      </c>
+      <c r="AD28">
+        <v>55</v>
+      </c>
+      <c r="AE28">
+        <v>210</v>
+      </c>
+      <c r="AF28">
+        <v>11.5</v>
+      </c>
+      <c r="AG28">
+        <v>14</v>
+      </c>
+      <c r="AH28">
+        <v>36</v>
+      </c>
+      <c r="AI28">
+        <v>150</v>
+      </c>
+      <c r="AJ28">
+        <v>12</v>
+      </c>
+      <c r="AK28">
+        <v>16</v>
+      </c>
+      <c r="AL28">
+        <v>38</v>
+      </c>
+      <c r="AM28">
+        <v>150</v>
+      </c>
+      <c r="AN28">
+        <v>4</v>
+      </c>
+      <c r="AO28">
+        <v>220</v>
+      </c>
+      <c r="AP28">
+        <v>4.8</v>
+      </c>
+      <c r="AQ28">
+        <v>4.9</v>
+      </c>
+      <c r="AR28">
+        <v>5.2</v>
+      </c>
+      <c r="AS28">
+        <v>5.3</v>
+      </c>
+      <c r="AT28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU28">
+        <v>13</v>
+      </c>
+      <c r="AV28">
+        <v>4.9</v>
+      </c>
+      <c r="AW28">
+        <v>5.3</v>
+      </c>
+      <c r="AX28">
+        <v>7.6</v>
+      </c>
+      <c r="AY28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28">
+        <v>4.7</v>
+      </c>
+      <c r="BA28">
+        <v>5.2</v>
+      </c>
+      <c r="BB28">
+        <v>8</v>
+      </c>
+      <c r="BC28">
+        <v>10.5</v>
+      </c>
+      <c r="BD28">
+        <v>4.7</v>
+      </c>
+      <c r="BE28">
+        <v>5.2</v>
+      </c>
+      <c r="BF28">
+        <v>2.92</v>
+      </c>
+      <c r="BG28">
+        <v>5.3</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.04</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.04</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.04</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.04</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.04</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.04</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.04</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.04</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.04</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.04</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29">
+        <v>2.74</v>
+      </c>
+      <c r="G29">
+        <v>2.94</v>
+      </c>
+      <c r="H29">
+        <v>2.56</v>
+      </c>
+      <c r="I29">
+        <v>2.72</v>
+      </c>
+      <c r="J29">
+        <v>3.6</v>
+      </c>
+      <c r="K29">
+        <v>3.75</v>
+      </c>
+      <c r="L29">
+        <v>1.33</v>
+      </c>
+      <c r="M29">
+        <v>1.06</v>
+      </c>
+      <c r="N29">
+        <v>4.3</v>
+      </c>
+      <c r="O29">
+        <v>1.26</v>
+      </c>
+      <c r="P29">
+        <v>2.12</v>
+      </c>
+      <c r="Q29">
+        <v>1.8</v>
+      </c>
+      <c r="R29">
+        <v>1.45</v>
+      </c>
+      <c r="S29">
+        <v>2.98</v>
+      </c>
+      <c r="T29">
+        <v>1.67</v>
+      </c>
+      <c r="U29">
+        <v>2.34</v>
+      </c>
+      <c r="V29">
+        <v>1.58</v>
+      </c>
+      <c r="W29">
+        <v>1.51</v>
+      </c>
+      <c r="X29">
+        <v>18</v>
+      </c>
+      <c r="Y29">
+        <v>12.5</v>
+      </c>
+      <c r="Z29">
+        <v>19</v>
+      </c>
+      <c r="AA29">
+        <v>46</v>
+      </c>
+      <c r="AB29">
+        <v>13.5</v>
+      </c>
+      <c r="AC29">
+        <v>8.4</v>
+      </c>
+      <c r="AD29">
+        <v>12.5</v>
+      </c>
+      <c r="AE29">
+        <v>29</v>
+      </c>
+      <c r="AF29">
+        <v>21</v>
+      </c>
+      <c r="AG29">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>16.5</v>
+      </c>
+      <c r="AI29">
+        <v>44</v>
+      </c>
+      <c r="AJ29">
+        <v>55</v>
+      </c>
+      <c r="AK29">
+        <v>36</v>
+      </c>
+      <c r="AL29">
+        <v>46</v>
+      </c>
+      <c r="AM29">
+        <v>90</v>
+      </c>
+      <c r="AN29">
+        <v>26</v>
+      </c>
+      <c r="AO29">
+        <v>21</v>
+      </c>
+      <c r="AP29">
+        <v>14.5</v>
+      </c>
+      <c r="AQ29">
+        <v>11</v>
+      </c>
+      <c r="AR29">
+        <v>16</v>
+      </c>
+      <c r="AS29">
+        <v>8.4</v>
+      </c>
+      <c r="AT29">
+        <v>12</v>
+      </c>
+      <c r="AU29">
+        <v>7.6</v>
+      </c>
+      <c r="AV29">
+        <v>11</v>
+      </c>
+      <c r="AW29">
+        <v>18.5</v>
+      </c>
+      <c r="AX29">
+        <v>16.5</v>
+      </c>
+      <c r="AY29">
+        <v>11.5</v>
+      </c>
+      <c r="AZ29">
+        <v>14.5</v>
+      </c>
+      <c r="BA29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB29">
+        <v>8.6</v>
+      </c>
+      <c r="BC29">
+        <v>7.8</v>
+      </c>
+      <c r="BD29">
+        <v>8.4</v>
+      </c>
+      <c r="BE29">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF29">
+        <v>17</v>
+      </c>
+      <c r="BG29">
+        <v>16.5</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>3.05</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>2.04</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>2.4</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.84</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>2.4</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>2.4</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.82</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>2.4</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>2.4</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>2.4</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
         <v>81</v>
       </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" t="s">
-        <v>132</v>
-      </c>
-      <c r="E28" t="s">
-        <v>159</v>
-      </c>
-      <c r="F28">
-        <v>4.4</v>
-      </c>
-      <c r="G28">
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30">
+        <v>2.18</v>
+      </c>
+      <c r="G30">
+        <v>2.32</v>
+      </c>
+      <c r="H30">
+        <v>3.95</v>
+      </c>
+      <c r="I30">
+        <v>4.3</v>
+      </c>
+      <c r="J30">
+        <v>3.05</v>
+      </c>
+      <c r="K30">
+        <v>3.3</v>
+      </c>
+      <c r="L30">
+        <v>1.56</v>
+      </c>
+      <c r="M30">
+        <v>1.12</v>
+      </c>
+      <c r="N30">
+        <v>2.68</v>
+      </c>
+      <c r="O30">
+        <v>1.52</v>
+      </c>
+      <c r="P30">
+        <v>1.58</v>
+      </c>
+      <c r="Q30">
+        <v>2.56</v>
+      </c>
+      <c r="R30">
+        <v>1.21</v>
+      </c>
+      <c r="S30">
+        <v>5.2</v>
+      </c>
+      <c r="T30">
+        <v>2.1</v>
+      </c>
+      <c r="U30">
+        <v>1.8</v>
+      </c>
+      <c r="V30">
+        <v>1.3</v>
+      </c>
+      <c r="W30">
+        <v>1.76</v>
+      </c>
+      <c r="X30">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y30">
+        <v>11.5</v>
+      </c>
+      <c r="Z30">
+        <v>60</v>
+      </c>
+      <c r="AA30">
+        <v>120</v>
+      </c>
+      <c r="AB30">
+        <v>7.4</v>
+      </c>
+      <c r="AC30">
+        <v>7.4</v>
+      </c>
+      <c r="AD30">
+        <v>19.5</v>
+      </c>
+      <c r="AE30">
+        <v>85</v>
+      </c>
+      <c r="AF30">
+        <v>13</v>
+      </c>
+      <c r="AG30">
+        <v>14</v>
+      </c>
+      <c r="AH30">
+        <v>55</v>
+      </c>
+      <c r="AI30">
+        <v>110</v>
+      </c>
+      <c r="AJ30">
+        <v>38</v>
+      </c>
+      <c r="AK30">
+        <v>38</v>
+      </c>
+      <c r="AL30">
+        <v>70</v>
+      </c>
+      <c r="AM30">
+        <v>220</v>
+      </c>
+      <c r="AN30">
+        <v>36</v>
+      </c>
+      <c r="AO30">
+        <v>120</v>
+      </c>
+      <c r="AP30">
+        <v>8</v>
+      </c>
+      <c r="AQ30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR30">
+        <v>20</v>
+      </c>
+      <c r="AS30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT30">
+        <v>6.6</v>
+      </c>
+      <c r="AU30">
+        <v>6.4</v>
+      </c>
+      <c r="AV30">
+        <v>15.5</v>
+      </c>
+      <c r="AW30">
+        <v>8.6</v>
+      </c>
+      <c r="AX30">
+        <v>11</v>
+      </c>
+      <c r="AY30">
+        <v>10</v>
+      </c>
+      <c r="AZ30">
+        <v>6.8</v>
+      </c>
+      <c r="BA30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB30">
+        <v>12</v>
+      </c>
+      <c r="BC30">
+        <v>7.6</v>
+      </c>
+      <c r="BD30">
+        <v>8.4</v>
+      </c>
+      <c r="BE30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF30">
+        <v>21</v>
+      </c>
+      <c r="BG30">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH30">
+        <v>2.78</v>
+      </c>
+      <c r="BI30">
+        <v>2.54</v>
+      </c>
+      <c r="BJ30">
+        <v>11.5</v>
+      </c>
+      <c r="BK30">
+        <v>6.6</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>15</v>
+      </c>
+      <c r="BN30">
         <v>4.8</v>
       </c>
-      <c r="H28">
+      <c r="BO30">
+        <v>4.2</v>
+      </c>
+      <c r="BP30">
+        <v>19</v>
+      </c>
+      <c r="BQ30">
+        <v>8.6</v>
+      </c>
+      <c r="BR30">
+        <v>1000</v>
+      </c>
+      <c r="BS30">
+        <v>11.5</v>
+      </c>
+      <c r="BT30">
+        <v>7.2</v>
+      </c>
+      <c r="BU30">
+        <v>5.7</v>
+      </c>
+      <c r="BV30">
+        <v>1000</v>
+      </c>
+      <c r="BW30">
+        <v>11.5</v>
+      </c>
+      <c r="BX30">
+        <v>1000</v>
+      </c>
+      <c r="BY30">
+        <v>12.5</v>
+      </c>
+      <c r="BZ30">
+        <v>1000</v>
+      </c>
+      <c r="CA30">
+        <v>11.5</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31">
+        <v>2.06</v>
+      </c>
+      <c r="G31">
+        <v>2.16</v>
+      </c>
+      <c r="H31">
+        <v>3.9</v>
+      </c>
+      <c r="I31">
+        <v>4.2</v>
+      </c>
+      <c r="J31">
+        <v>3.45</v>
+      </c>
+      <c r="K31">
+        <v>3.7</v>
+      </c>
+      <c r="L31">
+        <v>1.45</v>
+      </c>
+      <c r="M31">
+        <v>1.08</v>
+      </c>
+      <c r="N31">
+        <v>3.5</v>
+      </c>
+      <c r="O31">
+        <v>1.36</v>
+      </c>
+      <c r="P31">
+        <v>1.85</v>
+      </c>
+      <c r="Q31">
+        <v>2.06</v>
+      </c>
+      <c r="R31">
+        <v>1.33</v>
+      </c>
+      <c r="S31">
+        <v>3.7</v>
+      </c>
+      <c r="T31">
+        <v>1.86</v>
+      </c>
+      <c r="U31">
+        <v>2.06</v>
+      </c>
+      <c r="V31">
+        <v>1.31</v>
+      </c>
+      <c r="W31">
+        <v>1.86</v>
+      </c>
+      <c r="X31">
+        <v>13.5</v>
+      </c>
+      <c r="Y31">
+        <v>14</v>
+      </c>
+      <c r="Z31">
+        <v>36</v>
+      </c>
+      <c r="AA31">
+        <v>110</v>
+      </c>
+      <c r="AB31">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC31">
+        <v>8</v>
+      </c>
+      <c r="AD31">
+        <v>17</v>
+      </c>
+      <c r="AE31">
+        <v>65</v>
+      </c>
+      <c r="AF31">
+        <v>12.5</v>
+      </c>
+      <c r="AG31">
+        <v>11</v>
+      </c>
+      <c r="AH31">
+        <v>19</v>
+      </c>
+      <c r="AI31">
+        <v>75</v>
+      </c>
+      <c r="AJ31">
+        <v>46</v>
+      </c>
+      <c r="AK31">
+        <v>24</v>
+      </c>
+      <c r="AL31">
+        <v>40</v>
+      </c>
+      <c r="AM31">
+        <v>130</v>
+      </c>
+      <c r="AN31">
+        <v>16.5</v>
+      </c>
+      <c r="AO31">
+        <v>60</v>
+      </c>
+      <c r="AP31">
+        <v>11.5</v>
+      </c>
+      <c r="AQ31">
+        <v>12</v>
+      </c>
+      <c r="AR31">
+        <v>21</v>
+      </c>
+      <c r="AS31">
+        <v>12</v>
+      </c>
+      <c r="AT31">
+        <v>8</v>
+      </c>
+      <c r="AU31">
+        <v>7</v>
+      </c>
+      <c r="AV31">
+        <v>15</v>
+      </c>
+      <c r="AW31">
+        <v>25</v>
+      </c>
+      <c r="AX31">
+        <v>11</v>
+      </c>
+      <c r="AY31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31">
+        <v>17</v>
+      </c>
+      <c r="BA31">
+        <v>11.5</v>
+      </c>
+      <c r="BB31">
+        <v>22</v>
+      </c>
+      <c r="BC31">
+        <v>21</v>
+      </c>
+      <c r="BD31">
+        <v>10</v>
+      </c>
+      <c r="BE31">
+        <v>12</v>
+      </c>
+      <c r="BF31">
+        <v>14.5</v>
+      </c>
+      <c r="BG31">
+        <v>11</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>2</v>
+      </c>
+      <c r="BJ31">
+        <v>14.5</v>
+      </c>
+      <c r="BK31">
+        <v>3.6</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>1.99</v>
+      </c>
+      <c r="BN31">
+        <v>5.3</v>
+      </c>
+      <c r="BO31">
+        <v>2.48</v>
+      </c>
+      <c r="BP31">
+        <v>21</v>
+      </c>
+      <c r="BQ31">
+        <v>1.82</v>
+      </c>
+      <c r="BR31">
+        <v>46</v>
+      </c>
+      <c r="BS31">
         <v>1.91</v>
       </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
-      <c r="J28">
+      <c r="BT31">
+        <v>9</v>
+      </c>
+      <c r="BU31">
+        <v>6</v>
+      </c>
+      <c r="BV31">
+        <v>50</v>
+      </c>
+      <c r="BW31">
+        <v>1.92</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>1.94</v>
+      </c>
+      <c r="BZ31">
+        <v>40</v>
+      </c>
+      <c r="CA31">
+        <v>1.9</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32">
+        <v>4.2</v>
+      </c>
+      <c r="G32">
+        <v>4.6</v>
+      </c>
+      <c r="H32">
+        <v>1.96</v>
+      </c>
+      <c r="I32">
+        <v>2.02</v>
+      </c>
+      <c r="J32">
         <v>3.65</v>
       </c>
-      <c r="K28">
+      <c r="K32">
         <v>3.85</v>
       </c>
-      <c r="L28">
+      <c r="L32">
         <v>1.43</v>
       </c>
-      <c r="M28">
+      <c r="M32">
         <v>1.08</v>
       </c>
-      <c r="N28">
-        <v>3.5</v>
-      </c>
-      <c r="O28">
+      <c r="N32">
+        <v>3.45</v>
+      </c>
+      <c r="O32">
         <v>1.37</v>
       </c>
-      <c r="P28">
-        <v>1.8</v>
-      </c>
-      <c r="Q28">
+      <c r="P32">
+        <v>1.85</v>
+      </c>
+      <c r="Q32">
         <v>2.08</v>
       </c>
-      <c r="R28">
-        <v>1.31</v>
-      </c>
-      <c r="S28">
-        <v>3.75</v>
-      </c>
-      <c r="T28">
-        <v>1.89</v>
-      </c>
-      <c r="U28">
-        <v>1.98</v>
-      </c>
-      <c r="V28">
-        <v>2</v>
-      </c>
-      <c r="W28">
-        <v>1.26</v>
-      </c>
-      <c r="X28">
+      <c r="R32">
+        <v>1.32</v>
+      </c>
+      <c r="S32">
+        <v>3.8</v>
+      </c>
+      <c r="T32">
+        <v>1.92</v>
+      </c>
+      <c r="U32">
+        <v>1.97</v>
+      </c>
+      <c r="V32">
+        <v>1.99</v>
+      </c>
+      <c r="W32">
+        <v>1.28</v>
+      </c>
+      <c r="X32">
+        <v>15</v>
+      </c>
+      <c r="Y32">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z32">
+        <v>12.5</v>
+      </c>
+      <c r="AA32">
+        <v>27</v>
+      </c>
+      <c r="AB32">
+        <v>14.5</v>
+      </c>
+      <c r="AC32">
+        <v>8.4</v>
+      </c>
+      <c r="AD32">
+        <v>11</v>
+      </c>
+      <c r="AE32">
+        <v>24</v>
+      </c>
+      <c r="AF32">
+        <v>38</v>
+      </c>
+      <c r="AG32">
+        <v>19</v>
+      </c>
+      <c r="AH32">
+        <v>21</v>
+      </c>
+      <c r="AI32">
+        <v>48</v>
+      </c>
+      <c r="AJ32">
+        <v>120</v>
+      </c>
+      <c r="AK32">
+        <v>70</v>
+      </c>
+      <c r="AL32">
+        <v>80</v>
+      </c>
+      <c r="AM32">
+        <v>140</v>
+      </c>
+      <c r="AN32">
+        <v>85</v>
+      </c>
+      <c r="AO32">
+        <v>18.5</v>
+      </c>
+      <c r="AP32">
+        <v>11</v>
+      </c>
+      <c r="AQ32">
+        <v>7.4</v>
+      </c>
+      <c r="AR32">
+        <v>10</v>
+      </c>
+      <c r="AS32">
+        <v>20</v>
+      </c>
+      <c r="AT32">
+        <v>12</v>
+      </c>
+      <c r="AU32">
+        <v>7.2</v>
+      </c>
+      <c r="AV32">
+        <v>9.4</v>
+      </c>
+      <c r="AW32">
+        <v>19.5</v>
+      </c>
+      <c r="AX32">
+        <v>7.2</v>
+      </c>
+      <c r="AY32">
+        <v>15.5</v>
+      </c>
+      <c r="AZ32">
+        <v>17.5</v>
+      </c>
+      <c r="BA32">
+        <v>7.2</v>
+      </c>
+      <c r="BB32">
+        <v>7.4</v>
+      </c>
+      <c r="BC32">
+        <v>7.6</v>
+      </c>
+      <c r="BD32">
+        <v>7.8</v>
+      </c>
+      <c r="BE32">
+        <v>7.4</v>
+      </c>
+      <c r="BF32">
+        <v>7.8</v>
+      </c>
+      <c r="BG32">
         <v>13.5</v>
       </c>
-      <c r="Y28">
-        <v>8.6</v>
-      </c>
-      <c r="Z28">
+      <c r="BH32">
+        <v>3.6</v>
+      </c>
+      <c r="BI32">
+        <v>2.92</v>
+      </c>
+      <c r="BJ32">
         <v>12</v>
       </c>
-      <c r="AA28">
-        <v>27</v>
-      </c>
-      <c r="AB28">
-        <v>17</v>
-      </c>
-      <c r="AC28">
-        <v>8.4</v>
-      </c>
-      <c r="AD28">
-        <v>11</v>
-      </c>
-      <c r="AE28">
-        <v>26</v>
-      </c>
-      <c r="AF28">
-        <v>38</v>
-      </c>
-      <c r="AG28">
-        <v>19</v>
-      </c>
-      <c r="AH28">
-        <v>21</v>
-      </c>
-      <c r="AI28">
+      <c r="BK32">
+        <v>3.95</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>5.7</v>
+      </c>
+      <c r="BN32">
+        <v>9</v>
+      </c>
+      <c r="BO32">
+        <v>6</v>
+      </c>
+      <c r="BP32">
         <v>48</v>
       </c>
-      <c r="AJ28">
-        <v>120</v>
-      </c>
-      <c r="AK28">
-        <v>75</v>
-      </c>
-      <c r="AL28">
-        <v>80</v>
-      </c>
-      <c r="AM28">
-        <v>140</v>
-      </c>
-      <c r="AN28">
-        <v>90</v>
-      </c>
-      <c r="AO28">
-        <v>18</v>
-      </c>
-      <c r="AP28">
-        <v>11</v>
-      </c>
-      <c r="AQ28">
-        <v>7.4</v>
-      </c>
-      <c r="AR28">
-        <v>10</v>
-      </c>
-      <c r="AS28">
-        <v>19.5</v>
-      </c>
-      <c r="AT28">
-        <v>12.5</v>
-      </c>
-      <c r="AU28">
-        <v>7.2</v>
-      </c>
-      <c r="AV28">
-        <v>9.4</v>
-      </c>
-      <c r="AW28">
-        <v>18.5</v>
-      </c>
-      <c r="AX28">
-        <v>6.8</v>
-      </c>
-      <c r="AY28">
-        <v>15.5</v>
-      </c>
-      <c r="AZ28">
-        <v>17.5</v>
-      </c>
-      <c r="BA28">
-        <v>7.2</v>
-      </c>
-      <c r="BB28">
-        <v>7.8</v>
-      </c>
-      <c r="BC28">
-        <v>23</v>
-      </c>
-      <c r="BD28">
-        <v>28</v>
-      </c>
-      <c r="BE28">
-        <v>7.4</v>
-      </c>
-      <c r="BF28">
-        <v>7.6</v>
-      </c>
-      <c r="BG28">
-        <v>13.5</v>
-      </c>
-      <c r="BH28">
-        <v>3.6</v>
-      </c>
-      <c r="BI28">
-        <v>2.68</v>
-      </c>
-      <c r="BJ28">
-        <v>12</v>
-      </c>
-      <c r="BK28">
-        <v>3.95</v>
-      </c>
-      <c r="BL28">
-        <v>1000</v>
-      </c>
-      <c r="BM28">
-        <v>5.7</v>
-      </c>
-      <c r="BN28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO28">
-        <v>3.85</v>
-      </c>
-      <c r="BP28">
-        <v>48</v>
-      </c>
-      <c r="BQ28">
-        <v>5.2</v>
-      </c>
-      <c r="BR28">
+      <c r="BQ32">
+        <v>5.3</v>
+      </c>
+      <c r="BR32">
         <v>60</v>
       </c>
-      <c r="BS28">
-        <v>5.3</v>
-      </c>
-      <c r="BT28">
+      <c r="BS32">
+        <v>5.4</v>
+      </c>
+      <c r="BT32">
         <v>5.1</v>
       </c>
-      <c r="BU28">
+      <c r="BU32">
         <v>4</v>
       </c>
-      <c r="BV28">
+      <c r="BV32">
         <v>16</v>
       </c>
-      <c r="BW28">
+      <c r="BW32">
         <v>4.3</v>
       </c>
-      <c r="BX28">
+      <c r="BX32">
         <v>36</v>
       </c>
-      <c r="BY28">
+      <c r="BY32">
+        <v>5.1</v>
+      </c>
+      <c r="BZ32">
+        <v>32</v>
+      </c>
+      <c r="CA32">
         <v>5</v>
       </c>
-      <c r="BZ28">
-        <v>32</v>
-      </c>
-      <c r="CA28">
-        <v>4.9</v>
-      </c>
-      <c r="CB28" t="s">
-        <v>160</v>
+      <c r="CB32" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="178">
   <si>
     <t>League</t>
   </si>
@@ -334,6 +334,9 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>20:15:00</t>
+  </si>
+  <si>
     <t>20:30:00</t>
   </si>
   <si>
@@ -403,6 +406,9 @@
     <t>Belouizdad</t>
   </si>
   <si>
+    <t>CD Estudiantil CNI</t>
+  </si>
+  <si>
     <t>Vinotinto Ecuador</t>
   </si>
   <si>
@@ -496,6 +502,9 @@
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Universidad Cesar Vallejo</t>
+  </si>
+  <si>
     <t>CD Cuenca Juniors</t>
   </si>
   <si>
@@ -538,7 +547,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 12:50:18</t>
+    <t>2026-10-06 15:02:08</t>
   </si>
 </sst>
 </file>
@@ -870,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB32"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1126,16 +1135,16 @@
         <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H2">
         <v>2.28</v>
@@ -1156,40 +1165,40 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q2">
+        <v>1.45</v>
+      </c>
+      <c r="R2">
+        <v>1.87</v>
+      </c>
+      <c r="S2">
+        <v>2.12</v>
+      </c>
+      <c r="T2">
         <v>1.44</v>
       </c>
-      <c r="R2">
-        <v>1.91</v>
-      </c>
-      <c r="S2">
-        <v>2.06</v>
-      </c>
-      <c r="T2">
-        <v>1.43</v>
-      </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V2">
         <v>1.75</v>
       </c>
       <c r="W2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>21</v>
@@ -1198,7 +1207,7 @@
         <v>32</v>
       </c>
       <c r="AB2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1207,22 +1216,22 @@
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF2">
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <v>13</v>
       </c>
       <c r="AI2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK2">
         <v>27</v>
@@ -1237,22 +1246,22 @@
         <v>14.5</v>
       </c>
       <c r="AO2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AP2">
         <v>30</v>
       </c>
       <c r="AQ2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS2">
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU2">
         <v>10</v>
@@ -1270,10 +1279,10 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2">
         <v>44</v>
@@ -1282,22 +1291,22 @@
         <v>25</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE2">
         <v>34</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BI2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BJ2">
         <v>8.199999999999999</v>
@@ -1309,7 +1318,7 @@
         <v>60</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>7</v>
@@ -1321,13 +1330,13 @@
         <v>20</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>24</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>5.9</v>
@@ -1345,7 +1354,7 @@
         <v>20</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>12</v>
@@ -1354,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1368,16 +1377,16 @@
         <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H3">
         <v>1.33</v>
@@ -1392,10 +1401,10 @@
         <v>6</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>4.2</v>
@@ -1407,16 +1416,16 @@
         <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
         <v>1.67</v>
@@ -1434,7 +1443,7 @@
         <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA3">
         <v>9.800000000000001</v>
@@ -1452,7 +1461,7 @@
         <v>16.5</v>
       </c>
       <c r="AF3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AG3">
         <v>48</v>
@@ -1464,19 +1473,19 @@
         <v>50</v>
       </c>
       <c r="AJ3">
-        <v>720</v>
+        <v>610</v>
       </c>
       <c r="AK3">
         <v>260</v>
       </c>
       <c r="AL3">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="AM3">
         <v>260</v>
       </c>
       <c r="AN3">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AO3">
         <v>6.2</v>
@@ -1488,7 +1497,7 @@
         <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
         <v>9</v>
@@ -1506,7 +1515,7 @@
         <v>14</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY3">
         <v>38</v>
@@ -1518,13 +1527,13 @@
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BE3">
         <v>15</v>
@@ -1536,40 +1545,40 @@
         <v>5.8</v>
       </c>
       <c r="BH3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3">
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN3">
         <v>15.5</v>
       </c>
       <c r="BO3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BP3">
         <v>130</v>
       </c>
       <c r="BQ3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>120</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT3">
         <v>3.6</v>
@@ -1587,16 +1596,16 @@
         <v>29</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
         <v>15</v>
       </c>
       <c r="CA3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1610,28 +1619,28 @@
         <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G4">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1640,7 +1649,7 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O4">
         <v>1.46</v>
@@ -1649,25 +1658,25 @@
         <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
         <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
         <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1676,13 +1685,13 @@
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AA4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1694,10 +1703,10 @@
         <v>65</v>
       </c>
       <c r="AF4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1706,94 +1715,94 @@
         <v>80</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AK4">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AO4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR4">
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>46</v>
       </c>
       <c r="BB4">
-        <v>6.8</v>
+        <v>24</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>110</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BG4">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1802,43 +1811,43 @@
         <v>3.85</v>
       </c>
       <c r="BP4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BR4">
         <v>48</v>
       </c>
       <c r="BS4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BT4">
         <v>8</v>
       </c>
       <c r="BU4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>42</v>
       </c>
       <c r="BW4">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BZ4">
         <v>50</v>
       </c>
       <c r="CA4">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="CB4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1852,19 +1861,19 @@
         <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F5">
         <v>1.49</v>
       </c>
       <c r="G5">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>11</v>
@@ -1903,13 +1912,13 @@
         <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="V5">
         <v>1.1</v>
       </c>
       <c r="W5">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -2080,7 +2089,7 @@
         <v>5.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2094,28 +2103,28 @@
         <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F6">
         <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
         <v>2.8</v>
       </c>
       <c r="I6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
         <v>3.5</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
         <v>1.3</v>
@@ -2124,25 +2133,25 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6">
         <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="R6">
         <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
         <v>2.44</v>
@@ -2151,7 +2160,7 @@
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2163,7 +2172,7 @@
         <v>23</v>
       </c>
       <c r="AA6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB6">
         <v>15.5</v>
@@ -2223,13 +2232,13 @@
         <v>12.5</v>
       </c>
       <c r="AU6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX6">
         <v>14.5</v>
@@ -2241,10 +2250,10 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB6">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC6">
         <v>21</v>
@@ -2268,10 +2277,10 @@
         <v>3.15</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2280,7 +2289,7 @@
         <v>5.2</v>
       </c>
       <c r="BN6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO6">
         <v>4.6</v>
@@ -2322,7 +2331,7 @@
         <v>4.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2336,10 +2345,10 @@
         <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>6.2</v>
@@ -2351,7 +2360,7 @@
         <v>1.55</v>
       </c>
       <c r="I7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J7">
         <v>4.3</v>
@@ -2369,139 +2378,139 @@
         <v>4.5</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P7">
         <v>2.2</v>
       </c>
       <c r="Q7">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U7">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="W7">
         <v>1.16</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z7">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AA7">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
+        <v>10.5</v>
+      </c>
+      <c r="AE7">
+        <v>19</v>
+      </c>
+      <c r="AF7">
+        <v>70</v>
+      </c>
+      <c r="AG7">
+        <v>32</v>
+      </c>
+      <c r="AH7">
+        <v>26</v>
+      </c>
+      <c r="AI7">
+        <v>40</v>
+      </c>
+      <c r="AJ7">
+        <v>220</v>
+      </c>
+      <c r="AK7">
+        <v>110</v>
+      </c>
+      <c r="AL7">
+        <v>95</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>120</v>
+      </c>
+      <c r="AO7">
+        <v>7.6</v>
+      </c>
+      <c r="AP7">
+        <v>17</v>
+      </c>
+      <c r="AQ7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS7">
         <v>12.5</v>
       </c>
-      <c r="AE7">
-        <v>970</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>970</v>
-      </c>
-      <c r="AP7">
-        <v>2.18</v>
-      </c>
-      <c r="AQ7">
+      <c r="AT7">
+        <v>21</v>
+      </c>
+      <c r="AU7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV7">
         <v>8.6</v>
       </c>
-      <c r="AR7">
-        <v>1.83</v>
-      </c>
-      <c r="AS7">
-        <v>10.5</v>
-      </c>
-      <c r="AT7">
-        <v>14.5</v>
-      </c>
-      <c r="AU7">
-        <v>1.83</v>
-      </c>
-      <c r="AV7">
-        <v>8</v>
-      </c>
       <c r="AW7">
-        <v>1.99</v>
+        <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>2.18</v>
+        <v>5.8</v>
       </c>
       <c r="AY7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="BB7">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="BC7">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="BD7">
-        <v>2.18</v>
+        <v>5.8</v>
       </c>
       <c r="BE7">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="BF7">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="BG7">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2564,7 +2573,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2578,31 +2587,31 @@
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G8">
         <v>4.1</v>
       </c>
       <c r="H8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2611,10 +2620,10 @@
         <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2626,13 +2635,13 @@
         <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W8">
         <v>1.32</v>
@@ -2644,22 +2653,22 @@
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF8">
         <v>34</v>
@@ -2680,31 +2689,31 @@
         <v>60</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM8">
         <v>120</v>
       </c>
       <c r="AN8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8">
         <v>11</v>
       </c>
       <c r="AQ8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR8">
         <v>11.5</v>
       </c>
       <c r="AS8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU8">
         <v>7</v>
@@ -2713,10 +2722,10 @@
         <v>9.4</v>
       </c>
       <c r="AW8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2725,22 +2734,22 @@
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BB8">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC8">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD8">
+        <v>6</v>
+      </c>
+      <c r="BE8">
         <v>5.6</v>
       </c>
-      <c r="BE8">
-        <v>5.2</v>
-      </c>
       <c r="BF8">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG8">
         <v>15</v>
@@ -2806,7 +2815,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2820,172 +2829,172 @@
         <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F9">
+        <v>3.15</v>
+      </c>
+      <c r="G9">
+        <v>4.1</v>
+      </c>
+      <c r="H9">
+        <v>2.52</v>
+      </c>
+      <c r="I9">
         <v>3.05</v>
       </c>
-      <c r="G9">
-        <v>4.3</v>
-      </c>
-      <c r="H9">
-        <v>2.4</v>
-      </c>
-      <c r="I9">
-        <v>3.3</v>
-      </c>
       <c r="J9">
-        <v>1.12</v>
+        <v>2.8</v>
       </c>
       <c r="K9">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M9">
         <v>1.09</v>
       </c>
       <c r="N9">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="P9">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R9">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
-        <v>2.92</v>
+        <v>4.8</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3048,7 +3057,7 @@
         <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3062,10 +3071,10 @@
         <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F10">
         <v>1.77</v>
@@ -3089,13 +3098,13 @@
         <v>1.37</v>
       </c>
       <c r="M10">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N10">
         <v>2.74</v>
       </c>
       <c r="O10">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
         <v>1.63</v>
@@ -3290,7 +3299,7 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3304,31 +3313,31 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F11">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G11">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H11">
         <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3349,7 +3358,7 @@
         <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T11">
         <v>1.45</v>
@@ -3358,7 +3367,7 @@
         <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W11">
         <v>1.6</v>
@@ -3382,7 +3391,7 @@
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE11">
         <v>32</v>
@@ -3427,13 +3436,13 @@
         <v>17.5</v>
       </c>
       <c r="AS11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT11">
         <v>13.5</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV11">
         <v>10</v>
@@ -3463,7 +3472,7 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF11">
         <v>8.6</v>
@@ -3532,7 +3541,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3546,10 +3555,10 @@
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F12">
         <v>1.1</v>
@@ -3561,7 +3570,7 @@
         <v>1.1</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12">
         <v>1.1</v>
@@ -3600,10 +3609,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3774,7 +3783,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3788,16 +3797,16 @@
         <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F13">
         <v>1.1</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="H13">
         <v>1.1</v>
@@ -3809,7 +3818,7 @@
         <v>1.1</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3821,19 +3830,19 @@
         <v>1.08</v>
       </c>
       <c r="O13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P13">
         <v>1.08</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R13">
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3842,10 +3851,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3902,52 +3911,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -4016,7 +4025,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4030,37 +4039,37 @@
         <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F14">
         <v>4</v>
       </c>
       <c r="G14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H14">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="I14">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="J14">
         <v>3.9</v>
       </c>
       <c r="K14">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
         <v>1.33</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O14">
         <v>1.27</v>
@@ -4069,25 +4078,25 @@
         <v>2.16</v>
       </c>
       <c r="Q14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R14">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="T14">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
         <v>2.26</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X14">
         <v>18</v>
@@ -4096,28 +4105,28 @@
         <v>11</v>
       </c>
       <c r="Z14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA14">
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH14">
         <v>17.5</v>
@@ -4126,22 +4135,22 @@
         <v>32</v>
       </c>
       <c r="AJ14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM14">
         <v>85</v>
       </c>
       <c r="AN14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO14">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AP14">
         <v>15.5</v>
@@ -4150,7 +4159,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS14">
         <v>19.5</v>
@@ -4186,25 +4195,25 @@
         <v>40</v>
       </c>
       <c r="BD14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE14">
         <v>36</v>
       </c>
       <c r="BF14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BG14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BI14">
         <v>3.05</v>
       </c>
       <c r="BJ14">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
         <v>5.8</v>
@@ -4213,7 +4222,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BN14">
         <v>9</v>
@@ -4225,13 +4234,13 @@
         <v>48</v>
       </c>
       <c r="BQ14">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BR14">
         <v>990</v>
       </c>
       <c r="BS14">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BT14">
         <v>5.6</v>
@@ -4249,16 +4258,16 @@
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="CB14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4272,10 +4281,10 @@
         <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F15">
         <v>1.64</v>
@@ -4290,7 +4299,7 @@
         <v>8.4</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
         <v>3.8</v>
@@ -4305,7 +4314,7 @@
         <v>2.52</v>
       </c>
       <c r="O15">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P15">
         <v>1.5</v>
@@ -4320,10 +4329,10 @@
         <v>5.3</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="V15">
         <v>1.13</v>
@@ -4332,112 +4341,112 @@
         <v>2.28</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH15">
         <v>2.88</v>
@@ -4500,7 +4509,7 @@
         <v>1.95</v>
       </c>
       <c r="CB15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4514,10 +4523,10 @@
         <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F16">
         <v>2.32</v>
@@ -4526,16 +4535,16 @@
         <v>2.54</v>
       </c>
       <c r="H16">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I16">
         <v>4.1</v>
       </c>
       <c r="J16">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4742,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4756,10 +4765,10 @@
         <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F17">
         <v>1.1</v>
@@ -4777,7 +4786,7 @@
         <v>1.1</v>
       </c>
       <c r="K17">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4813,7 +4822,7 @@
         <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4870,52 +4879,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -4984,7 +4993,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4998,10 +5007,10 @@
         <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F18">
         <v>1.36</v>
@@ -5031,7 +5040,7 @@
         <v>3.35</v>
       </c>
       <c r="O18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P18">
         <v>1.82</v>
@@ -5049,7 +5058,7 @@
         <v>2.36</v>
       </c>
       <c r="U18">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V18">
         <v>1.07</v>
@@ -5187,7 +5196,7 @@
         <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BP18">
         <v>1000</v>
@@ -5226,12 +5235,12 @@
         <v>1.29</v>
       </c>
       <c r="CB18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
@@ -5240,28 +5249,28 @@
         <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F19">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="G19">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H19">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="I19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K19">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5270,22 +5279,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
       <c r="O19">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="P19">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="Q19">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S19">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5294,10 +5303,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5468,12 +5477,12 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
         <v>93</v>
@@ -5482,235 +5491,235 @@
         <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F20">
-        <v>2.14</v>
+        <v>1.49</v>
       </c>
       <c r="G20">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="H20">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="P20">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="Q20">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="R20">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="S20">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="T20">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="W20">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="X20">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AQ20">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AR20">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS20">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT20">
+        <v>4.2</v>
+      </c>
+      <c r="AU20">
         <v>7.4</v>
       </c>
-      <c r="AU20">
-        <v>6.8</v>
-      </c>
       <c r="AV20">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW20">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX20">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA20">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB20">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BC20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD20">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE20">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF20">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
         <v>1000</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
         <v>1000</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
         <v>1000</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5724,240 +5733,240 @@
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F21">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="G21">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="I21">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="J21">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O21">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q21">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="R21">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S21">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T21">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="U21">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="X21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y21">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="Z21">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AA21">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="AB21">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21">
         <v>9</v>
       </c>
       <c r="AD21">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE21">
+        <v>65</v>
+      </c>
+      <c r="AF21">
+        <v>15</v>
+      </c>
+      <c r="AG21">
+        <v>12.5</v>
+      </c>
+      <c r="AH21">
+        <v>23</v>
+      </c>
+      <c r="AI21">
+        <v>75</v>
+      </c>
+      <c r="AJ21">
         <v>32</v>
       </c>
-      <c r="AF21">
-        <v>32</v>
-      </c>
-      <c r="AG21">
-        <v>17</v>
-      </c>
-      <c r="AH21">
-        <v>25</v>
-      </c>
-      <c r="AI21">
-        <v>60</v>
-      </c>
-      <c r="AJ21">
-        <v>100</v>
-      </c>
       <c r="AK21">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="AL21">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AM21">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN21">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AO21">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="AP21">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR21">
+        <v>4.5</v>
+      </c>
+      <c r="AS21">
+        <v>5</v>
+      </c>
+      <c r="AT21">
+        <v>7.4</v>
+      </c>
+      <c r="AU21">
+        <v>6.8</v>
+      </c>
+      <c r="AV21">
+        <v>14.5</v>
+      </c>
+      <c r="AW21">
+        <v>4.8</v>
+      </c>
+      <c r="AX21">
         <v>10</v>
       </c>
-      <c r="AS21">
-        <v>21</v>
-      </c>
-      <c r="AT21">
-        <v>8.6</v>
-      </c>
-      <c r="AU21">
-        <v>5.6</v>
-      </c>
-      <c r="AV21">
-        <v>8.6</v>
-      </c>
-      <c r="AW21">
-        <v>21</v>
-      </c>
-      <c r="AX21">
-        <v>21</v>
-      </c>
       <c r="AY21">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21">
         <v>17</v>
       </c>
       <c r="BA21">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB21">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BC21">
-        <v>5.2</v>
+        <v>19</v>
       </c>
       <c r="BD21">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE21">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BF21">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="BG21">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BH21">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
         <v>93</v>
@@ -5966,235 +5975,235 @@
         <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F22">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="G22">
-        <v>1.91</v>
+        <v>4.1</v>
       </c>
       <c r="H22">
+        <v>2.22</v>
+      </c>
+      <c r="I22">
+        <v>2.4</v>
+      </c>
+      <c r="J22">
+        <v>3.1</v>
+      </c>
+      <c r="K22">
+        <v>3.45</v>
+      </c>
+      <c r="L22">
+        <v>1.5</v>
+      </c>
+      <c r="M22">
+        <v>1.1</v>
+      </c>
+      <c r="N22">
+        <v>2.92</v>
+      </c>
+      <c r="O22">
+        <v>1.45</v>
+      </c>
+      <c r="P22">
+        <v>1.66</v>
+      </c>
+      <c r="Q22">
+        <v>2.3</v>
+      </c>
+      <c r="R22">
+        <v>1.24</v>
+      </c>
+      <c r="S22">
         <v>4.4</v>
       </c>
-      <c r="I22">
-        <v>4.7</v>
-      </c>
-      <c r="J22">
-        <v>3.85</v>
-      </c>
-      <c r="K22">
-        <v>4.1</v>
-      </c>
-      <c r="L22">
-        <v>1.37</v>
-      </c>
-      <c r="M22">
-        <v>1.05</v>
-      </c>
-      <c r="N22">
-        <v>4.3</v>
-      </c>
-      <c r="O22">
-        <v>1.27</v>
-      </c>
-      <c r="P22">
-        <v>2.14</v>
-      </c>
-      <c r="Q22">
-        <v>1.81</v>
-      </c>
-      <c r="R22">
-        <v>1.45</v>
-      </c>
-      <c r="S22">
+      <c r="T22">
+        <v>1.95</v>
+      </c>
+      <c r="U22">
+        <v>1.9</v>
+      </c>
+      <c r="V22">
+        <v>1.71</v>
+      </c>
+      <c r="W22">
+        <v>1.33</v>
+      </c>
+      <c r="X22">
+        <v>11</v>
+      </c>
+      <c r="Y22">
+        <v>8.6</v>
+      </c>
+      <c r="Z22">
+        <v>15</v>
+      </c>
+      <c r="AA22">
+        <v>34</v>
+      </c>
+      <c r="AB22">
+        <v>14</v>
+      </c>
+      <c r="AC22">
+        <v>7.8</v>
+      </c>
+      <c r="AD22">
+        <v>14</v>
+      </c>
+      <c r="AE22">
+        <v>32</v>
+      </c>
+      <c r="AF22">
+        <v>32</v>
+      </c>
+      <c r="AG22">
+        <v>17</v>
+      </c>
+      <c r="AH22">
+        <v>25</v>
+      </c>
+      <c r="AI22">
+        <v>60</v>
+      </c>
+      <c r="AJ22">
+        <v>100</v>
+      </c>
+      <c r="AK22">
+        <v>70</v>
+      </c>
+      <c r="AL22">
+        <v>75</v>
+      </c>
+      <c r="AM22">
+        <v>170</v>
+      </c>
+      <c r="AN22">
+        <v>75</v>
+      </c>
+      <c r="AO22">
+        <v>27</v>
+      </c>
+      <c r="AP22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ22">
+        <v>6</v>
+      </c>
+      <c r="AR22">
+        <v>10</v>
+      </c>
+      <c r="AS22">
+        <v>21</v>
+      </c>
+      <c r="AT22">
+        <v>8.6</v>
+      </c>
+      <c r="AU22">
+        <v>5.6</v>
+      </c>
+      <c r="AV22">
+        <v>10</v>
+      </c>
+      <c r="AW22">
+        <v>21</v>
+      </c>
+      <c r="AX22">
+        <v>21</v>
+      </c>
+      <c r="AY22">
+        <v>13.5</v>
+      </c>
+      <c r="AZ22">
+        <v>17</v>
+      </c>
+      <c r="BA22">
+        <v>5.8</v>
+      </c>
+      <c r="BB22">
+        <v>6</v>
+      </c>
+      <c r="BC22">
+        <v>5.9</v>
+      </c>
+      <c r="BD22">
+        <v>5.9</v>
+      </c>
+      <c r="BE22">
+        <v>6.2</v>
+      </c>
+      <c r="BF22">
+        <v>5.9</v>
+      </c>
+      <c r="BG22">
+        <v>20</v>
+      </c>
+      <c r="BH22">
         <v>3.05</v>
       </c>
-      <c r="T22">
-        <v>1.75</v>
-      </c>
-      <c r="U22">
-        <v>2.22</v>
-      </c>
-      <c r="V22">
-        <v>1.27</v>
-      </c>
-      <c r="W22">
-        <v>2.1</v>
-      </c>
-      <c r="X22">
-        <v>22</v>
-      </c>
-      <c r="Y22">
-        <v>34</v>
-      </c>
-      <c r="Z22">
+      <c r="BI22">
+        <v>2.4</v>
+      </c>
+      <c r="BJ22">
+        <v>11</v>
+      </c>
+      <c r="BK22">
+        <v>5.4</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>10</v>
+      </c>
+      <c r="BN22">
+        <v>7.2</v>
+      </c>
+      <c r="BO22">
+        <v>5.2</v>
+      </c>
+      <c r="BP22">
+        <v>38</v>
+      </c>
+      <c r="BQ22">
+        <v>8.4</v>
+      </c>
+      <c r="BR22">
+        <v>55</v>
+      </c>
+      <c r="BS22">
+        <v>9</v>
+      </c>
+      <c r="BT22">
+        <v>5.1</v>
+      </c>
+      <c r="BU22">
+        <v>3.75</v>
+      </c>
+      <c r="BV22">
+        <v>19</v>
+      </c>
+      <c r="BW22">
+        <v>6.8</v>
+      </c>
+      <c r="BX22">
+        <v>38</v>
+      </c>
+      <c r="BY22">
+        <v>8.4</v>
+      </c>
+      <c r="BZ22">
         <v>40</v>
       </c>
-      <c r="AA22">
-        <v>120</v>
-      </c>
-      <c r="AB22">
-        <v>10.5</v>
-      </c>
-      <c r="AC22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD22">
-        <v>32</v>
-      </c>
-      <c r="AE22">
-        <v>65</v>
-      </c>
-      <c r="AF22">
-        <v>12.5</v>
-      </c>
-      <c r="AG22">
-        <v>10.5</v>
-      </c>
-      <c r="AH22">
-        <v>34</v>
-      </c>
-      <c r="AI22">
-        <v>70</v>
-      </c>
-      <c r="AJ22">
-        <v>40</v>
-      </c>
-      <c r="AK22">
-        <v>19.5</v>
-      </c>
-      <c r="AL22">
-        <v>38</v>
-      </c>
-      <c r="AM22">
-        <v>110</v>
-      </c>
-      <c r="AN22">
-        <v>11</v>
-      </c>
-      <c r="AO22">
-        <v>65</v>
-      </c>
-      <c r="AP22">
-        <v>14.5</v>
-      </c>
-      <c r="AQ22">
-        <v>16</v>
-      </c>
-      <c r="AR22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS22">
-        <v>11</v>
-      </c>
-      <c r="AT22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU22">
-        <v>8</v>
-      </c>
-      <c r="AV22">
-        <v>14.5</v>
-      </c>
-      <c r="AW22">
-        <v>10</v>
-      </c>
-      <c r="AX22">
-        <v>9.4</v>
-      </c>
-      <c r="AY22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22">
-        <v>15</v>
-      </c>
-      <c r="BA22">
-        <v>10</v>
-      </c>
-      <c r="BB22">
-        <v>16.5</v>
-      </c>
-      <c r="BC22">
-        <v>15</v>
-      </c>
-      <c r="BD22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE22">
-        <v>10.5</v>
-      </c>
-      <c r="BF22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG22">
-        <v>10</v>
-      </c>
-      <c r="BH22">
-        <v>3.7</v>
-      </c>
-      <c r="BI22">
-        <v>3.4</v>
-      </c>
-      <c r="BJ22">
-        <v>11.5</v>
-      </c>
-      <c r="BK22">
-        <v>4.5</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>7</v>
-      </c>
-      <c r="BN22">
-        <v>4.6</v>
-      </c>
-      <c r="BO22">
-        <v>4.2</v>
-      </c>
-      <c r="BP22">
-        <v>15</v>
-      </c>
-      <c r="BQ22">
-        <v>5.1</v>
-      </c>
-      <c r="BR22">
-        <v>32</v>
-      </c>
-      <c r="BS22">
-        <v>6</v>
-      </c>
-      <c r="BT22">
-        <v>9.6</v>
-      </c>
-      <c r="BU22">
-        <v>7.2</v>
-      </c>
-      <c r="BV22">
-        <v>44</v>
-      </c>
-      <c r="BW22">
-        <v>6.4</v>
-      </c>
-      <c r="BX22">
-        <v>55</v>
-      </c>
-      <c r="BY22">
-        <v>6.6</v>
-      </c>
-      <c r="BZ22">
-        <v>24</v>
-      </c>
       <c r="CA22">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="CB22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6205,238 +6214,238 @@
         <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F23">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="G23">
-        <v>2.44</v>
+        <v>1.91</v>
       </c>
       <c r="H23">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I23">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J23">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L23">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N23">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O23">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="P23">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="R23">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="S23">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="T23">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="W23">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="X23">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="Y23">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Z23">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AA23">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AB23">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC23">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="AE23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF23">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AI23">
         <v>70</v>
       </c>
       <c r="AJ23">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK23">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AL23">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AM23">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AN23">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="AO23">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AP23">
+        <v>14.5</v>
+      </c>
+      <c r="AQ23">
+        <v>16</v>
+      </c>
+      <c r="AR23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS23">
+        <v>11</v>
+      </c>
+      <c r="AT23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU23">
+        <v>8</v>
+      </c>
+      <c r="AV23">
+        <v>14.5</v>
+      </c>
+      <c r="AW23">
         <v>10</v>
       </c>
-      <c r="AQ23">
-        <v>10.5</v>
-      </c>
-      <c r="AR23">
-        <v>20</v>
-      </c>
-      <c r="AS23">
-        <v>32</v>
-      </c>
-      <c r="AT23">
-        <v>8.4</v>
-      </c>
-      <c r="AU23">
-        <v>6.8</v>
-      </c>
-      <c r="AV23">
-        <v>13</v>
-      </c>
-      <c r="AW23">
-        <v>20</v>
-      </c>
       <c r="AX23">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY23">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA23">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="BB23">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC23">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="BD23">
-        <v>20</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23">
         <v>10.5</v>
       </c>
       <c r="BF23">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG23">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH23">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BI23">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="BJ23">
+        <v>11.5</v>
+      </c>
+      <c r="BK23">
+        <v>4.5</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>7</v>
+      </c>
+      <c r="BN23">
+        <v>4.6</v>
+      </c>
+      <c r="BO23">
+        <v>4.2</v>
+      </c>
+      <c r="BP23">
         <v>15</v>
       </c>
-      <c r="BK23">
-        <v>7.8</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>4.8</v>
-      </c>
-      <c r="BN23">
+      <c r="BQ23">
+        <v>5.1</v>
+      </c>
+      <c r="BR23">
+        <v>32</v>
+      </c>
+      <c r="BS23">
         <v>6</v>
       </c>
-      <c r="BO23">
-        <v>2.68</v>
-      </c>
-      <c r="BP23">
-        <v>25</v>
-      </c>
-      <c r="BQ23">
-        <v>4</v>
-      </c>
-      <c r="BR23">
-        <v>50</v>
-      </c>
-      <c r="BS23">
-        <v>4.4</v>
-      </c>
       <c r="BT23">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BU23">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BV23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW23">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY23">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BZ23">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="CA23">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB23" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6447,480 +6456,480 @@
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F24">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G24">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H24">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I24">
+        <v>3.6</v>
+      </c>
+      <c r="J24">
         <v>3.3</v>
       </c>
-      <c r="J24">
-        <v>3.45</v>
-      </c>
       <c r="K24">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L24">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="O24">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="R24">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S24">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="T24">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U24">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X24">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y24">
+        <v>11.5</v>
+      </c>
+      <c r="Z24">
+        <v>24</v>
+      </c>
+      <c r="AA24">
+        <v>80</v>
+      </c>
+      <c r="AB24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24">
+        <v>7.4</v>
+      </c>
+      <c r="AD24">
+        <v>15.5</v>
+      </c>
+      <c r="AE24">
+        <v>48</v>
+      </c>
+      <c r="AF24">
+        <v>14</v>
+      </c>
+      <c r="AG24">
+        <v>12</v>
+      </c>
+      <c r="AH24">
+        <v>21</v>
+      </c>
+      <c r="AI24">
+        <v>60</v>
+      </c>
+      <c r="AJ24">
+        <v>34</v>
+      </c>
+      <c r="AK24">
+        <v>29</v>
+      </c>
+      <c r="AL24">
+        <v>50</v>
+      </c>
+      <c r="AM24">
+        <v>150</v>
+      </c>
+      <c r="AN24">
+        <v>24</v>
+      </c>
+      <c r="AO24">
+        <v>55</v>
+      </c>
+      <c r="AP24">
+        <v>10</v>
+      </c>
+      <c r="AQ24">
+        <v>10</v>
+      </c>
+      <c r="AR24">
+        <v>20</v>
+      </c>
+      <c r="AS24">
+        <v>42</v>
+      </c>
+      <c r="AT24">
+        <v>8.4</v>
+      </c>
+      <c r="AU24">
+        <v>6.8</v>
+      </c>
+      <c r="AV24">
         <v>13.5</v>
       </c>
-      <c r="Z24">
-        <v>23</v>
-      </c>
-      <c r="AA24">
-        <v>60</v>
-      </c>
-      <c r="AB24">
-        <v>11</v>
-      </c>
-      <c r="AC24">
-        <v>8</v>
-      </c>
-      <c r="AD24">
-        <v>14.5</v>
-      </c>
-      <c r="AE24">
-        <v>38</v>
-      </c>
-      <c r="AF24">
-        <v>16.5</v>
-      </c>
-      <c r="AG24">
-        <v>11.5</v>
-      </c>
-      <c r="AH24">
-        <v>17.5</v>
-      </c>
-      <c r="AI24">
-        <v>46</v>
-      </c>
-      <c r="AJ24">
+      <c r="AW24">
         <v>36</v>
       </c>
-      <c r="AK24">
-        <v>27</v>
-      </c>
-      <c r="AL24">
-        <v>40</v>
-      </c>
-      <c r="AM24">
-        <v>110</v>
-      </c>
-      <c r="AN24">
-        <v>20</v>
-      </c>
-      <c r="AO24">
-        <v>32</v>
-      </c>
-      <c r="AP24">
-        <v>13</v>
-      </c>
-      <c r="AQ24">
-        <v>11.5</v>
-      </c>
-      <c r="AR24">
-        <v>19</v>
-      </c>
-      <c r="AS24">
-        <v>10.5</v>
-      </c>
-      <c r="AT24">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU24">
-        <v>7.2</v>
-      </c>
-      <c r="AV24">
+      <c r="AX24">
         <v>12.5</v>
-      </c>
-      <c r="AW24">
-        <v>15.5</v>
-      </c>
-      <c r="AX24">
-        <v>14</v>
       </c>
       <c r="AY24">
         <v>10.5</v>
       </c>
       <c r="AZ24">
+        <v>17.5</v>
+      </c>
+      <c r="BA24">
+        <v>46</v>
+      </c>
+      <c r="BB24">
+        <v>26</v>
+      </c>
+      <c r="BC24">
+        <v>20</v>
+      </c>
+      <c r="BD24">
+        <v>38</v>
+      </c>
+      <c r="BE24">
+        <v>55</v>
+      </c>
+      <c r="BF24">
+        <v>20</v>
+      </c>
+      <c r="BG24">
+        <v>38</v>
+      </c>
+      <c r="BH24">
+        <v>3.2</v>
+      </c>
+      <c r="BI24">
+        <v>2.68</v>
+      </c>
+      <c r="BJ24">
         <v>15</v>
       </c>
-      <c r="BA24">
-        <v>10</v>
-      </c>
-      <c r="BB24">
-        <v>15</v>
-      </c>
-      <c r="BC24">
-        <v>23</v>
-      </c>
-      <c r="BD24">
-        <v>16.5</v>
-      </c>
-      <c r="BE24">
-        <v>12</v>
-      </c>
-      <c r="BF24">
-        <v>16.5</v>
-      </c>
-      <c r="BG24">
-        <v>9.4</v>
-      </c>
-      <c r="BH24">
-        <v>3.4</v>
-      </c>
-      <c r="BI24">
-        <v>3.15</v>
-      </c>
-      <c r="BJ24">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BK24">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="BN24">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BO24">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="BP24">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BQ24">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BR24">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BS24">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BT24">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV24">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="BW24">
-        <v>9.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BX24">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="BZ24">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="CB24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F25">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="G25">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="H25">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="I25">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="J25">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L25">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M25">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O25">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.69</v>
+        <v>1.96</v>
       </c>
       <c r="Q25">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="R25">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S25">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="T25">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="U25">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="X25">
+        <v>14.5</v>
+      </c>
+      <c r="Y25">
+        <v>13.5</v>
+      </c>
+      <c r="Z25">
+        <v>23</v>
+      </c>
+      <c r="AA25">
+        <v>60</v>
+      </c>
+      <c r="AB25">
         <v>11</v>
       </c>
-      <c r="Y25">
-        <v>12.5</v>
-      </c>
-      <c r="Z25">
-        <v>32</v>
-      </c>
-      <c r="AA25">
-        <v>110</v>
-      </c>
-      <c r="AB25">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AC25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD25">
+        <v>14.5</v>
+      </c>
+      <c r="AE25">
+        <v>38</v>
+      </c>
+      <c r="AF25">
+        <v>16</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
         <v>17.5</v>
       </c>
-      <c r="AE25">
-        <v>70</v>
-      </c>
-      <c r="AF25">
-        <v>13</v>
-      </c>
-      <c r="AG25">
-        <v>11.5</v>
-      </c>
-      <c r="AH25">
-        <v>26</v>
-      </c>
       <c r="AI25">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AJ25">
         <v>36</v>
       </c>
       <c r="AK25">
+        <v>27</v>
+      </c>
+      <c r="AL25">
+        <v>40</v>
+      </c>
+      <c r="AM25">
+        <v>110</v>
+      </c>
+      <c r="AN25">
+        <v>21</v>
+      </c>
+      <c r="AO25">
+        <v>32</v>
+      </c>
+      <c r="AP25">
+        <v>13</v>
+      </c>
+      <c r="AQ25">
+        <v>11.5</v>
+      </c>
+      <c r="AR25">
+        <v>19</v>
+      </c>
+      <c r="AS25">
+        <v>10</v>
+      </c>
+      <c r="AT25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU25">
+        <v>7.2</v>
+      </c>
+      <c r="AV25">
+        <v>12.5</v>
+      </c>
+      <c r="AW25">
+        <v>15.5</v>
+      </c>
+      <c r="AX25">
+        <v>14</v>
+      </c>
+      <c r="AY25">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25">
+        <v>15</v>
+      </c>
+      <c r="BA25">
+        <v>9.6</v>
+      </c>
+      <c r="BB25">
+        <v>15</v>
+      </c>
+      <c r="BC25">
+        <v>19</v>
+      </c>
+      <c r="BD25">
+        <v>16.5</v>
+      </c>
+      <c r="BE25">
+        <v>11</v>
+      </c>
+      <c r="BF25">
+        <v>17.5</v>
+      </c>
+      <c r="BG25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH25">
+        <v>3.4</v>
+      </c>
+      <c r="BI25">
+        <v>3.15</v>
+      </c>
+      <c r="BJ25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>13.5</v>
+      </c>
+      <c r="BN25">
+        <v>5.4</v>
+      </c>
+      <c r="BO25">
+        <v>4.9</v>
+      </c>
+      <c r="BP25">
+        <v>19</v>
+      </c>
+      <c r="BQ25">
+        <v>8.6</v>
+      </c>
+      <c r="BR25">
         <v>34</v>
       </c>
-      <c r="AL25">
-        <v>60</v>
-      </c>
-      <c r="AM25">
-        <v>170</v>
-      </c>
-      <c r="AN25">
-        <v>29</v>
-      </c>
-      <c r="AO25">
-        <v>90</v>
-      </c>
-      <c r="AP25">
+      <c r="BS25">
+        <v>10.5</v>
+      </c>
+      <c r="BT25">
+        <v>6.4</v>
+      </c>
+      <c r="BU25">
+        <v>5.6</v>
+      </c>
+      <c r="BV25">
+        <v>25</v>
+      </c>
+      <c r="BW25">
         <v>9.6</v>
       </c>
-      <c r="AQ25">
-        <v>10.5</v>
-      </c>
-      <c r="AR25">
-        <v>6.6</v>
-      </c>
-      <c r="AS25">
-        <v>7.8</v>
-      </c>
-      <c r="AT25">
-        <v>7</v>
-      </c>
-      <c r="AU25">
-        <v>6.8</v>
-      </c>
-      <c r="AV25">
-        <v>14.5</v>
-      </c>
-      <c r="AW25">
-        <v>22</v>
-      </c>
-      <c r="AX25">
+      <c r="BX25">
+        <v>38</v>
+      </c>
+      <c r="BY25">
         <v>11</v>
       </c>
-      <c r="AY25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ25">
-        <v>18</v>
-      </c>
-      <c r="BA25">
-        <v>7.8</v>
-      </c>
-      <c r="BB25">
-        <v>6.8</v>
-      </c>
-      <c r="BC25">
-        <v>6.6</v>
-      </c>
-      <c r="BD25">
-        <v>7.4</v>
-      </c>
-      <c r="BE25">
-        <v>8</v>
-      </c>
-      <c r="BF25">
-        <v>17</v>
-      </c>
-      <c r="BG25">
-        <v>7.8</v>
-      </c>
-      <c r="BH25">
-        <v>3.45</v>
-      </c>
-      <c r="BI25">
-        <v>2.72</v>
-      </c>
-      <c r="BJ25">
-        <v>12.5</v>
-      </c>
-      <c r="BK25">
-        <v>3.95</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
-        <v>4.8</v>
-      </c>
-      <c r="BN25">
-        <v>5.7</v>
-      </c>
-      <c r="BO25">
-        <v>4.3</v>
-      </c>
-      <c r="BP25">
-        <v>21</v>
-      </c>
-      <c r="BQ25">
-        <v>4</v>
-      </c>
-      <c r="BR25">
-        <v>44</v>
-      </c>
-      <c r="BS25">
-        <v>4.4</v>
-      </c>
-      <c r="BT25">
-        <v>8.6</v>
-      </c>
-      <c r="BU25">
-        <v>5.4</v>
-      </c>
-      <c r="BV25">
-        <v>44</v>
-      </c>
-      <c r="BW25">
-        <v>4.4</v>
-      </c>
-      <c r="BX25">
-        <v>65</v>
-      </c>
-      <c r="BY25">
-        <v>4.5</v>
-      </c>
       <c r="BZ25">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="CA25">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="CB25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -6931,243 +6940,243 @@
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F26">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="H26">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="I26">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="J26">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L26">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P26">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q26">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S26">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T26">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U26">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V26">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="X26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y26">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA26">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26">
         <v>7.8</v>
       </c>
       <c r="AD26">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AF26">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI26">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ26">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK26">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM26">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN26">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AO26">
         <v>90</v>
       </c>
       <c r="AP26">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR26">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS26">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT26">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU26">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV26">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AW26">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AX26">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY26">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
         <v>18</v>
       </c>
       <c r="BA26">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BB26">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BC26">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BD26">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BE26">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BF26">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG26">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BH26">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BI26">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="BJ26">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BN26">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO26">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP26">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BQ26">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="BR26">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BS26">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BT26">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BU26">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BV26">
         <v>44</v>
       </c>
       <c r="BW26">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX26">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY26">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="BZ26">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="CA26">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="CB26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
         <v>93</v>
@@ -7176,482 +7185,482 @@
         <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F27">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="G27">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="H27">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I27">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J27">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
+        <v>1.47</v>
+      </c>
+      <c r="M27">
+        <v>1.09</v>
+      </c>
+      <c r="N27">
+        <v>3.3</v>
+      </c>
+      <c r="O27">
         <v>1.4</v>
       </c>
-      <c r="M27">
-        <v>1.06</v>
-      </c>
-      <c r="N27">
-        <v>3.95</v>
-      </c>
-      <c r="O27">
-        <v>1.31</v>
-      </c>
       <c r="P27">
+        <v>1.78</v>
+      </c>
+      <c r="Q27">
+        <v>2.18</v>
+      </c>
+      <c r="R27">
+        <v>1.29</v>
+      </c>
+      <c r="S27">
+        <v>4.1</v>
+      </c>
+      <c r="T27">
         <v>2</v>
       </c>
-      <c r="Q27">
-        <v>1.89</v>
-      </c>
-      <c r="R27">
-        <v>1.4</v>
-      </c>
-      <c r="S27">
-        <v>3.3</v>
-      </c>
-      <c r="T27">
-        <v>1.89</v>
-      </c>
       <c r="U27">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V27">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="X27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y27">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Z27">
+        <v>38</v>
+      </c>
+      <c r="AA27">
+        <v>120</v>
+      </c>
+      <c r="AB27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC27">
+        <v>8</v>
+      </c>
+      <c r="AD27">
+        <v>20</v>
+      </c>
+      <c r="AE27">
+        <v>140</v>
+      </c>
+      <c r="AF27">
+        <v>11.5</v>
+      </c>
+      <c r="AG27">
+        <v>10.5</v>
+      </c>
+      <c r="AH27">
+        <v>22</v>
+      </c>
+      <c r="AI27">
         <v>80</v>
       </c>
-      <c r="AA27">
-        <v>170</v>
-      </c>
-      <c r="AB27">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD27">
-        <v>22</v>
-      </c>
-      <c r="AE27">
+      <c r="AJ27">
+        <v>42</v>
+      </c>
+      <c r="AK27">
+        <v>24</v>
+      </c>
+      <c r="AL27">
+        <v>85</v>
+      </c>
+      <c r="AM27">
+        <v>160</v>
+      </c>
+      <c r="AN27">
+        <v>17.5</v>
+      </c>
+      <c r="AO27">
         <v>90</v>
       </c>
-      <c r="AF27">
-        <v>10.5</v>
-      </c>
-      <c r="AG27">
+      <c r="AP27">
         <v>10</v>
       </c>
-      <c r="AH27">
-        <v>21</v>
-      </c>
-      <c r="AI27">
-        <v>90</v>
-      </c>
-      <c r="AJ27">
-        <v>19</v>
-      </c>
-      <c r="AK27">
-        <v>19</v>
-      </c>
-      <c r="AL27">
-        <v>75</v>
-      </c>
-      <c r="AM27">
-        <v>140</v>
-      </c>
-      <c r="AN27">
-        <v>10.5</v>
-      </c>
-      <c r="AO27">
-        <v>110</v>
-      </c>
-      <c r="AP27">
-        <v>14</v>
-      </c>
       <c r="AQ27">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AS27">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT27">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU27">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AV27">
         <v>16</v>
       </c>
       <c r="AW27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX27">
+        <v>10</v>
+      </c>
+      <c r="AY27">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27">
+        <v>10</v>
+      </c>
+      <c r="BA27">
+        <v>10.5</v>
+      </c>
+      <c r="BB27">
+        <v>20</v>
+      </c>
+      <c r="BC27">
+        <v>20</v>
+      </c>
+      <c r="BD27">
+        <v>19</v>
+      </c>
+      <c r="BE27">
+        <v>11</v>
+      </c>
+      <c r="BF27">
+        <v>15</v>
+      </c>
+      <c r="BG27">
+        <v>10.5</v>
+      </c>
+      <c r="BH27">
+        <v>3.1</v>
+      </c>
+      <c r="BI27">
+        <v>2.84</v>
+      </c>
+      <c r="BJ27">
+        <v>11</v>
+      </c>
+      <c r="BK27">
+        <v>6.2</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>12.5</v>
+      </c>
+      <c r="BN27">
+        <v>4.6</v>
+      </c>
+      <c r="BO27">
+        <v>4.1</v>
+      </c>
+      <c r="BP27">
+        <v>15.5</v>
+      </c>
+      <c r="BQ27">
+        <v>7.2</v>
+      </c>
+      <c r="BR27">
+        <v>34</v>
+      </c>
+      <c r="BS27">
         <v>9.6</v>
       </c>
-      <c r="AY27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ27">
-        <v>8.4</v>
-      </c>
-      <c r="BA27">
-        <v>12</v>
-      </c>
-      <c r="BB27">
-        <v>14.5</v>
-      </c>
-      <c r="BC27">
-        <v>15</v>
-      </c>
-      <c r="BD27">
+      <c r="BT27">
+        <v>8</v>
+      </c>
+      <c r="BU27">
+        <v>6.8</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
         <v>10</v>
       </c>
-      <c r="BE27">
-        <v>12.5</v>
-      </c>
-      <c r="BF27">
+      <c r="BX27">
+        <v>60</v>
+      </c>
+      <c r="BY27">
+        <v>11</v>
+      </c>
+      <c r="BZ27">
+        <v>32</v>
+      </c>
+      <c r="CA27">
         <v>9.4</v>
       </c>
-      <c r="BG27">
-        <v>12</v>
-      </c>
-      <c r="BH27">
-        <v>1000</v>
-      </c>
-      <c r="BI27">
-        <v>1.53</v>
-      </c>
-      <c r="BJ27">
-        <v>1000</v>
-      </c>
-      <c r="BK27">
-        <v>2.3</v>
-      </c>
-      <c r="BL27">
-        <v>1000</v>
-      </c>
-      <c r="BM27">
-        <v>1.06</v>
-      </c>
-      <c r="BN27">
-        <v>1000</v>
-      </c>
-      <c r="BO27">
-        <v>1.7</v>
-      </c>
-      <c r="BP27">
-        <v>1000</v>
-      </c>
-      <c r="BQ27">
-        <v>2.62</v>
-      </c>
-      <c r="BR27">
-        <v>1000</v>
-      </c>
-      <c r="BS27">
-        <v>1.06</v>
-      </c>
-      <c r="BT27">
-        <v>1000</v>
-      </c>
-      <c r="BU27">
-        <v>2.16</v>
-      </c>
-      <c r="BV27">
-        <v>1000</v>
-      </c>
-      <c r="BW27">
-        <v>1.06</v>
-      </c>
-      <c r="BX27">
-        <v>1000</v>
-      </c>
-      <c r="BY27">
-        <v>1.06</v>
-      </c>
-      <c r="BZ27">
-        <v>1000</v>
-      </c>
-      <c r="CA27">
-        <v>1.06</v>
-      </c>
       <c r="CB27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
         <v>93</v>
       </c>
       <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28">
+        <v>1.71</v>
+      </c>
+      <c r="G28">
+        <v>1.77</v>
+      </c>
+      <c r="H28">
+        <v>5.3</v>
+      </c>
+      <c r="I28">
+        <v>5.8</v>
+      </c>
+      <c r="J28">
+        <v>3.95</v>
+      </c>
+      <c r="K28">
+        <v>4.3</v>
+      </c>
+      <c r="L28">
+        <v>1.4</v>
+      </c>
+      <c r="M28">
+        <v>1.06</v>
+      </c>
+      <c r="N28">
+        <v>3.95</v>
+      </c>
+      <c r="O28">
+        <v>1.3</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>1.89</v>
+      </c>
+      <c r="R28">
+        <v>1.39</v>
+      </c>
+      <c r="S28">
+        <v>3.3</v>
+      </c>
+      <c r="T28">
+        <v>1.89</v>
+      </c>
+      <c r="U28">
+        <v>2.04</v>
+      </c>
+      <c r="V28">
+        <v>1.21</v>
+      </c>
+      <c r="W28">
+        <v>2.28</v>
+      </c>
+      <c r="X28">
+        <v>16</v>
+      </c>
+      <c r="Y28">
+        <v>19</v>
+      </c>
+      <c r="Z28">
+        <v>80</v>
+      </c>
+      <c r="AA28">
+        <v>170</v>
+      </c>
+      <c r="AB28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD28">
+        <v>22</v>
+      </c>
+      <c r="AE28">
+        <v>90</v>
+      </c>
+      <c r="AF28">
+        <v>10.5</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+      <c r="AH28">
+        <v>21</v>
+      </c>
+      <c r="AI28">
+        <v>90</v>
+      </c>
+      <c r="AJ28">
+        <v>18</v>
+      </c>
+      <c r="AK28">
+        <v>19</v>
+      </c>
+      <c r="AL28">
+        <v>70</v>
+      </c>
+      <c r="AM28">
+        <v>140</v>
+      </c>
+      <c r="AN28">
+        <v>10.5</v>
+      </c>
+      <c r="AO28">
         <v>110</v>
       </c>
-      <c r="D28" t="s">
-        <v>138</v>
-      </c>
-      <c r="E28" t="s">
-        <v>169</v>
-      </c>
-      <c r="F28">
-        <v>1.22</v>
-      </c>
-      <c r="G28">
-        <v>1.3</v>
-      </c>
-      <c r="H28">
+      <c r="AP28">
+        <v>14</v>
+      </c>
+      <c r="AQ28">
+        <v>14.5</v>
+      </c>
+      <c r="AR28">
         <v>10.5</v>
       </c>
-      <c r="I28">
-        <v>16.5</v>
-      </c>
-      <c r="J28">
-        <v>6.4</v>
-      </c>
-      <c r="K28">
+      <c r="AS28">
+        <v>13</v>
+      </c>
+      <c r="AT28">
+        <v>7.8</v>
+      </c>
+      <c r="AU28">
         <v>8.199999999999999</v>
       </c>
-      <c r="L28">
-        <v>1.01</v>
-      </c>
-      <c r="M28">
-        <v>1.01</v>
-      </c>
-      <c r="N28">
-        <v>6.6</v>
-      </c>
-      <c r="O28">
-        <v>1.13</v>
-      </c>
-      <c r="P28">
-        <v>2.8</v>
-      </c>
-      <c r="Q28">
-        <v>1.13</v>
-      </c>
-      <c r="R28">
-        <v>1.79</v>
-      </c>
-      <c r="S28">
-        <v>1.53</v>
-      </c>
-      <c r="T28">
-        <v>1.11</v>
-      </c>
-      <c r="U28">
-        <v>1.11</v>
-      </c>
-      <c r="V28">
-        <v>1.06</v>
-      </c>
-      <c r="W28">
-        <v>4.2</v>
-      </c>
-      <c r="X28">
-        <v>42</v>
-      </c>
-      <c r="Y28">
-        <v>950</v>
-      </c>
-      <c r="Z28">
-        <v>150</v>
-      </c>
-      <c r="AA28">
-        <v>520</v>
-      </c>
-      <c r="AB28">
-        <v>15</v>
-      </c>
-      <c r="AC28">
-        <v>19.5</v>
-      </c>
-      <c r="AD28">
-        <v>55</v>
-      </c>
-      <c r="AE28">
-        <v>210</v>
-      </c>
-      <c r="AF28">
-        <v>11.5</v>
-      </c>
-      <c r="AG28">
-        <v>14</v>
-      </c>
-      <c r="AH28">
-        <v>36</v>
-      </c>
-      <c r="AI28">
-        <v>150</v>
-      </c>
-      <c r="AJ28">
+      <c r="AV28">
+        <v>16</v>
+      </c>
+      <c r="AW28">
         <v>12</v>
       </c>
-      <c r="AK28">
-        <v>16</v>
-      </c>
-      <c r="AL28">
-        <v>38</v>
-      </c>
-      <c r="AM28">
-        <v>150</v>
-      </c>
-      <c r="AN28">
-        <v>4</v>
-      </c>
-      <c r="AO28">
-        <v>220</v>
-      </c>
-      <c r="AP28">
-        <v>4.8</v>
-      </c>
-      <c r="AQ28">
-        <v>4.9</v>
-      </c>
-      <c r="AR28">
-        <v>5.2</v>
-      </c>
-      <c r="AS28">
-        <v>5.3</v>
-      </c>
-      <c r="AT28">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU28">
-        <v>13</v>
-      </c>
-      <c r="AV28">
-        <v>4.9</v>
-      </c>
-      <c r="AW28">
-        <v>5.3</v>
-      </c>
       <c r="AX28">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY28">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BA28">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BB28">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="BC28">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BD28">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="BE28">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF28">
-        <v>2.92</v>
+        <v>9.4</v>
       </c>
       <c r="BG28">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BH28">
         <v>1000</v>
       </c>
       <c r="BI28">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="BJ28">
         <v>1000</v>
       </c>
       <c r="BK28">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BN28">
         <v>1000</v>
       </c>
       <c r="BO28">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BP28">
         <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BT28">
         <v>1000</v>
       </c>
       <c r="BU28">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="CB28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
         <v>93</v>
@@ -7660,477 +7669,477 @@
         <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F29">
-        <v>2.74</v>
+        <v>1.23</v>
       </c>
       <c r="G29">
+        <v>1.31</v>
+      </c>
+      <c r="H29">
+        <v>10.5</v>
+      </c>
+      <c r="I29">
+        <v>16.5</v>
+      </c>
+      <c r="J29">
+        <v>6.4</v>
+      </c>
+      <c r="K29">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>6.6</v>
+      </c>
+      <c r="O29">
+        <v>1.13</v>
+      </c>
+      <c r="P29">
         <v>2.94</v>
       </c>
-      <c r="H29">
-        <v>2.56</v>
-      </c>
-      <c r="I29">
-        <v>2.72</v>
-      </c>
-      <c r="J29">
-        <v>3.6</v>
-      </c>
-      <c r="K29">
-        <v>3.75</v>
-      </c>
-      <c r="L29">
-        <v>1.33</v>
-      </c>
-      <c r="M29">
+      <c r="Q29">
+        <v>1.4</v>
+      </c>
+      <c r="R29">
+        <v>1.79</v>
+      </c>
+      <c r="S29">
+        <v>1.99</v>
+      </c>
+      <c r="T29">
+        <v>1.87</v>
+      </c>
+      <c r="U29">
+        <v>1.89</v>
+      </c>
+      <c r="V29">
         <v>1.06</v>
       </c>
-      <c r="N29">
-        <v>4.3</v>
-      </c>
-      <c r="O29">
-        <v>1.26</v>
-      </c>
-      <c r="P29">
-        <v>2.12</v>
-      </c>
-      <c r="Q29">
-        <v>1.8</v>
-      </c>
-      <c r="R29">
-        <v>1.45</v>
-      </c>
-      <c r="S29">
-        <v>2.98</v>
-      </c>
-      <c r="T29">
-        <v>1.67</v>
-      </c>
-      <c r="U29">
-        <v>2.34</v>
-      </c>
-      <c r="V29">
-        <v>1.58</v>
-      </c>
       <c r="W29">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="X29">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Y29">
-        <v>12.5</v>
+        <v>950</v>
       </c>
       <c r="Z29">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="AA29">
-        <v>46</v>
+        <v>520</v>
       </c>
       <c r="AB29">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC29">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="AD29">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="AE29">
-        <v>29</v>
+        <v>210</v>
       </c>
       <c r="AF29">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AG29">
+        <v>14</v>
+      </c>
+      <c r="AH29">
+        <v>36</v>
+      </c>
+      <c r="AI29">
+        <v>150</v>
+      </c>
+      <c r="AJ29">
+        <v>12</v>
+      </c>
+      <c r="AK29">
+        <v>16</v>
+      </c>
+      <c r="AL29">
+        <v>38</v>
+      </c>
+      <c r="AM29">
+        <v>150</v>
+      </c>
+      <c r="AN29">
+        <v>4</v>
+      </c>
+      <c r="AO29">
+        <v>220</v>
+      </c>
+      <c r="AP29">
+        <v>4.8</v>
+      </c>
+      <c r="AQ29">
+        <v>4.9</v>
+      </c>
+      <c r="AR29">
+        <v>5.2</v>
+      </c>
+      <c r="AS29">
+        <v>5.3</v>
+      </c>
+      <c r="AT29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU29">
         <v>13</v>
       </c>
-      <c r="AH29">
-        <v>16.5</v>
-      </c>
-      <c r="AI29">
-        <v>44</v>
-      </c>
-      <c r="AJ29">
-        <v>55</v>
-      </c>
-      <c r="AK29">
-        <v>36</v>
-      </c>
-      <c r="AL29">
-        <v>46</v>
-      </c>
-      <c r="AM29">
-        <v>90</v>
-      </c>
-      <c r="AN29">
-        <v>26</v>
-      </c>
-      <c r="AO29">
-        <v>21</v>
-      </c>
-      <c r="AP29">
-        <v>14.5</v>
-      </c>
-      <c r="AQ29">
-        <v>11</v>
-      </c>
-      <c r="AR29">
-        <v>16</v>
-      </c>
-      <c r="AS29">
-        <v>8.4</v>
-      </c>
-      <c r="AT29">
-        <v>12</v>
-      </c>
-      <c r="AU29">
+      <c r="AV29">
+        <v>4.9</v>
+      </c>
+      <c r="AW29">
+        <v>5.3</v>
+      </c>
+      <c r="AX29">
         <v>7.6</v>
       </c>
-      <c r="AV29">
-        <v>11</v>
-      </c>
-      <c r="AW29">
-        <v>18.5</v>
-      </c>
-      <c r="AX29">
-        <v>16.5</v>
-      </c>
       <c r="AY29">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>14.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA29">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BB29">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC29">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BD29">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE29">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BF29">
-        <v>17</v>
+        <v>2.92</v>
       </c>
       <c r="BG29">
-        <v>16.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH29">
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s">
         <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F30">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="G30">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="H30">
-        <v>3.95</v>
+        <v>2.58</v>
       </c>
       <c r="I30">
+        <v>2.74</v>
+      </c>
+      <c r="J30">
+        <v>3.6</v>
+      </c>
+      <c r="K30">
+        <v>3.75</v>
+      </c>
+      <c r="L30">
+        <v>1.33</v>
+      </c>
+      <c r="M30">
+        <v>1.06</v>
+      </c>
+      <c r="N30">
         <v>4.3</v>
       </c>
-      <c r="J30">
+      <c r="O30">
+        <v>1.26</v>
+      </c>
+      <c r="P30">
+        <v>2.12</v>
+      </c>
+      <c r="Q30">
+        <v>1.76</v>
+      </c>
+      <c r="R30">
+        <v>1.45</v>
+      </c>
+      <c r="S30">
+        <v>2.9</v>
+      </c>
+      <c r="T30">
+        <v>1.67</v>
+      </c>
+      <c r="U30">
+        <v>2.34</v>
+      </c>
+      <c r="V30">
+        <v>1.57</v>
+      </c>
+      <c r="W30">
+        <v>1.52</v>
+      </c>
+      <c r="X30">
+        <v>17.5</v>
+      </c>
+      <c r="Y30">
+        <v>13</v>
+      </c>
+      <c r="Z30">
+        <v>19.5</v>
+      </c>
+      <c r="AA30">
+        <v>48</v>
+      </c>
+      <c r="AB30">
+        <v>13</v>
+      </c>
+      <c r="AC30">
+        <v>8.4</v>
+      </c>
+      <c r="AD30">
+        <v>12.5</v>
+      </c>
+      <c r="AE30">
+        <v>29</v>
+      </c>
+      <c r="AF30">
+        <v>21</v>
+      </c>
+      <c r="AG30">
+        <v>13</v>
+      </c>
+      <c r="AH30">
+        <v>16</v>
+      </c>
+      <c r="AI30">
+        <v>42</v>
+      </c>
+      <c r="AJ30">
+        <v>48</v>
+      </c>
+      <c r="AK30">
+        <v>36</v>
+      </c>
+      <c r="AL30">
+        <v>42</v>
+      </c>
+      <c r="AM30">
+        <v>90</v>
+      </c>
+      <c r="AN30">
+        <v>22</v>
+      </c>
+      <c r="AO30">
+        <v>21</v>
+      </c>
+      <c r="AP30">
+        <v>14.5</v>
+      </c>
+      <c r="AQ30">
+        <v>11.5</v>
+      </c>
+      <c r="AR30">
+        <v>16</v>
+      </c>
+      <c r="AS30">
+        <v>10</v>
+      </c>
+      <c r="AT30">
+        <v>11.5</v>
+      </c>
+      <c r="AU30">
+        <v>7.6</v>
+      </c>
+      <c r="AV30">
+        <v>11</v>
+      </c>
+      <c r="AW30">
+        <v>18.5</v>
+      </c>
+      <c r="AX30">
+        <v>17.5</v>
+      </c>
+      <c r="AY30">
+        <v>11.5</v>
+      </c>
+      <c r="AZ30">
+        <v>14</v>
+      </c>
+      <c r="BA30">
+        <v>9.6</v>
+      </c>
+      <c r="BB30">
+        <v>27</v>
+      </c>
+      <c r="BC30">
+        <v>23</v>
+      </c>
+      <c r="BD30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE30">
+        <v>11.5</v>
+      </c>
+      <c r="BF30">
+        <v>18</v>
+      </c>
+      <c r="BG30">
+        <v>17</v>
+      </c>
+      <c r="BH30">
+        <v>1000</v>
+      </c>
+      <c r="BI30">
         <v>3.05</v>
       </c>
-      <c r="K30">
-        <v>3.3</v>
-      </c>
-      <c r="L30">
-        <v>1.56</v>
-      </c>
-      <c r="M30">
-        <v>1.12</v>
-      </c>
-      <c r="N30">
-        <v>2.68</v>
-      </c>
-      <c r="O30">
-        <v>1.52</v>
-      </c>
-      <c r="P30">
-        <v>1.58</v>
-      </c>
-      <c r="Q30">
-        <v>2.56</v>
-      </c>
-      <c r="R30">
-        <v>1.21</v>
-      </c>
-      <c r="S30">
-        <v>5.2</v>
-      </c>
-      <c r="T30">
-        <v>2.1</v>
-      </c>
-      <c r="U30">
-        <v>1.8</v>
-      </c>
-      <c r="V30">
-        <v>1.3</v>
-      </c>
-      <c r="W30">
-        <v>1.76</v>
-      </c>
-      <c r="X30">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y30">
-        <v>11.5</v>
-      </c>
-      <c r="Z30">
-        <v>60</v>
-      </c>
-      <c r="AA30">
-        <v>120</v>
-      </c>
-      <c r="AB30">
-        <v>7.4</v>
-      </c>
-      <c r="AC30">
-        <v>7.4</v>
-      </c>
-      <c r="AD30">
-        <v>19.5</v>
-      </c>
-      <c r="AE30">
-        <v>85</v>
-      </c>
-      <c r="AF30">
-        <v>13</v>
-      </c>
-      <c r="AG30">
-        <v>14</v>
-      </c>
-      <c r="AH30">
-        <v>55</v>
-      </c>
-      <c r="AI30">
-        <v>110</v>
-      </c>
-      <c r="AJ30">
-        <v>38</v>
-      </c>
-      <c r="AK30">
-        <v>38</v>
-      </c>
-      <c r="AL30">
-        <v>70</v>
-      </c>
-      <c r="AM30">
-        <v>220</v>
-      </c>
-      <c r="AN30">
-        <v>36</v>
-      </c>
-      <c r="AO30">
-        <v>120</v>
-      </c>
-      <c r="AP30">
-        <v>8</v>
-      </c>
-      <c r="AQ30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR30">
-        <v>20</v>
-      </c>
-      <c r="AS30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT30">
-        <v>6.6</v>
-      </c>
-      <c r="AU30">
-        <v>6.4</v>
-      </c>
-      <c r="AV30">
-        <v>15.5</v>
-      </c>
-      <c r="AW30">
-        <v>8.6</v>
-      </c>
-      <c r="AX30">
-        <v>11</v>
-      </c>
-      <c r="AY30">
-        <v>10</v>
-      </c>
-      <c r="AZ30">
-        <v>6.8</v>
-      </c>
-      <c r="BA30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB30">
-        <v>12</v>
-      </c>
-      <c r="BC30">
-        <v>7.6</v>
-      </c>
-      <c r="BD30">
-        <v>8.4</v>
-      </c>
-      <c r="BE30">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF30">
-        <v>21</v>
-      </c>
-      <c r="BG30">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH30">
-        <v>2.78</v>
-      </c>
-      <c r="BI30">
-        <v>2.54</v>
-      </c>
       <c r="BJ30">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>6.6</v>
+        <v>2.04</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="BN30">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>4.2</v>
+        <v>1.84</v>
       </c>
       <c r="BP30">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>8.6</v>
+        <v>2.4</v>
       </c>
       <c r="BR30">
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="BT30">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>5.7</v>
+        <v>1.82</v>
       </c>
       <c r="BV30">
         <v>1000</v>
       </c>
       <c r="BW30">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="BX30">
         <v>1000</v>
       </c>
       <c r="BY30">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
       <c r="BZ30">
         <v>1000</v>
       </c>
       <c r="CA30">
-        <v>11.5</v>
+        <v>2.4</v>
       </c>
       <c r="CB30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8141,238 +8150,238 @@
         <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F31">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G31">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="H31">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I31">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J31">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="K31">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L31">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M31">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="O31">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="P31">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Q31">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S31">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="T31">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="U31">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="X31">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y31">
+        <v>11.5</v>
+      </c>
+      <c r="Z31">
+        <v>60</v>
+      </c>
+      <c r="AA31">
+        <v>130</v>
+      </c>
+      <c r="AB31">
+        <v>7.4</v>
+      </c>
+      <c r="AC31">
+        <v>7.4</v>
+      </c>
+      <c r="AD31">
+        <v>19.5</v>
+      </c>
+      <c r="AE31">
+        <v>85</v>
+      </c>
+      <c r="AF31">
+        <v>13</v>
+      </c>
+      <c r="AG31">
         <v>14</v>
       </c>
-      <c r="Z31">
+      <c r="AH31">
+        <v>55</v>
+      </c>
+      <c r="AI31">
+        <v>110</v>
+      </c>
+      <c r="AJ31">
+        <v>38</v>
+      </c>
+      <c r="AK31">
+        <v>38</v>
+      </c>
+      <c r="AL31">
+        <v>70</v>
+      </c>
+      <c r="AM31">
+        <v>220</v>
+      </c>
+      <c r="AN31">
         <v>36</v>
       </c>
-      <c r="AA31">
-        <v>110</v>
-      </c>
-      <c r="AB31">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC31">
+      <c r="AO31">
+        <v>130</v>
+      </c>
+      <c r="AP31">
         <v>8</v>
       </c>
-      <c r="AD31">
-        <v>17</v>
-      </c>
-      <c r="AE31">
-        <v>65</v>
-      </c>
-      <c r="AF31">
-        <v>12.5</v>
-      </c>
-      <c r="AG31">
-        <v>11</v>
-      </c>
-      <c r="AH31">
-        <v>19</v>
-      </c>
-      <c r="AI31">
-        <v>75</v>
-      </c>
-      <c r="AJ31">
-        <v>46</v>
-      </c>
-      <c r="AK31">
-        <v>24</v>
-      </c>
-      <c r="AL31">
-        <v>40</v>
-      </c>
-      <c r="AM31">
-        <v>130</v>
-      </c>
-      <c r="AN31">
-        <v>16.5</v>
-      </c>
-      <c r="AO31">
-        <v>60</v>
-      </c>
-      <c r="AP31">
-        <v>11.5</v>
-      </c>
       <c r="AQ31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AR31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AT31">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AU31">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV31">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW31">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX31">
         <v>11</v>
       </c>
       <c r="AY31">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ31">
         <v>17</v>
       </c>
       <c r="BA31">
+        <v>8.4</v>
+      </c>
+      <c r="BB31">
         <v>11.5</v>
       </c>
-      <c r="BB31">
-        <v>22</v>
-      </c>
       <c r="BC31">
+        <v>7.4</v>
+      </c>
+      <c r="BD31">
+        <v>26</v>
+      </c>
+      <c r="BE31">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF31">
         <v>21</v>
       </c>
-      <c r="BD31">
-        <v>10</v>
-      </c>
-      <c r="BE31">
+      <c r="BG31">
+        <v>8.6</v>
+      </c>
+      <c r="BH31">
+        <v>2.78</v>
+      </c>
+      <c r="BI31">
+        <v>2.54</v>
+      </c>
+      <c r="BJ31">
+        <v>11.5</v>
+      </c>
+      <c r="BK31">
+        <v>6.8</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>15</v>
+      </c>
+      <c r="BN31">
+        <v>4.8</v>
+      </c>
+      <c r="BO31">
+        <v>4.2</v>
+      </c>
+      <c r="BP31">
+        <v>1000</v>
+      </c>
+      <c r="BQ31">
+        <v>8.6</v>
+      </c>
+      <c r="BR31">
+        <v>1000</v>
+      </c>
+      <c r="BS31">
+        <v>11.5</v>
+      </c>
+      <c r="BT31">
+        <v>7.2</v>
+      </c>
+      <c r="BU31">
+        <v>5.7</v>
+      </c>
+      <c r="BV31">
+        <v>1000</v>
+      </c>
+      <c r="BW31">
+        <v>11.5</v>
+      </c>
+      <c r="BX31">
+        <v>1000</v>
+      </c>
+      <c r="BY31">
+        <v>13</v>
+      </c>
+      <c r="BZ31">
+        <v>1000</v>
+      </c>
+      <c r="CA31">
         <v>12</v>
       </c>
-      <c r="BF31">
-        <v>14.5</v>
-      </c>
-      <c r="BG31">
-        <v>11</v>
-      </c>
-      <c r="BH31">
-        <v>1000</v>
-      </c>
-      <c r="BI31">
-        <v>2</v>
-      </c>
-      <c r="BJ31">
-        <v>14.5</v>
-      </c>
-      <c r="BK31">
-        <v>3.6</v>
-      </c>
-      <c r="BL31">
-        <v>1000</v>
-      </c>
-      <c r="BM31">
-        <v>1.99</v>
-      </c>
-      <c r="BN31">
-        <v>5.3</v>
-      </c>
-      <c r="BO31">
-        <v>2.48</v>
-      </c>
-      <c r="BP31">
-        <v>21</v>
-      </c>
-      <c r="BQ31">
-        <v>1.82</v>
-      </c>
-      <c r="BR31">
-        <v>46</v>
-      </c>
-      <c r="BS31">
-        <v>1.91</v>
-      </c>
-      <c r="BT31">
-        <v>9</v>
-      </c>
-      <c r="BU31">
-        <v>6</v>
-      </c>
-      <c r="BV31">
-        <v>50</v>
-      </c>
-      <c r="BW31">
-        <v>1.92</v>
-      </c>
-      <c r="BX31">
-        <v>1000</v>
-      </c>
-      <c r="BY31">
-        <v>1.94</v>
-      </c>
-      <c r="BZ31">
-        <v>40</v>
-      </c>
-      <c r="CA31">
-        <v>1.9</v>
-      </c>
       <c r="CB31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8383,238 +8392,480 @@
         <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F32">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="G32">
-        <v>4.6</v>
+        <v>2.08</v>
       </c>
       <c r="H32">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="I32">
-        <v>2.02</v>
+        <v>4.5</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L32">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M32">
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="O32">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q32">
+        <v>2.04</v>
+      </c>
+      <c r="R32">
+        <v>1.34</v>
+      </c>
+      <c r="S32">
+        <v>3.65</v>
+      </c>
+      <c r="T32">
+        <v>1.88</v>
+      </c>
+      <c r="U32">
         <v>2.08</v>
       </c>
-      <c r="R32">
-        <v>1.32</v>
-      </c>
-      <c r="S32">
-        <v>3.8</v>
-      </c>
-      <c r="T32">
+      <c r="V32">
+        <v>1.29</v>
+      </c>
+      <c r="W32">
         <v>1.92</v>
       </c>
-      <c r="U32">
-        <v>1.97</v>
-      </c>
-      <c r="V32">
-        <v>1.99</v>
-      </c>
-      <c r="W32">
-        <v>1.28</v>
-      </c>
       <c r="X32">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y32">
+        <v>14.5</v>
+      </c>
+      <c r="Z32">
+        <v>36</v>
+      </c>
+      <c r="AA32">
+        <v>110</v>
+      </c>
+      <c r="AB32">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z32">
+      <c r="AC32">
+        <v>8</v>
+      </c>
+      <c r="AD32">
+        <v>17.5</v>
+      </c>
+      <c r="AE32">
+        <v>60</v>
+      </c>
+      <c r="AF32">
         <v>12.5</v>
       </c>
-      <c r="AA32">
-        <v>27</v>
-      </c>
-      <c r="AB32">
-        <v>14.5</v>
-      </c>
-      <c r="AC32">
-        <v>8.4</v>
-      </c>
-      <c r="AD32">
+      <c r="AG32">
         <v>11</v>
       </c>
-      <c r="AE32">
+      <c r="AH32">
+        <v>19.5</v>
+      </c>
+      <c r="AI32">
+        <v>60</v>
+      </c>
+      <c r="AJ32">
         <v>24</v>
       </c>
-      <c r="AF32">
-        <v>38</v>
-      </c>
-      <c r="AG32">
-        <v>19</v>
-      </c>
-      <c r="AH32">
-        <v>21</v>
-      </c>
-      <c r="AI32">
-        <v>48</v>
-      </c>
-      <c r="AJ32">
-        <v>120</v>
-      </c>
       <c r="AK32">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="AL32">
+        <v>40</v>
+      </c>
+      <c r="AM32">
+        <v>130</v>
+      </c>
+      <c r="AN32">
+        <v>15.5</v>
+      </c>
+      <c r="AO32">
         <v>80</v>
       </c>
-      <c r="AM32">
-        <v>140</v>
-      </c>
-      <c r="AN32">
-        <v>85</v>
-      </c>
-      <c r="AO32">
-        <v>18.5</v>
-      </c>
       <c r="AP32">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ32">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR32">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS32">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AT32">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AU32">
         <v>7.2</v>
       </c>
       <c r="AV32">
+        <v>14.5</v>
+      </c>
+      <c r="AW32">
+        <v>26</v>
+      </c>
+      <c r="AX32">
+        <v>11</v>
+      </c>
+      <c r="AY32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32">
+        <v>17</v>
+      </c>
+      <c r="BA32">
+        <v>11</v>
+      </c>
+      <c r="BB32">
+        <v>21</v>
+      </c>
+      <c r="BC32">
+        <v>20</v>
+      </c>
+      <c r="BD32">
+        <v>10</v>
+      </c>
+      <c r="BE32">
+        <v>12.5</v>
+      </c>
+      <c r="BF32">
+        <v>13.5</v>
+      </c>
+      <c r="BG32">
+        <v>11.5</v>
+      </c>
+      <c r="BH32">
+        <v>3.3</v>
+      </c>
+      <c r="BI32">
+        <v>3</v>
+      </c>
+      <c r="BJ32">
+        <v>10</v>
+      </c>
+      <c r="BK32">
+        <v>6.4</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>15.5</v>
+      </c>
+      <c r="BN32">
+        <v>4.6</v>
+      </c>
+      <c r="BO32">
+        <v>4.1</v>
+      </c>
+      <c r="BP32">
+        <v>14</v>
+      </c>
+      <c r="BQ32">
+        <v>7.8</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>11</v>
+      </c>
+      <c r="BT32">
+        <v>7.8</v>
+      </c>
+      <c r="BU32">
+        <v>6.8</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>12</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>13</v>
+      </c>
+      <c r="BZ32">
+        <v>27</v>
+      </c>
+      <c r="CA32">
+        <v>10.5</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33">
+        <v>4.3</v>
+      </c>
+      <c r="G33">
+        <v>4.7</v>
+      </c>
+      <c r="H33">
+        <v>1.95</v>
+      </c>
+      <c r="I33">
+        <v>2.02</v>
+      </c>
+      <c r="J33">
+        <v>3.6</v>
+      </c>
+      <c r="K33">
+        <v>3.85</v>
+      </c>
+      <c r="L33">
+        <v>1.43</v>
+      </c>
+      <c r="M33">
+        <v>1.08</v>
+      </c>
+      <c r="N33">
+        <v>3.45</v>
+      </c>
+      <c r="O33">
+        <v>1.37</v>
+      </c>
+      <c r="P33">
+        <v>1.82</v>
+      </c>
+      <c r="Q33">
+        <v>2.08</v>
+      </c>
+      <c r="R33">
+        <v>1.33</v>
+      </c>
+      <c r="S33">
+        <v>3.8</v>
+      </c>
+      <c r="T33">
+        <v>1.95</v>
+      </c>
+      <c r="U33">
+        <v>1.97</v>
+      </c>
+      <c r="V33">
+        <v>1.98</v>
+      </c>
+      <c r="W33">
+        <v>1.28</v>
+      </c>
+      <c r="X33">
+        <v>15</v>
+      </c>
+      <c r="Y33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z33">
+        <v>12.5</v>
+      </c>
+      <c r="AA33">
+        <v>28</v>
+      </c>
+      <c r="AB33">
+        <v>14.5</v>
+      </c>
+      <c r="AC33">
+        <v>8.4</v>
+      </c>
+      <c r="AD33">
+        <v>11</v>
+      </c>
+      <c r="AE33">
+        <v>24</v>
+      </c>
+      <c r="AF33">
+        <v>38</v>
+      </c>
+      <c r="AG33">
+        <v>19</v>
+      </c>
+      <c r="AH33">
+        <v>21</v>
+      </c>
+      <c r="AI33">
+        <v>48</v>
+      </c>
+      <c r="AJ33">
+        <v>120</v>
+      </c>
+      <c r="AK33">
+        <v>70</v>
+      </c>
+      <c r="AL33">
+        <v>80</v>
+      </c>
+      <c r="AM33">
+        <v>140</v>
+      </c>
+      <c r="AN33">
+        <v>85</v>
+      </c>
+      <c r="AO33">
+        <v>19</v>
+      </c>
+      <c r="AP33">
+        <v>11</v>
+      </c>
+      <c r="AQ33">
+        <v>7.4</v>
+      </c>
+      <c r="AR33">
+        <v>10</v>
+      </c>
+      <c r="AS33">
+        <v>20</v>
+      </c>
+      <c r="AT33">
+        <v>12</v>
+      </c>
+      <c r="AU33">
+        <v>7.2</v>
+      </c>
+      <c r="AV33">
         <v>9.4</v>
       </c>
-      <c r="AW32">
+      <c r="AW33">
         <v>19.5</v>
       </c>
-      <c r="AX32">
+      <c r="AX33">
         <v>7.2</v>
       </c>
-      <c r="AY32">
+      <c r="AY33">
         <v>15.5</v>
       </c>
-      <c r="AZ32">
+      <c r="AZ33">
         <v>17.5</v>
       </c>
-      <c r="BA32">
-        <v>7.2</v>
-      </c>
-      <c r="BB32">
+      <c r="BA33">
+        <v>7</v>
+      </c>
+      <c r="BB33">
+        <v>7.8</v>
+      </c>
+      <c r="BC33">
         <v>7.4</v>
       </c>
-      <c r="BC32">
+      <c r="BD33">
         <v>7.6</v>
       </c>
-      <c r="BD32">
-        <v>7.8</v>
-      </c>
-      <c r="BE32">
-        <v>7.4</v>
-      </c>
-      <c r="BF32">
-        <v>7.8</v>
-      </c>
-      <c r="BG32">
+      <c r="BE33">
+        <v>38</v>
+      </c>
+      <c r="BF33">
+        <v>7.6</v>
+      </c>
+      <c r="BG33">
         <v>13.5</v>
       </c>
-      <c r="BH32">
+      <c r="BH33">
         <v>3.6</v>
       </c>
-      <c r="BI32">
+      <c r="BI33">
         <v>2.92</v>
       </c>
-      <c r="BJ32">
+      <c r="BJ33">
         <v>12</v>
       </c>
-      <c r="BK32">
+      <c r="BK33">
         <v>3.95</v>
       </c>
-      <c r="BL32">
-        <v>1000</v>
-      </c>
-      <c r="BM32">
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
         <v>5.7</v>
       </c>
-      <c r="BN32">
+      <c r="BN33">
         <v>9</v>
       </c>
-      <c r="BO32">
+      <c r="BO33">
         <v>6</v>
       </c>
-      <c r="BP32">
+      <c r="BP33">
         <v>48</v>
       </c>
-      <c r="BQ32">
+      <c r="BQ33">
+        <v>5.2</v>
+      </c>
+      <c r="BR33">
+        <v>60</v>
+      </c>
+      <c r="BS33">
         <v>5.3</v>
       </c>
-      <c r="BR32">
-        <v>60</v>
-      </c>
-      <c r="BS32">
-        <v>5.4</v>
-      </c>
-      <c r="BT32">
+      <c r="BT33">
         <v>5.1</v>
       </c>
-      <c r="BU32">
+      <c r="BU33">
         <v>4</v>
       </c>
-      <c r="BV32">
-        <v>16</v>
-      </c>
-      <c r="BW32">
+      <c r="BV33">
+        <v>16.5</v>
+      </c>
+      <c r="BW33">
         <v>4.3</v>
       </c>
-      <c r="BX32">
+      <c r="BX33">
         <v>36</v>
       </c>
-      <c r="BY32">
-        <v>5.1</v>
-      </c>
-      <c r="BZ32">
+      <c r="BY33">
+        <v>5</v>
+      </c>
+      <c r="BZ33">
         <v>32</v>
       </c>
-      <c r="CA32">
+      <c r="CA33">
         <v>5</v>
       </c>
-      <c r="CB32" t="s">
-        <v>174</v>
+      <c r="CB33" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -547,7 +547,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 15:02:08</t>
+    <t>2026-10-06 17:13:21</t>
   </si>
 </sst>
 </file>
@@ -1147,10 +1147,10 @@
         <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
         <v>4.1</v>
@@ -1159,37 +1159,37 @@
         <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O2">
         <v>1.14</v>
       </c>
       <c r="P2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="S2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="T2">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U2">
         <v>3.1</v>
       </c>
       <c r="V2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W2">
         <v>1.47</v>
@@ -1207,7 +1207,7 @@
         <v>32</v>
       </c>
       <c r="AB2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC2">
         <v>10.5</v>
@@ -1216,13 +1216,13 @@
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF2">
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>13</v>
@@ -1243,10 +1243,10 @@
         <v>44</v>
       </c>
       <c r="AN2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AP2">
         <v>30</v>
@@ -1255,13 +1255,13 @@
         <v>18</v>
       </c>
       <c r="AR2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS2">
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU2">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX2">
         <v>26</v>
@@ -1279,13 +1279,13 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BC2">
         <v>25</v>
@@ -1336,7 +1336,7 @@
         <v>24</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>5.9</v>
@@ -1360,7 +1360,7 @@
         <v>12</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1392,46 +1392,46 @@
         <v>1.33</v>
       </c>
       <c r="I3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="J3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -1440,7 +1440,7 @@
         <v>18</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z3">
         <v>7.2</v>
@@ -1461,7 +1461,7 @@
         <v>16.5</v>
       </c>
       <c r="AF3">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AG3">
         <v>48</v>
@@ -1470,25 +1470,25 @@
         <v>38</v>
       </c>
       <c r="AI3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>610</v>
+        <v>740</v>
       </c>
       <c r="AK3">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AL3">
+        <v>210</v>
+      </c>
+      <c r="AM3">
         <v>270</v>
-      </c>
-      <c r="AM3">
-        <v>260</v>
       </c>
       <c r="AN3">
         <v>430</v>
       </c>
       <c r="AO3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP3">
         <v>15.5</v>
@@ -1497,7 +1497,7 @@
         <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS3">
         <v>9</v>
@@ -1509,10 +1509,10 @@
         <v>11.5</v>
       </c>
       <c r="AV3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
         <v>14</v>
@@ -1527,19 +1527,19 @@
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC3">
         <v>15</v>
       </c>
       <c r="BD3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BE3">
         <v>15</v>
       </c>
       <c r="BF3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG3">
         <v>5.8</v>
@@ -1554,31 +1554,31 @@
         <v>14</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BO3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BP3">
         <v>130</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>120</v>
       </c>
       <c r="BS3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT3">
         <v>3.6</v>
@@ -1596,13 +1596,13 @@
         <v>29</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>15</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1628,19 +1628,19 @@
         <v>2.28</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1667,7 +1667,7 @@
         <v>4.8</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U4">
         <v>1.86</v>
@@ -1676,7 +1676,7 @@
         <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1685,10 +1685,10 @@
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB4">
         <v>8.4</v>
@@ -1709,7 +1709,7 @@
         <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>80</v>
@@ -1727,10 +1727,10 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP4">
         <v>8.800000000000001</v>
@@ -1748,7 +1748,7 @@
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>12.5</v>
@@ -1769,10 +1769,10 @@
         <v>46</v>
       </c>
       <c r="BB4">
+        <v>25</v>
+      </c>
+      <c r="BC4">
         <v>24</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
       </c>
       <c r="BD4">
         <v>36</v>
@@ -1781,7 +1781,7 @@
         <v>110</v>
       </c>
       <c r="BF4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG4">
         <v>42</v>
@@ -1796,13 +1796,13 @@
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1811,7 +1811,7 @@
         <v>3.85</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ4">
         <v>4</v>
@@ -1820,7 +1820,7 @@
         <v>48</v>
       </c>
       <c r="BS4">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BT4">
         <v>8</v>
@@ -1832,19 +1832,19 @@
         <v>42</v>
       </c>
       <c r="BW4">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BZ4">
         <v>50</v>
       </c>
       <c r="CA4">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1870,10 +1870,10 @@
         <v>1.49</v>
       </c>
       <c r="G5">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>11</v>
@@ -1882,7 +1882,7 @@
         <v>3.55</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.42</v>
@@ -1900,10 +1900,10 @@
         <v>1.68</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S5">
         <v>3.55</v>
@@ -1918,13 +1918,13 @@
         <v>1.1</v>
       </c>
       <c r="W5">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="X5">
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z5">
         <v>95</v>
@@ -1957,7 +1957,7 @@
         <v>210</v>
       </c>
       <c r="AJ5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1969,64 +1969,64 @@
         <v>300</v>
       </c>
       <c r="AN5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO5">
         <v>440</v>
       </c>
       <c r="AP5">
+        <v>3.9</v>
+      </c>
+      <c r="AQ5">
+        <v>4.4</v>
+      </c>
+      <c r="AR5">
+        <v>5.2</v>
+      </c>
+      <c r="AS5">
+        <v>5.4</v>
+      </c>
+      <c r="AT5">
+        <v>3.1</v>
+      </c>
+      <c r="AU5">
         <v>3.7</v>
       </c>
-      <c r="AQ5">
-        <v>4.2</v>
-      </c>
-      <c r="AR5">
-        <v>4.9</v>
-      </c>
-      <c r="AS5">
-        <v>5.1</v>
-      </c>
-      <c r="AT5">
-        <v>3</v>
-      </c>
-      <c r="AU5">
-        <v>3.55</v>
-      </c>
       <c r="AV5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW5">
+        <v>5.3</v>
+      </c>
+      <c r="AX5">
+        <v>3.4</v>
+      </c>
+      <c r="AY5">
+        <v>3.75</v>
+      </c>
+      <c r="AZ5">
+        <v>4.8</v>
+      </c>
+      <c r="BA5">
+        <v>5.3</v>
+      </c>
+      <c r="BB5">
+        <v>4</v>
+      </c>
+      <c r="BC5">
+        <v>4.4</v>
+      </c>
+      <c r="BD5">
         <v>5</v>
       </c>
-      <c r="AX5">
-        <v>3.25</v>
-      </c>
-      <c r="AY5">
-        <v>3.6</v>
-      </c>
-      <c r="AZ5">
-        <v>4.5</v>
-      </c>
-      <c r="BA5">
-        <v>5</v>
-      </c>
-      <c r="BB5">
-        <v>3.9</v>
-      </c>
-      <c r="BC5">
-        <v>4.2</v>
-      </c>
-      <c r="BD5">
-        <v>4.8</v>
-      </c>
       <c r="BE5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG5">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH5">
         <v>3.2</v>
@@ -2109,22 +2109,22 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.3</v>
@@ -2133,34 +2133,34 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
         <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S6">
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2178,7 +2178,7 @@
         <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>14.5</v>
@@ -2193,25 +2193,25 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
         <v>40</v>
       </c>
-      <c r="AJ6">
-        <v>42</v>
-      </c>
       <c r="AK6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO6">
         <v>22</v>
@@ -2223,10 +2223,10 @@
         <v>12</v>
       </c>
       <c r="AR6">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT6">
         <v>12.5</v>
@@ -2238,7 +2238,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="AX6">
         <v>14.5</v>
@@ -2250,19 +2250,19 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB6">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>5.6</v>
+        <v>27</v>
       </c>
       <c r="BE6">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
         <v>14.5</v>
@@ -2354,16 +2354,16 @@
         <v>6.2</v>
       </c>
       <c r="G7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H7">
         <v>1.55</v>
       </c>
       <c r="I7">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
         <v>4.8</v>
@@ -2381,16 +2381,16 @@
         <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
         <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T7">
         <v>1.85</v>
@@ -2399,7 +2399,7 @@
         <v>2.08</v>
       </c>
       <c r="V7">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="W7">
         <v>1.16</v>
@@ -2447,7 +2447,7 @@
         <v>110</v>
       </c>
       <c r="AL7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM7">
         <v>130</v>
@@ -2462,7 +2462,7 @@
         <v>17</v>
       </c>
       <c r="AQ7">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7">
         <v>8.800000000000001</v>
@@ -2483,7 +2483,7 @@
         <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>5.8</v>
+        <v>42</v>
       </c>
       <c r="AY7">
         <v>21</v>
@@ -2495,19 +2495,19 @@
         <v>5.5</v>
       </c>
       <c r="BB7">
+        <v>6.2</v>
+      </c>
+      <c r="BC7">
         <v>6</v>
       </c>
-      <c r="BC7">
-        <v>5.9</v>
-      </c>
       <c r="BD7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG7">
         <v>6.2</v>
@@ -2593,22 +2593,22 @@
         <v>151</v>
       </c>
       <c r="F8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G8">
         <v>4.1</v>
       </c>
       <c r="H8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2617,13 +2617,13 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2635,7 +2635,7 @@
         <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U8">
         <v>2.08</v>
@@ -2647,7 +2647,7 @@
         <v>1.32</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y8">
         <v>11</v>
@@ -2725,7 +2725,7 @@
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>23</v>
+        <v>5.4</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2740,16 +2740,16 @@
         <v>5.5</v>
       </c>
       <c r="BC8">
+        <v>5.8</v>
+      </c>
+      <c r="BD8">
         <v>5.9</v>
-      </c>
-      <c r="BD8">
-        <v>6</v>
       </c>
       <c r="BE8">
         <v>5.6</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG8">
         <v>15</v>
@@ -2856,7 +2856,7 @@
         <v>1.3</v>
       </c>
       <c r="M9">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N9">
         <v>2.4</v>
@@ -2865,7 +2865,7 @@
         <v>1.62</v>
       </c>
       <c r="P9">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
         <v>2.56</v>
@@ -2886,7 +2886,7 @@
         <v>1.49</v>
       </c>
       <c r="W9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X9">
         <v>9.4</v>
@@ -3080,13 +3080,13 @@
         <v>1.77</v>
       </c>
       <c r="G10">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
         <v>4.2</v>
       </c>
       <c r="I10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>3.15</v>
@@ -3098,13 +3098,13 @@
         <v>1.37</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
         <v>2.74</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="P10">
         <v>1.63</v>
@@ -3128,7 +3128,7 @@
         <v>1.18</v>
       </c>
       <c r="W10">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3319,16 +3319,16 @@
         <v>154</v>
       </c>
       <c r="F11">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G11">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H11">
         <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="J11">
         <v>3.9</v>
@@ -3340,13 +3340,13 @@
         <v>1.18</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
         <v>6</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
         <v>2.72</v>
@@ -3358,19 +3358,19 @@
         <v>1.71</v>
       </c>
       <c r="S11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T11">
         <v>1.45</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W11">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X11">
         <v>32</v>
@@ -3475,7 +3475,7 @@
         <v>4.8</v>
       </c>
       <c r="BF11">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11">
         <v>9.6</v>
@@ -3564,13 +3564,13 @@
         <v>1.1</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12">
         <v>1.1</v>
       </c>
       <c r="I12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J12">
         <v>1.1</v>
@@ -3585,13 +3585,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q12">
         <v>1.42</v>
@@ -3609,7 +3609,7 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
         <v>1.02</v>
@@ -3827,22 +3827,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O13">
         <v>1.36</v>
       </c>
       <c r="P13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q13">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R13">
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4051,10 +4051,10 @@
         <v>4.2</v>
       </c>
       <c r="H14">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>3.9</v>
@@ -4078,25 +4078,25 @@
         <v>2.16</v>
       </c>
       <c r="Q14">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R14">
         <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T14">
         <v>1.73</v>
       </c>
       <c r="U14">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X14">
         <v>18</v>
@@ -4111,7 +4111,7 @@
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC14">
         <v>8.6</v>
@@ -4150,7 +4150,7 @@
         <v>42</v>
       </c>
       <c r="AO14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP14">
         <v>15.5</v>
@@ -4171,7 +4171,7 @@
         <v>8</v>
       </c>
       <c r="AV14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW14">
         <v>17</v>
@@ -4222,7 +4222,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BN14">
         <v>9</v>
@@ -4231,25 +4231,25 @@
         <v>5.9</v>
       </c>
       <c r="BP14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BQ14">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BR14">
         <v>990</v>
       </c>
       <c r="BS14">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BT14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU14">
         <v>4</v>
       </c>
       <c r="BV14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BW14">
         <v>8.199999999999999</v>
@@ -4258,13 +4258,13 @@
         <v>38</v>
       </c>
       <c r="BY14">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BZ14">
         <v>30</v>
       </c>
       <c r="CA14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="CB14" t="s">
         <v>177</v>
@@ -4290,61 +4290,61 @@
         <v>1.64</v>
       </c>
       <c r="G15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H15">
         <v>6.8</v>
       </c>
       <c r="I15">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J15">
         <v>3.3</v>
       </c>
       <c r="K15">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15">
         <v>2.52</v>
       </c>
       <c r="O15">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="P15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q15">
         <v>2.6</v>
       </c>
       <c r="R15">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S15">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U15">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W15">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X15">
         <v>10.5</v>
       </c>
       <c r="Y15">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z15">
         <v>75</v>
@@ -4353,10 +4353,10 @@
         <v>380</v>
       </c>
       <c r="AB15">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
         <v>40</v>
@@ -4377,7 +4377,7 @@
         <v>230</v>
       </c>
       <c r="AJ15">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AK15">
         <v>30</v>
@@ -4395,61 +4395,61 @@
         <v>460</v>
       </c>
       <c r="AP15">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR15">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AS15">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT15">
         <v>4.9</v>
       </c>
       <c r="AU15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW15">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX15">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY15">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15">
+        <v>5.4</v>
+      </c>
+      <c r="BA15">
+        <v>5.7</v>
+      </c>
+      <c r="BB15">
+        <v>15</v>
+      </c>
+      <c r="BC15">
+        <v>18</v>
+      </c>
+      <c r="BD15">
         <v>5.6</v>
       </c>
-      <c r="BA15">
-        <v>6.2</v>
-      </c>
-      <c r="BB15">
-        <v>12.5</v>
-      </c>
-      <c r="BC15">
-        <v>5.3</v>
-      </c>
-      <c r="BD15">
-        <v>6</v>
-      </c>
       <c r="BE15">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF15">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG15">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH15">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
         <v>1.25</v>
@@ -4458,13 +4458,13 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>1000</v>
@@ -4476,37 +4476,37 @@
         <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>177</v>
@@ -4535,7 +4535,7 @@
         <v>2.54</v>
       </c>
       <c r="H16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I16">
         <v>4.1</v>
@@ -4774,7 +4774,7 @@
         <v>1.1</v>
       </c>
       <c r="G17">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H17">
         <v>1.1</v>
@@ -4795,22 +4795,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P17">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R17">
         <v>1.08</v>
       </c>
       <c r="S17">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -4819,7 +4819,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W17">
         <v>1.02</v>
@@ -5013,58 +5013,58 @@
         <v>161</v>
       </c>
       <c r="F18">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J18">
         <v>4.6</v>
       </c>
       <c r="K18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="M18">
         <v>1.07</v>
       </c>
       <c r="N18">
+        <v>3.4</v>
+      </c>
+      <c r="O18">
+        <v>1.36</v>
+      </c>
+      <c r="P18">
+        <v>1.83</v>
+      </c>
+      <c r="Q18">
+        <v>2.04</v>
+      </c>
+      <c r="R18">
+        <v>1.31</v>
+      </c>
+      <c r="S18">
+        <v>3.75</v>
+      </c>
+      <c r="T18">
+        <v>2.42</v>
+      </c>
+      <c r="U18">
+        <v>1.64</v>
+      </c>
+      <c r="V18">
+        <v>1.08</v>
+      </c>
+      <c r="W18">
         <v>3.35</v>
-      </c>
-      <c r="O18">
-        <v>1.35</v>
-      </c>
-      <c r="P18">
-        <v>1.82</v>
-      </c>
-      <c r="Q18">
-        <v>2.02</v>
-      </c>
-      <c r="R18">
-        <v>1.3</v>
-      </c>
-      <c r="S18">
-        <v>3.65</v>
-      </c>
-      <c r="T18">
-        <v>2.36</v>
-      </c>
-      <c r="U18">
-        <v>1.58</v>
-      </c>
-      <c r="V18">
-        <v>1.07</v>
-      </c>
-      <c r="W18">
-        <v>3.3</v>
       </c>
       <c r="X18">
         <v>16</v>
@@ -5121,10 +5121,10 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AR18">
         <v>5.9</v>
@@ -5133,43 +5133,43 @@
         <v>6</v>
       </c>
       <c r="AT18">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU18">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV18">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW18">
         <v>6</v>
       </c>
       <c r="AX18">
+        <v>6.2</v>
+      </c>
+      <c r="AY18">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18">
         <v>6</v>
-      </c>
-      <c r="AY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18">
-        <v>5.4</v>
       </c>
       <c r="BA18">
         <v>6</v>
       </c>
       <c r="BB18">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC18">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD18">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE18">
         <v>6</v>
       </c>
       <c r="BF18">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG18">
         <v>6</v>
@@ -5178,19 +5178,19 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
         <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BN18">
         <v>1000</v>
@@ -5202,37 +5202,37 @@
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
         <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="CB18" t="s">
         <v>177</v>
@@ -5279,22 +5279,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R19">
         <v>1.08</v>
       </c>
       <c r="S19">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5497,52 +5497,52 @@
         <v>163</v>
       </c>
       <c r="F20">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G20">
         <v>1.62</v>
       </c>
       <c r="H20">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J20">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O20">
         <v>1.55</v>
       </c>
       <c r="P20">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Q20">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
         <v>5.4</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="V20">
         <v>1.1</v>
@@ -5551,55 +5551,55 @@
         <v>2.6</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO20">
         <v>1000</v>
@@ -5608,55 +5608,55 @@
         <v>7</v>
       </c>
       <c r="AQ20">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR20">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AS20">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AU20">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AW20">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AX20">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY20">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BA20">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BB20">
         <v>11</v>
       </c>
       <c r="BC20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD20">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE20">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF20">
         <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5739,10 +5739,10 @@
         <v>164</v>
       </c>
       <c r="F21">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H21">
         <v>3.8</v>
@@ -5751,7 +5751,7 @@
         <v>3.9</v>
       </c>
       <c r="J21">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K21">
         <v>3.6</v>
@@ -5769,7 +5769,7 @@
         <v>1.38</v>
       </c>
       <c r="P21">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q21">
         <v>2.12</v>
@@ -5781,28 +5781,28 @@
         <v>3.9</v>
       </c>
       <c r="T21">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
         <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="X21">
         <v>14</v>
       </c>
       <c r="Y21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB21">
         <v>9.800000000000001</v>
@@ -5811,10 +5811,10 @@
         <v>9</v>
       </c>
       <c r="AD21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF21">
         <v>15</v>
@@ -5826,7 +5826,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ21">
         <v>32</v>
@@ -5844,7 +5844,7 @@
         <v>24</v>
       </c>
       <c r="AO21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP21">
         <v>10.5</v>
@@ -5853,10 +5853,10 @@
         <v>10</v>
       </c>
       <c r="AR21">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AS21">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT21">
         <v>7.4</v>
@@ -5865,10 +5865,10 @@
         <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AW21">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX21">
         <v>10</v>
@@ -5880,7 +5880,7 @@
         <v>17</v>
       </c>
       <c r="BA21">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB21">
         <v>21</v>
@@ -5889,16 +5889,16 @@
         <v>19</v>
       </c>
       <c r="BD21">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE21">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF21">
         <v>15</v>
       </c>
       <c r="BG21">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -6164,7 +6164,7 @@
         <v>7.2</v>
       </c>
       <c r="BO22">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP22">
         <v>38</v>
@@ -6223,7 +6223,7 @@
         <v>166</v>
       </c>
       <c r="F23">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G23">
         <v>1.91</v>
@@ -6244,22 +6244,22 @@
         <v>1.37</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23">
         <v>4.3</v>
       </c>
       <c r="O23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P23">
         <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S23">
         <v>3.05</v>
@@ -6268,19 +6268,19 @@
         <v>1.75</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V23">
         <v>1.27</v>
       </c>
       <c r="W23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X23">
         <v>22</v>
       </c>
       <c r="Y23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z23">
         <v>40</v>
@@ -6295,7 +6295,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE23">
         <v>65</v>
@@ -6307,13 +6307,13 @@
         <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI23">
         <v>70</v>
       </c>
       <c r="AJ23">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK23">
         <v>19.5</v>
@@ -6465,19 +6465,19 @@
         <v>167</v>
       </c>
       <c r="F24">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G24">
         <v>2.46</v>
       </c>
       <c r="H24">
+        <v>3.4</v>
+      </c>
+      <c r="I24">
+        <v>3.55</v>
+      </c>
+      <c r="J24">
         <v>3.35</v>
-      </c>
-      <c r="I24">
-        <v>3.6</v>
-      </c>
-      <c r="J24">
-        <v>3.3</v>
       </c>
       <c r="K24">
         <v>3.4</v>
@@ -6492,22 +6492,22 @@
         <v>3.25</v>
       </c>
       <c r="O24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P24">
         <v>1.76</v>
       </c>
       <c r="Q24">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R24">
         <v>1.29</v>
       </c>
       <c r="S24">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -6525,10 +6525,10 @@
         <v>11.5</v>
       </c>
       <c r="Z24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA24">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
         <v>9.199999999999999</v>
@@ -6549,7 +6549,7 @@
         <v>12</v>
       </c>
       <c r="AH24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI24">
         <v>60</v>
@@ -6564,10 +6564,10 @@
         <v>50</v>
       </c>
       <c r="AM24">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO24">
         <v>55</v>
@@ -6582,7 +6582,7 @@
         <v>20</v>
       </c>
       <c r="AS24">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
@@ -6603,28 +6603,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ24">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA24">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BB24">
         <v>26</v>
       </c>
       <c r="BC24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD24">
         <v>38</v>
       </c>
       <c r="BE24">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BF24">
         <v>20</v>
       </c>
       <c r="BG24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH24">
         <v>3.2</v>
@@ -6707,7 +6707,7 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G25">
         <v>2.54</v>
@@ -6731,7 +6731,7 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O25">
         <v>1.32</v>
@@ -6740,19 +6740,19 @@
         <v>1.96</v>
       </c>
       <c r="Q25">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S25">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
         <v>1.76</v>
       </c>
       <c r="U25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
         <v>1.44</v>
@@ -6764,13 +6764,13 @@
         <v>14.5</v>
       </c>
       <c r="Y25">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z25">
         <v>23</v>
       </c>
       <c r="AA25">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB25">
         <v>11</v>
@@ -6779,7 +6779,7 @@
         <v>8</v>
       </c>
       <c r="AD25">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE25">
         <v>38</v>
@@ -6824,7 +6824,7 @@
         <v>19</v>
       </c>
       <c r="AS25">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT25">
         <v>9.800000000000001</v>
@@ -6833,10 +6833,10 @@
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW25">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX25">
         <v>14</v>
@@ -6848,25 +6848,25 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB25">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BC25">
         <v>19</v>
       </c>
       <c r="BD25">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BE25">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF25">
         <v>17.5</v>
       </c>
       <c r="BG25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH25">
         <v>3.4</v>
@@ -6878,7 +6878,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK25">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6893,7 +6893,7 @@
         <v>4.9</v>
       </c>
       <c r="BP25">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ25">
         <v>8.6</v>
@@ -6914,19 +6914,19 @@
         <v>25</v>
       </c>
       <c r="BW25">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX25">
         <v>38</v>
       </c>
       <c r="BY25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ25">
         <v>28</v>
       </c>
       <c r="CA25">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6952,19 +6952,19 @@
         <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H26">
         <v>3.85</v>
       </c>
       <c r="I26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L26">
         <v>1.49</v>
@@ -6976,7 +6976,7 @@
         <v>2.96</v>
       </c>
       <c r="O26">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P26">
         <v>1.69</v>
@@ -6997,7 +6997,7 @@
         <v>1.91</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
         <v>1.79</v>
@@ -7090,7 +7090,7 @@
         <v>18</v>
       </c>
       <c r="BA26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB26">
         <v>6.8</v>
@@ -7099,7 +7099,7 @@
         <v>6.6</v>
       </c>
       <c r="BD26">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE26">
         <v>8</v>
@@ -7108,7 +7108,7 @@
         <v>17</v>
       </c>
       <c r="BG26">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH26">
         <v>3.45</v>
@@ -7194,10 +7194,10 @@
         <v>1.95</v>
       </c>
       <c r="G27">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H27">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27">
         <v>4.9</v>
@@ -7215,7 +7215,7 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
         <v>1.4</v>
@@ -7224,7 +7224,7 @@
         <v>1.78</v>
       </c>
       <c r="Q27">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
         <v>1.29</v>
@@ -7233,16 +7233,16 @@
         <v>4.1</v>
       </c>
       <c r="T27">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V27">
         <v>1.26</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X27">
         <v>12</v>
@@ -7251,7 +7251,7 @@
         <v>15</v>
       </c>
       <c r="Z27">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA27">
         <v>120</v>
@@ -7305,7 +7305,7 @@
         <v>12.5</v>
       </c>
       <c r="AR27">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AS27">
         <v>11</v>
@@ -7433,13 +7433,13 @@
         <v>171</v>
       </c>
       <c r="F28">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G28">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H28">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I28">
         <v>5.8</v>
@@ -7490,10 +7490,10 @@
         <v>16</v>
       </c>
       <c r="Y28">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="Z28">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA28">
         <v>170</v>
@@ -7523,13 +7523,13 @@
         <v>90</v>
       </c>
       <c r="AJ28">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AK28">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AL28">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM28">
         <v>140</v>
@@ -7547,10 +7547,10 @@
         <v>14.5</v>
       </c>
       <c r="AR28">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS28">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AT28">
         <v>7.8</v>
@@ -7559,22 +7559,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX28">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ28">
         <v>17</v>
       </c>
       <c r="BA28">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB28">
         <v>14.5</v>
@@ -7583,10 +7583,10 @@
         <v>15</v>
       </c>
       <c r="BD28">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
@@ -7920,13 +7920,13 @@
         <v>2.72</v>
       </c>
       <c r="G30">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H30">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I30">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J30">
         <v>3.6</v>
@@ -7959,19 +7959,19 @@
         <v>2.9</v>
       </c>
       <c r="T30">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V30">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W30">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y30">
         <v>13</v>
@@ -7983,7 +7983,7 @@
         <v>48</v>
       </c>
       <c r="AB30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC30">
         <v>8.4</v>
@@ -7995,10 +7995,10 @@
         <v>29</v>
       </c>
       <c r="AF30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH30">
         <v>16</v>
@@ -8010,7 +8010,7 @@
         <v>48</v>
       </c>
       <c r="AK30">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL30">
         <v>42</v>
@@ -8019,13 +8019,13 @@
         <v>90</v>
       </c>
       <c r="AN30">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO30">
         <v>21</v>
       </c>
       <c r="AP30">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ30">
         <v>11.5</v>
@@ -8034,13 +8034,13 @@
         <v>16</v>
       </c>
       <c r="AS30">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AT30">
         <v>11.5</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV30">
         <v>11</v>
@@ -8049,34 +8049,34 @@
         <v>18.5</v>
       </c>
       <c r="AX30">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BB30">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BC30">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BD30">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BE30">
         <v>11.5</v>
       </c>
       <c r="BF30">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG30">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8162,10 +8162,10 @@
         <v>2.18</v>
       </c>
       <c r="G31">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>4.4</v>
@@ -8198,7 +8198,7 @@
         <v>1.2</v>
       </c>
       <c r="S31">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T31">
         <v>2.1</v>
@@ -8231,7 +8231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AE31">
         <v>85</v>
@@ -8297,19 +8297,19 @@
         <v>10</v>
       </c>
       <c r="AZ31">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="BA31">
         <v>8.4</v>
       </c>
       <c r="BB31">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC31">
         <v>7.4</v>
       </c>
       <c r="BD31">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE31">
         <v>8.199999999999999</v>
@@ -8425,34 +8425,34 @@
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O32">
         <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q32">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R32">
         <v>1.34</v>
       </c>
       <c r="S32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T32">
         <v>1.88</v>
       </c>
       <c r="U32">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V32">
         <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X32">
         <v>13.5</v>
@@ -8461,7 +8461,7 @@
         <v>14.5</v>
       </c>
       <c r="Z32">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA32">
         <v>110</v>
@@ -8554,7 +8554,7 @@
         <v>10</v>
       </c>
       <c r="BE32">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF32">
         <v>13.5</v>
@@ -8646,10 +8646,10 @@
         <v>4.3</v>
       </c>
       <c r="G33">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H33">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I33">
         <v>2.02</v>
@@ -8667,28 +8667,28 @@
         <v>1.08</v>
       </c>
       <c r="N33">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O33">
         <v>1.37</v>
       </c>
       <c r="P33">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R33">
         <v>1.33</v>
       </c>
       <c r="S33">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T33">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U33">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V33">
         <v>1.98</v>
@@ -8718,7 +8718,7 @@
         <v>11</v>
       </c>
       <c r="AE33">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AF33">
         <v>38</v>
@@ -8748,7 +8748,7 @@
         <v>85</v>
       </c>
       <c r="AO33">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP33">
         <v>11</v>
@@ -8775,7 +8775,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY33">
         <v>15.5</v>
@@ -8784,19 +8784,19 @@
         <v>17.5</v>
       </c>
       <c r="BA33">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BB33">
         <v>7.8</v>
       </c>
       <c r="BC33">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BD33">
         <v>7.6</v>
       </c>
       <c r="BE33">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BF33">
         <v>7.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -547,7 +547,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 17:13:21</t>
+    <t>2026-10-06 19:24:56</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1141,7 @@
         <v>145</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G2">
         <v>3.1</v>
@@ -1150,7 +1150,7 @@
         <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J2">
         <v>4.1</v>
@@ -1165,31 +1165,31 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q2">
         <v>1.44</v>
       </c>
       <c r="R2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T2">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W2">
         <v>1.47</v>
@@ -1198,25 +1198,25 @@
         <v>34</v>
       </c>
       <c r="Y2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z2">
         <v>21</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB2">
         <v>24</v>
       </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD2">
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF2">
         <v>28</v>
@@ -1225,43 +1225,43 @@
         <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK2">
         <v>27</v>
       </c>
       <c r="AL2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AN2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP2">
         <v>30</v>
       </c>
       <c r="AQ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
         <v>29</v>
       </c>
       <c r="AT2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2">
         <v>10</v>
@@ -1285,40 +1285,40 @@
         <v>21</v>
       </c>
       <c r="BB2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BC2">
         <v>25</v>
       </c>
       <c r="BD2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE2">
         <v>34</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI2">
         <v>4.6</v>
       </c>
       <c r="BJ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>60</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN2">
         <v>7</v>
@@ -1327,19 +1327,19 @@
         <v>6.2</v>
       </c>
       <c r="BP2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BQ2">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BR2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU2">
         <v>5.4</v>
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>12</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,226 +1383,226 @@
         <v>146</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H3">
         <v>1.33</v>
       </c>
       <c r="I3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="J3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K3">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="U3">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="V3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="Z3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA3">
         <v>9.800000000000001</v>
       </c>
       <c r="AB3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
+        <v>18.5</v>
+      </c>
+      <c r="AF3">
+        <v>140</v>
+      </c>
+      <c r="AG3">
+        <v>60</v>
+      </c>
+      <c r="AH3">
+        <v>46</v>
+      </c>
+      <c r="AI3">
+        <v>70</v>
+      </c>
+      <c r="AJ3">
+        <v>930</v>
+      </c>
+      <c r="AK3">
+        <v>390</v>
+      </c>
+      <c r="AL3">
+        <v>360</v>
+      </c>
+      <c r="AM3">
+        <v>460</v>
+      </c>
+      <c r="AN3">
+        <v>830</v>
+      </c>
+      <c r="AO3">
+        <v>7.6</v>
+      </c>
+      <c r="AP3">
         <v>13</v>
       </c>
-      <c r="AD3">
-        <v>11</v>
-      </c>
-      <c r="AE3">
-        <v>16.5</v>
-      </c>
-      <c r="AF3">
-        <v>160</v>
-      </c>
-      <c r="AG3">
-        <v>48</v>
-      </c>
-      <c r="AH3">
-        <v>38</v>
-      </c>
-      <c r="AI3">
-        <v>55</v>
-      </c>
-      <c r="AJ3">
-        <v>740</v>
-      </c>
-      <c r="AK3">
-        <v>270</v>
-      </c>
-      <c r="AL3">
-        <v>210</v>
-      </c>
-      <c r="AM3">
-        <v>270</v>
-      </c>
-      <c r="AN3">
-        <v>430</v>
-      </c>
-      <c r="AO3">
-        <v>6.4</v>
-      </c>
-      <c r="AP3">
-        <v>15.5</v>
-      </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS3">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>27</v>
       </c>
       <c r="AU3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="AY3">
         <v>38</v>
       </c>
       <c r="AZ3">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>19.5</v>
       </c>
       <c r="BB3">
+        <v>18</v>
+      </c>
+      <c r="BC3">
+        <v>17.5</v>
+      </c>
+      <c r="BD3">
+        <v>19</v>
+      </c>
+      <c r="BE3">
+        <v>17.5</v>
+      </c>
+      <c r="BF3">
+        <v>18</v>
+      </c>
+      <c r="BG3">
+        <v>7</v>
+      </c>
+      <c r="BH3">
+        <v>3.25</v>
+      </c>
+      <c r="BI3">
+        <v>2.94</v>
+      </c>
+      <c r="BJ3">
         <v>15.5</v>
       </c>
-      <c r="BC3">
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>16</v>
+      </c>
+      <c r="BN3">
+        <v>16</v>
+      </c>
+      <c r="BO3">
+        <v>8.6</v>
+      </c>
+      <c r="BP3">
+        <v>180</v>
+      </c>
+      <c r="BQ3">
+        <v>15.5</v>
+      </c>
+      <c r="BR3">
+        <v>160</v>
+      </c>
+      <c r="BS3">
         <v>15</v>
       </c>
-      <c r="BD3">
-        <v>14.5</v>
-      </c>
-      <c r="BE3">
-        <v>15</v>
-      </c>
-      <c r="BF3">
-        <v>15</v>
-      </c>
-      <c r="BG3">
-        <v>5.8</v>
-      </c>
-      <c r="BH3">
-        <v>3.75</v>
-      </c>
-      <c r="BI3">
-        <v>3.4</v>
-      </c>
-      <c r="BJ3">
-        <v>14</v>
-      </c>
-      <c r="BK3">
-        <v>7.6</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>13.5</v>
-      </c>
-      <c r="BN3">
-        <v>15</v>
-      </c>
-      <c r="BO3">
-        <v>7.6</v>
-      </c>
-      <c r="BP3">
-        <v>130</v>
-      </c>
-      <c r="BQ3">
-        <v>13</v>
-      </c>
-      <c r="BR3">
-        <v>120</v>
-      </c>
-      <c r="BS3">
-        <v>13</v>
-      </c>
       <c r="BT3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BU3">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BV3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BW3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,22 +1625,22 @@
         <v>147</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J4">
         <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1649,7 +1649,7 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.46</v>
@@ -1658,25 +1658,25 @@
         <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
         <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1688,10 +1688,10 @@
         <v>27</v>
       </c>
       <c r="AA4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1715,7 +1715,7 @@
         <v>80</v>
       </c>
       <c r="AJ4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK4">
         <v>40</v>
@@ -1727,10 +1727,10 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP4">
         <v>8.800000000000001</v>
@@ -1742,7 +1742,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1751,7 +1751,7 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4">
         <v>34</v>
@@ -1763,7 +1763,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
         <v>46</v>
@@ -1772,13 +1772,13 @@
         <v>25</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD4">
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1787,22 +1787,22 @@
         <v>42</v>
       </c>
       <c r="BH4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN4">
         <v>5.9</v>
@@ -1814,13 +1814,13 @@
         <v>23</v>
       </c>
       <c r="BQ4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BR4">
         <v>48</v>
       </c>
       <c r="BS4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BT4">
         <v>8</v>
@@ -1832,19 +1832,19 @@
         <v>42</v>
       </c>
       <c r="BW4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ4">
         <v>50</v>
       </c>
       <c r="CA4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1867,46 +1867,46 @@
         <v>148</v>
       </c>
       <c r="F5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>11</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
         <v>1.24</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>2.28</v>
@@ -1915,136 +1915,136 @@
         <v>1.63</v>
       </c>
       <c r="V5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W5">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X5">
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA5">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB5">
         <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE5">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5">
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI5">
         <v>210</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK5">
         <v>23</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM5">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AP5">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
+        <v>6.6</v>
+      </c>
+      <c r="AT5">
         <v>5.4</v>
       </c>
-      <c r="AT5">
-        <v>3.1</v>
-      </c>
       <c r="AU5">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW5">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX5">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY5">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB5">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF5">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG5">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>3.2</v>
       </c>
       <c r="BI5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
         <v>15</v>
       </c>
       <c r="BK5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BN5">
         <v>4.2</v>
@@ -2053,40 +2053,40 @@
         <v>3.05</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BT5">
         <v>13.5</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ5">
         <v>28</v>
       </c>
       <c r="CA5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="s">
         <v>177</v>
@@ -2109,28 +2109,28 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G6">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
         <v>3.45</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
         <v>1.3</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6">
         <v>4.6</v>
@@ -2151,7 +2151,7 @@
         <v>2.64</v>
       </c>
       <c r="T6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
         <v>2.46</v>
@@ -2160,7 +2160,7 @@
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
         <v>22</v>
@@ -2381,22 +2381,22 @@
         <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q7">
         <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S7">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T7">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
         <v>2.6</v>
@@ -2492,7 +2492,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>5.5</v>
+        <v>26</v>
       </c>
       <c r="BB7">
         <v>6.2</v>
@@ -2617,10 +2617,10 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P8">
         <v>1.85</v>
@@ -2638,7 +2638,7 @@
         <v>1.83</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
         <v>1.81</v>
@@ -2653,7 +2653,7 @@
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>32</v>
@@ -2674,7 +2674,7 @@
         <v>34</v>
       </c>
       <c r="AG8">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH8">
         <v>19.5</v>
@@ -2716,7 +2716,7 @@
         <v>12</v>
       </c>
       <c r="AU8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
         <v>9.4</v>
@@ -2725,7 +2725,7 @@
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2737,19 +2737,19 @@
         <v>32</v>
       </c>
       <c r="BB8">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG8">
         <v>15</v>
@@ -2838,19 +2838,19 @@
         <v>3.15</v>
       </c>
       <c r="G9">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="H9">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I9">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J9">
         <v>2.8</v>
       </c>
       <c r="K9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
         <v>1.3</v>
@@ -2859,22 +2859,22 @@
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O9">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
         <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R9">
         <v>1.16</v>
       </c>
       <c r="S9">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="T9">
         <v>2.14</v>
@@ -2883,43 +2883,43 @@
         <v>1.72</v>
       </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X9">
         <v>9.4</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AA9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF9">
         <v>27</v>
       </c>
       <c r="AG9">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI9">
         <v>90</v>
@@ -2928,7 +2928,7 @@
         <v>90</v>
       </c>
       <c r="AK9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL9">
         <v>110</v>
@@ -2940,61 +2940,61 @@
         <v>100</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AQ9">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AR9">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS9">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="AT9">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AU9">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="AV9">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="AW9">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX9">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AY9">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="AZ9">
-        <v>3.85</v>
+        <v>5.9</v>
       </c>
       <c r="BA9">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BB9">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BC9">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BD9">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE9">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF9">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG9">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3077,46 +3077,46 @@
         <v>153</v>
       </c>
       <c r="F10">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="G10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="R10">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="S10">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3125,10 +3125,10 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W10">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3322,16 +3322,16 @@
         <v>2.54</v>
       </c>
       <c r="G11">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H11">
         <v>2.56</v>
       </c>
       <c r="I11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
         <v>4.5</v>
@@ -3343,25 +3343,25 @@
         <v>1.02</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O11">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R11">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S11">
         <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U11">
         <v>2.8</v>
@@ -3394,7 +3394,7 @@
         <v>15</v>
       </c>
       <c r="AE11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF11">
         <v>24</v>
@@ -3421,10 +3421,10 @@
         <v>55</v>
       </c>
       <c r="AN11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO11">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP11">
         <v>21</v>
@@ -3436,7 +3436,7 @@
         <v>17.5</v>
       </c>
       <c r="AS11">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT11">
         <v>13.5</v>
@@ -3472,7 +3472,7 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF11">
         <v>9.800000000000001</v>
@@ -3669,52 +3669,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3830,13 +3830,13 @@
         <v>1.09</v>
       </c>
       <c r="O13">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P13">
         <v>1.09</v>
       </c>
       <c r="Q13">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="R13">
         <v>1.08</v>
@@ -3911,52 +3911,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -4048,13 +4048,13 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H14">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J14">
         <v>3.9</v>
@@ -4078,7 +4078,7 @@
         <v>2.16</v>
       </c>
       <c r="Q14">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
         <v>1.45</v>
@@ -4090,13 +4090,13 @@
         <v>1.73</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V14">
         <v>2</v>
       </c>
       <c r="W14">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X14">
         <v>18</v>
@@ -4105,13 +4105,13 @@
         <v>11</v>
       </c>
       <c r="Z14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA14">
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC14">
         <v>8.6</v>
@@ -4120,13 +4120,13 @@
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF14">
         <v>32</v>
       </c>
       <c r="AG14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH14">
         <v>17.5</v>
@@ -4135,10 +4135,10 @@
         <v>32</v>
       </c>
       <c r="AJ14">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL14">
         <v>50</v>
@@ -4147,7 +4147,7 @@
         <v>85</v>
       </c>
       <c r="AN14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AO14">
         <v>12</v>
@@ -4156,7 +4156,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR14">
         <v>12</v>
@@ -4195,7 +4195,7 @@
         <v>40</v>
       </c>
       <c r="BD14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE14">
         <v>36</v>
@@ -4204,7 +4204,7 @@
         <v>34</v>
       </c>
       <c r="BG14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH14">
         <v>50</v>
@@ -4237,7 +4237,7 @@
         <v>4.2</v>
       </c>
       <c r="BR14">
-        <v>990</v>
+        <v>890</v>
       </c>
       <c r="BS14">
         <v>4.3</v>
@@ -4296,22 +4296,22 @@
         <v>6.8</v>
       </c>
       <c r="I15">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N15">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O15">
         <v>1.54</v>
@@ -4335,7 +4335,7 @@
         <v>1.62</v>
       </c>
       <c r="V15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W15">
         <v>2.34</v>
@@ -4347,22 +4347,22 @@
         <v>20</v>
       </c>
       <c r="Z15">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA15">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="AB15">
         <v>5.8</v>
       </c>
       <c r="AC15">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>40</v>
       </c>
       <c r="AE15">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AF15">
         <v>8.800000000000001</v>
@@ -4374,22 +4374,22 @@
         <v>40</v>
       </c>
       <c r="AI15">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AJ15">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AK15">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL15">
         <v>85</v>
       </c>
       <c r="AM15">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="AN15">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AO15">
         <v>460</v>
@@ -4401,10 +4401,10 @@
         <v>14</v>
       </c>
       <c r="AR15">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS15">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT15">
         <v>4.9</v>
@@ -4413,10 +4413,10 @@
         <v>7.4</v>
       </c>
       <c r="AV15">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AX15">
         <v>7.2</v>
@@ -4425,10 +4425,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA15">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB15">
         <v>15</v>
@@ -4437,16 +4437,16 @@
         <v>18</v>
       </c>
       <c r="BD15">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE15">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF15">
         <v>15.5</v>
       </c>
       <c r="BG15">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4458,7 +4458,7 @@
         <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4482,13 +4482,13 @@
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BT15">
         <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BV15">
         <v>1000</v>
@@ -4500,7 +4500,7 @@
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
@@ -4780,7 +4780,7 @@
         <v>1.1</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J17">
         <v>1.1</v>
@@ -4879,52 +4879,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -5082,7 +5082,7 @@
         <v>7.4</v>
       </c>
       <c r="AC18">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD18">
         <v>55</v>
@@ -5109,7 +5109,7 @@
         <v>18.5</v>
       </c>
       <c r="AL18">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM18">
         <v>340</v>
@@ -5124,13 +5124,13 @@
         <v>12</v>
       </c>
       <c r="AQ18">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AR18">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT18">
         <v>5.7</v>
@@ -5139,10 +5139,10 @@
         <v>10</v>
       </c>
       <c r="AV18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX18">
         <v>6.2</v>
@@ -5151,10 +5151,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ18">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BA18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB18">
         <v>9.6</v>
@@ -5163,16 +5163,16 @@
         <v>15</v>
       </c>
       <c r="BD18">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF18">
         <v>7.2</v>
       </c>
       <c r="BG18">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5258,13 +5258,13 @@
         <v>1.1</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H19">
         <v>1.1</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J19">
         <v>1.1</v>
@@ -5279,7 +5279,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O19">
         <v>1.02</v>
@@ -5297,16 +5297,16 @@
         <v>1.5</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5363,52 +5363,52 @@
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
         <v>1.01</v>
@@ -5497,37 +5497,37 @@
         <v>163</v>
       </c>
       <c r="F20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G20">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H20">
         <v>8.800000000000001</v>
       </c>
       <c r="I20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J20">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M20">
         <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
         <v>1.55</v>
       </c>
       <c r="P20">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q20">
         <v>2.6</v>
@@ -5542,16 +5542,16 @@
         <v>2.64</v>
       </c>
       <c r="U20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V20">
         <v>1.1</v>
       </c>
       <c r="W20">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X20">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y20">
         <v>22</v>
@@ -5593,7 +5593,7 @@
         <v>25</v>
       </c>
       <c r="AL20">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM20">
         <v>480</v>
@@ -5611,10 +5611,10 @@
         <v>17</v>
       </c>
       <c r="AR20">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT20">
         <v>4.6</v>
@@ -5623,10 +5623,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20">
         <v>6.2</v>
@@ -5635,10 +5635,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA20">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB20">
         <v>11</v>
@@ -5647,16 +5647,16 @@
         <v>20</v>
       </c>
       <c r="BD20">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE20">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF20">
         <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5739,10 +5739,10 @@
         <v>164</v>
       </c>
       <c r="F21">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
         <v>3.8</v>
@@ -5751,10 +5751,10 @@
         <v>3.9</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L21">
         <v>1.02</v>
@@ -5763,25 +5763,25 @@
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O21">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q21">
         <v>2.12</v>
       </c>
       <c r="R21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T21">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U21">
         <v>1.98</v>
@@ -5790,13 +5790,13 @@
         <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X21">
+        <v>13</v>
+      </c>
+      <c r="Y21">
         <v>14</v>
-      </c>
-      <c r="Y21">
-        <v>14.5</v>
       </c>
       <c r="Z21">
         <v>32</v>
@@ -5805,10 +5805,10 @@
         <v>90</v>
       </c>
       <c r="AB21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD21">
         <v>18</v>
@@ -5835,10 +5835,10 @@
         <v>29</v>
       </c>
       <c r="AL21">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM21">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="AN21">
         <v>24</v>
@@ -5850,37 +5850,37 @@
         <v>10.5</v>
       </c>
       <c r="AQ21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR21">
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU21">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV21">
         <v>12</v>
       </c>
       <c r="AW21">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX21">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY21">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21">
         <v>17</v>
       </c>
       <c r="BA21">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BB21">
         <v>21</v>
@@ -5889,16 +5889,16 @@
         <v>19</v>
       </c>
       <c r="BD21">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE21">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF21">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BG21">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH21">
         <v>1000</v>
@@ -5981,22 +5981,22 @@
         <v>165</v>
       </c>
       <c r="F22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G22">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H22">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I22">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J22">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L22">
         <v>1.5</v>
@@ -6005,31 +6005,31 @@
         <v>1.1</v>
       </c>
       <c r="N22">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O22">
         <v>1.45</v>
       </c>
       <c r="P22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q22">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S22">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T22">
         <v>1.95</v>
       </c>
       <c r="U22">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V22">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W22">
         <v>1.33</v>
@@ -6038,52 +6038,52 @@
         <v>11</v>
       </c>
       <c r="Y22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA22">
         <v>34</v>
       </c>
       <c r="AB22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC22">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF22">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG22">
         <v>17</v>
       </c>
       <c r="AH22">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ22">
         <v>100</v>
       </c>
       <c r="AK22">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL22">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM22">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN22">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO22">
         <v>27</v>
@@ -6092,55 +6092,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ22">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AR22">
+        <v>11.5</v>
+      </c>
+      <c r="AS22">
+        <v>7.8</v>
+      </c>
+      <c r="AT22">
         <v>10</v>
       </c>
-      <c r="AS22">
-        <v>21</v>
-      </c>
-      <c r="AT22">
-        <v>8.6</v>
-      </c>
       <c r="AU22">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
         <v>10</v>
       </c>
       <c r="AW22">
+        <v>7.4</v>
+      </c>
+      <c r="AX22">
+        <v>7.2</v>
+      </c>
+      <c r="AY22">
+        <v>14</v>
+      </c>
+      <c r="AZ22">
+        <v>17.5</v>
+      </c>
+      <c r="BA22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE22">
+        <v>9</v>
+      </c>
+      <c r="BF22">
+        <v>9</v>
+      </c>
+      <c r="BG22">
         <v>21</v>
-      </c>
-      <c r="AX22">
-        <v>21</v>
-      </c>
-      <c r="AY22">
-        <v>13.5</v>
-      </c>
-      <c r="AZ22">
-        <v>17</v>
-      </c>
-      <c r="BA22">
-        <v>5.8</v>
-      </c>
-      <c r="BB22">
-        <v>6</v>
-      </c>
-      <c r="BC22">
-        <v>5.9</v>
-      </c>
-      <c r="BD22">
-        <v>5.9</v>
-      </c>
-      <c r="BE22">
-        <v>6.2</v>
-      </c>
-      <c r="BF22">
-        <v>5.9</v>
-      </c>
-      <c r="BG22">
-        <v>20</v>
       </c>
       <c r="BH22">
         <v>3.05</v>
@@ -6182,7 +6182,7 @@
         <v>5.1</v>
       </c>
       <c r="BU22">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV22">
         <v>19</v>
@@ -6229,13 +6229,13 @@
         <v>1.91</v>
       </c>
       <c r="H23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J23">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K23">
         <v>4.1</v>
@@ -6250,7 +6250,7 @@
         <v>4.3</v>
       </c>
       <c r="O23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P23">
         <v>2.14</v>
@@ -6271,22 +6271,22 @@
         <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X23">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Y23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z23">
         <v>40</v>
       </c>
       <c r="AA23">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB23">
         <v>10.5</v>
@@ -6301,13 +6301,13 @@
         <v>65</v>
       </c>
       <c r="AF23">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG23">
         <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI23">
         <v>70</v>
@@ -6322,7 +6322,7 @@
         <v>38</v>
       </c>
       <c r="AM23">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="AN23">
         <v>11</v>
@@ -6331,16 +6331,16 @@
         <v>65</v>
       </c>
       <c r="AP23">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ23">
         <v>16</v>
       </c>
       <c r="AR23">
-        <v>9.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AS23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT23">
         <v>9.199999999999999</v>
@@ -6349,13 +6349,13 @@
         <v>8</v>
       </c>
       <c r="AV23">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW23">
         <v>10</v>
       </c>
       <c r="AX23">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY23">
         <v>9.199999999999999</v>
@@ -6373,7 +6373,7 @@
         <v>15</v>
       </c>
       <c r="BD23">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BE23">
         <v>10.5</v>
@@ -6465,22 +6465,22 @@
         <v>167</v>
       </c>
       <c r="F24">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="G24">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="H24">
+        <v>3.6</v>
+      </c>
+      <c r="I24">
+        <v>3.7</v>
+      </c>
+      <c r="J24">
         <v>3.4</v>
       </c>
-      <c r="I24">
-        <v>3.55</v>
-      </c>
-      <c r="J24">
-        <v>3.35</v>
-      </c>
       <c r="K24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L24">
         <v>1.49</v>
@@ -6489,19 +6489,19 @@
         <v>1.09</v>
       </c>
       <c r="N24">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q24">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S24">
         <v>4.2</v>
@@ -6510,121 +6510,121 @@
         <v>1.92</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="X24">
         <v>11.5</v>
       </c>
       <c r="Y24">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE24">
         <v>48</v>
       </c>
       <c r="AF24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH24">
         <v>20</v>
       </c>
       <c r="AI24">
+        <v>65</v>
+      </c>
+      <c r="AJ24">
+        <v>30</v>
+      </c>
+      <c r="AK24">
+        <v>26</v>
+      </c>
+      <c r="AL24">
+        <v>44</v>
+      </c>
+      <c r="AM24">
+        <v>130</v>
+      </c>
+      <c r="AN24">
+        <v>23</v>
+      </c>
+      <c r="AO24">
+        <v>140</v>
+      </c>
+      <c r="AP24">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24">
+        <v>11.5</v>
+      </c>
+      <c r="AR24">
+        <v>21</v>
+      </c>
+      <c r="AS24">
         <v>60</v>
-      </c>
-      <c r="AJ24">
-        <v>34</v>
-      </c>
-      <c r="AK24">
-        <v>29</v>
-      </c>
-      <c r="AL24">
-        <v>50</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>25</v>
-      </c>
-      <c r="AO24">
-        <v>55</v>
-      </c>
-      <c r="AP24">
-        <v>10</v>
-      </c>
-      <c r="AQ24">
-        <v>10</v>
-      </c>
-      <c r="AR24">
-        <v>20</v>
-      </c>
-      <c r="AS24">
-        <v>44</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
       </c>
       <c r="AU24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW24">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX24">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY24">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA24">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB24">
         <v>26</v>
       </c>
       <c r="BC24">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE24">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="BF24">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG24">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BH24">
         <v>3.2</v>
@@ -6707,10 +6707,10 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G25">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H25">
         <v>3.05</v>
@@ -6737,7 +6737,7 @@
         <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <v>1.96</v>
@@ -6755,19 +6755,19 @@
         <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X25">
         <v>14.5</v>
       </c>
       <c r="Y25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA25">
         <v>55</v>
@@ -6776,7 +6776,7 @@
         <v>11</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD25">
         <v>14</v>
@@ -6806,7 +6806,7 @@
         <v>40</v>
       </c>
       <c r="AM25">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AN25">
         <v>21</v>
@@ -6824,7 +6824,7 @@
         <v>19</v>
       </c>
       <c r="AS25">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AT25">
         <v>9.800000000000001</v>
@@ -6836,37 +6836,37 @@
         <v>12</v>
       </c>
       <c r="AW25">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AX25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY25">
         <v>10.5</v>
       </c>
       <c r="AZ25">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA25">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BB25">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BC25">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD25">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BE25">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BF25">
         <v>17.5</v>
       </c>
       <c r="BG25">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BH25">
         <v>3.4</v>
@@ -6878,7 +6878,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK25">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL25">
         <v>1000</v>
@@ -6890,7 +6890,7 @@
         <v>5.4</v>
       </c>
       <c r="BO25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP25">
         <v>19.5</v>
@@ -6964,7 +6964,7 @@
         <v>3.25</v>
       </c>
       <c r="K26">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L26">
         <v>1.49</v>
@@ -6973,10 +6973,10 @@
         <v>1.1</v>
       </c>
       <c r="N26">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O26">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P26">
         <v>1.69</v>
@@ -6997,7 +6997,7 @@
         <v>1.91</v>
       </c>
       <c r="V26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
         <v>1.79</v>
@@ -7012,7 +7012,7 @@
         <v>32</v>
       </c>
       <c r="AA26">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB26">
         <v>8.199999999999999</v>
@@ -7024,7 +7024,7 @@
         <v>17.5</v>
       </c>
       <c r="AE26">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF26">
         <v>13</v>
@@ -7036,7 +7036,7 @@
         <v>26</v>
       </c>
       <c r="AI26">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AJ26">
         <v>36</v>
@@ -7048,13 +7048,13 @@
         <v>60</v>
       </c>
       <c r="AM26">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN26">
         <v>29</v>
       </c>
       <c r="AO26">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP26">
         <v>9.6</v>
@@ -7063,7 +7063,7 @@
         <v>10.5</v>
       </c>
       <c r="AR26">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS26">
         <v>7.8</v>
@@ -7078,7 +7078,7 @@
         <v>14.5</v>
       </c>
       <c r="AW26">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="AX26">
         <v>11</v>
@@ -7093,10 +7093,10 @@
         <v>7.6</v>
       </c>
       <c r="BB26">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BC26">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BD26">
         <v>7.2</v>
@@ -7191,10 +7191,10 @@
         <v>170</v>
       </c>
       <c r="F27">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G27">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H27">
         <v>4.5</v>
@@ -7203,7 +7203,7 @@
         <v>4.9</v>
       </c>
       <c r="J27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K27">
         <v>3.65</v>
@@ -7215,25 +7215,25 @@
         <v>1.09</v>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
         <v>1.4</v>
       </c>
       <c r="P27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
       </c>
       <c r="R27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
         <v>4.1</v>
       </c>
       <c r="T27">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U27">
         <v>1.95</v>
@@ -7242,7 +7242,7 @@
         <v>1.26</v>
       </c>
       <c r="W27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X27">
         <v>12</v>
@@ -7251,10 +7251,10 @@
         <v>15</v>
       </c>
       <c r="Z27">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AA27">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB27">
         <v>8.199999999999999</v>
@@ -7266,7 +7266,7 @@
         <v>20</v>
       </c>
       <c r="AE27">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AF27">
         <v>11.5</v>
@@ -7278,25 +7278,25 @@
         <v>22</v>
       </c>
       <c r="AI27">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AJ27">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AK27">
         <v>24</v>
       </c>
       <c r="AL27">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AM27">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN27">
-        <v>17.5</v>
+        <v>38</v>
       </c>
       <c r="AO27">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP27">
         <v>10</v>
@@ -7308,7 +7308,7 @@
         <v>27</v>
       </c>
       <c r="AS27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT27">
         <v>7.2</v>
@@ -7320,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="AW27">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AX27">
         <v>10</v>
@@ -7329,10 +7329,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ27">
+        <v>11.5</v>
+      </c>
+      <c r="BA27">
         <v>10</v>
-      </c>
-      <c r="BA27">
-        <v>10.5</v>
       </c>
       <c r="BB27">
         <v>20</v>
@@ -7341,7 +7341,7 @@
         <v>20</v>
       </c>
       <c r="BD27">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE27">
         <v>11</v>
@@ -7433,10 +7433,10 @@
         <v>171</v>
       </c>
       <c r="F28">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="G28">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H28">
         <v>5.2</v>
@@ -7448,7 +7448,7 @@
         <v>3.95</v>
       </c>
       <c r="K28">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L28">
         <v>1.4</v>
@@ -7457,22 +7457,22 @@
         <v>1.06</v>
       </c>
       <c r="N28">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P28">
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R28">
         <v>1.39</v>
       </c>
       <c r="S28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T28">
         <v>1.89</v>
@@ -7490,7 +7490,7 @@
         <v>16</v>
       </c>
       <c r="Y28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z28">
         <v>75</v>
@@ -7505,7 +7505,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AE28">
         <v>90</v>
@@ -7523,13 +7523,13 @@
         <v>90</v>
       </c>
       <c r="AJ28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL28">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM28">
         <v>140</v>
@@ -7547,10 +7547,10 @@
         <v>14.5</v>
       </c>
       <c r="AR28">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS28">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT28">
         <v>7.8</v>
@@ -7559,22 +7559,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28">
+        <v>18.5</v>
+      </c>
+      <c r="AW28">
+        <v>12</v>
+      </c>
+      <c r="AX28">
+        <v>9.6</v>
+      </c>
+      <c r="AY28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28">
         <v>17.5</v>
       </c>
-      <c r="AW28">
-        <v>11.5</v>
-      </c>
-      <c r="AX28">
-        <v>9.4</v>
-      </c>
-      <c r="AY28">
-        <v>9</v>
-      </c>
-      <c r="AZ28">
-        <v>17</v>
-      </c>
       <c r="BA28">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB28">
         <v>14.5</v>
@@ -7583,10 +7583,10 @@
         <v>15</v>
       </c>
       <c r="BD28">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE28">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
@@ -7610,7 +7610,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>1.06</v>
+        <v>2.32</v>
       </c>
       <c r="BN28">
         <v>1000</v>
@@ -7628,7 +7628,7 @@
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>1.06</v>
+        <v>2.32</v>
       </c>
       <c r="BT28">
         <v>1000</v>
@@ -7646,13 +7646,13 @@
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>1.06</v>
+        <v>2.32</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>1.06</v>
+        <v>2.32</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7678,7 +7678,7 @@
         <v>1.23</v>
       </c>
       <c r="G29">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H29">
         <v>10.5</v>
@@ -7917,22 +7917,22 @@
         <v>173</v>
       </c>
       <c r="F30">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="G30">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H30">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="I30">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="J30">
         <v>3.6</v>
       </c>
       <c r="K30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L30">
         <v>1.33</v>
@@ -7950,133 +7950,133 @@
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R30">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S30">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T30">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U30">
         <v>2.36</v>
       </c>
       <c r="V30">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W30">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X30">
+        <v>17.5</v>
+      </c>
+      <c r="Y30">
+        <v>12.5</v>
+      </c>
+      <c r="Z30">
         <v>18</v>
       </c>
-      <c r="Y30">
-        <v>13</v>
-      </c>
-      <c r="Z30">
-        <v>19.5</v>
-      </c>
       <c r="AA30">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AB30">
+        <v>14</v>
+      </c>
+      <c r="AC30">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30">
+        <v>12</v>
+      </c>
+      <c r="AE30">
+        <v>26</v>
+      </c>
+      <c r="AF30">
+        <v>21</v>
+      </c>
+      <c r="AG30">
         <v>13.5</v>
-      </c>
-      <c r="AC30">
-        <v>8.4</v>
-      </c>
-      <c r="AD30">
-        <v>12.5</v>
-      </c>
-      <c r="AE30">
-        <v>29</v>
-      </c>
-      <c r="AF30">
-        <v>20</v>
-      </c>
-      <c r="AG30">
-        <v>12.5</v>
       </c>
       <c r="AH30">
         <v>16</v>
       </c>
       <c r="AI30">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ30">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK30">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AM30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN30">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO30">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AP30">
+        <v>15</v>
+      </c>
+      <c r="AQ30">
+        <v>11</v>
+      </c>
+      <c r="AR30">
         <v>15.5</v>
       </c>
-      <c r="AQ30">
-        <v>11.5</v>
-      </c>
-      <c r="AR30">
-        <v>16</v>
-      </c>
       <c r="AS30">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AT30">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU30">
         <v>7.4</v>
       </c>
       <c r="AV30">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW30">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AX30">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ30">
         <v>14</v>
       </c>
       <c r="BA30">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB30">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="BC30">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="BD30">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE30">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BF30">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG30">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8201,7 +8201,7 @@
         <v>5.2</v>
       </c>
       <c r="T31">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U31">
         <v>1.8</v>
@@ -8431,7 +8431,7 @@
         <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q32">
         <v>2.06</v>
@@ -8443,7 +8443,7 @@
         <v>3.7</v>
       </c>
       <c r="T32">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U32">
         <v>2.06</v>
@@ -8452,7 +8452,7 @@
         <v>1.29</v>
       </c>
       <c r="W32">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X32">
         <v>13.5</v>
@@ -8551,7 +8551,7 @@
         <v>20</v>
       </c>
       <c r="BD32">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BE32">
         <v>12</v>
@@ -8643,7 +8643,7 @@
         <v>176</v>
       </c>
       <c r="F33">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G33">
         <v>4.6</v>
@@ -8652,10 +8652,10 @@
         <v>1.96</v>
       </c>
       <c r="I33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J33">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K33">
         <v>3.85</v>
@@ -8673,7 +8673,7 @@
         <v>1.37</v>
       </c>
       <c r="P33">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q33">
         <v>2.06</v>
@@ -8688,10 +8688,10 @@
         <v>1.93</v>
       </c>
       <c r="U33">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V33">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W33">
         <v>1.28</v>
@@ -8748,7 +8748,7 @@
         <v>85</v>
       </c>
       <c r="AO33">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AP33">
         <v>11</v>
@@ -8775,7 +8775,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY33">
         <v>15.5</v>
@@ -8787,19 +8787,19 @@
         <v>16</v>
       </c>
       <c r="BB33">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC33">
         <v>22</v>
       </c>
       <c r="BD33">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE33">
         <v>8</v>
       </c>
       <c r="BF33">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG33">
         <v>13.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -547,7 +547,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-06 19:24:56</t>
+    <t>2026-10-06 21:37:21</t>
   </si>
 </sst>
 </file>
@@ -1141,139 +1141,139 @@
         <v>145</v>
       </c>
       <c r="F2">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G2">
         <v>3.1</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M2">
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="Q2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="R2">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="S2">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="T2">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V2">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z2">
         <v>21</v>
       </c>
       <c r="AA2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB2">
         <v>24</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD2">
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AF2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH2">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AI2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK2">
+        <v>30</v>
+      </c>
+      <c r="AL2">
+        <v>30</v>
+      </c>
+      <c r="AM2">
+        <v>48</v>
+      </c>
+      <c r="AN2">
+        <v>16</v>
+      </c>
+      <c r="AO2">
+        <v>10.5</v>
+      </c>
+      <c r="AP2">
         <v>27</v>
       </c>
-      <c r="AL2">
-        <v>27</v>
-      </c>
-      <c r="AM2">
-        <v>42</v>
-      </c>
-      <c r="AN2">
-        <v>13.5</v>
-      </c>
-      <c r="AO2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP2">
+      <c r="AQ2">
+        <v>17</v>
+      </c>
+      <c r="AR2">
+        <v>19</v>
+      </c>
+      <c r="AS2">
         <v>30</v>
       </c>
-      <c r="AQ2">
-        <v>18.5</v>
-      </c>
-      <c r="AR2">
-        <v>19.5</v>
-      </c>
-      <c r="AS2">
-        <v>29</v>
-      </c>
       <c r="AT2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV2">
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY2">
         <v>13</v>
@@ -1282,85 +1282,85 @@
         <v>12</v>
       </c>
       <c r="BA2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BH2">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BI2">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BJ2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BN2">
         <v>7</v>
       </c>
       <c r="BO2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP2">
-        <v>19.5</v>
+        <v>980</v>
       </c>
       <c r="BQ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BR2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>4.4</v>
       </c>
       <c r="BT2">
         <v>6</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
-        <v>20</v>
+        <v>990</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BZ2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>177</v>
@@ -1383,34 +1383,34 @@
         <v>146</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G3">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="I3">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="J3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="K3">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M3">
         <v>1.07</v>
       </c>
       <c r="N3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P3">
         <v>1.85</v>
@@ -1419,190 +1419,190 @@
         <v>2.14</v>
       </c>
       <c r="R3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T3">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Z3">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA3">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AB3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AC3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF3">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="AG3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH3">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>930</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>390</v>
+        <v>740</v>
       </c>
       <c r="AL3">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>460</v>
+        <v>740</v>
       </c>
       <c r="AN3">
-        <v>830</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AP3">
+        <v>13.5</v>
+      </c>
+      <c r="AQ3">
+        <v>5.5</v>
+      </c>
+      <c r="AR3">
+        <v>5.5</v>
+      </c>
+      <c r="AS3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3">
+        <v>30</v>
+      </c>
+      <c r="AU3">
         <v>13</v>
       </c>
-      <c r="AQ3">
-        <v>5.7</v>
-      </c>
-      <c r="AR3">
-        <v>5.8</v>
-      </c>
-      <c r="AS3">
-        <v>8.4</v>
-      </c>
-      <c r="AT3">
-        <v>27</v>
-      </c>
-      <c r="AU3">
-        <v>12</v>
-      </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3">
         <v>17</v>
       </c>
       <c r="AX3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AY3">
+        <v>65</v>
+      </c>
+      <c r="AZ3">
+        <v>55</v>
+      </c>
+      <c r="BA3">
+        <v>60</v>
+      </c>
+      <c r="BB3">
+        <v>22</v>
+      </c>
+      <c r="BC3">
+        <v>22</v>
+      </c>
+      <c r="BD3">
+        <v>22</v>
+      </c>
+      <c r="BE3">
+        <v>200</v>
+      </c>
+      <c r="BF3">
+        <v>32</v>
+      </c>
+      <c r="BG3">
+        <v>6.4</v>
+      </c>
+      <c r="BH3">
+        <v>3.3</v>
+      </c>
+      <c r="BI3">
+        <v>3.1</v>
+      </c>
+      <c r="BJ3">
+        <v>17.5</v>
+      </c>
+      <c r="BK3">
+        <v>11.5</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>250</v>
+      </c>
+      <c r="BN3">
+        <v>18.5</v>
+      </c>
+      <c r="BO3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>19</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>18.5</v>
+      </c>
+      <c r="BT3">
+        <v>3.25</v>
+      </c>
+      <c r="BU3">
+        <v>3.1</v>
+      </c>
+      <c r="BV3">
+        <v>7.6</v>
+      </c>
+      <c r="BW3">
+        <v>6.8</v>
+      </c>
+      <c r="BX3">
         <v>38</v>
       </c>
-      <c r="AZ3">
-        <v>40</v>
-      </c>
-      <c r="BA3">
-        <v>19.5</v>
-      </c>
-      <c r="BB3">
-        <v>18</v>
-      </c>
-      <c r="BC3">
-        <v>17.5</v>
-      </c>
-      <c r="BD3">
+      <c r="BY3">
         <v>19</v>
       </c>
-      <c r="BE3">
-        <v>17.5</v>
-      </c>
-      <c r="BF3">
-        <v>18</v>
-      </c>
-      <c r="BG3">
-        <v>7</v>
-      </c>
-      <c r="BH3">
-        <v>3.25</v>
-      </c>
-      <c r="BI3">
-        <v>2.94</v>
-      </c>
-      <c r="BJ3">
-        <v>15.5</v>
-      </c>
-      <c r="BK3">
-        <v>8.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>16</v>
-      </c>
-      <c r="BN3">
-        <v>16</v>
-      </c>
-      <c r="BO3">
-        <v>8.6</v>
-      </c>
-      <c r="BP3">
-        <v>180</v>
-      </c>
-      <c r="BQ3">
-        <v>15.5</v>
-      </c>
-      <c r="BR3">
-        <v>160</v>
-      </c>
-      <c r="BS3">
-        <v>15</v>
-      </c>
-      <c r="BT3">
-        <v>3.45</v>
-      </c>
-      <c r="BU3">
-        <v>3.15</v>
-      </c>
-      <c r="BV3">
-        <v>8</v>
-      </c>
-      <c r="BW3">
-        <v>7.2</v>
-      </c>
-      <c r="BX3">
-        <v>36</v>
-      </c>
-      <c r="BY3">
-        <v>11.5</v>
-      </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
         <v>177</v>
@@ -1625,25 +1625,25 @@
         <v>147</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
+        <v>3.75</v>
+      </c>
+      <c r="I4">
+        <v>3.95</v>
+      </c>
+      <c r="J4">
+        <v>3.4</v>
+      </c>
+      <c r="K4">
         <v>3.55</v>
       </c>
-      <c r="I4">
-        <v>3.75</v>
-      </c>
-      <c r="J4">
-        <v>3.3</v>
-      </c>
-      <c r="K4">
-        <v>3.4</v>
-      </c>
       <c r="L4">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1652,19 +1652,19 @@
         <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q4">
         <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T4">
         <v>2.04</v>
@@ -1673,10 +1673,10 @@
         <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1688,163 +1688,163 @@
         <v>27</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
+        <v>30</v>
+      </c>
+      <c r="AK4">
         <v>36</v>
-      </c>
-      <c r="AK4">
-        <v>40</v>
       </c>
       <c r="AL4">
         <v>60</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX4">
         <v>11.5</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA4">
+        <v>55</v>
+      </c>
+      <c r="BB4">
+        <v>26</v>
+      </c>
+      <c r="BC4">
+        <v>25</v>
+      </c>
+      <c r="BD4">
         <v>46</v>
       </c>
-      <c r="BB4">
-        <v>25</v>
-      </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>36</v>
-      </c>
       <c r="BE4">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="BH4">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="BI4">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>3.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BN4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ4">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
         <v>48</v>
       </c>
       <c r="BS4">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BT4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
         <v>42</v>
       </c>
       <c r="BW4">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA4">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="s">
         <v>177</v>
@@ -1870,7 +1870,7 @@
         <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -1882,7 +1882,7 @@
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5">
         <v>1.41</v>
@@ -1918,7 +1918,7 @@
         <v>1.11</v>
       </c>
       <c r="W5">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1975,10 +1975,10 @@
         <v>420</v>
       </c>
       <c r="AP5">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AR5">
         <v>6.2</v>
@@ -1993,7 +1993,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AW5">
         <v>6.4</v>
@@ -2002,16 +2002,16 @@
         <v>6.6</v>
       </c>
       <c r="AY5">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA5">
         <v>6.4</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC5">
         <v>16.5</v>
@@ -2023,7 +2023,7 @@
         <v>6.4</v>
       </c>
       <c r="BF5">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BG5">
         <v>6.6</v>
@@ -2109,28 +2109,28 @@
         <v>149</v>
       </c>
       <c r="F6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6">
         <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>4.6</v>
@@ -2139,22 +2139,22 @@
         <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S6">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T6">
         <v>1.56</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
         <v>1.51</v>
@@ -2166,7 +2166,7 @@
         <v>22</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z6">
         <v>23</v>
@@ -2178,7 +2178,7 @@
         <v>15.5</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>14.5</v>
@@ -2187,10 +2187,10 @@
         <v>32</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6">
         <v>17</v>
@@ -2217,22 +2217,22 @@
         <v>22</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR6">
         <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
@@ -2241,19 +2241,19 @@
         <v>22</v>
       </c>
       <c r="AX6">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA6">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="BB6">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="BC6">
         <v>21</v>
@@ -2262,13 +2262,13 @@
         <v>27</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
         <v>4.4</v>
@@ -2280,16 +2280,16 @@
         <v>10</v>
       </c>
       <c r="BK6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO6">
         <v>4.6</v>
@@ -2298,13 +2298,13 @@
         <v>22</v>
       </c>
       <c r="BQ6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BR6">
         <v>32</v>
       </c>
       <c r="BS6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT6">
         <v>7</v>
@@ -2316,19 +2316,19 @@
         <v>23</v>
       </c>
       <c r="BW6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BX6">
         <v>34</v>
       </c>
       <c r="BY6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ6">
         <v>24</v>
       </c>
       <c r="CA6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="CB6" t="s">
         <v>177</v>
@@ -2354,7 +2354,7 @@
         <v>6.2</v>
       </c>
       <c r="G7">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H7">
         <v>1.55</v>
@@ -2369,7 +2369,7 @@
         <v>4.8</v>
       </c>
       <c r="L7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M7">
         <v>1.05</v>
@@ -2381,28 +2381,28 @@
         <v>1.23</v>
       </c>
       <c r="P7">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
         <v>1.48</v>
       </c>
       <c r="S7">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
         <v>1.81</v>
       </c>
       <c r="U7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
         <v>2.6</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2483,94 +2483,94 @@
         <v>13.5</v>
       </c>
       <c r="AX7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AY7">
         <v>21</v>
       </c>
       <c r="AZ7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA7">
         <v>26</v>
       </c>
       <c r="BB7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC7">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="BD7">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>65</v>
       </c>
       <c r="BF7">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BG7">
         <v>6.2</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB7" t="s">
         <v>177</v>
@@ -2611,19 +2611,19 @@
         <v>3.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
         <v>1.35</v>
       </c>
       <c r="P8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q8">
         <v>2</v>
@@ -2650,37 +2650,37 @@
         <v>15</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA8">
         <v>32</v>
       </c>
       <c r="AB8">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC8">
         <v>8.6</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>34</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH8">
         <v>19.5</v>
       </c>
       <c r="AI8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ8">
         <v>90</v>
@@ -2692,19 +2692,19 @@
         <v>65</v>
       </c>
       <c r="AM8">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN8">
         <v>60</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AP8">
         <v>11</v>
       </c>
       <c r="AQ8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR8">
         <v>11.5</v>
@@ -2719,13 +2719,13 @@
         <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8">
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="AY8">
         <v>13.5</v>
@@ -2737,82 +2737,82 @@
         <v>32</v>
       </c>
       <c r="BB8">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BC8">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BD8">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BG8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB8" t="s">
         <v>177</v>
@@ -2835,58 +2835,58 @@
         <v>152</v>
       </c>
       <c r="F9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="H9">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I9">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J9">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L9">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="M9">
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
         <v>1.58</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
         <v>5.7</v>
       </c>
       <c r="T9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X9">
         <v>9.4</v>
@@ -2913,148 +2913,148 @@
         <v>44</v>
       </c>
       <c r="AF9">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH9">
         <v>25</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK9">
         <v>60</v>
       </c>
       <c r="AL9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO9">
         <v>55</v>
       </c>
       <c r="AP9">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR9">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS9">
+        <v>7.6</v>
+      </c>
+      <c r="AT9">
+        <v>7.6</v>
+      </c>
+      <c r="AU9">
+        <v>6</v>
+      </c>
+      <c r="AV9">
+        <v>5.5</v>
+      </c>
+      <c r="AW9">
+        <v>7.4</v>
+      </c>
+      <c r="AX9">
+        <v>6.4</v>
+      </c>
+      <c r="AY9">
+        <v>5.7</v>
+      </c>
+      <c r="AZ9">
         <v>6.6</v>
       </c>
-      <c r="AT9">
-        <v>4.2</v>
-      </c>
-      <c r="AU9">
-        <v>3.75</v>
-      </c>
-      <c r="AV9">
-        <v>4.9</v>
-      </c>
-      <c r="AW9">
+      <c r="BA9">
+        <v>8</v>
+      </c>
+      <c r="BB9">
+        <v>8</v>
+      </c>
+      <c r="BC9">
+        <v>7.8</v>
+      </c>
+      <c r="BD9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE9">
+        <v>8.6</v>
+      </c>
+      <c r="BF9">
+        <v>8</v>
+      </c>
+      <c r="BG9">
+        <v>7.6</v>
+      </c>
+      <c r="BH9">
+        <v>2.68</v>
+      </c>
+      <c r="BI9">
+        <v>2.36</v>
+      </c>
+      <c r="BJ9">
+        <v>12</v>
+      </c>
+      <c r="BK9">
+        <v>5.9</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>11</v>
+      </c>
+      <c r="BN9">
         <v>6.4</v>
       </c>
-      <c r="AX9">
-        <v>6</v>
-      </c>
-      <c r="AY9">
-        <v>5.2</v>
-      </c>
-      <c r="AZ9">
-        <v>5.9</v>
-      </c>
-      <c r="BA9">
-        <v>7</v>
-      </c>
-      <c r="BB9">
-        <v>7</v>
-      </c>
-      <c r="BC9">
-        <v>6.8</v>
-      </c>
-      <c r="BD9">
-        <v>7.2</v>
-      </c>
-      <c r="BE9">
-        <v>7.4</v>
-      </c>
-      <c r="BF9">
-        <v>7</v>
-      </c>
-      <c r="BG9">
-        <v>6.6</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>1.04</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>1.04</v>
-      </c>
-      <c r="BN9">
-        <v>1000</v>
-      </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>177</v>
@@ -3077,226 +3077,226 @@
         <v>153</v>
       </c>
       <c r="F10">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>3.3</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q10">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W10">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="CB10" t="s">
         <v>177</v>
@@ -3322,7 +3322,7 @@
         <v>2.54</v>
       </c>
       <c r="G11">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H11">
         <v>2.56</v>
@@ -3355,7 +3355,7 @@
         <v>1.5</v>
       </c>
       <c r="R11">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="S11">
         <v>2.16</v>
@@ -3367,10 +3367,10 @@
         <v>2.8</v>
       </c>
       <c r="V11">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X11">
         <v>32</v>
@@ -3564,13 +3564,13 @@
         <v>1.1</v>
       </c>
       <c r="G12">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H12">
         <v>1.1</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J12">
         <v>1.1</v>
@@ -3585,7 +3585,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O12">
         <v>1.02</v>
@@ -3603,16 +3603,16 @@
         <v>1.43</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3806,13 +3806,13 @@
         <v>1.1</v>
       </c>
       <c r="G13">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="H13">
         <v>1.1</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J13">
         <v>1.1</v>
@@ -3827,7 +3827,7 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O13">
         <v>1.32</v>
@@ -3842,19 +3842,19 @@
         <v>1.08</v>
       </c>
       <c r="S13">
-        <v>1.39</v>
+        <v>2.58</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4045,40 +4045,40 @@
         <v>157</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H14">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="I14">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J14">
         <v>3.9</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <v>1.33</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O14">
         <v>1.27</v>
       </c>
       <c r="P14">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q14">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="R14">
         <v>1.45</v>
@@ -4087,13 +4087,13 @@
         <v>3</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U14">
         <v>2.3</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W14">
         <v>1.3</v>
@@ -4111,16 +4111,16 @@
         <v>23</v>
       </c>
       <c r="AB14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14">
         <v>10.5</v>
       </c>
       <c r="AE14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF14">
         <v>32</v>
@@ -4141,13 +4141,13 @@
         <v>48</v>
       </c>
       <c r="AL14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO14">
         <v>12</v>
@@ -4156,10 +4156,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS14">
         <v>19.5</v>
@@ -4171,7 +4171,7 @@
         <v>8</v>
       </c>
       <c r="AV14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
         <v>17</v>
@@ -4237,7 +4237,7 @@
         <v>4.2</v>
       </c>
       <c r="BR14">
-        <v>890</v>
+        <v>800</v>
       </c>
       <c r="BS14">
         <v>4.3</v>
@@ -4290,7 +4290,7 @@
         <v>1.64</v>
       </c>
       <c r="G15">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="H15">
         <v>6.8</v>
@@ -4338,7 +4338,7 @@
         <v>1.14</v>
       </c>
       <c r="W15">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X15">
         <v>10.5</v>
@@ -4392,7 +4392,7 @@
         <v>55</v>
       </c>
       <c r="AO15">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AP15">
         <v>7.6</v>
@@ -4401,7 +4401,7 @@
         <v>14</v>
       </c>
       <c r="AR15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS15">
         <v>6.8</v>
@@ -4425,7 +4425,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ15">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA15">
         <v>6.6</v>
@@ -4464,7 +4464,7 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="BN15">
         <v>1000</v>
@@ -4476,25 +4476,25 @@
         <v>1000</v>
       </c>
       <c r="BQ15">
+        <v>1.95</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
         <v>1.04</v>
       </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
         <v>1.95</v>
-      </c>
-      <c r="BT15">
-        <v>1000</v>
-      </c>
-      <c r="BU15">
-        <v>1.95</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
@@ -4774,13 +4774,13 @@
         <v>1.1</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H17">
         <v>1.1</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J17">
         <v>1.1</v>
@@ -4795,7 +4795,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
         <v>1.02</v>
@@ -4813,16 +4813,16 @@
         <v>1.46</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5022,7 +5022,7 @@
         <v>11</v>
       </c>
       <c r="I18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J18">
         <v>4.6</v>
@@ -5303,10 +5303,10 @@
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5742,7 +5742,7 @@
         <v>2.18</v>
       </c>
       <c r="G21">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H21">
         <v>3.8</v>
@@ -5778,7 +5778,7 @@
         <v>1.29</v>
       </c>
       <c r="S21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T21">
         <v>1.89</v>
@@ -5790,10 +5790,10 @@
         <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X21">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y21">
         <v>14</v>
@@ -5817,10 +5817,10 @@
         <v>60</v>
       </c>
       <c r="AF21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG21">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH21">
         <v>23</v>
@@ -5856,7 +5856,7 @@
         <v>20</v>
       </c>
       <c r="AS21">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT21">
         <v>7.6</v>
@@ -5865,7 +5865,7 @@
         <v>7</v>
       </c>
       <c r="AV21">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW21">
         <v>5.6</v>
@@ -5880,7 +5880,7 @@
         <v>17</v>
       </c>
       <c r="BA21">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB21">
         <v>21</v>
@@ -5889,10 +5889,10 @@
         <v>19</v>
       </c>
       <c r="BD21">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE21">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF21">
         <v>18.5</v>
@@ -5984,7 +5984,7 @@
         <v>3.6</v>
       </c>
       <c r="G22">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>2.24</v>
@@ -6014,7 +6014,7 @@
         <v>1.67</v>
       </c>
       <c r="Q22">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R22">
         <v>1.25</v>
@@ -6062,7 +6062,7 @@
         <v>27</v>
       </c>
       <c r="AG22">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH22">
         <v>22</v>
@@ -6110,10 +6110,10 @@
         <v>10</v>
       </c>
       <c r="AW22">
+        <v>7.6</v>
+      </c>
+      <c r="AX22">
         <v>7.4</v>
-      </c>
-      <c r="AX22">
-        <v>7.2</v>
       </c>
       <c r="AY22">
         <v>14</v>
@@ -6125,19 +6125,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB22">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC22">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD22">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG22">
         <v>21</v>
@@ -6226,16 +6226,16 @@
         <v>1.86</v>
       </c>
       <c r="G23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H23">
         <v>4.5</v>
       </c>
       <c r="I23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K23">
         <v>4.1</v>
@@ -6271,19 +6271,19 @@
         <v>2.22</v>
       </c>
       <c r="V23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X23">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y23">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Z23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA23">
         <v>500</v>
@@ -6295,7 +6295,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE23">
         <v>65</v>
@@ -6307,7 +6307,7 @@
         <v>10.5</v>
       </c>
       <c r="AH23">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI23">
         <v>70</v>
@@ -6340,10 +6340,10 @@
         <v>16</v>
       </c>
       <c r="AS23">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU23">
         <v>8</v>
@@ -6352,7 +6352,7 @@
         <v>16</v>
       </c>
       <c r="AW23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX23">
         <v>10.5</v>
@@ -6364,7 +6364,7 @@
         <v>15</v>
       </c>
       <c r="BA23">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB23">
         <v>16.5</v>
@@ -6376,7 +6376,7 @@
         <v>16</v>
       </c>
       <c r="BE23">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BF23">
         <v>9.800000000000001</v>
@@ -6394,13 +6394,13 @@
         <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN23">
         <v>4.6</v>
@@ -6412,10 +6412,10 @@
         <v>15</v>
       </c>
       <c r="BQ23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS23">
         <v>6</v>
@@ -6480,7 +6480,7 @@
         <v>3.4</v>
       </c>
       <c r="K24">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L24">
         <v>1.49</v>
@@ -6495,10 +6495,10 @@
         <v>1.4</v>
       </c>
       <c r="P24">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q24">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R24">
         <v>1.3</v>
@@ -6507,7 +6507,7 @@
         <v>4.2</v>
       </c>
       <c r="T24">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U24">
         <v>2.02</v>
@@ -6531,7 +6531,7 @@
         <v>75</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24">
         <v>7.6</v>
@@ -6564,7 +6564,7 @@
         <v>44</v>
       </c>
       <c r="AM24">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN24">
         <v>23</v>
@@ -6615,7 +6615,7 @@
         <v>23</v>
       </c>
       <c r="BD24">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE24">
         <v>42</v>
@@ -6707,16 +6707,16 @@
         <v>168</v>
       </c>
       <c r="F25">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G25">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="H25">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I25">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J25">
         <v>3.45</v>
@@ -6731,7 +6731,7 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O25">
         <v>1.32</v>
@@ -6743,37 +6743,37 @@
         <v>1.96</v>
       </c>
       <c r="R25">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S25">
         <v>3.4</v>
       </c>
       <c r="T25">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="X25">
         <v>14.5</v>
       </c>
       <c r="Y25">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA25">
         <v>55</v>
       </c>
       <c r="AB25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC25">
         <v>7.8</v>
@@ -6785,82 +6785,82 @@
         <v>38</v>
       </c>
       <c r="AF25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH25">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI25">
         <v>46</v>
       </c>
       <c r="AJ25">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK25">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL25">
         <v>40</v>
       </c>
       <c r="AM25">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AN25">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO25">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP25">
         <v>13</v>
       </c>
       <c r="AQ25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR25">
         <v>19</v>
       </c>
       <c r="AS25">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT25">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU25">
         <v>7.2</v>
       </c>
       <c r="AV25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW25">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AX25">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ25">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA25">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BB25">
+        <v>22</v>
+      </c>
+      <c r="BC25">
         <v>23</v>
       </c>
-      <c r="BC25">
-        <v>21</v>
-      </c>
       <c r="BD25">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE25">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF25">
         <v>17.5</v>
@@ -6881,25 +6881,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM25">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN25">
         <v>5.4</v>
       </c>
       <c r="BO25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP25">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ25">
         <v>8.6</v>
       </c>
       <c r="BR25">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS25">
         <v>10.5</v>
@@ -6908,25 +6908,25 @@
         <v>6.4</v>
       </c>
       <c r="BU25">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV25">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW25">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX25">
         <v>38</v>
       </c>
       <c r="BY25">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA25">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB25" t="s">
         <v>177</v>
@@ -6949,7 +6949,7 @@
         <v>169</v>
       </c>
       <c r="F26">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G26">
         <v>2.26</v>
@@ -6964,7 +6964,7 @@
         <v>3.25</v>
       </c>
       <c r="K26">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L26">
         <v>1.49</v>
@@ -6973,7 +6973,7 @@
         <v>1.1</v>
       </c>
       <c r="N26">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="O26">
         <v>1.44</v>
@@ -7033,7 +7033,7 @@
         <v>11.5</v>
       </c>
       <c r="AH26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI26">
         <v>200</v>
@@ -7078,7 +7078,7 @@
         <v>14.5</v>
       </c>
       <c r="AW26">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AX26">
         <v>11</v>
@@ -7120,16 +7120,16 @@
         <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BN26">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO26">
         <v>4.3</v>
@@ -7138,37 +7138,37 @@
         <v>21</v>
       </c>
       <c r="BQ26">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BR26">
         <v>44</v>
       </c>
       <c r="BS26">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BT26">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BU26">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV26">
         <v>44</v>
       </c>
       <c r="BW26">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BX26">
         <v>65</v>
       </c>
       <c r="BY26">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BZ26">
         <v>44</v>
       </c>
       <c r="CA26">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="CB26" t="s">
         <v>177</v>
@@ -7191,22 +7191,22 @@
         <v>170</v>
       </c>
       <c r="F27">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H27">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I27">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J27">
         <v>3.45</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>1.47</v>
@@ -7218,16 +7218,16 @@
         <v>3.3</v>
       </c>
       <c r="O27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P27">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S27">
         <v>4.1</v>
@@ -7236,55 +7236,55 @@
         <v>1.98</v>
       </c>
       <c r="U27">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="X27">
         <v>12</v>
       </c>
       <c r="Y27">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z27">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AA27">
         <v>900</v>
       </c>
       <c r="AB27">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC27">
         <v>8</v>
       </c>
       <c r="AD27">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE27">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AF27">
+        <v>18.5</v>
+      </c>
+      <c r="AG27">
         <v>11.5</v>
-      </c>
-      <c r="AG27">
-        <v>10.5</v>
       </c>
       <c r="AH27">
         <v>22</v>
       </c>
       <c r="AI27">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AJ27">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AK27">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL27">
         <v>100</v>
@@ -7293,70 +7293,70 @@
         <v>580</v>
       </c>
       <c r="AN27">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO27">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AP27">
         <v>10</v>
       </c>
       <c r="AQ27">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR27">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AS27">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="AT27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU27">
         <v>7</v>
       </c>
       <c r="AV27">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW27">
+        <v>44</v>
+      </c>
+      <c r="AX27">
+        <v>10.5</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>18.5</v>
+      </c>
+      <c r="BA27">
         <v>28</v>
       </c>
-      <c r="AX27">
+      <c r="BB27">
+        <v>21</v>
+      </c>
+      <c r="BC27">
+        <v>11.5</v>
+      </c>
+      <c r="BD27">
+        <v>36</v>
+      </c>
+      <c r="BE27">
+        <v>10.5</v>
+      </c>
+      <c r="BF27">
+        <v>17</v>
+      </c>
+      <c r="BG27">
         <v>10</v>
       </c>
-      <c r="AY27">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27">
-        <v>11.5</v>
-      </c>
-      <c r="BA27">
-        <v>10</v>
-      </c>
-      <c r="BB27">
-        <v>20</v>
-      </c>
-      <c r="BC27">
-        <v>20</v>
-      </c>
-      <c r="BD27">
-        <v>19.5</v>
-      </c>
-      <c r="BE27">
-        <v>11</v>
-      </c>
-      <c r="BF27">
-        <v>15</v>
-      </c>
-      <c r="BG27">
-        <v>10.5</v>
-      </c>
       <c r="BH27">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BJ27">
         <v>11</v>
@@ -7368,7 +7368,7 @@
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN27">
         <v>4.6</v>
@@ -7377,40 +7377,40 @@
         <v>4.1</v>
       </c>
       <c r="BP27">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ27">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR27">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS27">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT27">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BU27">
         <v>6.8</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX27">
         <v>60</v>
       </c>
       <c r="BY27">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ27">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA27">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB27" t="s">
         <v>177</v>
@@ -7433,16 +7433,16 @@
         <v>171</v>
       </c>
       <c r="F28">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G28">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H28">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I28">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J28">
         <v>3.95</v>
@@ -7460,13 +7460,13 @@
         <v>3.9</v>
       </c>
       <c r="O28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P28">
         <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="R28">
         <v>1.39</v>
@@ -7475,7 +7475,7 @@
         <v>3.25</v>
       </c>
       <c r="T28">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U28">
         <v>2.04</v>
@@ -7487,13 +7487,13 @@
         <v>2.28</v>
       </c>
       <c r="X28">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y28">
         <v>30</v>
       </c>
       <c r="Z28">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA28">
         <v>170</v>
@@ -7505,7 +7505,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD28">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AE28">
         <v>90</v>
@@ -7514,7 +7514,7 @@
         <v>10.5</v>
       </c>
       <c r="AG28">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH28">
         <v>21</v>
@@ -7523,10 +7523,10 @@
         <v>90</v>
       </c>
       <c r="AJ28">
+        <v>18</v>
+      </c>
+      <c r="AK28">
         <v>29</v>
-      </c>
-      <c r="AK28">
-        <v>30</v>
       </c>
       <c r="AL28">
         <v>65</v>
@@ -7544,13 +7544,13 @@
         <v>14</v>
       </c>
       <c r="AQ28">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR28">
+        <v>36</v>
+      </c>
+      <c r="AS28">
         <v>10.5</v>
-      </c>
-      <c r="AS28">
-        <v>13</v>
       </c>
       <c r="AT28">
         <v>7.8</v>
@@ -7559,10 +7559,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX28">
         <v>9.6</v>
@@ -7571,28 +7571,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA28">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB28">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BC28">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD28">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE28">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF28">
         <v>9.4</v>
       </c>
       <c r="BG28">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7610,7 +7610,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BN28">
         <v>1000</v>
@@ -7628,7 +7628,7 @@
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BT28">
         <v>1000</v>
@@ -7646,13 +7646,13 @@
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>2.32</v>
+        <v>1.06</v>
       </c>
       <c r="CB28" t="s">
         <v>177</v>
@@ -7675,16 +7675,16 @@
         <v>172</v>
       </c>
       <c r="F29">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="G29">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H29">
         <v>10.5</v>
       </c>
       <c r="I29">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
         <v>6.4</v>
@@ -7711,22 +7711,22 @@
         <v>1.4</v>
       </c>
       <c r="R29">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="S29">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T29">
         <v>1.87</v>
       </c>
       <c r="U29">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W29">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X29">
         <v>42</v>
@@ -7756,7 +7756,7 @@
         <v>11.5</v>
       </c>
       <c r="AG29">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH29">
         <v>36</v>
@@ -7765,13 +7765,13 @@
         <v>150</v>
       </c>
       <c r="AJ29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK29">
         <v>16</v>
       </c>
       <c r="AL29">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM29">
         <v>150</v>
@@ -7783,16 +7783,16 @@
         <v>220</v>
       </c>
       <c r="AP29">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AR29">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS29">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT29">
         <v>9.800000000000001</v>
@@ -7801,10 +7801,10 @@
         <v>13</v>
       </c>
       <c r="AV29">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AW29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX29">
         <v>7.6</v>
@@ -7813,28 +7813,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA29">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB29">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC29">
         <v>10.5</v>
       </c>
       <c r="BD29">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE29">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF29">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BG29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -7917,16 +7917,16 @@
         <v>173</v>
       </c>
       <c r="F30">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H30">
+        <v>2.5</v>
+      </c>
+      <c r="I30">
         <v>2.54</v>
-      </c>
-      <c r="I30">
-        <v>2.58</v>
       </c>
       <c r="J30">
         <v>3.6</v>
@@ -7941,16 +7941,16 @@
         <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O30">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R30">
         <v>1.44</v>
@@ -7959,16 +7959,16 @@
         <v>3.05</v>
       </c>
       <c r="T30">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U30">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W30">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X30">
         <v>17.5</v>
@@ -7977,7 +7977,7 @@
         <v>12.5</v>
       </c>
       <c r="Z30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA30">
         <v>36</v>
@@ -7989,13 +7989,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE30">
         <v>26</v>
       </c>
       <c r="AF30">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG30">
         <v>13.5</v>
@@ -8004,7 +8004,7 @@
         <v>16</v>
       </c>
       <c r="AI30">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ30">
         <v>55</v>
@@ -8019,13 +8019,13 @@
         <v>95</v>
       </c>
       <c r="AN30">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP30">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ30">
         <v>11</v>
@@ -8037,10 +8037,10 @@
         <v>29</v>
       </c>
       <c r="AT30">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV30">
         <v>10.5</v>
@@ -8073,7 +8073,7 @@
         <v>50</v>
       </c>
       <c r="BF30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG30">
         <v>16</v>
@@ -8082,7 +8082,7 @@
         <v>1000</v>
       </c>
       <c r="BI30">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="BJ30">
         <v>1000</v>
@@ -8162,7 +8162,7 @@
         <v>2.18</v>
       </c>
       <c r="G31">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -8171,7 +8171,7 @@
         <v>4.4</v>
       </c>
       <c r="J31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
         <v>3.3</v>
@@ -8219,7 +8219,7 @@
         <v>11.5</v>
       </c>
       <c r="Z31">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA31">
         <v>130</v>
@@ -8231,7 +8231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE31">
         <v>85</v>
@@ -8243,16 +8243,16 @@
         <v>14</v>
       </c>
       <c r="AH31">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AI31">
         <v>110</v>
       </c>
       <c r="AJ31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK31">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL31">
         <v>70</v>
@@ -8276,7 +8276,7 @@
         <v>20</v>
       </c>
       <c r="AS31">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT31">
         <v>6.6</v>
@@ -8288,7 +8288,7 @@
         <v>15.5</v>
       </c>
       <c r="AW31">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX31">
         <v>11</v>
@@ -8297,28 +8297,28 @@
         <v>10</v>
       </c>
       <c r="AZ31">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA31">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC31">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD31">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE31">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF31">
         <v>21</v>
       </c>
       <c r="BG31">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH31">
         <v>2.78</v>
@@ -8360,7 +8360,7 @@
         <v>7.2</v>
       </c>
       <c r="BU31">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV31">
         <v>1000</v>
@@ -8401,22 +8401,22 @@
         <v>175</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G32">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I32">
         <v>4.5</v>
       </c>
       <c r="J32">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32">
         <v>1.44</v>
@@ -8431,25 +8431,25 @@
         <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q32">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R32">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S32">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T32">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U32">
         <v>2.06</v>
       </c>
       <c r="V32">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W32">
         <v>1.94</v>
@@ -8470,7 +8470,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC32">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32">
         <v>17.5</v>
@@ -8485,37 +8485,37 @@
         <v>11</v>
       </c>
       <c r="AH32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI32">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ32">
         <v>24</v>
       </c>
       <c r="AK32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL32">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AM32">
         <v>130</v>
       </c>
       <c r="AN32">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO32">
         <v>80</v>
       </c>
       <c r="AP32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ32">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR32">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS32">
         <v>12</v>
@@ -8524,13 +8524,13 @@
         <v>8</v>
       </c>
       <c r="AU32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV32">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW32">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX32">
         <v>11</v>
@@ -8539,25 +8539,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ32">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA32">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BB32">
         <v>21</v>
       </c>
       <c r="BC32">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD32">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="BE32">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF32">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG32">
         <v>11.5</v>
@@ -8572,7 +8572,7 @@
         <v>10</v>
       </c>
       <c r="BK32">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8652,10 +8652,10 @@
         <v>1.96</v>
       </c>
       <c r="I33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J33">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K33">
         <v>3.85</v>
@@ -8673,7 +8673,7 @@
         <v>1.37</v>
       </c>
       <c r="P33">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q33">
         <v>2.06</v>
@@ -8682,16 +8682,16 @@
         <v>1.33</v>
       </c>
       <c r="S33">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T33">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U33">
         <v>2</v>
       </c>
       <c r="V33">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W33">
         <v>1.28</v>
@@ -8700,13 +8700,13 @@
         <v>15</v>
       </c>
       <c r="Y33">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Z33">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB33">
         <v>14.5</v>
@@ -8718,13 +8718,13 @@
         <v>11</v>
       </c>
       <c r="AE33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF33">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG33">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH33">
         <v>21</v>
@@ -8748,7 +8748,7 @@
         <v>85</v>
       </c>
       <c r="AO33">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP33">
         <v>11</v>
@@ -8766,7 +8766,7 @@
         <v>12</v>
       </c>
       <c r="AU33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV33">
         <v>9.4</v>
@@ -8775,7 +8775,7 @@
         <v>19.5</v>
       </c>
       <c r="AX33">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY33">
         <v>15.5</v>
@@ -8784,22 +8784,22 @@
         <v>17.5</v>
       </c>
       <c r="BA33">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB33">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BC33">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE33">
         <v>8</v>
       </c>
       <c r="BF33">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG33">
         <v>13.5</v>
@@ -8808,7 +8808,7 @@
         <v>3.6</v>
       </c>
       <c r="BI33">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ33">
         <v>12</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-10-07.xlsx
@@ -514,7 +514,7 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
-    <t>2026-10-07 02:01:18</t>
+    <t>2026-10-07 04:13:12</t>
   </si>
 </sst>
 </file>
@@ -1108,82 +1108,82 @@
         <v>137</v>
       </c>
       <c r="F2">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="G2">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2">
+        <v>10.5</v>
+      </c>
+      <c r="J2">
+        <v>4.7</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1.41</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.75</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.95</v>
+      </c>
+      <c r="Q2">
+        <v>1.96</v>
+      </c>
+      <c r="R2">
+        <v>1.35</v>
+      </c>
+      <c r="S2">
+        <v>3.45</v>
+      </c>
+      <c r="T2">
+        <v>2.2</v>
+      </c>
+      <c r="U2">
+        <v>1.72</v>
+      </c>
+      <c r="V2">
+        <v>1.11</v>
+      </c>
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
+        <v>25</v>
+      </c>
+      <c r="Z2">
+        <v>170</v>
+      </c>
+      <c r="AA2">
+        <v>400</v>
+      </c>
+      <c r="AB2">
         <v>7.6</v>
       </c>
-      <c r="I2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>4.5</v>
-      </c>
-      <c r="L2">
-        <v>1.46</v>
-      </c>
-      <c r="M2">
-        <v>1.08</v>
-      </c>
-      <c r="N2">
-        <v>3.2</v>
-      </c>
-      <c r="O2">
-        <v>1.39</v>
-      </c>
-      <c r="P2">
-        <v>1.78</v>
-      </c>
-      <c r="Q2">
-        <v>2.18</v>
-      </c>
-      <c r="R2">
-        <v>1.27</v>
-      </c>
-      <c r="S2">
-        <v>4.2</v>
-      </c>
-      <c r="T2">
-        <v>2.26</v>
-      </c>
-      <c r="U2">
-        <v>1.67</v>
-      </c>
-      <c r="V2">
-        <v>1.13</v>
-      </c>
-      <c r="W2">
-        <v>2.68</v>
-      </c>
-      <c r="X2">
-        <v>14.5</v>
-      </c>
-      <c r="Y2">
-        <v>21</v>
-      </c>
-      <c r="Z2">
-        <v>75</v>
-      </c>
-      <c r="AA2">
-        <v>390</v>
-      </c>
-      <c r="AB2">
-        <v>6.6</v>
-      </c>
       <c r="AC2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE2">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AF2">
         <v>8.199999999999999</v>
@@ -1195,136 +1195,136 @@
         <v>34</v>
       </c>
       <c r="AI2">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>790</v>
       </c>
       <c r="AN2">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO2">
-        <v>490</v>
+        <v>300</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>65</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BA2">
-        <v>60</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE2">
         <v>170</v>
       </c>
       <c r="BF2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2">
         <v>14</v>
       </c>
       <c r="BK2">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>200</v>
+        <v>8.4</v>
       </c>
       <c r="BN2">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BO2">
         <v>3.3</v>
       </c>
       <c r="BP2">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BW2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BZ2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="CA2">
         <v>6</v>
@@ -1350,22 +1350,22 @@
         <v>138</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G3">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H3">
         <v>2.76</v>
       </c>
       <c r="I3">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="J3">
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1377,73 +1377,73 @@
         <v>5</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R3">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z3">
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AL3">
         <v>55</v>
@@ -1452,7 +1452,7 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO3">
         <v>22</v>
@@ -1461,34 +1461,34 @@
         <v>17</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS3">
+        <v>32</v>
+      </c>
+      <c r="AT3">
+        <v>12.5</v>
+      </c>
+      <c r="AU3">
         <v>7.4</v>
-      </c>
-      <c r="AT3">
-        <v>13</v>
-      </c>
-      <c r="AU3">
-        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA3">
         <v>27</v>
@@ -1503,25 +1503,25 @@
         <v>23</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI3">
         <v>3.25</v>
       </c>
       <c r="BJ3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1533,7 +1533,7 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP3">
         <v>21</v>
@@ -1542,22 +1542,22 @@
         <v>4.7</v>
       </c>
       <c r="BR3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT3">
         <v>6.8</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BX3">
         <v>32</v>
@@ -1592,22 +1592,22 @@
         <v>139</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="H4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I4">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="J4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L4">
         <v>1.29</v>
@@ -1625,43 +1625,43 @@
         <v>2.58</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R4">
         <v>1.62</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="W4">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
+        <v>11</v>
+      </c>
+      <c r="AA4">
+        <v>15</v>
+      </c>
+      <c r="AB4">
+        <v>29</v>
+      </c>
+      <c r="AC4">
         <v>11.5</v>
-      </c>
-      <c r="AA4">
-        <v>15.5</v>
-      </c>
-      <c r="AB4">
-        <v>28</v>
-      </c>
-      <c r="AC4">
-        <v>12</v>
       </c>
       <c r="AD4">
         <v>10.5</v>
@@ -1670,43 +1670,43 @@
         <v>16</v>
       </c>
       <c r="AF4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
         <v>180</v>
       </c>
       <c r="AK4">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AL4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP4">
         <v>20</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AS4">
         <v>12.5</v>
@@ -1715,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="AU4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV4">
         <v>8.800000000000001</v>
@@ -1724,94 +1724,94 @@
         <v>12.5</v>
       </c>
       <c r="AX4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AY4">
         <v>20</v>
       </c>
       <c r="AZ4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
         <v>23</v>
       </c>
       <c r="BB4">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE4">
         <v>55</v>
       </c>
       <c r="BF4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BG4">
         <v>5.5</v>
       </c>
       <c r="BH4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>10.5</v>
       </c>
       <c r="BO4">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP4">
+        <v>55</v>
+      </c>
+      <c r="BQ4">
+        <v>10</v>
+      </c>
+      <c r="BR4">
         <v>1000</v>
       </c>
-      <c r="BQ4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>48</v>
-      </c>
       <c r="BS4">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT4">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU4">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BV4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BW4">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BX4">
         <v>21</v>
       </c>
       <c r="BY4">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA4">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="CB4" t="s">
         <v>166</v>
@@ -1834,82 +1834,82 @@
         <v>140</v>
       </c>
       <c r="F5">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H5">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="I5">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="Q5">
         <v>2.02</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="W5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X5">
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC5">
         <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF5">
         <v>34</v>
@@ -1927,7 +1927,7 @@
         <v>90</v>
       </c>
       <c r="AK5">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AL5">
         <v>65</v>
@@ -1939,7 +1939,7 @@
         <v>60</v>
       </c>
       <c r="AO5">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AP5">
         <v>11.5</v>
@@ -1948,22 +1948,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>9.6</v>
       </c>
       <c r="AW5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX5">
         <v>24</v>
@@ -1972,40 +1972,40 @@
         <v>14</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD5">
         <v>40</v>
       </c>
       <c r="BE5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH5">
         <v>3.75</v>
       </c>
       <c r="BI5">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="BJ5">
         <v>11.5</v>
       </c>
       <c r="BK5">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2014,31 +2014,31 @@
         <v>5.6</v>
       </c>
       <c r="BN5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BS5">
         <v>5.2</v>
       </c>
       <c r="BT5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU5">
         <v>4.2</v>
       </c>
       <c r="BV5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW5">
         <v>4.3</v>
@@ -2050,7 +2050,7 @@
         <v>4.9</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA5">
         <v>4.9</v>
@@ -2076,10 +2076,10 @@
         <v>141</v>
       </c>
       <c r="F6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H6">
         <v>2.58</v>
@@ -2094,34 +2094,34 @@
         <v>3.1</v>
       </c>
       <c r="L6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="P6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="R6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T6">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V6">
         <v>1.53</v>
@@ -2130,13 +2130,13 @@
         <v>1.4</v>
       </c>
       <c r="X6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA6">
         <v>48</v>
@@ -2154,7 +2154,7 @@
         <v>42</v>
       </c>
       <c r="AF6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG6">
         <v>16</v>
@@ -2190,10 +2190,10 @@
         <v>6.8</v>
       </c>
       <c r="AR6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AT6">
         <v>7.8</v>
@@ -2202,58 +2202,58 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW6">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AX6">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AY6">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB6">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6">
+        <v>9</v>
+      </c>
+      <c r="BG6">
         <v>8.4</v>
       </c>
-      <c r="BE6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG6">
-        <v>7.8</v>
-      </c>
       <c r="BH6">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
         <v>6.4</v>
@@ -2265,16 +2265,16 @@
         <v>34</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU6">
         <v>4.1</v>
@@ -2283,19 +2283,19 @@
         <v>26</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>166</v>
@@ -2318,40 +2318,40 @@
         <v>142</v>
       </c>
       <c r="F7">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K7">
         <v>3.8</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
         <v>1.39</v>
       </c>
       <c r="P7">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
         <v>1.26</v>
@@ -2360,22 +2360,22 @@
         <v>3.75</v>
       </c>
       <c r="T7">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
         <v>1.22</v>
       </c>
       <c r="W7">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X7">
         <v>12.5</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
         <v>46</v>
@@ -2387,7 +2387,7 @@
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD7">
         <v>24</v>
@@ -2399,7 +2399,7 @@
         <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
         <v>22</v>
@@ -2417,7 +2417,7 @@
         <v>44</v>
       </c>
       <c r="AM7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN7">
         <v>16.5</v>
@@ -2426,58 +2426,58 @@
         <v>120</v>
       </c>
       <c r="AP7">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AR7">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS7">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
+        <v>4.4</v>
+      </c>
+      <c r="AU7">
+        <v>4.5</v>
+      </c>
+      <c r="AV7">
+        <v>5.9</v>
+      </c>
+      <c r="AW7">
+        <v>7.2</v>
+      </c>
+      <c r="AX7">
+        <v>4.6</v>
+      </c>
+      <c r="AY7">
+        <v>5.4</v>
+      </c>
+      <c r="AZ7">
         <v>5.7</v>
       </c>
-      <c r="AU7">
+      <c r="BA7">
+        <v>7.2</v>
+      </c>
+      <c r="BB7">
         <v>5.8</v>
       </c>
-      <c r="AV7">
-        <v>14</v>
-      </c>
-      <c r="AW7">
-        <v>25</v>
-      </c>
-      <c r="AX7">
-        <v>8</v>
-      </c>
-      <c r="AY7">
-        <v>7.6</v>
-      </c>
-      <c r="AZ7">
-        <v>16</v>
-      </c>
-      <c r="BA7">
-        <v>27</v>
-      </c>
-      <c r="BB7">
-        <v>15</v>
-      </c>
       <c r="BC7">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD7">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="BE7">
-        <v>55</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG7">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BH7">
         <v>3.65</v>
@@ -2560,85 +2560,85 @@
         <v>143</v>
       </c>
       <c r="F8">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G8">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="H8">
         <v>2.4</v>
       </c>
       <c r="I8">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M8">
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P8">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q8">
+        <v>1.53</v>
+      </c>
+      <c r="R8">
+        <v>1.69</v>
+      </c>
+      <c r="S8">
+        <v>2.32</v>
+      </c>
+      <c r="T8">
+        <v>1.48</v>
+      </c>
+      <c r="U8">
+        <v>2.68</v>
+      </c>
+      <c r="V8">
+        <v>1.67</v>
+      </c>
+      <c r="W8">
         <v>1.5</v>
       </c>
-      <c r="R8">
-        <v>1.77</v>
-      </c>
-      <c r="S8">
-        <v>2.2</v>
-      </c>
-      <c r="T8">
-        <v>1.45</v>
-      </c>
-      <c r="U8">
-        <v>2.8</v>
-      </c>
-      <c r="V8">
-        <v>1.66</v>
-      </c>
-      <c r="W8">
-        <v>1.52</v>
-      </c>
       <c r="X8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y8">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8">
         <v>23</v>
       </c>
       <c r="AF8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG8">
         <v>14</v>
@@ -2647,43 +2647,43 @@
         <v>14.5</v>
       </c>
       <c r="AI8">
+        <v>29</v>
+      </c>
+      <c r="AJ8">
+        <v>48</v>
+      </c>
+      <c r="AK8">
         <v>28</v>
       </c>
-      <c r="AJ8">
-        <v>46</v>
-      </c>
-      <c r="AK8">
-        <v>27</v>
-      </c>
       <c r="AL8">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN8">
+        <v>17.5</v>
+      </c>
+      <c r="AO8">
+        <v>12.5</v>
+      </c>
+      <c r="AP8">
+        <v>22</v>
+      </c>
+      <c r="AQ8">
+        <v>14</v>
+      </c>
+      <c r="AR8">
+        <v>17</v>
+      </c>
+      <c r="AS8">
+        <v>26</v>
+      </c>
+      <c r="AT8">
         <v>15.5</v>
       </c>
-      <c r="AO8">
-        <v>11.5</v>
-      </c>
-      <c r="AP8">
-        <v>18.5</v>
-      </c>
-      <c r="AQ8">
-        <v>15.5</v>
-      </c>
-      <c r="AR8">
-        <v>18.5</v>
-      </c>
-      <c r="AS8">
-        <v>25</v>
-      </c>
-      <c r="AT8">
-        <v>17</v>
-      </c>
       <c r="AU8">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AV8">
         <v>10.5</v>
@@ -2692,7 +2692,7 @@
         <v>18.5</v>
       </c>
       <c r="AX8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY8">
         <v>11.5</v>
@@ -2701,28 +2701,28 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE8">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH8">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
         <v>3.75</v>
@@ -2737,7 +2737,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
         <v>6.8</v>
@@ -2746,19 +2746,19 @@
         <v>5.1</v>
       </c>
       <c r="BP8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU8">
         <v>4.8</v>
@@ -2767,19 +2767,19 @@
         <v>16</v>
       </c>
       <c r="BW8">
+        <v>6.6</v>
+      </c>
+      <c r="BX8">
+        <v>24</v>
+      </c>
+      <c r="BY8">
+        <v>7.6</v>
+      </c>
+      <c r="BZ8">
+        <v>15.5</v>
+      </c>
+      <c r="CA8">
         <v>6.4</v>
-      </c>
-      <c r="BX8">
-        <v>23</v>
-      </c>
-      <c r="BY8">
-        <v>7.4</v>
-      </c>
-      <c r="BZ8">
-        <v>14</v>
-      </c>
-      <c r="CA8">
-        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>166</v>
@@ -2802,226 +2802,226 @@
         <v>144</v>
       </c>
       <c r="F9">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="G9">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="H9">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>10.5</v>
       </c>
       <c r="J9">
-        <v>1.13</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
-        <v>85</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N9">
-        <v>1.13</v>
+        <v>2.86</v>
       </c>
       <c r="O9">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P9">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="S9">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="T9">
+        <v>2.28</v>
+      </c>
+      <c r="U9">
+        <v>1.6</v>
+      </c>
+      <c r="V9">
         <v>1.11</v>
       </c>
-      <c r="U9">
-        <v>1.11</v>
-      </c>
-      <c r="V9">
-        <v>1.05</v>
-      </c>
       <c r="W9">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="CB9" t="s">
         <v>166</v>
@@ -3044,88 +3044,88 @@
         <v>145</v>
       </c>
       <c r="F10">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="G10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H10">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="I10">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M10">
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S10">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="U10">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W10">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z10">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AA10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
         <v>13</v>
       </c>
       <c r="AE10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>21</v>
@@ -3137,7 +3137,7 @@
         <v>130</v>
       </c>
       <c r="AK10">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL10">
         <v>130</v>
@@ -3146,46 +3146,46 @@
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO10">
         <v>30</v>
       </c>
       <c r="AP10">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU10">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY10">
         <v>4.4</v>
       </c>
       <c r="AZ10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB10">
         <v>5.5</v>
@@ -3197,73 +3197,73 @@
         <v>5.5</v>
       </c>
       <c r="BE10">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF10">
         <v>5.3</v>
       </c>
       <c r="BG10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH10">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ10">
         <v>11</v>
       </c>
       <c r="BK10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN10">
         <v>6.8</v>
       </c>
       <c r="BO10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ10">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BR10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BT10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV10">
         <v>25</v>
       </c>
       <c r="BW10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BZ10">
         <v>36</v>
       </c>
       <c r="CA10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB10" t="s">
         <v>166</v>
@@ -3286,88 +3286,88 @@
         <v>146</v>
       </c>
       <c r="F11">
+        <v>4.3</v>
+      </c>
+      <c r="G11">
+        <v>4.6</v>
+      </c>
+      <c r="H11">
+        <v>1.89</v>
+      </c>
+      <c r="I11">
+        <v>1.91</v>
+      </c>
+      <c r="J11">
         <v>3.95</v>
       </c>
-      <c r="G11">
+      <c r="K11">
         <v>4.1</v>
       </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>2.02</v>
-      </c>
-      <c r="J11">
-        <v>3.85</v>
-      </c>
-      <c r="K11">
-        <v>3.95</v>
-      </c>
       <c r="L11">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R11">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T11">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U11">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V11">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="W11">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y11">
         <v>11.5</v>
       </c>
       <c r="Z11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA11">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB11">
+        <v>19.5</v>
+      </c>
+      <c r="AC11">
+        <v>9</v>
+      </c>
+      <c r="AD11">
+        <v>10</v>
+      </c>
+      <c r="AE11">
         <v>18</v>
       </c>
-      <c r="AC11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD11">
-        <v>10.5</v>
-      </c>
-      <c r="AE11">
-        <v>19.5</v>
-      </c>
       <c r="AF11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG11">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH11">
         <v>17</v>
@@ -3376,25 +3376,25 @@
         <v>32</v>
       </c>
       <c r="AJ11">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK11">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AL11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM11">
         <v>80</v>
       </c>
       <c r="AN11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AO11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ11">
         <v>10</v>
@@ -3403,22 +3403,22 @@
         <v>12</v>
       </c>
       <c r="AS11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT11">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU11">
         <v>8</v>
       </c>
       <c r="AV11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AY11">
         <v>14.5</v>
@@ -3427,34 +3427,34 @@
         <v>15</v>
       </c>
       <c r="BA11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB11">
+        <v>48</v>
+      </c>
+      <c r="BC11">
         <v>36</v>
       </c>
-      <c r="BC11">
-        <v>38</v>
-      </c>
       <c r="BD11">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BE11">
+        <v>50</v>
+      </c>
+      <c r="BF11">
         <v>36</v>
       </c>
-      <c r="BF11">
-        <v>32</v>
-      </c>
       <c r="BG11">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH11">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BI11">
         <v>3.45</v>
       </c>
       <c r="BJ11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK11">
         <v>8.199999999999999</v>
@@ -3463,49 +3463,49 @@
         <v>120</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN11">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BP11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BQ11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11">
         <v>38</v>
       </c>
       <c r="BS11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT11">
         <v>4.9</v>
       </c>
       <c r="BU11">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BV11">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BW11">
         <v>8.199999999999999</v>
       </c>
       <c r="BX11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BZ11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA11">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>166</v>
@@ -3531,61 +3531,61 @@
         <v>1.66</v>
       </c>
       <c r="G12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I12">
         <v>9</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
         <v>3.65</v>
       </c>
       <c r="L12">
+        <v>1.66</v>
+      </c>
+      <c r="M12">
+        <v>1.15</v>
+      </c>
+      <c r="N12">
+        <v>2.42</v>
+      </c>
+      <c r="O12">
         <v>1.65</v>
       </c>
-      <c r="M12">
-        <v>1.14</v>
-      </c>
-      <c r="N12">
-        <v>2.44</v>
-      </c>
-      <c r="O12">
-        <v>1.63</v>
-      </c>
       <c r="P12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q12">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="R12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S12">
         <v>6.6</v>
       </c>
       <c r="T12">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="U12">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="V12">
         <v>1.12</v>
       </c>
       <c r="W12">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X12">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z12">
         <v>160</v>
@@ -3606,7 +3606,7 @@
         <v>700</v>
       </c>
       <c r="AF12">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG12">
         <v>14.5</v>
@@ -3630,7 +3630,7 @@
         <v>700</v>
       </c>
       <c r="AN12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO12">
         <v>1000</v>
@@ -3642,22 +3642,22 @@
         <v>14</v>
       </c>
       <c r="AR12">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AS12">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX12">
         <v>6.8</v>
@@ -3666,88 +3666,88 @@
         <v>10</v>
       </c>
       <c r="AZ12">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="BA12">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB12">
         <v>14.5</v>
       </c>
       <c r="BC12">
-        <v>5.3</v>
+        <v>12</v>
       </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG12">
+        <v>7.6</v>
+      </c>
+      <c r="BH12">
+        <v>2.58</v>
+      </c>
+      <c r="BI12">
+        <v>2.3</v>
+      </c>
+      <c r="BJ12">
+        <v>18</v>
+      </c>
+      <c r="BK12">
         <v>5.9</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.25</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.95</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ12">
-        <v>1.95</v>
+        <v>5.7</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU12">
-        <v>1.95</v>
+        <v>5.3</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="s">
         <v>166</v>
@@ -3770,22 +3770,22 @@
         <v>148</v>
       </c>
       <c r="F13">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H13">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I13">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K13">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4012,226 +4012,226 @@
         <v>149</v>
       </c>
       <c r="F14">
+        <v>2.14</v>
+      </c>
+      <c r="G14">
+        <v>2.36</v>
+      </c>
+      <c r="H14">
+        <v>3.45</v>
+      </c>
+      <c r="I14">
+        <v>4.1</v>
+      </c>
+      <c r="J14">
+        <v>3.15</v>
+      </c>
+      <c r="K14">
+        <v>3.65</v>
+      </c>
+      <c r="L14">
+        <v>1.45</v>
+      </c>
+      <c r="M14">
+        <v>1.1</v>
+      </c>
+      <c r="N14">
+        <v>3.05</v>
+      </c>
+      <c r="O14">
+        <v>1.42</v>
+      </c>
+      <c r="P14">
+        <v>1.71</v>
+      </c>
+      <c r="Q14">
+        <v>2.14</v>
+      </c>
+      <c r="R14">
+        <v>1.25</v>
+      </c>
+      <c r="S14">
+        <v>3.8</v>
+      </c>
+      <c r="T14">
         <v>1.12</v>
       </c>
-      <c r="G14">
-        <v>990</v>
-      </c>
-      <c r="H14">
-        <v>1.12</v>
-      </c>
-      <c r="I14">
-        <v>990</v>
-      </c>
-      <c r="J14">
-        <v>1.12</v>
-      </c>
-      <c r="K14">
-        <v>950</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>1.1</v>
-      </c>
-      <c r="O14">
-        <v>1.02</v>
-      </c>
-      <c r="P14">
-        <v>1.09</v>
-      </c>
-      <c r="Q14">
-        <v>1.45</v>
-      </c>
-      <c r="R14">
-        <v>1.08</v>
-      </c>
-      <c r="S14">
-        <v>1.46</v>
-      </c>
-      <c r="T14">
-        <v>1.11</v>
-      </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.74</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="s">
         <v>166</v>
@@ -4254,226 +4254,226 @@
         <v>150</v>
       </c>
       <c r="F15">
+        <v>1.45</v>
+      </c>
+      <c r="G15">
+        <v>1.48</v>
+      </c>
+      <c r="H15">
+        <v>9.6</v>
+      </c>
+      <c r="I15">
+        <v>11.5</v>
+      </c>
+      <c r="J15">
+        <v>4.4</v>
+      </c>
+      <c r="K15">
+        <v>4.9</v>
+      </c>
+      <c r="L15">
+        <v>1.46</v>
+      </c>
+      <c r="M15">
+        <v>1.08</v>
+      </c>
+      <c r="N15">
+        <v>3.35</v>
+      </c>
+      <c r="O15">
         <v>1.39</v>
       </c>
-      <c r="G15">
-        <v>1.42</v>
-      </c>
-      <c r="H15">
+      <c r="P15">
+        <v>1.8</v>
+      </c>
+      <c r="Q15">
+        <v>2.16</v>
+      </c>
+      <c r="R15">
+        <v>1.3</v>
+      </c>
+      <c r="S15">
+        <v>4</v>
+      </c>
+      <c r="T15">
+        <v>2.34</v>
+      </c>
+      <c r="U15">
+        <v>1.65</v>
+      </c>
+      <c r="V15">
+        <v>1.1</v>
+      </c>
+      <c r="W15">
+        <v>3.05</v>
+      </c>
+      <c r="X15">
+        <v>15.5</v>
+      </c>
+      <c r="Y15">
+        <v>27</v>
+      </c>
+      <c r="Z15">
+        <v>110</v>
+      </c>
+      <c r="AA15">
+        <v>510</v>
+      </c>
+      <c r="AB15">
+        <v>6.4</v>
+      </c>
+      <c r="AC15">
+        <v>11.5</v>
+      </c>
+      <c r="AD15">
+        <v>40</v>
+      </c>
+      <c r="AE15">
+        <v>290</v>
+      </c>
+      <c r="AF15">
+        <v>7.8</v>
+      </c>
+      <c r="AG15">
         <v>11</v>
       </c>
-      <c r="I15">
+      <c r="AH15">
+        <v>36</v>
+      </c>
+      <c r="AI15">
+        <v>250</v>
+      </c>
+      <c r="AJ15">
         <v>13.5</v>
       </c>
-      <c r="J15">
+      <c r="AK15">
+        <v>19</v>
+      </c>
+      <c r="AL15">
+        <v>55</v>
+      </c>
+      <c r="AM15">
+        <v>250</v>
+      </c>
+      <c r="AN15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO15">
+        <v>670</v>
+      </c>
+      <c r="AP15">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15">
+        <v>21</v>
+      </c>
+      <c r="AR15">
+        <v>55</v>
+      </c>
+      <c r="AS15">
+        <v>9</v>
+      </c>
+      <c r="AT15">
+        <v>5.6</v>
+      </c>
+      <c r="AU15">
+        <v>9.4</v>
+      </c>
+      <c r="AV15">
+        <v>26</v>
+      </c>
+      <c r="AW15">
+        <v>10.5</v>
+      </c>
+      <c r="AX15">
+        <v>6.6</v>
+      </c>
+      <c r="AY15">
+        <v>9</v>
+      </c>
+      <c r="AZ15">
+        <v>23</v>
+      </c>
+      <c r="BA15">
+        <v>11</v>
+      </c>
+      <c r="BB15">
+        <v>11</v>
+      </c>
+      <c r="BC15">
+        <v>15.5</v>
+      </c>
+      <c r="BD15">
+        <v>29</v>
+      </c>
+      <c r="BE15">
+        <v>11</v>
+      </c>
+      <c r="BF15">
+        <v>8.6</v>
+      </c>
+      <c r="BG15">
+        <v>15</v>
+      </c>
+      <c r="BH15">
+        <v>3.6</v>
+      </c>
+      <c r="BI15">
+        <v>2.68</v>
+      </c>
+      <c r="BJ15">
+        <v>13.5</v>
+      </c>
+      <c r="BK15">
         <v>4.6</v>
-      </c>
-      <c r="K15">
-        <v>5.1</v>
-      </c>
-      <c r="L15">
-        <v>1.43</v>
-      </c>
-      <c r="M15">
-        <v>1.07</v>
-      </c>
-      <c r="N15">
-        <v>3.5</v>
-      </c>
-      <c r="O15">
-        <v>1.36</v>
-      </c>
-      <c r="P15">
-        <v>1.83</v>
-      </c>
-      <c r="Q15">
-        <v>2.08</v>
-      </c>
-      <c r="R15">
-        <v>1.31</v>
-      </c>
-      <c r="S15">
-        <v>3.8</v>
-      </c>
-      <c r="T15">
-        <v>2.42</v>
-      </c>
-      <c r="U15">
-        <v>1.64</v>
-      </c>
-      <c r="V15">
-        <v>1.08</v>
-      </c>
-      <c r="W15">
-        <v>3.35</v>
-      </c>
-      <c r="X15">
-        <v>16.5</v>
-      </c>
-      <c r="Y15">
-        <v>32</v>
-      </c>
-      <c r="Z15">
-        <v>130</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>7.4</v>
-      </c>
-      <c r="AC15">
-        <v>12</v>
-      </c>
-      <c r="AD15">
-        <v>55</v>
-      </c>
-      <c r="AE15">
-        <v>310</v>
-      </c>
-      <c r="AF15">
-        <v>7.4</v>
-      </c>
-      <c r="AG15">
-        <v>12.5</v>
-      </c>
-      <c r="AH15">
-        <v>40</v>
-      </c>
-      <c r="AI15">
-        <v>260</v>
-      </c>
-      <c r="AJ15">
-        <v>13</v>
-      </c>
-      <c r="AK15">
-        <v>18.5</v>
-      </c>
-      <c r="AL15">
-        <v>150</v>
-      </c>
-      <c r="AM15">
-        <v>320</v>
-      </c>
-      <c r="AN15">
-        <v>8.6</v>
-      </c>
-      <c r="AO15">
-        <v>600</v>
-      </c>
-      <c r="AP15">
-        <v>12</v>
-      </c>
-      <c r="AQ15">
-        <v>13</v>
-      </c>
-      <c r="AR15">
-        <v>6.8</v>
-      </c>
-      <c r="AS15">
-        <v>6.6</v>
-      </c>
-      <c r="AT15">
-        <v>5.8</v>
-      </c>
-      <c r="AU15">
-        <v>10</v>
-      </c>
-      <c r="AV15">
-        <v>6.4</v>
-      </c>
-      <c r="AW15">
-        <v>6.6</v>
-      </c>
-      <c r="AX15">
-        <v>6.2</v>
-      </c>
-      <c r="AY15">
-        <v>9.4</v>
-      </c>
-      <c r="AZ15">
-        <v>18</v>
-      </c>
-      <c r="BA15">
-        <v>6.4</v>
-      </c>
-      <c r="BB15">
-        <v>9.6</v>
-      </c>
-      <c r="BC15">
-        <v>15</v>
-      </c>
-      <c r="BD15">
-        <v>6.6</v>
-      </c>
-      <c r="BE15">
-        <v>6.6</v>
-      </c>
-      <c r="BF15">
-        <v>7.2</v>
-      </c>
-      <c r="BG15">
-        <v>7.2</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>1.04</v>
-      </c>
-      <c r="BJ15">
-        <v>1000</v>
-      </c>
-      <c r="BK15">
-        <v>1.22</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ15">
-        <v>1.22</v>
+        <v>4.2</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU15">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA15">
-        <v>1.22</v>
+        <v>5.3</v>
       </c>
       <c r="CB15" t="s">
         <v>166</v>
@@ -4496,226 +4496,226 @@
         <v>151</v>
       </c>
       <c r="F16">
-        <v>1.12</v>
+        <v>2.56</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>3.2</v>
       </c>
       <c r="H16">
-        <v>1.12</v>
+        <v>2.7</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
-        <v>1.12</v>
+        <v>2.8</v>
       </c>
       <c r="K16">
-        <v>85</v>
+        <v>3.8</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O16">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P16">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="Q16">
-        <v>1.49</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V16">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB16" t="s">
         <v>166</v>
@@ -4741,10 +4741,10 @@
         <v>1.54</v>
       </c>
       <c r="G17">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I17">
         <v>9.6</v>
@@ -4762,34 +4762,34 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q17">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T17">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W17">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X17">
         <v>14</v>
@@ -4801,16 +4801,16 @@
         <v>160</v>
       </c>
       <c r="AA17">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AB17">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC17">
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE17">
         <v>180</v>
@@ -4825,13 +4825,13 @@
         <v>32</v>
       </c>
       <c r="AI17">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK17">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL17">
         <v>48</v>
@@ -4843,19 +4843,19 @@
         <v>12</v>
       </c>
       <c r="AO17">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AP17">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AR17">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT17">
         <v>6</v>
@@ -4864,100 +4864,100 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW17">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY17">
         <v>8.4</v>
       </c>
       <c r="AZ17">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BA17">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB17">
         <v>11</v>
       </c>
       <c r="BC17">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD17">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE17">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF17">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB17" t="s">
         <v>166</v>
@@ -4980,226 +4980,226 @@
         <v>153</v>
       </c>
       <c r="F18">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="H18">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="I18">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J18">
+        <v>3.9</v>
+      </c>
+      <c r="K18">
+        <v>4.1</v>
+      </c>
+      <c r="L18">
+        <v>1.44</v>
+      </c>
+      <c r="M18">
+        <v>1.07</v>
+      </c>
+      <c r="N18">
         <v>3.55</v>
       </c>
-      <c r="K18">
+      <c r="O18">
+        <v>1.37</v>
+      </c>
+      <c r="P18">
+        <v>1.86</v>
+      </c>
+      <c r="Q18">
+        <v>2.06</v>
+      </c>
+      <c r="R18">
+        <v>1.33</v>
+      </c>
+      <c r="S18">
         <v>3.75</v>
       </c>
-      <c r="L18">
-        <v>1.45</v>
-      </c>
-      <c r="M18">
-        <v>1.08</v>
-      </c>
-      <c r="N18">
-        <v>3.4</v>
-      </c>
-      <c r="O18">
-        <v>1.38</v>
-      </c>
-      <c r="P18">
-        <v>1.81</v>
-      </c>
-      <c r="Q18">
-        <v>2.16</v>
-      </c>
-      <c r="R18">
-        <v>1.3</v>
-      </c>
-      <c r="S18">
-        <v>4</v>
-      </c>
       <c r="T18">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U18">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V18">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="X18">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y18">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z18">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA18">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AB18">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>21</v>
       </c>
       <c r="AE18">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AF18">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG18">
+        <v>10</v>
+      </c>
+      <c r="AH18">
+        <v>24</v>
+      </c>
+      <c r="AI18">
+        <v>500</v>
+      </c>
+      <c r="AJ18">
+        <v>19.5</v>
+      </c>
+      <c r="AK18">
+        <v>19.5</v>
+      </c>
+      <c r="AL18">
+        <v>40</v>
+      </c>
+      <c r="AM18">
+        <v>160</v>
+      </c>
+      <c r="AN18">
+        <v>13</v>
+      </c>
+      <c r="AO18">
+        <v>120</v>
+      </c>
+      <c r="AP18">
+        <v>12.5</v>
+      </c>
+      <c r="AQ18">
+        <v>14.5</v>
+      </c>
+      <c r="AR18">
+        <v>34</v>
+      </c>
+      <c r="AS18">
+        <v>14</v>
+      </c>
+      <c r="AT18">
+        <v>7.2</v>
+      </c>
+      <c r="AU18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV18">
+        <v>18</v>
+      </c>
+      <c r="AW18">
+        <v>20</v>
+      </c>
+      <c r="AX18">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY18">
+        <v>9</v>
+      </c>
+      <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
+        <v>28</v>
+      </c>
+      <c r="BB18">
+        <v>17</v>
+      </c>
+      <c r="BC18">
+        <v>16.5</v>
+      </c>
+      <c r="BD18">
+        <v>36</v>
+      </c>
+      <c r="BE18">
+        <v>14</v>
+      </c>
+      <c r="BF18">
         <v>10.5</v>
       </c>
-      <c r="AH18">
-        <v>25</v>
-      </c>
-      <c r="AI18">
-        <v>85</v>
-      </c>
-      <c r="AJ18">
-        <v>22</v>
-      </c>
-      <c r="AK18">
-        <v>23</v>
-      </c>
-      <c r="AL18">
-        <v>50</v>
-      </c>
-      <c r="AM18">
-        <v>440</v>
-      </c>
-      <c r="AN18">
-        <v>16</v>
-      </c>
-      <c r="AO18">
-        <v>95</v>
-      </c>
-      <c r="AP18">
-        <v>11</v>
-      </c>
-      <c r="AQ18">
+      <c r="BG18">
+        <v>13.5</v>
+      </c>
+      <c r="BH18">
+        <v>3.65</v>
+      </c>
+      <c r="BI18">
+        <v>2.72</v>
+      </c>
+      <c r="BJ18">
         <v>12.5</v>
       </c>
-      <c r="AR18">
-        <v>11.5</v>
-      </c>
-      <c r="AS18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT18">
-        <v>7</v>
-      </c>
-      <c r="AU18">
-        <v>7.4</v>
-      </c>
-      <c r="AV18">
-        <v>16</v>
-      </c>
-      <c r="AW18">
-        <v>8.6</v>
-      </c>
-      <c r="AX18">
-        <v>10</v>
-      </c>
-      <c r="AY18">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18">
-        <v>18.5</v>
-      </c>
-      <c r="BA18">
-        <v>8</v>
-      </c>
-      <c r="BB18">
-        <v>19</v>
-      </c>
-      <c r="BC18">
-        <v>19</v>
-      </c>
-      <c r="BD18">
-        <v>8</v>
-      </c>
-      <c r="BE18">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF18">
-        <v>14</v>
-      </c>
-      <c r="BG18">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH18">
-        <v>1000</v>
-      </c>
-      <c r="BI18">
-        <v>1.04</v>
-      </c>
-      <c r="BJ18">
-        <v>1000</v>
-      </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB18" t="s">
         <v>166</v>
@@ -5228,13 +5228,13 @@
         <v>3.95</v>
       </c>
       <c r="H19">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I19">
         <v>2.34</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19">
         <v>3.4</v>
@@ -5246,7 +5246,7 @@
         <v>1.1</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O19">
         <v>1.46</v>
@@ -5264,16 +5264,16 @@
         <v>4.5</v>
       </c>
       <c r="T19">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U19">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V19">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X19">
         <v>11</v>
@@ -5324,7 +5324,7 @@
         <v>580</v>
       </c>
       <c r="AN19">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AO19">
         <v>27</v>
@@ -5333,13 +5333,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ19">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR19">
         <v>11.5</v>
       </c>
       <c r="AS19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19">
         <v>10</v>
@@ -5351,10 +5351,10 @@
         <v>10</v>
       </c>
       <c r="AW19">
+        <v>8.4</v>
+      </c>
+      <c r="AX19">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AX19">
-        <v>8</v>
       </c>
       <c r="AY19">
         <v>14</v>
@@ -5372,13 +5372,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BD19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE19">
         <v>10</v>
       </c>
       <c r="BF19">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG19">
         <v>21</v>
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="BK19">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5423,7 +5423,7 @@
         <v>5.1</v>
       </c>
       <c r="BU19">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV19">
         <v>19</v>
@@ -5464,19 +5464,19 @@
         <v>155</v>
       </c>
       <c r="F20">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G20">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J20">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5488,40 +5488,40 @@
         <v>1.06</v>
       </c>
       <c r="N20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O20">
         <v>1.27</v>
       </c>
       <c r="P20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R20">
         <v>1.46</v>
       </c>
       <c r="S20">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U20">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X20">
         <v>21</v>
       </c>
       <c r="Y20">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z20">
         <v>36</v>
@@ -5533,7 +5533,7 @@
         <v>10.5</v>
       </c>
       <c r="AC20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD20">
         <v>19</v>
@@ -5542,19 +5542,19 @@
         <v>65</v>
       </c>
       <c r="AF20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH20">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI20">
         <v>65</v>
       </c>
       <c r="AJ20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK20">
         <v>21</v>
@@ -5569,13 +5569,13 @@
         <v>10.5</v>
       </c>
       <c r="AO20">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP20">
         <v>16</v>
       </c>
       <c r="AQ20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR20">
         <v>30</v>
@@ -5590,7 +5590,7 @@
         <v>8</v>
       </c>
       <c r="AV20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW20">
         <v>23</v>
@@ -5614,34 +5614,34 @@
         <v>16.5</v>
       </c>
       <c r="BD20">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BE20">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="BF20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG20">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BH20">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ20">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BK20">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BN20">
         <v>4.6</v>
@@ -5650,19 +5650,19 @@
         <v>4.2</v>
       </c>
       <c r="BP20">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BQ20">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BR20">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BS20">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="BT20">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU20">
         <v>7.2</v>
@@ -5671,19 +5671,19 @@
         <v>42</v>
       </c>
       <c r="BW20">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX20">
         <v>50</v>
       </c>
       <c r="BY20">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BZ20">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA20">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB20" t="s">
         <v>166</v>
@@ -5706,16 +5706,16 @@
         <v>156</v>
       </c>
       <c r="F21">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G21">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H21">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J21">
         <v>3.35</v>
@@ -5724,49 +5724,49 @@
         <v>3.4</v>
       </c>
       <c r="L21">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
         <v>1.1</v>
       </c>
       <c r="N21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P21">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q21">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
         <v>1.26</v>
       </c>
       <c r="S21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T21">
         <v>2</v>
       </c>
       <c r="U21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
         <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X21">
         <v>11</v>
       </c>
       <c r="Y21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA21">
         <v>75</v>
@@ -5799,16 +5799,16 @@
         <v>32</v>
       </c>
       <c r="AK21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL21">
         <v>50</v>
       </c>
       <c r="AM21">
-        <v>440</v>
+        <v>140</v>
       </c>
       <c r="AN21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO21">
         <v>60</v>
@@ -5820,7 +5820,7 @@
         <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS21">
         <v>60</v>
@@ -5850,82 +5850,82 @@
         <v>55</v>
       </c>
       <c r="BB21">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BC21">
         <v>25</v>
       </c>
       <c r="BD21">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE21">
         <v>100</v>
       </c>
       <c r="BF21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG21">
         <v>46</v>
       </c>
       <c r="BH21">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="BI21">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="BJ21">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BK21">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="BM21">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="BN21">
+        <v>4.9</v>
+      </c>
+      <c r="BO21">
+        <v>4.6</v>
+      </c>
+      <c r="BP21">
+        <v>23</v>
+      </c>
+      <c r="BQ21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR21">
+        <v>38</v>
+      </c>
+      <c r="BS21">
+        <v>10</v>
+      </c>
+      <c r="BT21">
+        <v>6.6</v>
+      </c>
+      <c r="BU21">
         <v>6</v>
       </c>
-      <c r="BO21">
-        <v>2.66</v>
-      </c>
-      <c r="BP21">
-        <v>26</v>
-      </c>
-      <c r="BQ21">
-        <v>4</v>
-      </c>
-      <c r="BR21">
+      <c r="BV21">
+        <v>34</v>
+      </c>
+      <c r="BW21">
+        <v>10</v>
+      </c>
+      <c r="BX21">
         <v>50</v>
       </c>
-      <c r="BS21">
-        <v>4.4</v>
-      </c>
-      <c r="BT21">
-        <v>7.8</v>
-      </c>
-      <c r="BU21">
-        <v>5.5</v>
-      </c>
-      <c r="BV21">
-        <v>46</v>
-      </c>
-      <c r="BW21">
-        <v>4.3</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
       <c r="BY21">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="BZ21">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="CA21">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="CB21" t="s">
         <v>166</v>
@@ -5948,7 +5948,7 @@
         <v>157</v>
       </c>
       <c r="F22">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G22">
         <v>2.2</v>
@@ -5957,7 +5957,7 @@
         <v>3.6</v>
       </c>
       <c r="I22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J22">
         <v>3.7</v>
@@ -5966,7 +5966,7 @@
         <v>3.75</v>
       </c>
       <c r="L22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M22">
         <v>1.07</v>
@@ -5978,13 +5978,13 @@
         <v>1.31</v>
       </c>
       <c r="P22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q22">
         <v>1.96</v>
       </c>
       <c r="R22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
         <v>3.4</v>
@@ -5993,10 +5993,10 @@
         <v>1.78</v>
       </c>
       <c r="U22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
         <v>1.83</v>
@@ -6005,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="Y22">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z22">
         <v>26</v>
@@ -6020,7 +6020,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE22">
         <v>42</v>
@@ -6029,7 +6029,7 @@
         <v>14</v>
       </c>
       <c r="AG22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH22">
         <v>17.5</v>
@@ -6047,7 +6047,7 @@
         <v>36</v>
       </c>
       <c r="AM22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN22">
         <v>16</v>
@@ -6056,7 +6056,7 @@
         <v>40</v>
       </c>
       <c r="AP22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22">
         <v>13.5</v>
@@ -6065,7 +6065,7 @@
         <v>23</v>
       </c>
       <c r="AS22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT22">
         <v>9.4</v>
@@ -6074,7 +6074,7 @@
         <v>7.6</v>
       </c>
       <c r="AV22">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW22">
         <v>38</v>
@@ -6086,13 +6086,13 @@
         <v>10</v>
       </c>
       <c r="AZ22">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA22">
         <v>46</v>
       </c>
       <c r="BB22">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC22">
         <v>20</v>
@@ -6101,16 +6101,16 @@
         <v>32</v>
       </c>
       <c r="BE22">
+        <v>75</v>
+      </c>
+      <c r="BF22">
+        <v>14.5</v>
+      </c>
+      <c r="BG22">
         <v>36</v>
       </c>
-      <c r="BF22">
-        <v>14</v>
-      </c>
-      <c r="BG22">
-        <v>34</v>
-      </c>
       <c r="BH22">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI22">
         <v>3.25</v>
@@ -6190,10 +6190,10 @@
         <v>158</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G23">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H23">
         <v>3.85</v>
@@ -6205,7 +6205,7 @@
         <v>3.25</v>
       </c>
       <c r="K23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L23">
         <v>1.52</v>
@@ -6220,13 +6220,13 @@
         <v>1.45</v>
       </c>
       <c r="P23">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q23">
         <v>2.36</v>
       </c>
       <c r="R23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S23">
         <v>4.5</v>
@@ -6235,13 +6235,13 @@
         <v>1.98</v>
       </c>
       <c r="U23">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V23">
         <v>1.32</v>
       </c>
       <c r="W23">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X23">
         <v>11</v>
@@ -6256,10 +6256,10 @@
         <v>900</v>
       </c>
       <c r="AB23">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD23">
         <v>17</v>
@@ -6292,10 +6292,10 @@
         <v>580</v>
       </c>
       <c r="AN23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO23">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AP23">
         <v>9.6</v>
@@ -6307,7 +6307,7 @@
         <v>11.5</v>
       </c>
       <c r="AS23">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23">
         <v>7</v>
@@ -6319,7 +6319,7 @@
         <v>14.5</v>
       </c>
       <c r="AW23">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="AX23">
         <v>11</v>
@@ -6331,46 +6331,46 @@
         <v>18</v>
       </c>
       <c r="BA23">
+        <v>8</v>
+      </c>
+      <c r="BB23">
+        <v>25</v>
+      </c>
+      <c r="BC23">
+        <v>23</v>
+      </c>
+      <c r="BD23">
         <v>7.6</v>
       </c>
-      <c r="BB23">
-        <v>13</v>
-      </c>
-      <c r="BC23">
-        <v>13</v>
-      </c>
-      <c r="BD23">
-        <v>7.2</v>
-      </c>
       <c r="BE23">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF23">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG23">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI23">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ23">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK23">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BN23">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO23">
         <v>4.3</v>
@@ -6379,37 +6379,37 @@
         <v>21</v>
       </c>
       <c r="BQ23">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BR23">
         <v>44</v>
       </c>
       <c r="BS23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BT23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU23">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV23">
         <v>44</v>
       </c>
       <c r="BW23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BX23">
         <v>65</v>
       </c>
       <c r="BY23">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BZ23">
         <v>44</v>
       </c>
       <c r="CA23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="CB23" t="s">
         <v>166</v>
@@ -6432,40 +6432,40 @@
         <v>159</v>
       </c>
       <c r="F24">
+        <v>1.88</v>
+      </c>
+      <c r="G24">
         <v>1.91</v>
       </c>
-      <c r="G24">
-        <v>1.94</v>
-      </c>
       <c r="H24">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I24">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L24">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M24">
         <v>1.1</v>
       </c>
       <c r="N24">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P24">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
         <v>1.25</v>
@@ -6474,16 +6474,16 @@
         <v>4.7</v>
       </c>
       <c r="T24">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X24">
         <v>11</v>
@@ -6492,22 +6492,22 @@
         <v>13.5</v>
       </c>
       <c r="Z24">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA24">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC24">
         <v>8</v>
       </c>
       <c r="AD24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE24">
-        <v>80</v>
+        <v>470</v>
       </c>
       <c r="AF24">
         <v>10.5</v>
@@ -6516,13 +6516,13 @@
         <v>11</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI24">
-        <v>95</v>
+        <v>370</v>
       </c>
       <c r="AJ24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK24">
         <v>24</v>
@@ -6531,16 +6531,16 @@
         <v>55</v>
       </c>
       <c r="AM24">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN24">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO24">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ24">
         <v>12.5</v>
@@ -6549,25 +6549,25 @@
         <v>30</v>
       </c>
       <c r="AS24">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AT24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV24">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW24">
         <v>60</v>
       </c>
       <c r="AX24">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24">
         <v>20</v>
@@ -6576,7 +6576,7 @@
         <v>75</v>
       </c>
       <c r="BB24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC24">
         <v>20</v>
@@ -6585,40 +6585,40 @@
         <v>42</v>
       </c>
       <c r="BE24">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH24">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI24">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ24">
         <v>11.5</v>
       </c>
       <c r="BK24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO24">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ24">
         <v>7.8</v>
@@ -6630,16 +6630,16 @@
         <v>11</v>
       </c>
       <c r="BT24">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU24">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BV24">
         <v>55</v>
       </c>
       <c r="BW24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX24">
         <v>1000</v>
@@ -6648,7 +6648,7 @@
         <v>13.5</v>
       </c>
       <c r="BZ24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA24">
         <v>11</v>
@@ -6674,16 +6674,16 @@
         <v>160</v>
       </c>
       <c r="F25">
+        <v>1.66</v>
+      </c>
+      <c r="G25">
         <v>1.68</v>
       </c>
-      <c r="G25">
-        <v>1.7</v>
-      </c>
       <c r="H25">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J25">
         <v>4.1</v>
@@ -6695,25 +6695,25 @@
         <v>1.4</v>
       </c>
       <c r="M25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
         <v>4.1</v>
       </c>
       <c r="O25">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P25">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R25">
         <v>1.4</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T25">
         <v>1.91</v>
@@ -6722,40 +6722,40 @@
         <v>2.02</v>
       </c>
       <c r="V25">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W25">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X25">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y25">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z25">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AA25">
         <v>170</v>
       </c>
       <c r="AB25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD25">
         <v>23</v>
       </c>
       <c r="AE25">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AF25">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25">
         <v>21</v>
@@ -6764,46 +6764,46 @@
         <v>85</v>
       </c>
       <c r="AJ25">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK25">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL25">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AM25">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN25">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP25">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ25">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR25">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="AS25">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AT25">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU25">
         <v>8.4</v>
       </c>
       <c r="AV25">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW25">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AX25">
         <v>9.199999999999999</v>
@@ -6812,10 +6812,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA25">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BB25">
         <v>15</v>
@@ -6824,76 +6824,76 @@
         <v>16</v>
       </c>
       <c r="BD25">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE25">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BF25">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG25">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI25">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK25">
-        <v>2.3</v>
+        <v>6.6</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.06</v>
+        <v>16</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO25">
-        <v>1.7</v>
+        <v>3.85</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ25">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS25">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU25">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW25">
-        <v>2.32</v>
+        <v>13.5</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY25">
-        <v>1.06</v>
+        <v>14</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA25">
-        <v>2.32</v>
+        <v>9.4</v>
       </c>
       <c r="CB25" t="s">
         <v>166</v>
@@ -6916,28 +6916,28 @@
         <v>161</v>
       </c>
       <c r="F26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G26">
         <v>1.36</v>
       </c>
       <c r="H26">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J26">
         <v>5.8</v>
       </c>
       <c r="K26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L26">
         <v>1.24</v>
       </c>
       <c r="M26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
         <v>6.8</v>
@@ -6949,61 +6949,61 @@
         <v>3</v>
       </c>
       <c r="Q26">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R26">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T26">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="U26">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V26">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X26">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y26">
         <v>950</v>
       </c>
       <c r="Z26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA26">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AB26">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC26">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AD26">
         <v>40</v>
       </c>
       <c r="AE26">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF26">
         <v>11.5</v>
       </c>
       <c r="AG26">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI26">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ26">
         <v>12.5</v>
@@ -7018,73 +7018,73 @@
         <v>110</v>
       </c>
       <c r="AN26">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AO26">
         <v>120</v>
       </c>
       <c r="AP26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AR26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AS26">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT26">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU26">
         <v>13</v>
       </c>
       <c r="AV26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX26">
         <v>8.4</v>
       </c>
       <c r="AY26">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
         <v>20</v>
       </c>
       <c r="BA26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB26">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD26">
         <v>21</v>
       </c>
       <c r="BE26">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF26">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BG26">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
         <v>1.04</v>
@@ -7096,25 +7096,25 @@
         <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS26">
         <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BU26">
         <v>1.04</v>
@@ -7132,7 +7132,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA26">
         <v>1.04</v>
@@ -7164,7 +7164,7 @@
         <v>3.2</v>
       </c>
       <c r="H27">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="I27">
         <v>2.42</v>
@@ -7179,31 +7179,31 @@
         <v>1.36</v>
       </c>
       <c r="M27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N27">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q27">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R27">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S27">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T27">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U27">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V27">
         <v>1.7</v>
@@ -7212,7 +7212,7 @@
         <v>1.45</v>
       </c>
       <c r="X27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y27">
         <v>12.5</v>
@@ -7221,16 +7221,16 @@
         <v>17</v>
       </c>
       <c r="AA27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AB27">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC27">
         <v>8.199999999999999</v>
       </c>
       <c r="AD27">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE27">
         <v>24</v>
@@ -7245,7 +7245,7 @@
         <v>15.5</v>
       </c>
       <c r="AI27">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ27">
         <v>55</v>
@@ -7263,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="AO27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP27">
         <v>16</v>
@@ -7278,7 +7278,7 @@
         <v>30</v>
       </c>
       <c r="AT27">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU27">
         <v>7.6</v>
@@ -7293,13 +7293,13 @@
         <v>19.5</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27">
         <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB27">
         <v>44</v>
@@ -7311,73 +7311,73 @@
         <v>34</v>
       </c>
       <c r="BE27">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF27">
         <v>22</v>
       </c>
       <c r="BG27">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI27">
-        <v>1.54</v>
+        <v>3.55</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK27">
-        <v>2.08</v>
+        <v>7.8</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM27">
-        <v>2.46</v>
+        <v>11</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO27">
-        <v>1.87</v>
+        <v>5.9</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ27">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS27">
-        <v>2.46</v>
+        <v>9.4</v>
       </c>
       <c r="BT27">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU27">
-        <v>1.82</v>
+        <v>4.9</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW27">
-        <v>2.46</v>
+        <v>12.5</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY27">
-        <v>2.46</v>
+        <v>9</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA27">
-        <v>2.46</v>
+        <v>7.6</v>
       </c>
       <c r="CB27" t="s">
         <v>166</v>
@@ -7403,19 +7403,19 @@
         <v>2.16</v>
       </c>
       <c r="G28">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I28">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28">
         <v>3.15</v>
       </c>
       <c r="K28">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L28">
         <v>1.58</v>
@@ -7427,7 +7427,7 @@
         <v>2.8</v>
       </c>
       <c r="O28">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P28">
         <v>1.58</v>
@@ -7439,19 +7439,19 @@
         <v>1.21</v>
       </c>
       <c r="S28">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T28">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U28">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V28">
         <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -7472,7 +7472,7 @@
         <v>7.4</v>
       </c>
       <c r="AD28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE28">
         <v>85</v>
@@ -7481,19 +7481,19 @@
         <v>12.5</v>
       </c>
       <c r="AG28">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AI28">
         <v>110</v>
       </c>
       <c r="AJ28">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AK28">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AL28">
         <v>70</v>
@@ -7517,7 +7517,7 @@
         <v>15</v>
       </c>
       <c r="AS28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT28">
         <v>6.4</v>
@@ -7547,19 +7547,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC28">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD28">
         <v>32</v>
       </c>
       <c r="BE28">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF28">
         <v>21</v>
       </c>
       <c r="BG28">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH28">
         <v>2.8</v>
@@ -7571,7 +7571,7 @@
         <v>11.5</v>
       </c>
       <c r="BK28">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL28">
         <v>1000</v>
@@ -7642,46 +7642,46 @@
         <v>164</v>
       </c>
       <c r="F29">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G29">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H29">
         <v>4.7</v>
       </c>
       <c r="I29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K29">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M29">
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P29">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q29">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R29">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S29">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="T29">
         <v>1.89</v>
@@ -7693,28 +7693,28 @@
         <v>1.25</v>
       </c>
       <c r="W29">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X29">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y29">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z29">
         <v>38</v>
       </c>
       <c r="AA29">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB29">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC29">
         <v>8.6</v>
       </c>
       <c r="AD29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE29">
         <v>70</v>
@@ -7723,10 +7723,10 @@
         <v>11</v>
       </c>
       <c r="AG29">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29">
         <v>80</v>
@@ -7735,7 +7735,7 @@
         <v>21</v>
       </c>
       <c r="AK29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29">
         <v>38</v>
@@ -7744,34 +7744,34 @@
         <v>130</v>
       </c>
       <c r="AN29">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO29">
         <v>75</v>
       </c>
       <c r="AP29">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ29">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT29">
+        <v>8</v>
+      </c>
+      <c r="AU29">
         <v>7.8</v>
-      </c>
-      <c r="AU29">
-        <v>7.4</v>
       </c>
       <c r="AV29">
         <v>17</v>
       </c>
       <c r="AW29">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX29">
         <v>10</v>
@@ -7783,43 +7783,43 @@
         <v>17.5</v>
       </c>
       <c r="BA29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB29">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC29">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD29">
         <v>32</v>
       </c>
       <c r="BE29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG29">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH29">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BI29">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ29">
         <v>10</v>
       </c>
       <c r="BK29">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN29">
         <v>4.5</v>
@@ -7828,28 +7828,28 @@
         <v>4.1</v>
       </c>
       <c r="BP29">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ29">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS29">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT29">
         <v>8.199999999999999</v>
       </c>
       <c r="BU29">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BV29">
         <v>42</v>
       </c>
       <c r="BW29">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX29">
         <v>50</v>
@@ -7858,10 +7858,10 @@
         <v>13.5</v>
       </c>
       <c r="BZ29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA29">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB29" t="s">
         <v>166</v>
@@ -7884,25 +7884,25 @@
         <v>165</v>
       </c>
       <c r="F30">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G30">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H30">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I30">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L30">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M30">
         <v>1.08</v>
@@ -7926,13 +7926,13 @@
         <v>3.9</v>
       </c>
       <c r="T30">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U30">
         <v>1.99</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W30">
         <v>1.27</v>
@@ -7941,13 +7941,13 @@
         <v>15</v>
       </c>
       <c r="Y30">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z30">
         <v>12</v>
       </c>
       <c r="AA30">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB30">
         <v>14.5</v>
@@ -7965,7 +7965,7 @@
         <v>36</v>
       </c>
       <c r="AG30">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH30">
         <v>21</v>
@@ -7995,7 +7995,7 @@
         <v>11</v>
       </c>
       <c r="AQ30">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR30">
         <v>10</v>
@@ -8004,16 +8004,16 @@
         <v>20</v>
       </c>
       <c r="AT30">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU30">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV30">
         <v>9.4</v>
       </c>
       <c r="AW30">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX30">
         <v>16</v>
@@ -8025,22 +8025,22 @@
         <v>17.5</v>
       </c>
       <c r="BA30">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB30">
         <v>9</v>
       </c>
       <c r="BC30">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BD30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE30">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG30">
         <v>13.5</v>
@@ -8055,55 +8055,55 @@
         <v>12</v>
       </c>
       <c r="BK30">
-        <v>3.85</v>
+        <v>8</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BN30">
         <v>9</v>
       </c>
       <c r="BO30">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BP30">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BQ30">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR30">
         <v>60</v>
       </c>
       <c r="BS30">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BT30">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BV30">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW30">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BX30">
         <v>36</v>
       </c>
       <c r="BY30">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BZ30">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA30">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB30" t="s">
         <v>166</v>
